--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-07.xlsx
@@ -679,7 +679,7 @@
     <t>Real Sociedad</t>
   </si>
   <si>
-    <t>2026-09-05 00:43:57</t>
+    <t>2026-09-05 03:16:26</t>
   </si>
 </sst>
 </file>
@@ -1276,13 +1276,13 @@
         <v>1.1</v>
       </c>
       <c r="G2">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="H2">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="I2">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J2">
         <v>1.1</v>
@@ -1297,7 +1297,7 @@
         <v>1.01</v>
       </c>
       <c r="N2">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="O2">
         <v>1.18</v>
@@ -1321,10 +1321,10 @@
         <v>1.01</v>
       </c>
       <c r="V2">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W2">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="X2">
         <v>1000</v>
@@ -1515,22 +1515,22 @@
         <v>177</v>
       </c>
       <c r="F3">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="G3">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="H3">
         <v>3</v>
       </c>
       <c r="I3">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="J3">
         <v>2.82</v>
       </c>
       <c r="K3">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="L3">
         <v>1.01</v>
@@ -1542,7 +1542,7 @@
         <v>2.42</v>
       </c>
       <c r="O3">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P3">
         <v>1.52</v>
@@ -1563,10 +1563,10 @@
         <v>1.01</v>
       </c>
       <c r="V3">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="W3">
-        <v>1.55</v>
+        <v>1.76</v>
       </c>
       <c r="X3">
         <v>1000</v>
@@ -2044,7 +2044,7 @@
         <v>1.01</v>
       </c>
       <c r="U5">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="V5">
         <v>1.19</v>
@@ -4180,7 +4180,7 @@
         <v>2.06</v>
       </c>
       <c r="G14">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H14">
         <v>4.5</v>
@@ -4189,7 +4189,7 @@
         <v>4.6</v>
       </c>
       <c r="J14">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K14">
         <v>3.4</v>
@@ -4210,7 +4210,7 @@
         <v>1.64</v>
       </c>
       <c r="Q14">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R14">
         <v>1.24</v>
@@ -4234,13 +4234,13 @@
         <v>10</v>
       </c>
       <c r="Y14">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z14">
         <v>32</v>
       </c>
       <c r="AA14">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AB14">
         <v>7.4</v>
@@ -4249,13 +4249,13 @@
         <v>7.4</v>
       </c>
       <c r="AD14">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE14">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AF14">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG14">
         <v>11</v>
@@ -4297,7 +4297,7 @@
         <v>38</v>
       </c>
       <c r="AT14">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU14">
         <v>6.8</v>
@@ -4330,7 +4330,7 @@
         <v>29</v>
       </c>
       <c r="BE14">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="BF14">
         <v>20</v>
@@ -4661,22 +4661,22 @@
         <v>190</v>
       </c>
       <c r="F16">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="G16">
-        <v>1.86</v>
+        <v>1000</v>
       </c>
       <c r="H16">
-        <v>4.4</v>
+        <v>1.3</v>
       </c>
       <c r="I16">
-        <v>4.9</v>
+        <v>60</v>
       </c>
       <c r="J16">
-        <v>4.2</v>
+        <v>1.1</v>
       </c>
       <c r="K16">
-        <v>4.6</v>
+        <v>170</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -4691,10 +4691,10 @@
         <v>0</v>
       </c>
       <c r="P16">
-        <v>2.56</v>
+        <v>1.25</v>
       </c>
       <c r="Q16">
-        <v>1.49</v>
+        <v>1.04</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -4903,10 +4903,10 @@
         <v>191</v>
       </c>
       <c r="F17">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="G17">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="H17">
         <v>4.3</v>
@@ -4915,10 +4915,10 @@
         <v>4.7</v>
       </c>
       <c r="J17">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="K17">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -5145,7 +5145,7 @@
         <v>192</v>
       </c>
       <c r="F18">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="G18">
         <v>1.96</v>
@@ -5154,13 +5154,13 @@
         <v>4.6</v>
       </c>
       <c r="I18">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J18">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K18">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -5390,10 +5390,10 @@
         <v>4.1</v>
       </c>
       <c r="G19">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="H19">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="I19">
         <v>1.95</v>
@@ -5402,7 +5402,7 @@
         <v>3.65</v>
       </c>
       <c r="K19">
-        <v>5.2</v>
+        <v>180</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -6113,7 +6113,7 @@
         <v>196</v>
       </c>
       <c r="F22">
-        <v>1.67</v>
+        <v>1.1</v>
       </c>
       <c r="G22">
         <v>1.92</v>
@@ -6122,7 +6122,7 @@
         <v>2.12</v>
       </c>
       <c r="I22">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J22">
         <v>3.85</v>
@@ -6385,10 +6385,10 @@
         <v>1.24</v>
       </c>
       <c r="P23">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="Q23">
-        <v>1.64</v>
+        <v>1.46</v>
       </c>
       <c r="R23">
         <v>1.34</v>
@@ -6597,7 +6597,7 @@
         <v>198</v>
       </c>
       <c r="F24">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="G24">
         <v>2.18</v>
@@ -6612,7 +6612,7 @@
         <v>3.9</v>
       </c>
       <c r="K24">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -7102,7 +7102,7 @@
         <v>0</v>
       </c>
       <c r="M26">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="N26">
         <v>2.36</v>
@@ -7111,7 +7111,7 @@
         <v>1.7</v>
       </c>
       <c r="P26">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Q26">
         <v>3.1</v>
@@ -7141,10 +7141,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="Z26">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA26">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AB26">
         <v>6.8</v>
@@ -7156,13 +7156,13 @@
         <v>18.5</v>
       </c>
       <c r="AE26">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AF26">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG26">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH26">
         <v>29</v>
@@ -7171,16 +7171,16 @@
         <v>120</v>
       </c>
       <c r="AJ26">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AK26">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AL26">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AM26">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="AN26">
         <v>55</v>
@@ -7198,7 +7198,7 @@
         <v>20</v>
       </c>
       <c r="AS26">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="AT26">
         <v>6.2</v>
@@ -7222,25 +7222,25 @@
         <v>19</v>
       </c>
       <c r="BA26">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BB26">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="BC26">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="BD26">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BE26">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BF26">
         <v>26</v>
       </c>
       <c r="BG26">
-        <v>13.5</v>
+        <v>38</v>
       </c>
       <c r="BH26">
         <v>2.64</v>
@@ -8058,10 +8058,10 @@
         <v>2.6</v>
       </c>
       <c r="I30">
+        <v>3.15</v>
+      </c>
+      <c r="J30">
         <v>3.05</v>
-      </c>
-      <c r="J30">
-        <v>3.45</v>
       </c>
       <c r="K30">
         <v>4.3</v>
@@ -8097,7 +8097,7 @@
         <v>1.01</v>
       </c>
       <c r="V30">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="W30">
         <v>1.55</v>
@@ -8778,19 +8778,19 @@
         <v>2.18</v>
       </c>
       <c r="G33">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="H33">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="I33">
         <v>4.3</v>
       </c>
       <c r="J33">
-        <v>3</v>
+        <v>2.68</v>
       </c>
       <c r="K33">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -9534,7 +9534,7 @@
         <v>2.46</v>
       </c>
       <c r="Q36">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="R36">
         <v>0</v>
@@ -9743,16 +9743,16 @@
         <v>211</v>
       </c>
       <c r="F37">
-        <v>1.79</v>
+        <v>1.32</v>
       </c>
       <c r="G37">
         <v>1.91</v>
       </c>
       <c r="H37">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="I37">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="J37">
         <v>3.5</v>
@@ -10260,7 +10260,7 @@
         <v>1.07</v>
       </c>
       <c r="Q39">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="R39">
         <v>0</v>
@@ -10735,7 +10735,7 @@
         <v>1.11</v>
       </c>
       <c r="N41">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="O41">
         <v>1.48</v>
@@ -10744,13 +10744,13 @@
         <v>1.65</v>
       </c>
       <c r="Q41">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="R41">
         <v>1.24</v>
       </c>
       <c r="S41">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="T41">
         <v>2.04</v>
@@ -10986,7 +10986,7 @@
         <v>1.94</v>
       </c>
       <c r="Q42">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="R42">
         <v>0</v>
@@ -11198,10 +11198,10 @@
         <v>2.46</v>
       </c>
       <c r="G43">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="H43">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="I43">
         <v>3.4</v>
@@ -11210,7 +11210,7 @@
         <v>1.1</v>
       </c>
       <c r="K43">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -11228,7 +11228,7 @@
         <v>1.25</v>
       </c>
       <c r="Q43">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="R43">
         <v>0</v>
@@ -11688,7 +11688,7 @@
         <v>3.2</v>
       </c>
       <c r="I45">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="J45">
         <v>3.35</v>
@@ -11709,7 +11709,7 @@
         <v>0</v>
       </c>
       <c r="P45">
-        <v>1.96</v>
+        <v>1.25</v>
       </c>
       <c r="Q45">
         <v>1.01</v>
@@ -11954,19 +11954,19 @@
         <v>2.16</v>
       </c>
       <c r="Q46">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R46">
         <v>1.45</v>
       </c>
       <c r="S46">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T46">
         <v>1.67</v>
       </c>
       <c r="U46">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V46">
         <v>0</v>
@@ -11993,7 +11993,7 @@
         <v>8.4</v>
       </c>
       <c r="AD46">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AE46">
         <v>25</v>
@@ -12005,7 +12005,7 @@
         <v>13.5</v>
       </c>
       <c r="AH46">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AI46">
         <v>36</v>
@@ -12053,7 +12053,7 @@
         <v>16.5</v>
       </c>
       <c r="AX46">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AY46">
         <v>12</v>
@@ -12074,7 +12074,7 @@
         <v>24</v>
       </c>
       <c r="BE46">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BF46">
         <v>19.5</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-07.xlsx
@@ -679,7 +679,7 @@
     <t>Real Sociedad</t>
   </si>
   <si>
-    <t>2026-09-05 03:16:26</t>
+    <t>2026-09-05 05:49:46</t>
   </si>
 </sst>
 </file>
@@ -1321,7 +1321,7 @@
         <v>1.01</v>
       </c>
       <c r="V2">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W2">
         <v>2.16</v>
@@ -1542,7 +1542,7 @@
         <v>2.42</v>
       </c>
       <c r="O3">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P3">
         <v>1.52</v>
@@ -1760,16 +1760,16 @@
         <v>1.66</v>
       </c>
       <c r="G4">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="H4">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="I4">
         <v>7</v>
       </c>
       <c r="J4">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K4">
         <v>4.1</v>
@@ -1781,19 +1781,19 @@
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="O4">
         <v>1.35</v>
       </c>
       <c r="P4">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="Q4">
         <v>2</v>
       </c>
       <c r="R4">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S4">
         <v>3.5</v>
@@ -1805,10 +1805,10 @@
         <v>1.01</v>
       </c>
       <c r="V4">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W4">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="X4">
         <v>1000</v>
@@ -1999,22 +1999,22 @@
         <v>179</v>
       </c>
       <c r="F5">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="G5">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="H5">
-        <v>5</v>
+        <v>1.1</v>
       </c>
       <c r="I5">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="J5">
-        <v>3.45</v>
+        <v>2.74</v>
       </c>
       <c r="K5">
-        <v>4.2</v>
+        <v>110</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -2023,22 +2023,22 @@
         <v>1.01</v>
       </c>
       <c r="N5">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="O5">
         <v>1.01</v>
       </c>
       <c r="P5">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="Q5">
-        <v>2.44</v>
+        <v>2.02</v>
       </c>
       <c r="R5">
         <v>1.18</v>
       </c>
       <c r="S5">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="T5">
         <v>1.01</v>
@@ -2050,7 +2050,7 @@
         <v>1.19</v>
       </c>
       <c r="W5">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -2740,7 +2740,7 @@
         <v>1.08</v>
       </c>
       <c r="K8">
-        <v>100</v>
+        <v>320</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -2979,7 +2979,7 @@
         <v>3.9</v>
       </c>
       <c r="J9">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K9">
         <v>7.6</v>
@@ -2997,10 +2997,10 @@
         <v>0</v>
       </c>
       <c r="P9">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q9">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -3466,7 +3466,7 @@
         <v>1.08</v>
       </c>
       <c r="K11">
-        <v>100</v>
+        <v>270</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -3702,7 +3702,7 @@
         <v>6.6</v>
       </c>
       <c r="I12">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="J12">
         <v>4.3</v>
@@ -3950,7 +3950,7 @@
         <v>1.08</v>
       </c>
       <c r="K13">
-        <v>100</v>
+        <v>320</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -4180,7 +4180,7 @@
         <v>2.06</v>
       </c>
       <c r="G14">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H14">
         <v>4.5</v>
@@ -4192,7 +4192,7 @@
         <v>3.3</v>
       </c>
       <c r="K14">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -4213,7 +4213,7 @@
         <v>2.44</v>
       </c>
       <c r="R14">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S14">
         <v>5</v>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="X14">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y14">
         <v>13</v>
@@ -4291,13 +4291,13 @@
         <v>11</v>
       </c>
       <c r="AR14">
-        <v>19.5</v>
+        <v>28</v>
       </c>
       <c r="AS14">
         <v>38</v>
       </c>
       <c r="AT14">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU14">
         <v>6.8</v>
@@ -4330,7 +4330,7 @@
         <v>29</v>
       </c>
       <c r="BE14">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BF14">
         <v>20</v>
@@ -4422,10 +4422,10 @@
         <v>1.99</v>
       </c>
       <c r="G15">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="H15">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="I15">
         <v>4.3</v>
@@ -4434,7 +4434,7 @@
         <v>3.15</v>
       </c>
       <c r="K15">
-        <v>5</v>
+        <v>3.95</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -4664,19 +4664,19 @@
         <v>1.74</v>
       </c>
       <c r="G16">
-        <v>1000</v>
+        <v>1.87</v>
       </c>
       <c r="H16">
-        <v>1.3</v>
+        <v>3.75</v>
       </c>
       <c r="I16">
-        <v>60</v>
+        <v>5.9</v>
       </c>
       <c r="J16">
-        <v>1.1</v>
+        <v>3.45</v>
       </c>
       <c r="K16">
-        <v>170</v>
+        <v>5.1</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -4903,22 +4903,22 @@
         <v>191</v>
       </c>
       <c r="F17">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="G17">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="H17">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I17">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J17">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K17">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -4933,10 +4933,10 @@
         <v>0</v>
       </c>
       <c r="P17">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q17">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -5145,40 +5145,40 @@
         <v>192</v>
       </c>
       <c r="F18">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="G18">
+        <v>1.95</v>
+      </c>
+      <c r="H18">
+        <v>4.7</v>
+      </c>
+      <c r="I18">
+        <v>55</v>
+      </c>
+      <c r="J18">
+        <v>2.88</v>
+      </c>
+      <c r="K18">
+        <v>4.1</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>1.12</v>
+      </c>
+      <c r="Q18">
         <v>1.96</v>
-      </c>
-      <c r="H18">
-        <v>4.6</v>
-      </c>
-      <c r="I18">
-        <v>5.3</v>
-      </c>
-      <c r="J18">
-        <v>3.45</v>
-      </c>
-      <c r="K18">
-        <v>3.8</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="O18">
-        <v>0</v>
-      </c>
-      <c r="P18">
-        <v>1.1</v>
-      </c>
-      <c r="Q18">
-        <v>1.01</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -5390,10 +5390,10 @@
         <v>4.1</v>
       </c>
       <c r="G19">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="H19">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="I19">
         <v>1.95</v>
@@ -5402,7 +5402,7 @@
         <v>3.65</v>
       </c>
       <c r="K19">
-        <v>180</v>
+        <v>5.2</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -6113,7 +6113,7 @@
         <v>196</v>
       </c>
       <c r="F22">
-        <v>1.1</v>
+        <v>1.69</v>
       </c>
       <c r="G22">
         <v>1.92</v>
@@ -6122,13 +6122,13 @@
         <v>2.12</v>
       </c>
       <c r="I22">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="J22">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K22">
-        <v>100</v>
+        <v>240</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -6385,10 +6385,10 @@
         <v>1.24</v>
       </c>
       <c r="P23">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="Q23">
-        <v>1.46</v>
+        <v>1.64</v>
       </c>
       <c r="R23">
         <v>1.34</v>
@@ -6854,7 +6854,7 @@
         <v>3.9</v>
       </c>
       <c r="K25">
-        <v>100</v>
+        <v>190</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -7090,7 +7090,7 @@
         <v>3.65</v>
       </c>
       <c r="I26">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J26">
         <v>2.96</v>
@@ -7102,7 +7102,7 @@
         <v>0</v>
       </c>
       <c r="M26">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N26">
         <v>2.36</v>
@@ -7123,7 +7123,7 @@
         <v>7</v>
       </c>
       <c r="T26">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="U26">
         <v>1.67</v>
@@ -7135,58 +7135,58 @@
         <v>0</v>
       </c>
       <c r="X26">
-        <v>7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y26">
-        <v>8.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="Z26">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AA26">
+        <v>1000</v>
+      </c>
+      <c r="AB26">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC26">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD26">
+        <v>21</v>
+      </c>
+      <c r="AE26">
+        <v>1000</v>
+      </c>
+      <c r="AF26">
+        <v>36</v>
+      </c>
+      <c r="AG26">
+        <v>40</v>
+      </c>
+      <c r="AH26">
+        <v>46</v>
+      </c>
+      <c r="AI26">
+        <v>1000</v>
+      </c>
+      <c r="AJ26">
         <v>90</v>
       </c>
-      <c r="AB26">
-        <v>6.8</v>
-      </c>
-      <c r="AC26">
-        <v>7</v>
-      </c>
-      <c r="AD26">
-        <v>18.5</v>
-      </c>
-      <c r="AE26">
-        <v>75</v>
-      </c>
-      <c r="AF26">
-        <v>14</v>
-      </c>
-      <c r="AG26">
-        <v>13.5</v>
-      </c>
-      <c r="AH26">
-        <v>29</v>
-      </c>
-      <c r="AI26">
-        <v>120</v>
-      </c>
-      <c r="AJ26">
-        <v>42</v>
-      </c>
       <c r="AK26">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="AL26">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM26">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AN26">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AO26">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP26">
         <v>6.4</v>
@@ -7195,22 +7195,22 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR26">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AS26">
-        <v>36</v>
+        <v>4.5</v>
       </c>
       <c r="AT26">
         <v>6.2</v>
       </c>
       <c r="AU26">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV26">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AW26">
-        <v>32</v>
+        <v>4.5</v>
       </c>
       <c r="AX26">
         <v>12</v>
@@ -7219,31 +7219,31 @@
         <v>12.5</v>
       </c>
       <c r="AZ26">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA26">
-        <v>15.5</v>
+        <v>4.5</v>
       </c>
       <c r="BB26">
-        <v>34</v>
+        <v>4.3</v>
       </c>
       <c r="BC26">
-        <v>34</v>
+        <v>4.3</v>
       </c>
       <c r="BD26">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="BE26">
-        <v>16.5</v>
+        <v>3.5</v>
       </c>
       <c r="BF26">
-        <v>26</v>
+        <v>4.2</v>
       </c>
       <c r="BG26">
-        <v>38</v>
+        <v>4.5</v>
       </c>
       <c r="BH26">
-        <v>2.64</v>
+        <v>1000</v>
       </c>
       <c r="BI26">
         <v>2.16</v>
@@ -7332,10 +7332,10 @@
         <v>2.2</v>
       </c>
       <c r="I27">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="J27">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K27">
         <v>6.8</v>
@@ -7565,16 +7565,16 @@
         <v>202</v>
       </c>
       <c r="F28">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="G28">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="H28">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="I28">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="J28">
         <v>4.4</v>
@@ -7807,13 +7807,13 @@
         <v>203</v>
       </c>
       <c r="F29">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="G29">
         <v>18</v>
       </c>
       <c r="H29">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="I29">
         <v>16</v>
@@ -8058,10 +8058,10 @@
         <v>2.6</v>
       </c>
       <c r="I30">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="J30">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="K30">
         <v>4.3</v>
@@ -8097,7 +8097,7 @@
         <v>1.01</v>
       </c>
       <c r="V30">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="W30">
         <v>1.55</v>
@@ -8291,22 +8291,22 @@
         <v>205</v>
       </c>
       <c r="F31">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="G31">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="H31">
         <v>5</v>
       </c>
       <c r="I31">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J31">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="K31">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -8775,7 +8775,7 @@
         <v>207</v>
       </c>
       <c r="F33">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="G33">
         <v>3.35</v>
@@ -8787,7 +8787,7 @@
         <v>4.3</v>
       </c>
       <c r="J33">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="K33">
         <v>5.2</v>
@@ -9507,7 +9507,7 @@
         <v>2.7</v>
       </c>
       <c r="H36">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="I36">
         <v>3.35</v>
@@ -9516,7 +9516,7 @@
         <v>3.8</v>
       </c>
       <c r="K36">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -9534,7 +9534,7 @@
         <v>2.46</v>
       </c>
       <c r="Q36">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="R36">
         <v>0</v>
@@ -9743,19 +9743,19 @@
         <v>211</v>
       </c>
       <c r="F37">
-        <v>1.32</v>
+        <v>1.76</v>
       </c>
       <c r="G37">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="H37">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="I37">
         <v>1000</v>
       </c>
       <c r="J37">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="K37">
         <v>4.1</v>
@@ -9988,7 +9988,7 @@
         <v>1.76</v>
       </c>
       <c r="G38">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="H38">
         <v>3.5</v>
@@ -10242,7 +10242,7 @@
         <v>2.38</v>
       </c>
       <c r="K39">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -10711,7 +10711,7 @@
         <v>215</v>
       </c>
       <c r="F41">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="G41">
         <v>3.05</v>
@@ -10720,13 +10720,13 @@
         <v>2.76</v>
       </c>
       <c r="I41">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="J41">
         <v>3.2</v>
       </c>
       <c r="K41">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -10735,7 +10735,7 @@
         <v>1.11</v>
       </c>
       <c r="N41">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="O41">
         <v>1.48</v>
@@ -10744,19 +10744,19 @@
         <v>1.65</v>
       </c>
       <c r="Q41">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="R41">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S41">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T41">
         <v>2.04</v>
       </c>
       <c r="U41">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="V41">
         <v>0</v>
@@ -10789,10 +10789,10 @@
         <v>38</v>
       </c>
       <c r="AF41">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG41">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH41">
         <v>22</v>
@@ -10801,19 +10801,19 @@
         <v>70</v>
       </c>
       <c r="AJ41">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK41">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AL41">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM41">
         <v>170</v>
       </c>
       <c r="AN41">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AO41">
         <v>42</v>
@@ -10825,10 +10825,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR41">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AS41">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="AT41">
         <v>8.6</v>
@@ -10840,7 +10840,7 @@
         <v>12</v>
       </c>
       <c r="AW41">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AX41">
         <v>16.5</v>
@@ -10858,16 +10858,16 @@
         <v>27</v>
       </c>
       <c r="BC41">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="BD41">
         <v>32</v>
       </c>
       <c r="BE41">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BF41">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="BG41">
         <v>23</v>
@@ -10953,10 +10953,10 @@
         <v>216</v>
       </c>
       <c r="F42">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="G42">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="H42">
         <v>1.58</v>
@@ -10965,10 +10965,10 @@
         <v>2.06</v>
       </c>
       <c r="J42">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="K42">
-        <v>100</v>
+        <v>13</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -11195,22 +11195,22 @@
         <v>217</v>
       </c>
       <c r="F43">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="G43">
+        <v>2.76</v>
+      </c>
+      <c r="H43">
         <v>2.86</v>
       </c>
-      <c r="H43">
-        <v>2.76</v>
-      </c>
       <c r="I43">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="J43">
-        <v>1.1</v>
+        <v>3.25</v>
       </c>
       <c r="K43">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -11225,10 +11225,10 @@
         <v>0</v>
       </c>
       <c r="P43">
-        <v>1.25</v>
+        <v>1.69</v>
       </c>
       <c r="Q43">
-        <v>1.81</v>
+        <v>2.16</v>
       </c>
       <c r="R43">
         <v>0</v>
@@ -11709,7 +11709,7 @@
         <v>0</v>
       </c>
       <c r="P45">
-        <v>1.25</v>
+        <v>1.98</v>
       </c>
       <c r="Q45">
         <v>1.01</v>
@@ -11954,13 +11954,13 @@
         <v>2.16</v>
       </c>
       <c r="Q46">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R46">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="S46">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="T46">
         <v>1.67</v>
@@ -12074,7 +12074,7 @@
         <v>24</v>
       </c>
       <c r="BE46">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="BF46">
         <v>19.5</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-07.xlsx
@@ -679,7 +679,7 @@
     <t>Real Sociedad</t>
   </si>
   <si>
-    <t>2026-09-05 05:49:46</t>
+    <t>2026-09-05 08:22:18</t>
   </si>
 </sst>
 </file>
@@ -1784,7 +1784,7 @@
         <v>2.96</v>
       </c>
       <c r="O4">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="P4">
         <v>1.71</v>
@@ -1999,22 +1999,22 @@
         <v>179</v>
       </c>
       <c r="F5">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="G5">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="H5">
-        <v>1.1</v>
+        <v>4.7</v>
       </c>
       <c r="I5">
-        <v>7.8</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="K5">
-        <v>110</v>
+        <v>3.65</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -2023,34 +2023,34 @@
         <v>1.01</v>
       </c>
       <c r="N5">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="O5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P5">
         <v>1.56</v>
       </c>
       <c r="Q5">
-        <v>2.02</v>
+        <v>2.44</v>
       </c>
       <c r="R5">
         <v>1.18</v>
       </c>
       <c r="S5">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="T5">
         <v>1.01</v>
       </c>
       <c r="U5">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="V5">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W5">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -2758,7 +2758,7 @@
         <v>1.25</v>
       </c>
       <c r="Q8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -2982,7 +2982,7 @@
         <v>3.35</v>
       </c>
       <c r="K9">
-        <v>7.6</v>
+        <v>3.9</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -3938,16 +3938,16 @@
         <v>1.08</v>
       </c>
       <c r="G13">
-        <v>1000</v>
+        <v>1.34</v>
       </c>
       <c r="H13">
-        <v>1.08</v>
+        <v>4</v>
       </c>
       <c r="I13">
         <v>1000</v>
       </c>
       <c r="J13">
-        <v>1.08</v>
+        <v>3.85</v>
       </c>
       <c r="K13">
         <v>320</v>
@@ -4210,7 +4210,7 @@
         <v>1.64</v>
       </c>
       <c r="Q14">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R14">
         <v>1.23</v>
@@ -4667,16 +4667,16 @@
         <v>1.87</v>
       </c>
       <c r="H16">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="I16">
         <v>5.9</v>
       </c>
       <c r="J16">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="K16">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -4691,7 +4691,7 @@
         <v>0</v>
       </c>
       <c r="P16">
-        <v>1.25</v>
+        <v>2.56</v>
       </c>
       <c r="Q16">
         <v>1.04</v>
@@ -4906,13 +4906,13 @@
         <v>1.92</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="H17">
         <v>4.5</v>
       </c>
       <c r="I17">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="J17">
         <v>3.6</v>
@@ -4936,7 +4936,7 @@
         <v>2.02</v>
       </c>
       <c r="Q17">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -5145,19 +5145,19 @@
         <v>192</v>
       </c>
       <c r="F18">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="G18">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="H18">
         <v>4.7</v>
       </c>
       <c r="I18">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="J18">
-        <v>2.88</v>
+        <v>3.35</v>
       </c>
       <c r="K18">
         <v>4.1</v>
@@ -5638,7 +5638,7 @@
         <v>2.84</v>
       </c>
       <c r="I20">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="J20">
         <v>3.55</v>
@@ -6612,7 +6612,7 @@
         <v>3.9</v>
       </c>
       <c r="K24">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -7108,10 +7108,10 @@
         <v>2.36</v>
       </c>
       <c r="O26">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="P26">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Q26">
         <v>3.1</v>
@@ -7123,7 +7123,7 @@
         <v>7</v>
       </c>
       <c r="T26">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="U26">
         <v>1.67</v>
@@ -7135,112 +7135,112 @@
         <v>0</v>
       </c>
       <c r="X26">
-        <v>9.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="Y26">
+        <v>9</v>
+      </c>
+      <c r="Z26">
+        <v>24</v>
+      </c>
+      <c r="AA26">
+        <v>90</v>
+      </c>
+      <c r="AB26">
+        <v>7</v>
+      </c>
+      <c r="AC26">
+        <v>7</v>
+      </c>
+      <c r="AD26">
+        <v>18.5</v>
+      </c>
+      <c r="AE26">
+        <v>75</v>
+      </c>
+      <c r="AF26">
         <v>14</v>
       </c>
-      <c r="Z26">
-        <v>32</v>
-      </c>
-      <c r="AA26">
-        <v>1000</v>
-      </c>
-      <c r="AB26">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC26">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD26">
-        <v>21</v>
-      </c>
-      <c r="AE26">
-        <v>1000</v>
-      </c>
-      <c r="AF26">
-        <v>36</v>
-      </c>
       <c r="AG26">
-        <v>40</v>
+        <v>14.5</v>
       </c>
       <c r="AH26">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="AI26">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ26">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="AK26">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="AL26">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM26">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AN26">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AO26">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP26">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ26">
         <v>8.199999999999999</v>
       </c>
       <c r="AR26">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="AS26">
-        <v>4.5</v>
+        <v>12.5</v>
       </c>
       <c r="AT26">
         <v>6.2</v>
       </c>
       <c r="AU26">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV26">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW26">
-        <v>4.5</v>
+        <v>12</v>
       </c>
       <c r="AX26">
+        <v>12.5</v>
+      </c>
+      <c r="AY26">
         <v>12</v>
-      </c>
-      <c r="AY26">
-        <v>12.5</v>
       </c>
       <c r="AZ26">
         <v>20</v>
       </c>
       <c r="BA26">
-        <v>4.5</v>
+        <v>13</v>
       </c>
       <c r="BB26">
-        <v>4.3</v>
+        <v>29</v>
       </c>
       <c r="BC26">
-        <v>4.3</v>
+        <v>30</v>
       </c>
       <c r="BD26">
-        <v>4.5</v>
+        <v>12</v>
       </c>
       <c r="BE26">
-        <v>3.5</v>
+        <v>14</v>
       </c>
       <c r="BF26">
-        <v>4.2</v>
+        <v>26</v>
       </c>
       <c r="BG26">
-        <v>4.5</v>
+        <v>13</v>
       </c>
       <c r="BH26">
         <v>1000</v>
@@ -7335,7 +7335,7 @@
         <v>2.94</v>
       </c>
       <c r="J27">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K27">
         <v>6.8</v>
@@ -7840,7 +7840,7 @@
         <v>1.24</v>
       </c>
       <c r="Q29">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R29">
         <v>0</v>
@@ -8049,22 +8049,22 @@
         <v>204</v>
       </c>
       <c r="F30">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="G30">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="H30">
         <v>2.6</v>
       </c>
       <c r="I30">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="J30">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K30">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L30">
         <v>1.01</v>
@@ -8097,10 +8097,10 @@
         <v>1.01</v>
       </c>
       <c r="V30">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="W30">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="X30">
         <v>1000</v>
@@ -8294,19 +8294,19 @@
         <v>1.61</v>
       </c>
       <c r="G31">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="H31">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I31">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J31">
         <v>3.9</v>
       </c>
       <c r="K31">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -9534,7 +9534,7 @@
         <v>2.46</v>
       </c>
       <c r="Q36">
-        <v>1.5</v>
+        <v>1.02</v>
       </c>
       <c r="R36">
         <v>0</v>
@@ -9746,16 +9746,16 @@
         <v>1.76</v>
       </c>
       <c r="G37">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="H37">
         <v>4.8</v>
       </c>
       <c r="I37">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="J37">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="K37">
         <v>4.1</v>
@@ -10242,7 +10242,7 @@
         <v>2.38</v>
       </c>
       <c r="K39">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -10260,7 +10260,7 @@
         <v>1.07</v>
       </c>
       <c r="Q39">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="R39">
         <v>0</v>
@@ -10735,7 +10735,7 @@
         <v>1.11</v>
       </c>
       <c r="N41">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="O41">
         <v>1.48</v>
@@ -10744,19 +10744,19 @@
         <v>1.65</v>
       </c>
       <c r="Q41">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="R41">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S41">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="T41">
         <v>2.04</v>
       </c>
       <c r="U41">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V41">
         <v>0</v>
@@ -10765,7 +10765,7 @@
         <v>0</v>
       </c>
       <c r="X41">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y41">
         <v>9</v>
@@ -10774,7 +10774,7 @@
         <v>17</v>
       </c>
       <c r="AA41">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AB41">
         <v>9.800000000000001</v>
@@ -10789,7 +10789,7 @@
         <v>38</v>
       </c>
       <c r="AF41">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AG41">
         <v>14</v>
@@ -10801,7 +10801,7 @@
         <v>70</v>
       </c>
       <c r="AJ41">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AK41">
         <v>50</v>
@@ -10813,7 +10813,7 @@
         <v>170</v>
       </c>
       <c r="AN41">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AO41">
         <v>42</v>
@@ -10846,7 +10846,7 @@
         <v>16.5</v>
       </c>
       <c r="AY41">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ41">
         <v>18.5</v>
@@ -10864,7 +10864,7 @@
         <v>32</v>
       </c>
       <c r="BE41">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BF41">
         <v>25</v>
@@ -11195,19 +11195,19 @@
         <v>217</v>
       </c>
       <c r="F43">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="G43">
-        <v>2.76</v>
+        <v>2.94</v>
       </c>
       <c r="H43">
         <v>2.86</v>
       </c>
       <c r="I43">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J43">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K43">
         <v>3.65</v>
@@ -11225,10 +11225,10 @@
         <v>0</v>
       </c>
       <c r="P43">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="Q43">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="R43">
         <v>0</v>
@@ -11470,7 +11470,7 @@
         <v>1.24</v>
       </c>
       <c r="Q44">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R44">
         <v>0</v>
@@ -11682,16 +11682,16 @@
         <v>2.34</v>
       </c>
       <c r="G45">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H45">
         <v>3.2</v>
       </c>
       <c r="I45">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J45">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K45">
         <v>3.85</v>
@@ -11712,7 +11712,7 @@
         <v>1.98</v>
       </c>
       <c r="Q45">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="R45">
         <v>0</v>
@@ -11924,13 +11924,13 @@
         <v>3.1</v>
       </c>
       <c r="G46">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H46">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="I46">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="J46">
         <v>3.65</v>
@@ -11948,7 +11948,7 @@
         <v>4.4</v>
       </c>
       <c r="O46">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P46">
         <v>2.16</v>
@@ -11957,10 +11957,10 @@
         <v>1.83</v>
       </c>
       <c r="R46">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S46">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="T46">
         <v>1.67</v>
@@ -11990,7 +11990,7 @@
         <v>14.5</v>
       </c>
       <c r="AC46">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD46">
         <v>12</v>
@@ -12065,7 +12065,7 @@
         <v>22</v>
       </c>
       <c r="BB46">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC46">
         <v>20</v>
@@ -12074,7 +12074,7 @@
         <v>24</v>
       </c>
       <c r="BE46">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BF46">
         <v>19.5</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-07.xlsx
@@ -679,7 +679,7 @@
     <t>Real Sociedad</t>
   </si>
   <si>
-    <t>2026-09-05 08:22:18</t>
+    <t>2026-09-05 10:52:23</t>
   </si>
 </sst>
 </file>
@@ -1285,7 +1285,7 @@
         <v>110</v>
       </c>
       <c r="J2">
-        <v>1.1</v>
+        <v>3.85</v>
       </c>
       <c r="K2">
         <v>250</v>
@@ -1297,7 +1297,7 @@
         <v>1.01</v>
       </c>
       <c r="N2">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="O2">
         <v>1.18</v>
@@ -1312,7 +1312,7 @@
         <v>1.08</v>
       </c>
       <c r="S2">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="T2">
         <v>1.01</v>
@@ -1521,16 +1521,16 @@
         <v>2.3</v>
       </c>
       <c r="H3">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="I3">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="J3">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="K3">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="L3">
         <v>1.01</v>
@@ -1539,22 +1539,22 @@
         <v>1.01</v>
       </c>
       <c r="N3">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="O3">
         <v>1.4</v>
       </c>
       <c r="P3">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="Q3">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R3">
         <v>1.18</v>
       </c>
       <c r="S3">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="T3">
         <v>1.01</v>
@@ -1563,7 +1563,7 @@
         <v>1.01</v>
       </c>
       <c r="V3">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W3">
         <v>1.76</v>
@@ -1677,10 +1677,10 @@
         <v>1.01</v>
       </c>
       <c r="BH3">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BI3">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="BJ3">
         <v>1000</v>
@@ -1757,7 +1757,7 @@
         <v>178</v>
       </c>
       <c r="F4">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="G4">
         <v>1.96</v>
@@ -1766,37 +1766,37 @@
         <v>4.6</v>
       </c>
       <c r="I4">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="J4">
         <v>3.5</v>
       </c>
       <c r="K4">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L4">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M4">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N4">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="O4">
         <v>1.33</v>
       </c>
       <c r="P4">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q4">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="R4">
         <v>1.25</v>
       </c>
       <c r="S4">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="T4">
         <v>1.01</v>
@@ -1805,7 +1805,7 @@
         <v>1.01</v>
       </c>
       <c r="V4">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W4">
         <v>2.04</v>
@@ -2002,16 +2002,16 @@
         <v>1.8</v>
       </c>
       <c r="G5">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="H5">
         <v>4.7</v>
       </c>
       <c r="I5">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J5">
-        <v>2.62</v>
+        <v>3.4</v>
       </c>
       <c r="K5">
         <v>3.65</v>
@@ -2023,7 +2023,7 @@
         <v>1.01</v>
       </c>
       <c r="N5">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="O5">
         <v>1.02</v>
@@ -2038,7 +2038,7 @@
         <v>1.18</v>
       </c>
       <c r="S5">
-        <v>2.44</v>
+        <v>4.3</v>
       </c>
       <c r="T5">
         <v>1.01</v>
@@ -2047,10 +2047,10 @@
         <v>1.57</v>
       </c>
       <c r="V5">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W5">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -2241,10 +2241,10 @@
         <v>180</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G6">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="H6">
         <v>2.08</v>
@@ -2253,10 +2253,10 @@
         <v>2.72</v>
       </c>
       <c r="J6">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K6">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -2271,10 +2271,10 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="Q6">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -2483,19 +2483,19 @@
         <v>181</v>
       </c>
       <c r="F7">
+        <v>1.35</v>
+      </c>
+      <c r="G7">
+        <v>4.2</v>
+      </c>
+      <c r="H7">
+        <v>2.4</v>
+      </c>
+      <c r="I7">
         <v>3.05</v>
       </c>
-      <c r="G7">
-        <v>3.75</v>
-      </c>
-      <c r="H7">
-        <v>2.36</v>
-      </c>
-      <c r="I7">
-        <v>2.74</v>
-      </c>
       <c r="J7">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="K7">
         <v>3.8</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>1.54</v>
+        <v>1.25</v>
       </c>
       <c r="Q7">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -2970,19 +2970,19 @@
         <v>2.08</v>
       </c>
       <c r="G9">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="H9">
         <v>2.6</v>
       </c>
       <c r="I9">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="J9">
         <v>3.35</v>
       </c>
       <c r="K9">
-        <v>3.9</v>
+        <v>7.6</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -2997,7 +2997,7 @@
         <v>0</v>
       </c>
       <c r="P9">
-        <v>1.87</v>
+        <v>1.12</v>
       </c>
       <c r="Q9">
         <v>1.67</v>
@@ -3209,22 +3209,22 @@
         <v>184</v>
       </c>
       <c r="F10">
-        <v>2.42</v>
+        <v>1.2</v>
       </c>
       <c r="G10">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="H10">
-        <v>2.36</v>
+        <v>1.2</v>
       </c>
       <c r="I10">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="J10">
-        <v>2.86</v>
+        <v>1.08</v>
       </c>
       <c r="K10">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -3693,7 +3693,7 @@
         <v>186</v>
       </c>
       <c r="F12">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="G12">
         <v>1.51</v>
@@ -3702,13 +3702,13 @@
         <v>6.6</v>
       </c>
       <c r="I12">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="J12">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="K12">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -3723,7 +3723,7 @@
         <v>0</v>
       </c>
       <c r="P12">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q12">
         <v>1.51</v>
@@ -3935,7 +3935,7 @@
         <v>187</v>
       </c>
       <c r="F13">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="G13">
         <v>1.34</v>
@@ -4177,19 +4177,19 @@
         <v>188</v>
       </c>
       <c r="F14">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G14">
         <v>2.1</v>
       </c>
       <c r="H14">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I14">
         <v>4.6</v>
       </c>
       <c r="J14">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K14">
         <v>3.35</v>
@@ -4210,7 +4210,7 @@
         <v>1.64</v>
       </c>
       <c r="Q14">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="R14">
         <v>1.23</v>
@@ -4222,7 +4222,7 @@
         <v>2.12</v>
       </c>
       <c r="U14">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="V14">
         <v>0</v>
@@ -4234,7 +4234,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Y14">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z14">
         <v>32</v>
@@ -4252,10 +4252,10 @@
         <v>19</v>
       </c>
       <c r="AE14">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AF14">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG14">
         <v>11</v>
@@ -4279,19 +4279,19 @@
         <v>1000</v>
       </c>
       <c r="AN14">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO14">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP14">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ14">
         <v>11</v>
       </c>
       <c r="AR14">
-        <v>28</v>
+        <v>19.5</v>
       </c>
       <c r="AS14">
         <v>38</v>
@@ -4330,7 +4330,7 @@
         <v>29</v>
       </c>
       <c r="BE14">
-        <v>16.5</v>
+        <v>46</v>
       </c>
       <c r="BF14">
         <v>20</v>
@@ -4449,7 +4449,7 @@
         <v>0</v>
       </c>
       <c r="P15">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q15">
         <v>1.71</v>
@@ -4664,19 +4664,19 @@
         <v>1.74</v>
       </c>
       <c r="G16">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="H16">
         <v>4.2</v>
       </c>
       <c r="I16">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="J16">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="K16">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -4691,7 +4691,7 @@
         <v>0</v>
       </c>
       <c r="P16">
-        <v>2.56</v>
+        <v>1.25</v>
       </c>
       <c r="Q16">
         <v>1.04</v>
@@ -4903,7 +4903,7 @@
         <v>191</v>
       </c>
       <c r="F17">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="G17">
         <v>1.99</v>
@@ -4912,13 +4912,13 @@
         <v>4.5</v>
       </c>
       <c r="I17">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="J17">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="K17">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -4936,7 +4936,7 @@
         <v>2.02</v>
       </c>
       <c r="Q17">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -5145,7 +5145,7 @@
         <v>192</v>
       </c>
       <c r="F18">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="G18">
         <v>1.94</v>
@@ -5154,13 +5154,13 @@
         <v>4.7</v>
       </c>
       <c r="I18">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J18">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K18">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -5178,7 +5178,7 @@
         <v>1.12</v>
       </c>
       <c r="Q18">
-        <v>1.96</v>
+        <v>1.04</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -5420,7 +5420,7 @@
         <v>2.16</v>
       </c>
       <c r="Q19">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -5871,22 +5871,22 @@
         <v>195</v>
       </c>
       <c r="F21">
-        <v>3.7</v>
+        <v>2.04</v>
       </c>
       <c r="G21">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="H21">
-        <v>1.63</v>
+        <v>1.08</v>
       </c>
       <c r="I21">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="J21">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K21">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -5904,7 +5904,7 @@
         <v>2.06</v>
       </c>
       <c r="Q21">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="R21">
         <v>0</v>
@@ -6119,13 +6119,13 @@
         <v>1.92</v>
       </c>
       <c r="H22">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="I22">
         <v>6.6</v>
       </c>
       <c r="J22">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K22">
         <v>240</v>
@@ -6146,7 +6146,7 @@
         <v>2.04</v>
       </c>
       <c r="Q22">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -6358,19 +6358,19 @@
         <v>1.35</v>
       </c>
       <c r="G23">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="H23">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="I23">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="J23">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="K23">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="L23">
         <v>1.01</v>
@@ -6379,7 +6379,7 @@
         <v>1.01</v>
       </c>
       <c r="N23">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="O23">
         <v>1.24</v>
@@ -6403,10 +6403,10 @@
         <v>1.01</v>
       </c>
       <c r="V23">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W23">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="X23">
         <v>1000</v>
@@ -6600,16 +6600,16 @@
         <v>1.99</v>
       </c>
       <c r="G24">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H24">
         <v>3.35</v>
       </c>
       <c r="I24">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J24">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K24">
         <v>4.3</v>
@@ -6627,10 +6627,10 @@
         <v>0</v>
       </c>
       <c r="P24">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="Q24">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -6839,7 +6839,7 @@
         <v>199</v>
       </c>
       <c r="F25">
-        <v>1.81</v>
+        <v>2.32</v>
       </c>
       <c r="G25">
         <v>3.75</v>
@@ -6854,7 +6854,7 @@
         <v>3.9</v>
       </c>
       <c r="K25">
-        <v>190</v>
+        <v>7.6</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -6869,7 +6869,7 @@
         <v>0</v>
       </c>
       <c r="P25">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q25">
         <v>1.63</v>
@@ -7084,16 +7084,16 @@
         <v>2.52</v>
       </c>
       <c r="G26">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H26">
         <v>3.65</v>
       </c>
       <c r="I26">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J26">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="K26">
         <v>3</v>
@@ -7105,10 +7105,10 @@
         <v>1.16</v>
       </c>
       <c r="N26">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="O26">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="P26">
         <v>1.44</v>
@@ -7123,7 +7123,7 @@
         <v>7</v>
       </c>
       <c r="T26">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="U26">
         <v>1.67</v>
@@ -7147,7 +7147,7 @@
         <v>90</v>
       </c>
       <c r="AB26">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AC26">
         <v>7</v>
@@ -7162,7 +7162,7 @@
         <v>14</v>
       </c>
       <c r="AG26">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH26">
         <v>29</v>
@@ -7171,7 +7171,7 @@
         <v>120</v>
       </c>
       <c r="AJ26">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK26">
         <v>44</v>
@@ -7198,7 +7198,7 @@
         <v>19.5</v>
       </c>
       <c r="AS26">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT26">
         <v>6.2</v>
@@ -7210,7 +7210,7 @@
         <v>16</v>
       </c>
       <c r="AW26">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="AX26">
         <v>12.5</v>
@@ -7219,28 +7219,28 @@
         <v>12</v>
       </c>
       <c r="AZ26">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BA26">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BB26">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="BC26">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="BD26">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BE26">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BF26">
         <v>26</v>
       </c>
       <c r="BG26">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BH26">
         <v>1000</v>
@@ -7323,22 +7323,22 @@
         <v>201</v>
       </c>
       <c r="F27">
-        <v>2.52</v>
+        <v>2.02</v>
       </c>
       <c r="G27">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="H27">
-        <v>2.2</v>
+        <v>1.21</v>
       </c>
       <c r="I27">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="J27">
         <v>3.4</v>
       </c>
       <c r="K27">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -7353,7 +7353,7 @@
         <v>0</v>
       </c>
       <c r="P27">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="Q27">
         <v>1.71</v>
@@ -7568,7 +7568,7 @@
         <v>2.76</v>
       </c>
       <c r="G28">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="H28">
         <v>1.46</v>
@@ -7577,7 +7577,7 @@
         <v>1.59</v>
       </c>
       <c r="J28">
-        <v>4.4</v>
+        <v>2.68</v>
       </c>
       <c r="K28">
         <v>100</v>
@@ -7598,7 +7598,7 @@
         <v>2.14</v>
       </c>
       <c r="Q28">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R28">
         <v>0</v>
@@ -8055,7 +8055,7 @@
         <v>2.72</v>
       </c>
       <c r="H30">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="I30">
         <v>2.84</v>
@@ -8064,7 +8064,7 @@
         <v>3.55</v>
       </c>
       <c r="K30">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L30">
         <v>1.01</v>
@@ -8082,10 +8082,10 @@
         <v>2.36</v>
       </c>
       <c r="Q30">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R30">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="S30">
         <v>2.34</v>
@@ -8294,10 +8294,10 @@
         <v>1.61</v>
       </c>
       <c r="G31">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="H31">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="I31">
         <v>8.199999999999999</v>
@@ -8306,7 +8306,7 @@
         <v>3.9</v>
       </c>
       <c r="K31">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -8321,10 +8321,10 @@
         <v>0</v>
       </c>
       <c r="P31">
-        <v>2.16</v>
+        <v>1.04</v>
       </c>
       <c r="Q31">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R31">
         <v>0</v>
@@ -8533,16 +8533,16 @@
         <v>206</v>
       </c>
       <c r="F32">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="G32">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="H32">
         <v>3.6</v>
       </c>
       <c r="I32">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J32">
         <v>3.2</v>
@@ -8563,7 +8563,7 @@
         <v>0</v>
       </c>
       <c r="P32">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q32">
         <v>2.02</v>
@@ -8775,22 +8775,22 @@
         <v>207</v>
       </c>
       <c r="F33">
-        <v>2.16</v>
+        <v>1.27</v>
       </c>
       <c r="G33">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H33">
-        <v>2.92</v>
+        <v>1.1</v>
       </c>
       <c r="I33">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="J33">
-        <v>2.66</v>
+        <v>1.1</v>
       </c>
       <c r="K33">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -8805,10 +8805,10 @@
         <v>0</v>
       </c>
       <c r="P33">
-        <v>1.56</v>
+        <v>1.07</v>
       </c>
       <c r="Q33">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="R33">
         <v>0</v>
@@ -9020,19 +9020,19 @@
         <v>1.29</v>
       </c>
       <c r="G34">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="H34">
-        <v>6.8</v>
+        <v>2.92</v>
       </c>
       <c r="I34">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="J34">
         <v>4.8</v>
       </c>
       <c r="K34">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -9047,10 +9047,10 @@
         <v>0</v>
       </c>
       <c r="P34">
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="Q34">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="R34">
         <v>0</v>
@@ -9259,22 +9259,22 @@
         <v>209</v>
       </c>
       <c r="F35">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="G35">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="H35">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="I35">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J35">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K35">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -9289,10 +9289,10 @@
         <v>0</v>
       </c>
       <c r="P35">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q35">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="R35">
         <v>0</v>
@@ -9501,22 +9501,22 @@
         <v>210</v>
       </c>
       <c r="F36">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G36">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="H36">
         <v>2.66</v>
       </c>
       <c r="I36">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J36">
         <v>3.8</v>
       </c>
       <c r="K36">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L36">
         <v>0</v>
@@ -9531,10 +9531,10 @@
         <v>0</v>
       </c>
       <c r="P36">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q36">
-        <v>1.02</v>
+        <v>1.5</v>
       </c>
       <c r="R36">
         <v>0</v>
@@ -9743,10 +9743,10 @@
         <v>211</v>
       </c>
       <c r="F37">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="G37">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="H37">
         <v>4.8</v>
@@ -9755,10 +9755,10 @@
         <v>6.2</v>
       </c>
       <c r="J37">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K37">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -9985,22 +9985,22 @@
         <v>212</v>
       </c>
       <c r="F38">
-        <v>1.76</v>
+        <v>1.19</v>
       </c>
       <c r="G38">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="H38">
-        <v>3.5</v>
+        <v>1.11</v>
       </c>
       <c r="I38">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="J38">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="K38">
-        <v>7</v>
+        <v>240</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -10015,10 +10015,10 @@
         <v>0</v>
       </c>
       <c r="P38">
-        <v>1.87</v>
+        <v>1.07</v>
       </c>
       <c r="Q38">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R38">
         <v>0</v>
@@ -10227,7 +10227,7 @@
         <v>213</v>
       </c>
       <c r="F39">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="G39">
         <v>2.74</v>
@@ -10236,13 +10236,13 @@
         <v>3.25</v>
       </c>
       <c r="I39">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J39">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="K39">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -10260,7 +10260,7 @@
         <v>1.07</v>
       </c>
       <c r="Q39">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="R39">
         <v>0</v>
@@ -10478,13 +10478,13 @@
         <v>3.65</v>
       </c>
       <c r="I40">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J40">
         <v>3.25</v>
       </c>
       <c r="K40">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="P40">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q40">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R40">
         <v>0</v>
@@ -10717,7 +10717,7 @@
         <v>3.05</v>
       </c>
       <c r="H41">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="I41">
         <v>2.82</v>
@@ -10744,7 +10744,7 @@
         <v>1.65</v>
       </c>
       <c r="Q41">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R41">
         <v>1.24</v>
@@ -10768,19 +10768,19 @@
         <v>10</v>
       </c>
       <c r="Y41">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z41">
         <v>17</v>
       </c>
       <c r="AA41">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AB41">
         <v>9.800000000000001</v>
       </c>
       <c r="AC41">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD41">
         <v>13.5</v>
@@ -10789,7 +10789,7 @@
         <v>38</v>
       </c>
       <c r="AF41">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG41">
         <v>14</v>
@@ -10801,10 +10801,10 @@
         <v>70</v>
       </c>
       <c r="AJ41">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AK41">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AL41">
         <v>70</v>
@@ -10813,7 +10813,7 @@
         <v>170</v>
       </c>
       <c r="AN41">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AO41">
         <v>42</v>
@@ -10828,7 +10828,7 @@
         <v>14.5</v>
       </c>
       <c r="AS41">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="AT41">
         <v>8.6</v>
@@ -10840,7 +10840,7 @@
         <v>12</v>
       </c>
       <c r="AW41">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="AX41">
         <v>16.5</v>
@@ -10849,7 +10849,7 @@
         <v>12</v>
       </c>
       <c r="AZ41">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BA41">
         <v>32</v>
@@ -10858,7 +10858,7 @@
         <v>27</v>
       </c>
       <c r="BC41">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="BD41">
         <v>32</v>
@@ -10953,22 +10953,22 @@
         <v>216</v>
       </c>
       <c r="F42">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="G42">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="H42">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="I42">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="J42">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K42">
-        <v>13</v>
+        <v>4.6</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -10983,10 +10983,10 @@
         <v>0</v>
       </c>
       <c r="P42">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q42">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="R42">
         <v>0</v>
@@ -11195,19 +11195,19 @@
         <v>217</v>
       </c>
       <c r="F43">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="G43">
-        <v>2.94</v>
+        <v>2.78</v>
       </c>
       <c r="H43">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="I43">
         <v>3.15</v>
       </c>
       <c r="J43">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K43">
         <v>3.65</v>
@@ -11216,7 +11216,7 @@
         <v>0</v>
       </c>
       <c r="M43">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N43">
         <v>0</v>
@@ -11225,7 +11225,7 @@
         <v>0</v>
       </c>
       <c r="P43">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="Q43">
         <v>2.1</v>
@@ -11679,22 +11679,22 @@
         <v>219</v>
       </c>
       <c r="F45">
-        <v>2.34</v>
+        <v>1.48</v>
       </c>
       <c r="G45">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="H45">
         <v>3.2</v>
       </c>
       <c r="I45">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="J45">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K45">
-        <v>3.85</v>
+        <v>1000</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -11712,7 +11712,7 @@
         <v>1.98</v>
       </c>
       <c r="Q45">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="R45">
         <v>0</v>
@@ -11924,10 +11924,10 @@
         <v>3.1</v>
       </c>
       <c r="G46">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="H46">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="I46">
         <v>2.48</v>
@@ -11948,13 +11948,13 @@
         <v>4.4</v>
       </c>
       <c r="O46">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P46">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q46">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="R46">
         <v>1.45</v>
@@ -12005,16 +12005,16 @@
         <v>13.5</v>
       </c>
       <c r="AH46">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AI46">
         <v>36</v>
       </c>
       <c r="AJ46">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AK46">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL46">
         <v>40</v>
@@ -12041,10 +12041,10 @@
         <v>21</v>
       </c>
       <c r="AT46">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AU46">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV46">
         <v>10.5</v>
@@ -12053,7 +12053,7 @@
         <v>16.5</v>
       </c>
       <c r="AX46">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AY46">
         <v>12</v>
@@ -12065,7 +12065,7 @@
         <v>22</v>
       </c>
       <c r="BB46">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC46">
         <v>20</v>
@@ -12074,13 +12074,13 @@
         <v>24</v>
       </c>
       <c r="BE46">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BF46">
         <v>19.5</v>
       </c>
       <c r="BG46">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BH46">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-07.xlsx
@@ -679,7 +679,7 @@
     <t>Real Sociedad</t>
   </si>
   <si>
-    <t>2026-09-05 10:52:23</t>
+    <t>2026-09-05 13:18:05</t>
   </si>
 </sst>
 </file>
@@ -1276,16 +1276,16 @@
         <v>1.1</v>
       </c>
       <c r="G2">
-        <v>1.87</v>
+        <v>1.69</v>
       </c>
       <c r="H2">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="I2">
         <v>110</v>
       </c>
       <c r="J2">
-        <v>3.85</v>
+        <v>2.7</v>
       </c>
       <c r="K2">
         <v>250</v>
@@ -1297,7 +1297,7 @@
         <v>1.01</v>
       </c>
       <c r="N2">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="O2">
         <v>1.18</v>
@@ -1312,7 +1312,7 @@
         <v>1.08</v>
       </c>
       <c r="S2">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="T2">
         <v>1.01</v>
@@ -1324,7 +1324,7 @@
         <v>1.04</v>
       </c>
       <c r="W2">
-        <v>2.16</v>
+        <v>2.44</v>
       </c>
       <c r="X2">
         <v>1000</v>
@@ -1515,7 +1515,7 @@
         <v>177</v>
       </c>
       <c r="F3">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="G3">
         <v>2.3</v>
@@ -1524,13 +1524,13 @@
         <v>3.35</v>
       </c>
       <c r="I3">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J3">
         <v>2.92</v>
       </c>
       <c r="K3">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L3">
         <v>1.01</v>
@@ -1539,19 +1539,19 @@
         <v>1.01</v>
       </c>
       <c r="N3">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="O3">
         <v>1.4</v>
       </c>
       <c r="P3">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="Q3">
         <v>2.1</v>
       </c>
       <c r="R3">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S3">
         <v>3.8</v>
@@ -1563,7 +1563,7 @@
         <v>1.01</v>
       </c>
       <c r="V3">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W3">
         <v>1.76</v>
@@ -1677,7 +1677,7 @@
         <v>1.01</v>
       </c>
       <c r="BH3">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BI3">
         <v>2.42</v>
@@ -1757,7 +1757,7 @@
         <v>178</v>
       </c>
       <c r="F4">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="G4">
         <v>1.96</v>
@@ -1766,7 +1766,7 @@
         <v>4.6</v>
       </c>
       <c r="I4">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="J4">
         <v>3.5</v>
@@ -1778,10 +1778,10 @@
         <v>1.35</v>
       </c>
       <c r="M4">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N4">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O4">
         <v>1.33</v>
@@ -1796,7 +1796,7 @@
         <v>1.25</v>
       </c>
       <c r="S4">
-        <v>3.6</v>
+        <v>2.38</v>
       </c>
       <c r="T4">
         <v>1.01</v>
@@ -1999,22 +1999,22 @@
         <v>179</v>
       </c>
       <c r="F5">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="G5">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="H5">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I5">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="J5">
         <v>3.4</v>
       </c>
       <c r="K5">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -2023,7 +2023,7 @@
         <v>1.01</v>
       </c>
       <c r="N5">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="O5">
         <v>1.02</v>
@@ -2035,22 +2035,22 @@
         <v>2.44</v>
       </c>
       <c r="R5">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="S5">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T5">
         <v>1.01</v>
       </c>
       <c r="U5">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="V5">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W5">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -2244,10 +2244,10 @@
         <v>3.05</v>
       </c>
       <c r="G6">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H6">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="I6">
         <v>2.72</v>
@@ -2256,19 +2256,19 @@
         <v>3.3</v>
       </c>
       <c r="K6">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P6">
         <v>1.86</v>
@@ -2277,190 +2277,190 @@
         <v>1.69</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BI6">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BJ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="s">
         <v>221</v>
@@ -2483,226 +2483,226 @@
         <v>181</v>
       </c>
       <c r="F7">
-        <v>1.35</v>
+        <v>3.1</v>
       </c>
       <c r="G7">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="H7">
+        <v>2.38</v>
+      </c>
+      <c r="I7">
+        <v>2.7</v>
+      </c>
+      <c r="J7">
+        <v>3.15</v>
+      </c>
+      <c r="K7">
+        <v>3.35</v>
+      </c>
+      <c r="L7">
+        <v>1.48</v>
+      </c>
+      <c r="M7">
+        <v>1.01</v>
+      </c>
+      <c r="N7">
+        <v>1.01</v>
+      </c>
+      <c r="O7">
+        <v>1.48</v>
+      </c>
+      <c r="P7">
+        <v>1.54</v>
+      </c>
+      <c r="Q7">
         <v>2.4</v>
       </c>
-      <c r="I7">
-        <v>3.05</v>
-      </c>
-      <c r="J7">
-        <v>2.9</v>
-      </c>
-      <c r="K7">
-        <v>3.8</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>1.25</v>
-      </c>
-      <c r="Q7">
-        <v>1.01</v>
-      </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AU7">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AV7">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AW7">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AX7">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AY7">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ7">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BA7">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BB7">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BC7">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BD7">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BE7">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BF7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="s">
         <v>221</v>
@@ -2725,226 +2725,226 @@
         <v>182</v>
       </c>
       <c r="F8">
-        <v>1.08</v>
+        <v>1.38</v>
       </c>
       <c r="G8">
-        <v>1000</v>
+        <v>2.1</v>
       </c>
       <c r="H8">
-        <v>1.08</v>
+        <v>1.94</v>
       </c>
       <c r="I8">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J8">
-        <v>1.08</v>
+        <v>1.94</v>
       </c>
       <c r="K8">
         <v>320</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P8">
         <v>1.25</v>
       </c>
       <c r="Q8">
-        <v>1.02</v>
+        <v>1.36</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AU8">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV8">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AW8">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AX8">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AY8">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ8">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BA8">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="s">
         <v>221</v>
@@ -2967,13 +2967,13 @@
         <v>183</v>
       </c>
       <c r="F9">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="G9">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="H9">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="I9">
         <v>3.7</v>
@@ -2982,211 +2982,211 @@
         <v>3.35</v>
       </c>
       <c r="K9">
-        <v>7.6</v>
+        <v>110</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P9">
-        <v>1.12</v>
+        <v>2.02</v>
       </c>
       <c r="Q9">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AU9">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV9">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW9">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AX9">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AY9">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ9">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BA9">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BB9">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BC9">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BD9">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BE9">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="s">
         <v>221</v>
@@ -3209,226 +3209,226 @@
         <v>184</v>
       </c>
       <c r="F10">
-        <v>1.2</v>
+        <v>2.46</v>
       </c>
       <c r="G10">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="H10">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="I10">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="J10">
-        <v>1.08</v>
+        <v>2.9</v>
       </c>
       <c r="K10">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P10">
-        <v>1.72</v>
+        <v>1.24</v>
       </c>
       <c r="Q10">
         <v>1.81</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH10">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BI10">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BJ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="s">
         <v>221</v>
@@ -3469,208 +3469,208 @@
         <v>270</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="P11">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Q11">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="s">
         <v>221</v>
@@ -3693,226 +3693,226 @@
         <v>186</v>
       </c>
       <c r="F12">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="G12">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="H12">
         <v>6.6</v>
       </c>
       <c r="I12">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="J12">
         <v>4.5</v>
       </c>
       <c r="K12">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="P12">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q12">
         <v>1.51</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="s">
         <v>221</v>
@@ -3947,214 +3947,214 @@
         <v>1000</v>
       </c>
       <c r="J13">
-        <v>3.85</v>
+        <v>5.3</v>
       </c>
       <c r="K13">
         <v>320</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="P13">
         <v>1.24</v>
       </c>
       <c r="Q13">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB13" t="s">
         <v>221</v>
@@ -4183,19 +4183,19 @@
         <v>2.1</v>
       </c>
       <c r="H14">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I14">
         <v>4.6</v>
       </c>
       <c r="J14">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K14">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M14">
         <v>1.11</v>
@@ -4210,7 +4210,7 @@
         <v>1.64</v>
       </c>
       <c r="Q14">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="R14">
         <v>1.23</v>
@@ -4225,13 +4225,13 @@
         <v>1.85</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="X14">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Y14">
         <v>12.5</v>
@@ -4246,19 +4246,19 @@
         <v>7.4</v>
       </c>
       <c r="AC14">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD14">
         <v>19</v>
       </c>
       <c r="AE14">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AF14">
         <v>11</v>
       </c>
       <c r="AG14">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH14">
         <v>23</v>
@@ -4270,7 +4270,7 @@
         <v>26</v>
       </c>
       <c r="AK14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL14">
         <v>55</v>
@@ -4279,16 +4279,16 @@
         <v>1000</v>
       </c>
       <c r="AN14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO14">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AP14">
         <v>8.800000000000001</v>
       </c>
       <c r="AQ14">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR14">
         <v>19.5</v>
@@ -4297,16 +4297,16 @@
         <v>38</v>
       </c>
       <c r="AT14">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU14">
         <v>6.8</v>
       </c>
       <c r="AV14">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AW14">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="AX14">
         <v>10</v>
@@ -4318,7 +4318,7 @@
         <v>20</v>
       </c>
       <c r="BA14">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="BB14">
         <v>17</v>
@@ -4327,7 +4327,7 @@
         <v>17.5</v>
       </c>
       <c r="BD14">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="BE14">
         <v>46</v>
@@ -4422,19 +4422,19 @@
         <v>1.99</v>
       </c>
       <c r="G15">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="H15">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="I15">
         <v>4.3</v>
       </c>
       <c r="J15">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="K15">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -4661,22 +4661,22 @@
         <v>190</v>
       </c>
       <c r="F16">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="G16">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="H16">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I16">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="J16">
         <v>4.2</v>
       </c>
       <c r="K16">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -4691,10 +4691,10 @@
         <v>0</v>
       </c>
       <c r="P16">
-        <v>1.25</v>
+        <v>2.6</v>
       </c>
       <c r="Q16">
-        <v>1.04</v>
+        <v>1.56</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -4912,10 +4912,10 @@
         <v>4.5</v>
       </c>
       <c r="I17">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J17">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="K17">
         <v>3.95</v>
@@ -4933,10 +4933,10 @@
         <v>0</v>
       </c>
       <c r="P17">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q17">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -5154,13 +5154,13 @@
         <v>4.7</v>
       </c>
       <c r="I18">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="J18">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="K18">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -5178,7 +5178,7 @@
         <v>1.12</v>
       </c>
       <c r="Q18">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -5390,19 +5390,19 @@
         <v>4.1</v>
       </c>
       <c r="G19">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="H19">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="I19">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="J19">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="K19">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -5420,7 +5420,7 @@
         <v>2.16</v>
       </c>
       <c r="Q19">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -5629,22 +5629,22 @@
         <v>194</v>
       </c>
       <c r="F20">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="G20">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="H20">
         <v>2.84</v>
       </c>
       <c r="I20">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="J20">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K20">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -5871,13 +5871,13 @@
         <v>195</v>
       </c>
       <c r="F21">
-        <v>2.04</v>
+        <v>3.8</v>
       </c>
       <c r="G21">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="H21">
-        <v>1.08</v>
+        <v>1.65</v>
       </c>
       <c r="I21">
         <v>1.95</v>
@@ -5886,7 +5886,7 @@
         <v>3.65</v>
       </c>
       <c r="K21">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -5904,7 +5904,7 @@
         <v>2.06</v>
       </c>
       <c r="Q21">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="R21">
         <v>0</v>
@@ -6113,7 +6113,7 @@
         <v>196</v>
       </c>
       <c r="F22">
-        <v>1.69</v>
+        <v>1.1</v>
       </c>
       <c r="G22">
         <v>1.92</v>
@@ -6122,10 +6122,10 @@
         <v>2.18</v>
       </c>
       <c r="I22">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J22">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K22">
         <v>240</v>
@@ -6146,7 +6146,7 @@
         <v>2.04</v>
       </c>
       <c r="Q22">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -6364,7 +6364,7 @@
         <v>6.6</v>
       </c>
       <c r="I23">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="J23">
         <v>4.4</v>
@@ -6391,7 +6391,7 @@
         <v>1.64</v>
       </c>
       <c r="R23">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S23">
         <v>2.58</v>
@@ -6597,19 +6597,19 @@
         <v>198</v>
       </c>
       <c r="F24">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="G24">
         <v>2.16</v>
       </c>
       <c r="H24">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I24">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="J24">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K24">
         <v>4.3</v>
@@ -6627,10 +6627,10 @@
         <v>0</v>
       </c>
       <c r="P24">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="Q24">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -6869,10 +6869,10 @@
         <v>0</v>
       </c>
       <c r="P25">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="Q25">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -7081,10 +7081,10 @@
         <v>200</v>
       </c>
       <c r="F26">
+        <v>2.48</v>
+      </c>
+      <c r="G26">
         <v>2.52</v>
-      </c>
-      <c r="G26">
-        <v>2.54</v>
       </c>
       <c r="H26">
         <v>3.65</v>
@@ -7096,7 +7096,7 @@
         <v>2.98</v>
       </c>
       <c r="K26">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -7108,7 +7108,7 @@
         <v>2.38</v>
       </c>
       <c r="O26">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="P26">
         <v>1.44</v>
@@ -7117,7 +7117,7 @@
         <v>3.1</v>
       </c>
       <c r="R26">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S26">
         <v>7</v>
@@ -7135,13 +7135,13 @@
         <v>0</v>
       </c>
       <c r="X26">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="Y26">
         <v>9</v>
       </c>
       <c r="Z26">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA26">
         <v>90</v>
@@ -7159,7 +7159,7 @@
         <v>75</v>
       </c>
       <c r="AF26">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG26">
         <v>14</v>
@@ -7171,7 +7171,7 @@
         <v>120</v>
       </c>
       <c r="AJ26">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK26">
         <v>44</v>
@@ -7183,7 +7183,7 @@
         <v>320</v>
       </c>
       <c r="AN26">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AO26">
         <v>120</v>
@@ -7195,10 +7195,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR26">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AS26">
-        <v>14.5</v>
+        <v>34</v>
       </c>
       <c r="AT26">
         <v>6.2</v>
@@ -7219,10 +7219,10 @@
         <v>12</v>
       </c>
       <c r="AZ26">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="BA26">
-        <v>15.5</v>
+        <v>40</v>
       </c>
       <c r="BB26">
         <v>23</v>
@@ -7231,16 +7231,16 @@
         <v>24</v>
       </c>
       <c r="BD26">
-        <v>14.5</v>
+        <v>36</v>
       </c>
       <c r="BE26">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="BF26">
         <v>26</v>
       </c>
       <c r="BG26">
-        <v>15.5</v>
+        <v>38</v>
       </c>
       <c r="BH26">
         <v>1000</v>
@@ -7323,22 +7323,22 @@
         <v>201</v>
       </c>
       <c r="F27">
-        <v>2.02</v>
+        <v>2.82</v>
       </c>
       <c r="G27">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="H27">
-        <v>1.21</v>
+        <v>2.48</v>
       </c>
       <c r="I27">
-        <v>3.25</v>
+        <v>2.86</v>
       </c>
       <c r="J27">
         <v>3.4</v>
       </c>
       <c r="K27">
-        <v>6</v>
+        <v>3.8</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -7353,10 +7353,10 @@
         <v>0</v>
       </c>
       <c r="P27">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q27">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R27">
         <v>0</v>
@@ -7565,19 +7565,19 @@
         <v>202</v>
       </c>
       <c r="F28">
-        <v>2.76</v>
+        <v>1.1</v>
       </c>
       <c r="G28">
         <v>1000</v>
       </c>
       <c r="H28">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="I28">
         <v>1.59</v>
       </c>
       <c r="J28">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="K28">
         <v>100</v>
@@ -7595,7 +7595,7 @@
         <v>0</v>
       </c>
       <c r="P28">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q28">
         <v>1.68</v>
@@ -8291,22 +8291,22 @@
         <v>205</v>
       </c>
       <c r="F31">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="G31">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="H31">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="I31">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="J31">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="K31">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -8321,10 +8321,10 @@
         <v>0</v>
       </c>
       <c r="P31">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="Q31">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="R31">
         <v>0</v>
@@ -8545,7 +8545,7 @@
         <v>4.4</v>
       </c>
       <c r="J32">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K32">
         <v>3.7</v>
@@ -8775,22 +8775,22 @@
         <v>207</v>
       </c>
       <c r="F33">
-        <v>1.27</v>
+        <v>2.22</v>
       </c>
       <c r="G33">
-        <v>3.4</v>
+        <v>2.98</v>
       </c>
       <c r="H33">
-        <v>1.1</v>
+        <v>3.05</v>
       </c>
       <c r="I33">
-        <v>5.8</v>
+        <v>3.95</v>
       </c>
       <c r="J33">
-        <v>1.1</v>
+        <v>2.72</v>
       </c>
       <c r="K33">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -8805,10 +8805,10 @@
         <v>0</v>
       </c>
       <c r="P33">
-        <v>1.07</v>
+        <v>1.54</v>
       </c>
       <c r="Q33">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="R33">
         <v>0</v>
@@ -9047,10 +9047,10 @@
         <v>0</v>
       </c>
       <c r="P34">
-        <v>1.25</v>
+        <v>2.54</v>
       </c>
       <c r="Q34">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="R34">
         <v>0</v>
@@ -9259,7 +9259,7 @@
         <v>209</v>
       </c>
       <c r="F35">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="G35">
         <v>2.32</v>
@@ -9268,13 +9268,13 @@
         <v>3.1</v>
       </c>
       <c r="I35">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J35">
         <v>3.8</v>
       </c>
       <c r="K35">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -9292,7 +9292,7 @@
         <v>3.1</v>
       </c>
       <c r="Q35">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="R35">
         <v>0</v>
@@ -9746,19 +9746,19 @@
         <v>1.78</v>
       </c>
       <c r="G37">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="H37">
         <v>4.8</v>
       </c>
       <c r="I37">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="J37">
         <v>3.55</v>
       </c>
       <c r="K37">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -9776,7 +9776,7 @@
         <v>1.86</v>
       </c>
       <c r="Q37">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="R37">
         <v>0</v>
@@ -9985,22 +9985,22 @@
         <v>212</v>
       </c>
       <c r="F38">
-        <v>1.19</v>
+        <v>1.9</v>
       </c>
       <c r="G38">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="H38">
-        <v>1.11</v>
+        <v>3.85</v>
       </c>
       <c r="I38">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="J38">
         <v>3.65</v>
       </c>
       <c r="K38">
-        <v>240</v>
+        <v>4.3</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -10015,7 +10015,7 @@
         <v>0</v>
       </c>
       <c r="P38">
-        <v>1.07</v>
+        <v>1.89</v>
       </c>
       <c r="Q38">
         <v>1.68</v>
@@ -10484,7 +10484,7 @@
         <v>3.25</v>
       </c>
       <c r="K40">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -10499,7 +10499,7 @@
         <v>0</v>
       </c>
       <c r="P40">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="Q40">
         <v>1.9</v>
@@ -10714,13 +10714,13 @@
         <v>3</v>
       </c>
       <c r="G41">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H41">
+        <v>2.74</v>
+      </c>
+      <c r="I41">
         <v>2.78</v>
-      </c>
-      <c r="I41">
-        <v>2.82</v>
       </c>
       <c r="J41">
         <v>3.2</v>
@@ -10744,7 +10744,7 @@
         <v>1.65</v>
       </c>
       <c r="Q41">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="R41">
         <v>1.24</v>
@@ -10756,7 +10756,7 @@
         <v>2.04</v>
       </c>
       <c r="U41">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V41">
         <v>0</v>
@@ -10768,58 +10768,58 @@
         <v>10</v>
       </c>
       <c r="Y41">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="Z41">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AA41">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AB41">
         <v>9.800000000000001</v>
       </c>
       <c r="AC41">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD41">
         <v>13.5</v>
       </c>
       <c r="AE41">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="AF41">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AG41">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AH41">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AI41">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AJ41">
-        <v>55</v>
+        <v>190</v>
       </c>
       <c r="AK41">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AL41">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM41">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AN41">
         <v>50</v>
       </c>
       <c r="AO41">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AP41">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ41">
         <v>8.199999999999999</v>
@@ -10831,7 +10831,7 @@
         <v>36</v>
       </c>
       <c r="AT41">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU41">
         <v>6.6</v>
@@ -10846,13 +10846,13 @@
         <v>16.5</v>
       </c>
       <c r="AY41">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ41">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA41">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BB41">
         <v>27</v>
@@ -10864,13 +10864,13 @@
         <v>32</v>
       </c>
       <c r="BE41">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="BF41">
         <v>25</v>
       </c>
       <c r="BG41">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="BH41">
         <v>1000</v>
@@ -10953,22 +10953,22 @@
         <v>216</v>
       </c>
       <c r="F42">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="G42">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="H42">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="I42">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J42">
-        <v>3.85</v>
+        <v>2.4</v>
       </c>
       <c r="K42">
-        <v>4.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -10986,7 +10986,7 @@
         <v>1.96</v>
       </c>
       <c r="Q42">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="R42">
         <v>0</v>
@@ -11195,19 +11195,19 @@
         <v>217</v>
       </c>
       <c r="F43">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="G43">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="H43">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="I43">
         <v>3.15</v>
       </c>
       <c r="J43">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="K43">
         <v>3.65</v>
@@ -11225,7 +11225,7 @@
         <v>0</v>
       </c>
       <c r="P43">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Q43">
         <v>2.1</v>
@@ -11679,22 +11679,22 @@
         <v>219</v>
       </c>
       <c r="F45">
-        <v>1.48</v>
+        <v>2.36</v>
       </c>
       <c r="G45">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="H45">
+        <v>3.1</v>
+      </c>
+      <c r="I45">
+        <v>3.5</v>
+      </c>
+      <c r="J45">
         <v>3.2</v>
       </c>
-      <c r="I45">
-        <v>1000</v>
-      </c>
-      <c r="J45">
-        <v>3.35</v>
-      </c>
       <c r="K45">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="L45">
         <v>0</v>
@@ -11709,10 +11709,10 @@
         <v>0</v>
       </c>
       <c r="P45">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="Q45">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="R45">
         <v>0</v>
@@ -11927,10 +11927,10 @@
         <v>3.2</v>
       </c>
       <c r="H46">
+        <v>2.42</v>
+      </c>
+      <c r="I46">
         <v>2.44</v>
-      </c>
-      <c r="I46">
-        <v>2.48</v>
       </c>
       <c r="J46">
         <v>3.65</v>
@@ -11954,7 +11954,7 @@
         <v>2.2</v>
       </c>
       <c r="Q46">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R46">
         <v>1.45</v>
@@ -11990,10 +11990,10 @@
         <v>14.5</v>
       </c>
       <c r="AC46">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD46">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE46">
         <v>25</v>
@@ -12011,10 +12011,10 @@
         <v>36</v>
       </c>
       <c r="AJ46">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AK46">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL46">
         <v>40</v>
@@ -12029,7 +12029,7 @@
         <v>17.5</v>
       </c>
       <c r="AP46">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AQ46">
         <v>11</v>
@@ -12050,13 +12050,13 @@
         <v>10.5</v>
       </c>
       <c r="AW46">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="AX46">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AY46">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ46">
         <v>13.5</v>
@@ -12074,13 +12074,13 @@
         <v>24</v>
       </c>
       <c r="BE46">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="BF46">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="BG46">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BH46">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-07.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="227">
   <si>
     <t>League</t>
   </si>
@@ -340,6 +340,9 @@
     <t>Canadian Premier League</t>
   </si>
   <si>
+    <t>English Sky Bet League 1</t>
+  </si>
+  <si>
     <t>Paraguayan Primera Division</t>
   </si>
   <si>
@@ -463,15 +466,15 @@
     <t>Manisa FK</t>
   </si>
   <si>
+    <t>Malmo FF</t>
+  </si>
+  <si>
+    <t>Getafe</t>
+  </si>
+  <si>
     <t>Kalmar FF</t>
   </si>
   <si>
-    <t>Getafe</t>
-  </si>
-  <si>
-    <t>Malmo FF</t>
-  </si>
-  <si>
     <t>Hapoel Tel Aviv</t>
   </si>
   <si>
@@ -538,6 +541,9 @@
     <t>HFX Wanderers</t>
   </si>
   <si>
+    <t>Bromley</t>
+  </si>
+  <si>
     <t>Guarani (Par)</t>
   </si>
   <si>
@@ -601,15 +607,15 @@
     <t>Bursaspor</t>
   </si>
   <si>
+    <t>AIK</t>
+  </si>
+  <si>
+    <t>Celta Vigo</t>
+  </si>
+  <si>
     <t>Djurgardens</t>
   </si>
   <si>
-    <t>Celta Vigo</t>
-  </si>
-  <si>
-    <t>AIK</t>
-  </si>
-  <si>
     <t>Hapoel Ramat Gan</t>
   </si>
   <si>
@@ -676,6 +682,9 @@
     <t>Cavalry</t>
   </si>
   <si>
+    <t>AFC Wimbledon</t>
+  </si>
+  <si>
     <t>Deportivo Recoleta</t>
   </si>
   <si>
@@ -685,7 +694,7 @@
     <t>Real Sociedad</t>
   </si>
   <si>
-    <t>2026-09-05 15:42:50</t>
+    <t>2026-09-05 18:05:27</t>
   </si>
 </sst>
 </file>
@@ -1017,7 +1026,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB47"/>
+  <dimension ref="A1:CB48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1267,34 +1276,34 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F2">
-        <v>1.16</v>
+        <v>1.49</v>
       </c>
       <c r="G2">
         <v>1.65</v>
       </c>
       <c r="H2">
-        <v>2.6</v>
+        <v>5</v>
       </c>
       <c r="I2">
         <v>8.199999999999999</v>
       </c>
       <c r="J2">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="K2">
-        <v>250</v>
+        <v>6</v>
       </c>
       <c r="L2">
         <v>1.01</v>
@@ -1303,22 +1312,22 @@
         <v>1.01</v>
       </c>
       <c r="N2">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="O2">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P2">
         <v>1.26</v>
       </c>
       <c r="Q2">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="R2">
         <v>1.08</v>
       </c>
       <c r="S2">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="T2">
         <v>1.01</v>
@@ -1501,7 +1510,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1509,178 +1518,178 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F3">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="G3">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H3">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="J3">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="K3">
+        <v>3.55</v>
+      </c>
+      <c r="L3">
+        <v>1.41</v>
+      </c>
+      <c r="M3">
+        <v>1.09</v>
+      </c>
+      <c r="N3">
+        <v>2.98</v>
+      </c>
+      <c r="O3">
+        <v>1.42</v>
+      </c>
+      <c r="P3">
+        <v>1.65</v>
+      </c>
+      <c r="Q3">
+        <v>2.26</v>
+      </c>
+      <c r="R3">
+        <v>1.24</v>
+      </c>
+      <c r="S3">
+        <v>4.3</v>
+      </c>
+      <c r="T3">
+        <v>1.93</v>
+      </c>
+      <c r="U3">
+        <v>1.86</v>
+      </c>
+      <c r="V3">
+        <v>1.27</v>
+      </c>
+      <c r="W3">
+        <v>1.78</v>
+      </c>
+      <c r="X3">
+        <v>13</v>
+      </c>
+      <c r="Y3">
+        <v>15</v>
+      </c>
+      <c r="Z3">
+        <v>36</v>
+      </c>
+      <c r="AA3">
+        <v>940</v>
+      </c>
+      <c r="AB3">
+        <v>9.4</v>
+      </c>
+      <c r="AC3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD3">
+        <v>21</v>
+      </c>
+      <c r="AE3">
+        <v>940</v>
+      </c>
+      <c r="AF3">
+        <v>15.5</v>
+      </c>
+      <c r="AG3">
+        <v>13.5</v>
+      </c>
+      <c r="AH3">
+        <v>26</v>
+      </c>
+      <c r="AI3">
+        <v>940</v>
+      </c>
+      <c r="AJ3">
+        <v>34</v>
+      </c>
+      <c r="AK3">
+        <v>34</v>
+      </c>
+      <c r="AL3">
+        <v>60</v>
+      </c>
+      <c r="AM3">
+        <v>940</v>
+      </c>
+      <c r="AN3">
+        <v>28</v>
+      </c>
+      <c r="AO3">
+        <v>940</v>
+      </c>
+      <c r="AP3">
+        <v>7.8</v>
+      </c>
+      <c r="AQ3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR3">
+        <v>21</v>
+      </c>
+      <c r="AS3">
+        <v>65</v>
+      </c>
+      <c r="AT3">
+        <v>5.9</v>
+      </c>
+      <c r="AU3">
         <v>5.7</v>
       </c>
-      <c r="L3">
-        <v>1.01</v>
-      </c>
-      <c r="M3">
-        <v>1.01</v>
-      </c>
-      <c r="N3">
-        <v>2.48</v>
-      </c>
-      <c r="O3">
-        <v>1.41</v>
-      </c>
-      <c r="P3">
-        <v>1.56</v>
-      </c>
-      <c r="Q3">
-        <v>2.1</v>
-      </c>
-      <c r="R3">
-        <v>1.19</v>
-      </c>
-      <c r="S3">
-        <v>3.8</v>
-      </c>
-      <c r="T3">
-        <v>1.01</v>
-      </c>
-      <c r="U3">
-        <v>1.01</v>
-      </c>
-      <c r="V3">
-        <v>1.25</v>
-      </c>
-      <c r="W3">
-        <v>1.76</v>
-      </c>
-      <c r="X3">
-        <v>1000</v>
-      </c>
-      <c r="Y3">
-        <v>1000</v>
-      </c>
-      <c r="Z3">
-        <v>1000</v>
-      </c>
-      <c r="AA3">
-        <v>1000</v>
-      </c>
-      <c r="AB3">
-        <v>1000</v>
-      </c>
-      <c r="AC3">
-        <v>1000</v>
-      </c>
-      <c r="AD3">
-        <v>1000</v>
-      </c>
-      <c r="AE3">
-        <v>1000</v>
-      </c>
-      <c r="AF3">
-        <v>1000</v>
-      </c>
-      <c r="AG3">
-        <v>1000</v>
-      </c>
-      <c r="AH3">
-        <v>1000</v>
-      </c>
-      <c r="AI3">
-        <v>1000</v>
-      </c>
-      <c r="AJ3">
-        <v>1000</v>
-      </c>
-      <c r="AK3">
-        <v>1000</v>
-      </c>
-      <c r="AL3">
-        <v>1000</v>
-      </c>
-      <c r="AM3">
-        <v>1000</v>
-      </c>
-      <c r="AN3">
-        <v>1000</v>
-      </c>
-      <c r="AO3">
-        <v>1000</v>
-      </c>
-      <c r="AP3">
-        <v>1.01</v>
-      </c>
-      <c r="AQ3">
-        <v>1.01</v>
-      </c>
-      <c r="AR3">
-        <v>1.01</v>
-      </c>
-      <c r="AS3">
-        <v>1.01</v>
-      </c>
-      <c r="AT3">
-        <v>1.01</v>
-      </c>
-      <c r="AU3">
-        <v>1.01</v>
-      </c>
       <c r="AV3">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AW3">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="AX3">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY3">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ3">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BA3">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BB3">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BC3">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BD3">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BE3">
-        <v>1.01</v>
+        <v>100</v>
       </c>
       <c r="BF3">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BG3">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BH3">
         <v>3.55</v>
@@ -1692,58 +1701,58 @@
         <v>1000</v>
       </c>
       <c r="BK3">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BN3">
         <v>1000</v>
       </c>
       <c r="BO3">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BT3">
         <v>1000</v>
       </c>
       <c r="BU3">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="CB3" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1751,16 +1760,16 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F4">
         <v>1.76</v>
@@ -1784,7 +1793,7 @@
         <v>1.35</v>
       </c>
       <c r="M4">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N4">
         <v>3</v>
@@ -1811,7 +1820,7 @@
         <v>1.01</v>
       </c>
       <c r="V4">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W4">
         <v>2.04</v>
@@ -1985,7 +1994,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1993,178 +2002,178 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F5">
         <v>1.83</v>
       </c>
       <c r="G5">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="H5">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="I5">
         <v>5.8</v>
       </c>
       <c r="J5">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K5">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L5">
         <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N5">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O5">
-        <v>1.02</v>
+        <v>1.45</v>
       </c>
       <c r="P5">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="Q5">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R5">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="S5">
-        <v>2.44</v>
+        <v>4.2</v>
       </c>
       <c r="T5">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="U5">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="V5">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W5">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="X5">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y5">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z5">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA5">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="AB5">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AC5">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD5">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AE5">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="AF5">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG5">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH5">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI5">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="AJ5">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AK5">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL5">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM5">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="AN5">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AO5">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="AP5">
         <v>8.6</v>
       </c>
       <c r="AQ5">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AR5">
-        <v>25</v>
+        <v>4.6</v>
       </c>
       <c r="AS5">
-        <v>85</v>
+        <v>5</v>
       </c>
       <c r="AT5">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AU5">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV5">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW5">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="AX5">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AY5">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ5">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BA5">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="BB5">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BC5">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BD5">
-        <v>38</v>
+        <v>4.8</v>
       </c>
       <c r="BE5">
-        <v>100</v>
+        <v>5.1</v>
       </c>
       <c r="BF5">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BG5">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -2227,7 +2236,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2235,16 +2244,16 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E6" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F6">
         <v>3.05</v>
@@ -2469,7 +2478,7 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2477,16 +2486,16 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E7" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F7">
         <v>3.1</v>
@@ -2597,52 +2606,52 @@
         <v>1000</v>
       </c>
       <c r="AP7">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR7">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AS7">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="AT7">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AU7">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV7">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW7">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="AX7">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AY7">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BA7">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BB7">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BC7">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BD7">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BE7">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BF7">
         <v>1.01</v>
@@ -2711,7 +2720,7 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2719,70 +2728,70 @@
         <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E8" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F8">
-        <v>1.38</v>
+        <v>1.9</v>
       </c>
       <c r="G8">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H8">
+        <v>4.4</v>
+      </c>
+      <c r="I8">
+        <v>6</v>
+      </c>
+      <c r="J8">
+        <v>3.25</v>
+      </c>
+      <c r="K8">
+        <v>3.65</v>
+      </c>
+      <c r="L8">
+        <v>1.42</v>
+      </c>
+      <c r="M8">
+        <v>1.01</v>
+      </c>
+      <c r="N8">
+        <v>2.78</v>
+      </c>
+      <c r="O8">
+        <v>1.4</v>
+      </c>
+      <c r="P8">
+        <v>1.65</v>
+      </c>
+      <c r="Q8">
+        <v>2.2</v>
+      </c>
+      <c r="R8">
+        <v>1.22</v>
+      </c>
+      <c r="S8">
+        <v>4.1</v>
+      </c>
+      <c r="T8">
+        <v>1.01</v>
+      </c>
+      <c r="U8">
+        <v>1.01</v>
+      </c>
+      <c r="V8">
+        <v>1.22</v>
+      </c>
+      <c r="W8">
         <v>1.94</v>
-      </c>
-      <c r="I8">
-        <v>110</v>
-      </c>
-      <c r="J8">
-        <v>1.94</v>
-      </c>
-      <c r="K8">
-        <v>320</v>
-      </c>
-      <c r="L8">
-        <v>1.01</v>
-      </c>
-      <c r="M8">
-        <v>1.01</v>
-      </c>
-      <c r="N8">
-        <v>1.65</v>
-      </c>
-      <c r="O8">
-        <v>1.36</v>
-      </c>
-      <c r="P8">
-        <v>1.25</v>
-      </c>
-      <c r="Q8">
-        <v>1.36</v>
-      </c>
-      <c r="R8">
-        <v>1.08</v>
-      </c>
-      <c r="S8">
-        <v>1.37</v>
-      </c>
-      <c r="T8">
-        <v>1.01</v>
-      </c>
-      <c r="U8">
-        <v>1.01</v>
-      </c>
-      <c r="V8">
-        <v>1.01</v>
-      </c>
-      <c r="W8">
-        <v>1.9</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2842,46 +2851,46 @@
         <v>9.4</v>
       </c>
       <c r="AQ8">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR8">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AS8">
         <v>40</v>
       </c>
       <c r="AT8">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AU8">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV8">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AW8">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AX8">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY8">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ8">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA8">
         <v>40</v>
       </c>
       <c r="BB8">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC8">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BD8">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BE8">
         <v>40</v>
@@ -2953,7 +2962,7 @@
         <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2961,178 +2970,178 @@
         <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="G9">
-        <v>2.86</v>
+        <v>2.46</v>
       </c>
       <c r="H9">
-        <v>2.38</v>
+        <v>3.05</v>
       </c>
       <c r="I9">
-        <v>110</v>
+        <v>3.45</v>
       </c>
       <c r="J9">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="K9">
-        <v>110</v>
+        <v>3.95</v>
       </c>
       <c r="L9">
         <v>1.01</v>
       </c>
       <c r="M9">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N9">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="O9">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="P9">
-        <v>1.86</v>
+        <v>2.06</v>
       </c>
       <c r="Q9">
         <v>1.8</v>
       </c>
       <c r="R9">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="S9">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="T9">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="U9">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="V9">
-        <v>1.05</v>
+        <v>1.41</v>
       </c>
       <c r="W9">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="X9">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Y9">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z9">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB9">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC9">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD9">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE9">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF9">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AG9">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH9">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI9">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ9">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK9">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL9">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM9">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN9">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AO9">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP9">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ9">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR9">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AS9">
-        <v>32</v>
+        <v>4.7</v>
       </c>
       <c r="AT9">
         <v>9</v>
       </c>
       <c r="AU9">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AV9">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AW9">
-        <v>23</v>
+        <v>4.5</v>
       </c>
       <c r="AX9">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ9">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BA9">
-        <v>28</v>
+        <v>4.6</v>
       </c>
       <c r="BB9">
-        <v>23</v>
+        <v>4.4</v>
       </c>
       <c r="BC9">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BD9">
-        <v>24</v>
+        <v>4.5</v>
       </c>
       <c r="BE9">
-        <v>40</v>
+        <v>4.8</v>
       </c>
       <c r="BF9">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BG9">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH9">
         <v>1000</v>
@@ -3195,7 +3204,7 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3203,157 +3212,157 @@
         <v>87</v>
       </c>
       <c r="B10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E10" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F10">
-        <v>2.46</v>
+        <v>2.66</v>
       </c>
       <c r="G10">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="H10">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="I10">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="J10">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="K10">
-        <v>5.7</v>
+        <v>3.8</v>
       </c>
       <c r="L10">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M10">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N10">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="O10">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="P10">
-        <v>1.24</v>
+        <v>1.78</v>
       </c>
       <c r="Q10">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="R10">
         <v>1.15</v>
       </c>
       <c r="S10">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="T10">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="U10">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="V10">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="W10">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="X10">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y10">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z10">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA10">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB10">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC10">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD10">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE10">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF10">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG10">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH10">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI10">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ10">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK10">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL10">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM10">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN10">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO10">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP10">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AQ10">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AR10">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AS10">
         <v>1.01</v>
       </c>
       <c r="AT10">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU10">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV10">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AW10">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="AX10">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AY10">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ10">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA10">
         <v>1.01</v>
@@ -3362,7 +3371,7 @@
         <v>1.01</v>
       </c>
       <c r="BC10">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BD10">
         <v>1.01</v>
@@ -3371,22 +3380,22 @@
         <v>1.01</v>
       </c>
       <c r="BF10">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BG10">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BH10">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="BI10">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="BJ10">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK10">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BL10">
         <v>1000</v>
@@ -3395,49 +3404,49 @@
         <v>1.01</v>
       </c>
       <c r="BN10">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO10">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BP10">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ10">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BR10">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS10">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BT10">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU10">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BV10">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BW10">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BX10">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY10">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA10">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="CB10" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3445,16 +3454,16 @@
         <v>88</v>
       </c>
       <c r="B11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D11" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E11" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F11">
         <v>1.08</v>
@@ -3508,7 +3517,7 @@
         <v>1.01</v>
       </c>
       <c r="W11">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3679,7 +3688,7 @@
         <v>1.01</v>
       </c>
       <c r="CB11" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3687,16 +3696,16 @@
         <v>89</v>
       </c>
       <c r="B12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E12" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F12">
         <v>1.35</v>
@@ -3747,7 +3756,7 @@
         <v>1.01</v>
       </c>
       <c r="V12">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W12">
         <v>2.92</v>
@@ -3921,7 +3930,7 @@
         <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3929,16 +3938,16 @@
         <v>88</v>
       </c>
       <c r="B13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D13" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E13" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F13">
         <v>1.25</v>
@@ -3992,7 +4001,7 @@
         <v>1.01</v>
       </c>
       <c r="W13">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -4163,7 +4172,7 @@
         <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4171,16 +4180,16 @@
         <v>90</v>
       </c>
       <c r="B14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D14" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E14" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F14">
         <v>2.08</v>
@@ -4189,7 +4198,7 @@
         <v>2.12</v>
       </c>
       <c r="H14">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I14">
         <v>4.6</v>
@@ -4201,13 +4210,13 @@
         <v>3.35</v>
       </c>
       <c r="L14">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="M14">
         <v>1.11</v>
       </c>
       <c r="N14">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="O14">
         <v>1.49</v>
@@ -4216,13 +4225,13 @@
         <v>1.64</v>
       </c>
       <c r="Q14">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="R14">
         <v>1.23</v>
       </c>
       <c r="S14">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T14">
         <v>2.12</v>
@@ -4234,7 +4243,7 @@
         <v>1.28</v>
       </c>
       <c r="W14">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X14">
         <v>9.4</v>
@@ -4249,19 +4258,19 @@
         <v>110</v>
       </c>
       <c r="AB14">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AC14">
         <v>7.4</v>
       </c>
       <c r="AD14">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE14">
         <v>75</v>
       </c>
       <c r="AF14">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG14">
         <v>11</v>
@@ -4294,7 +4303,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AQ14">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR14">
         <v>27</v>
@@ -4303,7 +4312,7 @@
         <v>38</v>
       </c>
       <c r="AT14">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU14">
         <v>7</v>
@@ -4312,10 +4321,10 @@
         <v>17</v>
       </c>
       <c r="AW14">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="AX14">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY14">
         <v>10.5</v>
@@ -4324,7 +4333,7 @@
         <v>21</v>
       </c>
       <c r="BA14">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="BB14">
         <v>23</v>
@@ -4339,64 +4348,64 @@
         <v>46</v>
       </c>
       <c r="BF14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG14">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="BH14">
         <v>1000</v>
       </c>
       <c r="BI14">
-        <v>1.23</v>
+        <v>2.42</v>
       </c>
       <c r="BJ14">
         <v>1000</v>
       </c>
       <c r="BK14">
-        <v>6.6</v>
+        <v>2.62</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>34</v>
+        <v>1.1</v>
       </c>
       <c r="BN14">
         <v>1000</v>
       </c>
       <c r="BO14">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="BP14">
         <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>8.4</v>
+        <v>2.62</v>
       </c>
       <c r="BR14">
         <v>1000</v>
       </c>
       <c r="BS14">
-        <v>15</v>
+        <v>1.1</v>
       </c>
       <c r="BT14">
         <v>1000</v>
       </c>
       <c r="BU14">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="BV14">
         <v>1000</v>
       </c>
       <c r="BW14">
-        <v>14</v>
+        <v>1.1</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>17</v>
+        <v>1.1</v>
       </c>
       <c r="BZ14">
         <v>0</v>
@@ -4405,7 +4414,7 @@
         <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4413,16 +4422,16 @@
         <v>91</v>
       </c>
       <c r="B15" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C15" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D15" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E15" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F15">
         <v>1.99</v>
@@ -4647,7 +4656,7 @@
         <v>1.01</v>
       </c>
       <c r="CB15" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4655,16 +4664,16 @@
         <v>92</v>
       </c>
       <c r="B16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C16" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D16" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E16" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F16">
         <v>2.42</v>
@@ -4691,28 +4700,28 @@
         <v>1.04</v>
       </c>
       <c r="N16">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="O16">
         <v>1.21</v>
       </c>
       <c r="P16">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q16">
         <v>1.66</v>
       </c>
       <c r="R16">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S16">
         <v>2.62</v>
       </c>
       <c r="T16">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="U16">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="V16">
         <v>1.48</v>
@@ -4721,112 +4730,112 @@
         <v>1.65</v>
       </c>
       <c r="X16">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y16">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Z16">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA16">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB16">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AC16">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD16">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE16">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF16">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG16">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH16">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI16">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ16">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK16">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL16">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM16">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN16">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AO16">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AP16">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ16">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR16">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AS16">
-        <v>34</v>
+        <v>3.95</v>
       </c>
       <c r="AT16">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU16">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AV16">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AW16">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY16">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ16">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA16">
-        <v>26</v>
+        <v>3.9</v>
       </c>
       <c r="BB16">
-        <v>22</v>
+        <v>3.85</v>
       </c>
       <c r="BC16">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD16">
-        <v>23</v>
+        <v>3.85</v>
       </c>
       <c r="BE16">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="BF16">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BG16">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -4889,7 +4898,7 @@
         <v>1.01</v>
       </c>
       <c r="CB16" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4897,16 +4906,16 @@
         <v>93</v>
       </c>
       <c r="B17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C17" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D17" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E17" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F17">
         <v>1.91</v>
@@ -4930,22 +4939,22 @@
         <v>1.01</v>
       </c>
       <c r="M17">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N17">
-        <v>2.36</v>
+        <v>4.1</v>
       </c>
       <c r="O17">
         <v>1.27</v>
       </c>
       <c r="P17">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q17">
-        <v>1.27</v>
+        <v>1.67</v>
       </c>
       <c r="R17">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S17">
         <v>2.96</v>
@@ -5017,52 +5026,52 @@
         <v>1000</v>
       </c>
       <c r="AP17">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR17">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AS17">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="AT17">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU17">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV17">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW17">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AX17">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY17">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA17">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BB17">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC17">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD17">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BE17">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="BF17">
         <v>1.01</v>
@@ -5131,7 +5140,7 @@
         <v>1.01</v>
       </c>
       <c r="CB17" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -5139,19 +5148,19 @@
         <v>93</v>
       </c>
       <c r="B18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C18" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D18" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E18" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F18">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="G18">
         <v>1.94</v>
@@ -5172,7 +5181,7 @@
         <v>1.01</v>
       </c>
       <c r="M18">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N18">
         <v>3.5</v>
@@ -5190,10 +5199,10 @@
         <v>1.33</v>
       </c>
       <c r="S18">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T18">
-        <v>1.87</v>
+        <v>1.71</v>
       </c>
       <c r="U18">
         <v>2</v>
@@ -5259,22 +5268,22 @@
         <v>95</v>
       </c>
       <c r="AP18">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AQ18">
         <v>11.5</v>
       </c>
       <c r="AR18">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AS18">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT18">
-        <v>6.2</v>
+        <v>3.05</v>
       </c>
       <c r="AU18">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV18">
         <v>13.5</v>
@@ -5283,28 +5292,28 @@
         <v>4.1</v>
       </c>
       <c r="AX18">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AY18">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ18">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BA18">
         <v>4.1</v>
       </c>
       <c r="BB18">
-        <v>16</v>
+        <v>3.75</v>
       </c>
       <c r="BC18">
         <v>3.7</v>
       </c>
       <c r="BD18">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BE18">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF18">
         <v>10.5</v>
@@ -5313,16 +5322,16 @@
         <v>4.1</v>
       </c>
       <c r="BH18">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="BI18">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="BJ18">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK18">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BL18">
         <v>1000</v>
@@ -5331,49 +5340,49 @@
         <v>1.01</v>
       </c>
       <c r="BN18">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO18">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BP18">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BQ18">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BR18">
         <v>1000</v>
       </c>
       <c r="BS18">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BT18">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU18">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BV18">
         <v>1000</v>
       </c>
       <c r="BW18">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BZ18">
         <v>1000</v>
       </c>
       <c r="CA18">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="CB18" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5381,16 +5390,16 @@
         <v>83</v>
       </c>
       <c r="B19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C19" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D19" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E19" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F19">
         <v>3.8</v>
@@ -5615,7 +5624,7 @@
         <v>1.01</v>
       </c>
       <c r="CB19" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5623,241 +5632,241 @@
         <v>92</v>
       </c>
       <c r="B20" t="s">
+        <v>111</v>
+      </c>
+      <c r="C20" t="s">
+        <v>122</v>
+      </c>
+      <c r="D20" t="s">
+        <v>150</v>
+      </c>
+      <c r="E20" t="s">
+        <v>197</v>
+      </c>
+      <c r="F20">
+        <v>1.82</v>
+      </c>
+      <c r="G20">
+        <v>1.85</v>
+      </c>
+      <c r="H20">
+        <v>4.4</v>
+      </c>
+      <c r="I20">
+        <v>4.6</v>
+      </c>
+      <c r="J20">
+        <v>4.3</v>
+      </c>
+      <c r="K20">
+        <v>4.4</v>
+      </c>
+      <c r="L20">
+        <v>1.01</v>
+      </c>
+      <c r="M20">
+        <v>1.04</v>
+      </c>
+      <c r="N20">
+        <v>5.8</v>
+      </c>
+      <c r="O20">
+        <v>1.19</v>
+      </c>
+      <c r="P20">
+        <v>2.62</v>
+      </c>
+      <c r="Q20">
+        <v>1.56</v>
+      </c>
+      <c r="R20">
+        <v>1.66</v>
+      </c>
+      <c r="S20">
+        <v>2.36</v>
+      </c>
+      <c r="T20">
+        <v>1.58</v>
+      </c>
+      <c r="U20">
+        <v>2.54</v>
+      </c>
+      <c r="V20">
+        <v>1.28</v>
+      </c>
+      <c r="W20">
+        <v>2.16</v>
+      </c>
+      <c r="X20">
+        <v>32</v>
+      </c>
+      <c r="Y20">
+        <v>29</v>
+      </c>
+      <c r="Z20">
+        <v>40</v>
+      </c>
+      <c r="AA20">
         <v>110</v>
       </c>
-      <c r="C20" t="s">
-        <v>121</v>
-      </c>
-      <c r="D20" t="s">
-        <v>149</v>
-      </c>
-      <c r="E20" t="s">
-        <v>195</v>
-      </c>
-      <c r="F20">
-        <v>4.3</v>
-      </c>
-      <c r="G20">
+      <c r="AB20">
+        <v>17</v>
+      </c>
+      <c r="AC20">
+        <v>10.5</v>
+      </c>
+      <c r="AD20">
+        <v>23</v>
+      </c>
+      <c r="AE20">
+        <v>60</v>
+      </c>
+      <c r="AF20">
+        <v>17.5</v>
+      </c>
+      <c r="AG20">
+        <v>13.5</v>
+      </c>
+      <c r="AH20">
+        <v>16</v>
+      </c>
+      <c r="AI20">
+        <v>55</v>
+      </c>
+      <c r="AJ20">
+        <v>25</v>
+      </c>
+      <c r="AK20">
+        <v>21</v>
+      </c>
+      <c r="AL20">
+        <v>32</v>
+      </c>
+      <c r="AM20">
+        <v>70</v>
+      </c>
+      <c r="AN20">
+        <v>7.6</v>
+      </c>
+      <c r="AO20">
+        <v>42</v>
+      </c>
+      <c r="AP20">
         <v>4.6</v>
       </c>
-      <c r="H20">
-        <v>1.85</v>
-      </c>
-      <c r="I20">
-        <v>1.89</v>
-      </c>
-      <c r="J20">
-        <v>4</v>
-      </c>
-      <c r="K20">
-        <v>4.2</v>
-      </c>
-      <c r="L20">
-        <v>1.01</v>
-      </c>
-      <c r="M20">
-        <v>1.05</v>
-      </c>
-      <c r="N20">
-        <v>4.6</v>
-      </c>
-      <c r="O20">
-        <v>1.23</v>
-      </c>
-      <c r="P20">
-        <v>2.22</v>
-      </c>
-      <c r="Q20">
-        <v>1.69</v>
-      </c>
-      <c r="R20">
-        <v>1.47</v>
-      </c>
-      <c r="S20">
-        <v>2.62</v>
-      </c>
-      <c r="T20">
-        <v>1.6</v>
-      </c>
-      <c r="U20">
-        <v>2.08</v>
-      </c>
-      <c r="V20">
-        <v>2.12</v>
-      </c>
-      <c r="W20">
-        <v>1.28</v>
-      </c>
-      <c r="X20">
-        <v>23</v>
-      </c>
-      <c r="Y20">
+      <c r="AQ20">
+        <v>20</v>
+      </c>
+      <c r="AR20">
+        <v>4.7</v>
+      </c>
+      <c r="AS20">
+        <v>5.1</v>
+      </c>
+      <c r="AT20">
+        <v>12</v>
+      </c>
+      <c r="AU20">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV20">
+        <v>16</v>
+      </c>
+      <c r="AW20">
+        <v>4.9</v>
+      </c>
+      <c r="AX20">
         <v>12.5</v>
       </c>
-      <c r="Z20">
-        <v>15</v>
-      </c>
-      <c r="AA20">
-        <v>24</v>
-      </c>
-      <c r="AB20">
-        <v>22</v>
-      </c>
-      <c r="AC20">
-        <v>10</v>
-      </c>
-      <c r="AD20">
-        <v>12</v>
-      </c>
-      <c r="AE20">
-        <v>19</v>
-      </c>
-      <c r="AF20">
-        <v>42</v>
-      </c>
-      <c r="AG20">
-        <v>19</v>
-      </c>
-      <c r="AH20">
-        <v>20</v>
-      </c>
-      <c r="AI20">
-        <v>36</v>
-      </c>
-      <c r="AJ20">
-        <v>110</v>
-      </c>
-      <c r="AK20">
-        <v>60</v>
-      </c>
-      <c r="AL20">
-        <v>60</v>
-      </c>
-      <c r="AM20">
-        <v>95</v>
-      </c>
-      <c r="AN20">
-        <v>55</v>
-      </c>
-      <c r="AO20">
-        <v>11.5</v>
-      </c>
-      <c r="AP20">
-        <v>17</v>
-      </c>
-      <c r="AQ20">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR20">
-        <v>10.5</v>
-      </c>
-      <c r="AS20">
-        <v>17</v>
-      </c>
-      <c r="AT20">
-        <v>16</v>
-      </c>
-      <c r="AU20">
-        <v>8</v>
-      </c>
-      <c r="AV20">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW20">
-        <v>15</v>
-      </c>
-      <c r="AX20">
-        <v>5</v>
-      </c>
       <c r="AY20">
-        <v>15</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ20">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA20">
         <v>4.9</v>
       </c>
       <c r="BB20">
-        <v>5.4</v>
+        <v>17.5</v>
       </c>
       <c r="BC20">
-        <v>5.2</v>
+        <v>15</v>
       </c>
       <c r="BD20">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="BE20">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="BF20">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="BG20">
+        <v>4.8</v>
+      </c>
+      <c r="BH20">
+        <v>1000</v>
+      </c>
+      <c r="BI20">
+        <v>1.01</v>
+      </c>
+      <c r="BJ20">
+        <v>13</v>
+      </c>
+      <c r="BK20">
+        <v>5.6</v>
+      </c>
+      <c r="BL20">
+        <v>1000</v>
+      </c>
+      <c r="BM20">
+        <v>21</v>
+      </c>
+      <c r="BN20">
+        <v>6.8</v>
+      </c>
+      <c r="BO20">
+        <v>3.3</v>
+      </c>
+      <c r="BP20">
+        <v>16</v>
+      </c>
+      <c r="BQ20">
+        <v>7</v>
+      </c>
+      <c r="BR20">
+        <v>30</v>
+      </c>
+      <c r="BS20">
+        <v>12</v>
+      </c>
+      <c r="BT20">
+        <v>12</v>
+      </c>
+      <c r="BU20">
+        <v>5.3</v>
+      </c>
+      <c r="BV20">
+        <v>46</v>
+      </c>
+      <c r="BW20">
+        <v>18.5</v>
+      </c>
+      <c r="BX20">
+        <v>50</v>
+      </c>
+      <c r="BY20">
+        <v>20</v>
+      </c>
+      <c r="BZ20">
+        <v>20</v>
+      </c>
+      <c r="CA20">
         <v>8.4</v>
       </c>
-      <c r="BH20">
-        <v>1000</v>
-      </c>
-      <c r="BI20">
-        <v>1.01</v>
-      </c>
-      <c r="BJ20">
-        <v>1000</v>
-      </c>
-      <c r="BK20">
-        <v>1.01</v>
-      </c>
-      <c r="BL20">
-        <v>1000</v>
-      </c>
-      <c r="BM20">
-        <v>1.01</v>
-      </c>
-      <c r="BN20">
-        <v>1000</v>
-      </c>
-      <c r="BO20">
-        <v>1.01</v>
-      </c>
-      <c r="BP20">
-        <v>1000</v>
-      </c>
-      <c r="BQ20">
-        <v>1.01</v>
-      </c>
-      <c r="BR20">
-        <v>1000</v>
-      </c>
-      <c r="BS20">
-        <v>1.01</v>
-      </c>
-      <c r="BT20">
-        <v>1000</v>
-      </c>
-      <c r="BU20">
-        <v>1.01</v>
-      </c>
-      <c r="BV20">
-        <v>1000</v>
-      </c>
-      <c r="BW20">
-        <v>1.01</v>
-      </c>
-      <c r="BX20">
-        <v>1000</v>
-      </c>
-      <c r="BY20">
-        <v>1.01</v>
-      </c>
-      <c r="BZ20">
-        <v>1000</v>
-      </c>
-      <c r="CA20">
-        <v>1.01</v>
-      </c>
       <c r="CB20" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5865,37 +5874,37 @@
         <v>94</v>
       </c>
       <c r="B21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C21" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D21" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E21" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F21">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G21">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="H21">
+        <v>3.65</v>
+      </c>
+      <c r="I21">
         <v>3.7</v>
-      </c>
-      <c r="I21">
-        <v>3.75</v>
       </c>
       <c r="J21">
         <v>2.98</v>
       </c>
       <c r="K21">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="L21">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="M21">
         <v>1.16</v>
@@ -5907,82 +5916,82 @@
         <v>1.69</v>
       </c>
       <c r="P21">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="Q21">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R21">
         <v>1.15</v>
       </c>
       <c r="S21">
+        <v>7.2</v>
+      </c>
+      <c r="T21">
+        <v>2.4</v>
+      </c>
+      <c r="U21">
+        <v>1.68</v>
+      </c>
+      <c r="V21">
+        <v>1.37</v>
+      </c>
+      <c r="W21">
+        <v>1.64</v>
+      </c>
+      <c r="X21">
         <v>7</v>
       </c>
-      <c r="T21">
-        <v>2.42</v>
-      </c>
-      <c r="U21">
-        <v>1.63</v>
-      </c>
-      <c r="V21">
-        <v>1.36</v>
-      </c>
-      <c r="W21">
-        <v>1.65</v>
-      </c>
-      <c r="X21">
-        <v>7.4</v>
-      </c>
       <c r="Y21">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Z21">
         <v>23</v>
       </c>
       <c r="AA21">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB21">
+        <v>6.8</v>
+      </c>
+      <c r="AC21">
         <v>7</v>
       </c>
-      <c r="AC21">
-        <v>7.2</v>
-      </c>
       <c r="AD21">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE21">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AF21">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG21">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AH21">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AI21">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ21">
         <v>42</v>
       </c>
       <c r="AK21">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AL21">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AM21">
-        <v>330</v>
+        <v>260</v>
       </c>
       <c r="AN21">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AO21">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AP21">
         <v>6.6</v>
@@ -5991,13 +6000,13 @@
         <v>8.4</v>
       </c>
       <c r="AR21">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS21">
         <v>34</v>
       </c>
       <c r="AT21">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AU21">
         <v>6.6</v>
@@ -6006,10 +6015,10 @@
         <v>16</v>
       </c>
       <c r="AW21">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AX21">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY21">
         <v>12.5</v>
@@ -6021,10 +6030,10 @@
         <v>40</v>
       </c>
       <c r="BB21">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="BC21">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="BD21">
         <v>36</v>
@@ -6033,73 +6042,73 @@
         <v>50</v>
       </c>
       <c r="BF21">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="BG21">
         <v>38</v>
       </c>
       <c r="BH21">
-        <v>2.74</v>
+        <v>2.44</v>
       </c>
       <c r="BI21">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="BJ21">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK21">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BL21">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="BM21">
         <v>15.5</v>
       </c>
       <c r="BN21">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO21">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="BP21">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BQ21">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BR21">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS21">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="BT21">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU21">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BV21">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW21">
         <v>12</v>
       </c>
       <c r="BX21">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BY21">
-        <v>17</v>
+        <v>13.5</v>
       </c>
       <c r="BZ21">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="CA21">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="CB21" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -6107,178 +6116,178 @@
         <v>92</v>
       </c>
       <c r="B22" t="s">
+        <v>111</v>
+      </c>
+      <c r="C22" t="s">
+        <v>122</v>
+      </c>
+      <c r="D22" t="s">
+        <v>152</v>
+      </c>
+      <c r="E22" t="s">
+        <v>199</v>
+      </c>
+      <c r="F22">
+        <v>4.5</v>
+      </c>
+      <c r="G22">
+        <v>4.7</v>
+      </c>
+      <c r="H22">
+        <v>1.84</v>
+      </c>
+      <c r="I22">
+        <v>1.87</v>
+      </c>
+      <c r="J22">
+        <v>4</v>
+      </c>
+      <c r="K22">
+        <v>4.2</v>
+      </c>
+      <c r="L22">
+        <v>1.01</v>
+      </c>
+      <c r="M22">
+        <v>1.05</v>
+      </c>
+      <c r="N22">
+        <v>4.6</v>
+      </c>
+      <c r="O22">
+        <v>1.23</v>
+      </c>
+      <c r="P22">
+        <v>2.12</v>
+      </c>
+      <c r="Q22">
+        <v>1.69</v>
+      </c>
+      <c r="R22">
+        <v>1.47</v>
+      </c>
+      <c r="S22">
+        <v>2.62</v>
+      </c>
+      <c r="T22">
+        <v>1.6</v>
+      </c>
+      <c r="U22">
+        <v>2.08</v>
+      </c>
+      <c r="V22">
+        <v>2.14</v>
+      </c>
+      <c r="W22">
+        <v>1.27</v>
+      </c>
+      <c r="X22">
+        <v>23</v>
+      </c>
+      <c r="Y22">
+        <v>12.5</v>
+      </c>
+      <c r="Z22">
+        <v>15</v>
+      </c>
+      <c r="AA22">
+        <v>24</v>
+      </c>
+      <c r="AB22">
+        <v>22</v>
+      </c>
+      <c r="AC22">
+        <v>11</v>
+      </c>
+      <c r="AD22">
+        <v>12</v>
+      </c>
+      <c r="AE22">
+        <v>21</v>
+      </c>
+      <c r="AF22">
+        <v>42</v>
+      </c>
+      <c r="AG22">
+        <v>21</v>
+      </c>
+      <c r="AH22">
+        <v>20</v>
+      </c>
+      <c r="AI22">
+        <v>36</v>
+      </c>
+      <c r="AJ22">
         <v>110</v>
       </c>
-      <c r="C22" t="s">
-        <v>121</v>
-      </c>
-      <c r="D22" t="s">
-        <v>151</v>
-      </c>
-      <c r="E22" t="s">
-        <v>197</v>
-      </c>
-      <c r="F22">
-        <v>1.82</v>
-      </c>
-      <c r="G22">
-        <v>1.84</v>
-      </c>
-      <c r="H22">
-        <v>4.4</v>
-      </c>
-      <c r="I22">
+      <c r="AK22">
+        <v>60</v>
+      </c>
+      <c r="AL22">
+        <v>60</v>
+      </c>
+      <c r="AM22">
+        <v>95</v>
+      </c>
+      <c r="AN22">
+        <v>55</v>
+      </c>
+      <c r="AO22">
+        <v>11.5</v>
+      </c>
+      <c r="AP22">
+        <v>17</v>
+      </c>
+      <c r="AQ22">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR22">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS22">
+        <v>17.5</v>
+      </c>
+      <c r="AT22">
+        <v>14.5</v>
+      </c>
+      <c r="AU22">
+        <v>8</v>
+      </c>
+      <c r="AV22">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW22">
+        <v>14</v>
+      </c>
+      <c r="AX22">
         <v>4.6</v>
       </c>
-      <c r="J22">
-        <v>4.3</v>
-      </c>
-      <c r="K22">
-        <v>4.4</v>
-      </c>
-      <c r="L22">
-        <v>1.01</v>
-      </c>
-      <c r="M22">
-        <v>1.04</v>
-      </c>
-      <c r="N22">
-        <v>5.8</v>
-      </c>
-      <c r="O22">
-        <v>1.19</v>
-      </c>
-      <c r="P22">
-        <v>2.62</v>
-      </c>
-      <c r="Q22">
-        <v>1.56</v>
-      </c>
-      <c r="R22">
-        <v>1.66</v>
-      </c>
-      <c r="S22">
-        <v>2.36</v>
-      </c>
-      <c r="T22">
-        <v>1.58</v>
-      </c>
-      <c r="U22">
-        <v>2.54</v>
-      </c>
-      <c r="V22">
-        <v>1.28</v>
-      </c>
-      <c r="W22">
-        <v>2.18</v>
-      </c>
-      <c r="X22">
-        <v>32</v>
-      </c>
-      <c r="Y22">
-        <v>29</v>
-      </c>
-      <c r="Z22">
-        <v>48</v>
-      </c>
-      <c r="AA22">
-        <v>110</v>
-      </c>
-      <c r="AB22">
-        <v>17</v>
-      </c>
-      <c r="AC22">
-        <v>12.5</v>
-      </c>
-      <c r="AD22">
-        <v>23</v>
-      </c>
-      <c r="AE22">
-        <v>60</v>
-      </c>
-      <c r="AF22">
-        <v>17.5</v>
-      </c>
-      <c r="AG22">
+      <c r="AY22">
         <v>13.5</v>
       </c>
-      <c r="AH22">
-        <v>19</v>
-      </c>
-      <c r="AI22">
-        <v>55</v>
-      </c>
-      <c r="AJ22">
-        <v>25</v>
-      </c>
-      <c r="AK22">
-        <v>21</v>
-      </c>
-      <c r="AL22">
-        <v>32</v>
-      </c>
-      <c r="AM22">
-        <v>70</v>
-      </c>
-      <c r="AN22">
-        <v>9</v>
-      </c>
-      <c r="AO22">
-        <v>42</v>
-      </c>
-      <c r="AP22">
-        <v>3.75</v>
-      </c>
-      <c r="AQ22">
-        <v>20</v>
-      </c>
-      <c r="AR22">
-        <v>3.9</v>
-      </c>
-      <c r="AS22">
-        <v>4.1</v>
-      </c>
-      <c r="AT22">
-        <v>12</v>
-      </c>
-      <c r="AU22">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV22">
-        <v>16</v>
-      </c>
-      <c r="AW22">
-        <v>4</v>
-      </c>
-      <c r="AX22">
-        <v>12.5</v>
-      </c>
-      <c r="AY22">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AZ22">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA22">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="BB22">
-        <v>17.5</v>
+        <v>4.9</v>
       </c>
       <c r="BC22">
-        <v>15</v>
+        <v>4.7</v>
       </c>
       <c r="BD22">
-        <v>3.75</v>
+        <v>4.7</v>
       </c>
       <c r="BE22">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="BF22">
-        <v>6.8</v>
+        <v>4.7</v>
       </c>
       <c r="BG22">
-        <v>3.85</v>
+        <v>7.8</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -6341,7 +6350,7 @@
         <v>1.01</v>
       </c>
       <c r="CB22" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6349,16 +6358,16 @@
         <v>91</v>
       </c>
       <c r="B23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C23" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D23" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E23" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F23">
         <v>1.35</v>
@@ -6409,7 +6418,7 @@
         <v>1.01</v>
       </c>
       <c r="V23">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W23">
         <v>2.64</v>
@@ -6583,7 +6592,7 @@
         <v>1.01</v>
       </c>
       <c r="CB23" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="24" spans="1:80">
@@ -6591,34 +6600,34 @@
         <v>95</v>
       </c>
       <c r="B24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C24" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D24" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E24" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F24">
-        <v>2.58</v>
+        <v>3.85</v>
       </c>
       <c r="G24">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="H24">
-        <v>1.38</v>
+        <v>2.1</v>
       </c>
       <c r="I24">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="J24">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="K24">
-        <v>330</v>
+        <v>3.8</v>
       </c>
       <c r="L24">
         <v>1.01</v>
@@ -6633,16 +6642,16 @@
         <v>1.32</v>
       </c>
       <c r="P24">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="Q24">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="R24">
         <v>1.21</v>
       </c>
       <c r="S24">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="T24">
         <v>1.01</v>
@@ -6651,10 +6660,10 @@
         <v>1.01</v>
       </c>
       <c r="V24">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="W24">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="X24">
         <v>1000</v>
@@ -6825,7 +6834,7 @@
         <v>1.01</v>
       </c>
       <c r="CB24" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="25" spans="1:80">
@@ -6833,16 +6842,16 @@
         <v>95</v>
       </c>
       <c r="B25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C25" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D25" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E25" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F25">
         <v>1.72</v>
@@ -6854,10 +6863,10 @@
         <v>5.6</v>
       </c>
       <c r="I25">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J25">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="K25">
         <v>3.55</v>
@@ -6869,7 +6878,7 @@
         <v>1.01</v>
       </c>
       <c r="N25">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="O25">
         <v>1.01</v>
@@ -7067,7 +7076,7 @@
         <v>1.01</v>
       </c>
       <c r="CB25" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="26" spans="1:80">
@@ -7075,16 +7084,16 @@
         <v>96</v>
       </c>
       <c r="B26" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C26" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D26" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E26" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F26">
         <v>2.06</v>
@@ -7243,7 +7252,7 @@
         <v>4.2</v>
       </c>
       <c r="BF26">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="BG26">
         <v>19</v>
@@ -7309,7 +7318,7 @@
         <v>1.01</v>
       </c>
       <c r="CB26" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="27" spans="1:80">
@@ -7317,16 +7326,16 @@
         <v>89</v>
       </c>
       <c r="B27" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C27" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D27" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E27" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F27">
         <v>2.84</v>
@@ -7551,7 +7560,7 @@
         <v>1.01</v>
       </c>
       <c r="CB27" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="28" spans="1:80">
@@ -7559,34 +7568,34 @@
         <v>97</v>
       </c>
       <c r="B28" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C28" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D28" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E28" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F28">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="G28">
         <v>1.87</v>
       </c>
       <c r="H28">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I28">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="J28">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K28">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="L28">
         <v>1.01</v>
@@ -7595,16 +7604,16 @@
         <v>1.01</v>
       </c>
       <c r="N28">
-        <v>2.04</v>
+        <v>2.68</v>
       </c>
       <c r="O28">
         <v>1.24</v>
       </c>
       <c r="P28">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q28">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="R28">
         <v>1.41</v>
@@ -7619,7 +7628,7 @@
         <v>1.01</v>
       </c>
       <c r="V28">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W28">
         <v>2.14</v>
@@ -7793,7 +7802,7 @@
         <v>1.01</v>
       </c>
       <c r="CB28" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="29" spans="1:80">
@@ -7801,34 +7810,34 @@
         <v>98</v>
       </c>
       <c r="B29" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C29" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D29" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E29" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F29">
-        <v>2.82</v>
+        <v>2.42</v>
       </c>
       <c r="G29">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="H29">
-        <v>2.48</v>
+        <v>2.22</v>
       </c>
       <c r="I29">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="J29">
-        <v>3.5</v>
+        <v>2.66</v>
       </c>
       <c r="K29">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="L29">
         <v>1.01</v>
@@ -7840,7 +7849,7 @@
         <v>3.4</v>
       </c>
       <c r="O29">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P29">
         <v>1.85</v>
@@ -8035,7 +8044,7 @@
         <v>1.01</v>
       </c>
       <c r="CB29" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="30" spans="1:80">
@@ -8043,16 +8052,16 @@
         <v>91</v>
       </c>
       <c r="B30" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C30" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D30" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E30" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F30">
         <v>6</v>
@@ -8061,7 +8070,7 @@
         <v>9</v>
       </c>
       <c r="H30">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="I30">
         <v>1.63</v>
@@ -8070,7 +8079,7 @@
         <v>4.2</v>
       </c>
       <c r="K30">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="L30">
         <v>1.01</v>
@@ -8079,16 +8088,16 @@
         <v>1.01</v>
       </c>
       <c r="N30">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O30">
         <v>1.22</v>
       </c>
       <c r="P30">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="Q30">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R30">
         <v>1.43</v>
@@ -8106,7 +8115,7 @@
         <v>2.58</v>
       </c>
       <c r="W30">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X30">
         <v>1000</v>
@@ -8277,7 +8286,7 @@
         <v>1.01</v>
       </c>
       <c r="CB30" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="31" spans="1:80">
@@ -8285,34 +8294,34 @@
         <v>99</v>
       </c>
       <c r="B31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C31" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D31" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E31" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F31">
-        <v>1.21</v>
+        <v>2.76</v>
       </c>
       <c r="G31">
-        <v>110</v>
+        <v>2.88</v>
       </c>
       <c r="H31">
-        <v>1.21</v>
+        <v>2.72</v>
       </c>
       <c r="I31">
-        <v>110</v>
+        <v>3.1</v>
       </c>
       <c r="J31">
-        <v>1.13</v>
+        <v>3.1</v>
       </c>
       <c r="K31">
-        <v>210</v>
+        <v>3.5</v>
       </c>
       <c r="L31">
         <v>1.01</v>
@@ -8321,22 +8330,22 @@
         <v>1.01</v>
       </c>
       <c r="N31">
-        <v>1.25</v>
+        <v>2.48</v>
       </c>
       <c r="O31">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="P31">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="Q31">
-        <v>1.34</v>
+        <v>2.42</v>
       </c>
       <c r="R31">
         <v>1.08</v>
       </c>
       <c r="S31">
-        <v>1.34</v>
+        <v>4.5</v>
       </c>
       <c r="T31">
         <v>1.01</v>
@@ -8345,10 +8354,10 @@
         <v>1.01</v>
       </c>
       <c r="V31">
-        <v>1.06</v>
+        <v>1.48</v>
       </c>
       <c r="W31">
-        <v>1.05</v>
+        <v>1.53</v>
       </c>
       <c r="X31">
         <v>1000</v>
@@ -8519,7 +8528,7 @@
         <v>0</v>
       </c>
       <c r="CB31" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="32" spans="1:80">
@@ -8527,16 +8536,16 @@
         <v>91</v>
       </c>
       <c r="B32" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C32" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D32" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E32" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F32">
         <v>2.48</v>
@@ -8551,7 +8560,7 @@
         <v>2.92</v>
       </c>
       <c r="J32">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="K32">
         <v>4.6</v>
@@ -8563,7 +8572,7 @@
         <v>1.01</v>
       </c>
       <c r="N32">
-        <v>2.36</v>
+        <v>4.7</v>
       </c>
       <c r="O32">
         <v>1.19</v>
@@ -8572,13 +8581,13 @@
         <v>2.36</v>
       </c>
       <c r="Q32">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="R32">
         <v>1.53</v>
       </c>
       <c r="S32">
-        <v>2.24</v>
+        <v>2.42</v>
       </c>
       <c r="T32">
         <v>1.01</v>
@@ -8761,7 +8770,7 @@
         <v>1.01</v>
       </c>
       <c r="CB32" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="33" spans="1:80">
@@ -8769,16 +8778,16 @@
         <v>84</v>
       </c>
       <c r="B33" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C33" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D33" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E33" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F33">
         <v>1.58</v>
@@ -8802,7 +8811,7 @@
         <v>1.01</v>
       </c>
       <c r="M33">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N33">
         <v>4.4</v>
@@ -8811,7 +8820,7 @@
         <v>1.23</v>
       </c>
       <c r="P33">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q33">
         <v>1.69</v>
@@ -8826,7 +8835,7 @@
         <v>1.65</v>
       </c>
       <c r="U33">
-        <v>1.9</v>
+        <v>2.06</v>
       </c>
       <c r="V33">
         <v>1.17</v>
@@ -8835,112 +8844,112 @@
         <v>2.42</v>
       </c>
       <c r="X33">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y33">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Z33">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA33">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AB33">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC33">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD33">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AE33">
+        <v>95</v>
+      </c>
+      <c r="AF33">
+        <v>13</v>
+      </c>
+      <c r="AG33">
+        <v>12.5</v>
+      </c>
+      <c r="AH33">
+        <v>25</v>
+      </c>
+      <c r="AI33">
+        <v>85</v>
+      </c>
+      <c r="AJ33">
+        <v>19.5</v>
+      </c>
+      <c r="AK33">
+        <v>20</v>
+      </c>
+      <c r="AL33">
+        <v>38</v>
+      </c>
+      <c r="AM33">
+        <v>120</v>
+      </c>
+      <c r="AN33">
+        <v>9.6</v>
+      </c>
+      <c r="AO33">
         <v>100</v>
       </c>
-      <c r="AF33">
-        <v>1000</v>
-      </c>
-      <c r="AG33">
-        <v>1000</v>
-      </c>
-      <c r="AH33">
-        <v>1000</v>
-      </c>
-      <c r="AI33">
-        <v>90</v>
-      </c>
-      <c r="AJ33">
-        <v>1000</v>
-      </c>
-      <c r="AK33">
-        <v>21</v>
-      </c>
-      <c r="AL33">
-        <v>40</v>
-      </c>
-      <c r="AM33">
-        <v>1000</v>
-      </c>
-      <c r="AN33">
-        <v>1000</v>
-      </c>
-      <c r="AO33">
-        <v>1000</v>
-      </c>
       <c r="AP33">
-        <v>1.1</v>
+        <v>14</v>
       </c>
       <c r="AQ33">
-        <v>1.1</v>
+        <v>16.5</v>
       </c>
       <c r="AR33">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="AS33">
-        <v>1.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT33">
-        <v>1.1</v>
+        <v>8</v>
       </c>
       <c r="AU33">
-        <v>1.1</v>
+        <v>7.4</v>
       </c>
       <c r="AV33">
-        <v>1.1</v>
+        <v>16.5</v>
       </c>
       <c r="AW33">
-        <v>1.09</v>
+        <v>4.1</v>
       </c>
       <c r="AX33">
-        <v>1.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY33">
-        <v>1.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ33">
-        <v>1.1</v>
+        <v>16</v>
       </c>
       <c r="BA33">
-        <v>1.09</v>
+        <v>4</v>
       </c>
       <c r="BB33">
-        <v>1.1</v>
+        <v>11.5</v>
       </c>
       <c r="BC33">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BD33">
-        <v>1.07</v>
+        <v>22</v>
       </c>
       <c r="BE33">
-        <v>1.1</v>
+        <v>4.1</v>
       </c>
       <c r="BF33">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BG33">
-        <v>1.1</v>
+        <v>4.1</v>
       </c>
       <c r="BH33">
         <v>1000</v>
@@ -9003,7 +9012,7 @@
         <v>1.01</v>
       </c>
       <c r="CB33" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="34" spans="1:80">
@@ -9011,16 +9020,16 @@
         <v>100</v>
       </c>
       <c r="B34" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C34" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D34" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E34" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F34">
         <v>1.99</v>
@@ -9245,7 +9254,7 @@
         <v>1.01</v>
       </c>
       <c r="CB34" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="35" spans="1:80">
@@ -9253,16 +9262,16 @@
         <v>101</v>
       </c>
       <c r="B35" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C35" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D35" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E35" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F35">
         <v>2.22</v>
@@ -9289,7 +9298,7 @@
         <v>1.01</v>
       </c>
       <c r="N35">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="O35">
         <v>1.37</v>
@@ -9298,10 +9307,10 @@
         <v>1.54</v>
       </c>
       <c r="Q35">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="R35">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="S35">
         <v>2.86</v>
@@ -9487,7 +9496,7 @@
         <v>1.01</v>
       </c>
       <c r="CB35" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="36" spans="1:80">
@@ -9495,16 +9504,16 @@
         <v>102</v>
       </c>
       <c r="B36" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C36" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D36" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E36" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F36">
         <v>2.32</v>
@@ -9729,7 +9738,7 @@
         <v>1.01</v>
       </c>
       <c r="CB36" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="37" spans="1:80">
@@ -9737,34 +9746,34 @@
         <v>102</v>
       </c>
       <c r="B37" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C37" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D37" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E37" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F37">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="G37">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="H37">
         <v>3.1</v>
       </c>
       <c r="I37">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="J37">
         <v>3.8</v>
       </c>
       <c r="K37">
-        <v>7.4</v>
+        <v>5.1</v>
       </c>
       <c r="L37">
         <v>1.01</v>
@@ -9773,34 +9782,34 @@
         <v>1.01</v>
       </c>
       <c r="N37">
-        <v>3.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O37">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="P37">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="Q37">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="R37">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="S37">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="T37">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="U37">
         <v>1.01</v>
       </c>
       <c r="V37">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="W37">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="X37">
         <v>1000</v>
@@ -9971,7 +9980,7 @@
         <v>1.01</v>
       </c>
       <c r="CB37" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="38" spans="1:80">
@@ -9979,19 +9988,19 @@
         <v>86</v>
       </c>
       <c r="B38" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C38" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D38" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E38" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F38">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="G38">
         <v>1.39</v>
@@ -10030,7 +10039,7 @@
         <v>1.7</v>
       </c>
       <c r="S38">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="T38">
         <v>1.01</v>
@@ -10039,7 +10048,7 @@
         <v>1.01</v>
       </c>
       <c r="V38">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W38">
         <v>2.92</v>
@@ -10213,7 +10222,7 @@
         <v>1.01</v>
       </c>
       <c r="CB38" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="39" spans="1:80">
@@ -10221,16 +10230,16 @@
         <v>103</v>
       </c>
       <c r="B39" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C39" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D39" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E39" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F39">
         <v>1.82</v>
@@ -10251,34 +10260,34 @@
         <v>3.9</v>
       </c>
       <c r="L39">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M39">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N39">
-        <v>1.86</v>
+        <v>3.4</v>
       </c>
       <c r="O39">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="P39">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="Q39">
         <v>2.02</v>
       </c>
       <c r="R39">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="S39">
-        <v>2.02</v>
+        <v>3.65</v>
       </c>
       <c r="T39">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="U39">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="V39">
         <v>1.22</v>
@@ -10287,112 +10296,112 @@
         <v>2.08</v>
       </c>
       <c r="X39">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y39">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Z39">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA39">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AB39">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC39">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD39">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE39">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AF39">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG39">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH39">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI39">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ39">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK39">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL39">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM39">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AN39">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AO39">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP39">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AQ39">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AR39">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AS39">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AT39">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AU39">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV39">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AW39">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AX39">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AY39">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ39">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BA39">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BB39">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BC39">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BD39">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BE39">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BF39">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BG39">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH39">
         <v>1000</v>
@@ -10455,7 +10464,7 @@
         <v>1.01</v>
       </c>
       <c r="CB39" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="40" spans="1:80">
@@ -10463,16 +10472,16 @@
         <v>104</v>
       </c>
       <c r="B40" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C40" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D40" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E40" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="F40">
         <v>1.9</v>
@@ -10499,7 +10508,7 @@
         <v>1.01</v>
       </c>
       <c r="N40">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="O40">
         <v>1.24</v>
@@ -10508,10 +10517,10 @@
         <v>1.9</v>
       </c>
       <c r="Q40">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="R40">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="S40">
         <v>2.4</v>
@@ -10697,7 +10706,7 @@
         <v>1.01</v>
       </c>
       <c r="CB40" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="41" spans="1:80">
@@ -10705,58 +10714,58 @@
         <v>105</v>
       </c>
       <c r="B41" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C41" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D41" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E41" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F41">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="G41">
-        <v>2.74</v>
+        <v>2.46</v>
       </c>
       <c r="H41">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="I41">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J41">
-        <v>2.42</v>
+        <v>2.86</v>
       </c>
       <c r="K41">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="L41">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="M41">
         <v>1.01</v>
       </c>
       <c r="N41">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="O41">
         <v>1.37</v>
       </c>
       <c r="P41">
-        <v>1.07</v>
+        <v>1.61</v>
       </c>
       <c r="Q41">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="R41">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S41">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="T41">
         <v>1.01</v>
@@ -10765,10 +10774,10 @@
         <v>1.01</v>
       </c>
       <c r="V41">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W41">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="X41">
         <v>1000</v>
@@ -10939,7 +10948,7 @@
         <v>1.01</v>
       </c>
       <c r="CB41" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="42" spans="1:80">
@@ -10947,16 +10956,16 @@
         <v>106</v>
       </c>
       <c r="B42" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C42" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D42" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E42" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F42">
         <v>1.87</v>
@@ -10968,25 +10977,25 @@
         <v>3.65</v>
       </c>
       <c r="I42">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="J42">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="K42">
         <v>5.3</v>
       </c>
       <c r="L42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P42">
         <v>1.8</v>
@@ -10995,193 +11004,193 @@
         <v>1.9</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH42">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BI42">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="BJ42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB42" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="43" spans="1:80">
@@ -11189,16 +11198,16 @@
         <v>90</v>
       </c>
       <c r="B43" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C43" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D43" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E43" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F43">
         <v>3</v>
@@ -11207,7 +11216,7 @@
         <v>3.1</v>
       </c>
       <c r="H43">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="I43">
         <v>2.78</v>
@@ -11219,7 +11228,7 @@
         <v>3.25</v>
       </c>
       <c r="L43">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M43">
         <v>1.11</v>
@@ -11228,97 +11237,97 @@
         <v>2.98</v>
       </c>
       <c r="O43">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P43">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="Q43">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="R43">
         <v>1.24</v>
       </c>
       <c r="S43">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="T43">
         <v>2.04</v>
       </c>
       <c r="U43">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="X43">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y43">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z43">
         <v>16.5</v>
       </c>
       <c r="AA43">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB43">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC43">
         <v>7.2</v>
       </c>
       <c r="AD43">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE43">
+        <v>38</v>
+      </c>
+      <c r="AF43">
+        <v>18.5</v>
+      </c>
+      <c r="AG43">
+        <v>14</v>
+      </c>
+      <c r="AH43">
+        <v>20</v>
+      </c>
+      <c r="AI43">
+        <v>60</v>
+      </c>
+      <c r="AJ43">
+        <v>55</v>
+      </c>
+      <c r="AK43">
         <v>42</v>
       </c>
-      <c r="AF43">
-        <v>19</v>
-      </c>
-      <c r="AG43">
-        <v>14.5</v>
-      </c>
-      <c r="AH43">
-        <v>23</v>
-      </c>
-      <c r="AI43">
-        <v>1000</v>
-      </c>
-      <c r="AJ43">
-        <v>190</v>
-      </c>
-      <c r="AK43">
+      <c r="AL43">
+        <v>65</v>
+      </c>
+      <c r="AM43">
+        <v>140</v>
+      </c>
+      <c r="AN43">
         <v>48</v>
       </c>
-      <c r="AL43">
-        <v>1000</v>
-      </c>
-      <c r="AM43">
-        <v>1000</v>
-      </c>
-      <c r="AN43">
-        <v>50</v>
-      </c>
       <c r="AO43">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AP43">
         <v>9</v>
       </c>
       <c r="AQ43">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR43">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AS43">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="AT43">
         <v>8.800000000000001</v>
@@ -11330,34 +11339,34 @@
         <v>11.5</v>
       </c>
       <c r="AW43">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AX43">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AY43">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ43">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BA43">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BB43">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="BC43">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BD43">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="BE43">
         <v>44</v>
       </c>
       <c r="BF43">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="BG43">
         <v>22</v>
@@ -11366,55 +11375,55 @@
         <v>1000</v>
       </c>
       <c r="BI43">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BJ43">
         <v>1000</v>
       </c>
       <c r="BK43">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BL43">
         <v>1000</v>
       </c>
       <c r="BM43">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BN43">
         <v>1000</v>
       </c>
       <c r="BO43">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BP43">
         <v>1000</v>
       </c>
       <c r="BQ43">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BR43">
         <v>1000</v>
       </c>
       <c r="BS43">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BT43">
         <v>1000</v>
       </c>
       <c r="BU43">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BV43">
         <v>1000</v>
       </c>
       <c r="BW43">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BX43">
         <v>1000</v>
       </c>
       <c r="BY43">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="BZ43">
         <v>0</v>
@@ -11423,7 +11432,7 @@
         <v>0</v>
       </c>
       <c r="CB43" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="44" spans="1:80">
@@ -11431,241 +11440,241 @@
         <v>107</v>
       </c>
       <c r="B44" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C44" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D44" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E44" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F44">
-        <v>2.52</v>
+        <v>3.75</v>
       </c>
       <c r="G44">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="H44">
         <v>1.65</v>
       </c>
       <c r="I44">
-        <v>2.1</v>
+        <v>2.48</v>
       </c>
       <c r="J44">
-        <v>2.54</v>
+        <v>1.1</v>
       </c>
       <c r="K44">
-        <v>100</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L44">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P44">
-        <v>1.25</v>
+        <v>1.98</v>
       </c>
       <c r="Q44">
         <v>1.63</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH44">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI44">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL44">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM44">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN44">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO44">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH44">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BI44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ44">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL44">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN44">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP44">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR44">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT44">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV44">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX44">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ44">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA44">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB44" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="45" spans="1:80">
@@ -11673,241 +11682,241 @@
         <v>108</v>
       </c>
       <c r="B45" t="s">
+        <v>111</v>
+      </c>
+      <c r="C45" t="s">
+        <v>129</v>
+      </c>
+      <c r="D45" t="s">
+        <v>175</v>
+      </c>
+      <c r="E45" t="s">
+        <v>222</v>
+      </c>
+      <c r="F45">
+        <v>2.6</v>
+      </c>
+      <c r="G45">
+        <v>2.72</v>
+      </c>
+      <c r="H45">
+        <v>2.9</v>
+      </c>
+      <c r="I45">
+        <v>3.15</v>
+      </c>
+      <c r="J45">
+        <v>3.3</v>
+      </c>
+      <c r="K45">
+        <v>3.45</v>
+      </c>
+      <c r="L45">
+        <v>1.36</v>
+      </c>
+      <c r="M45">
+        <v>1.08</v>
+      </c>
+      <c r="N45">
+        <v>3.4</v>
+      </c>
+      <c r="O45">
+        <v>1.34</v>
+      </c>
+      <c r="P45">
+        <v>1.83</v>
+      </c>
+      <c r="Q45">
+        <v>2.1</v>
+      </c>
+      <c r="R45">
+        <v>1.32</v>
+      </c>
+      <c r="S45">
+        <v>3.7</v>
+      </c>
+      <c r="T45">
+        <v>1.66</v>
+      </c>
+      <c r="U45">
+        <v>2.08</v>
+      </c>
+      <c r="V45">
+        <v>1.47</v>
+      </c>
+      <c r="W45">
+        <v>1.58</v>
+      </c>
+      <c r="X45">
+        <v>13</v>
+      </c>
+      <c r="Y45">
+        <v>13.5</v>
+      </c>
+      <c r="Z45">
+        <v>20</v>
+      </c>
+      <c r="AA45">
+        <v>50</v>
+      </c>
+      <c r="AB45">
+        <v>12.5</v>
+      </c>
+      <c r="AC45">
+        <v>7.6</v>
+      </c>
+      <c r="AD45">
+        <v>13.5</v>
+      </c>
+      <c r="AE45">
+        <v>36</v>
+      </c>
+      <c r="AF45">
+        <v>17.5</v>
+      </c>
+      <c r="AG45">
+        <v>12.5</v>
+      </c>
+      <c r="AH45">
+        <v>18.5</v>
+      </c>
+      <c r="AI45">
+        <v>50</v>
+      </c>
+      <c r="AJ45">
+        <v>40</v>
+      </c>
+      <c r="AK45">
+        <v>38</v>
+      </c>
+      <c r="AL45">
+        <v>46</v>
+      </c>
+      <c r="AM45">
         <v>110</v>
       </c>
-      <c r="C45" t="s">
-        <v>128</v>
-      </c>
-      <c r="D45" t="s">
-        <v>174</v>
-      </c>
-      <c r="E45" t="s">
-        <v>220</v>
-      </c>
-      <c r="F45">
-        <v>0</v>
-      </c>
-      <c r="G45">
-        <v>0</v>
-      </c>
-      <c r="H45">
-        <v>0</v>
-      </c>
-      <c r="I45">
-        <v>0</v>
-      </c>
-      <c r="J45">
-        <v>0</v>
-      </c>
-      <c r="K45">
-        <v>0</v>
-      </c>
-      <c r="L45">
-        <v>0</v>
-      </c>
-      <c r="M45">
-        <v>0</v>
-      </c>
-      <c r="N45">
-        <v>0</v>
-      </c>
-      <c r="O45">
-        <v>0</v>
-      </c>
-      <c r="P45">
-        <v>1.24</v>
-      </c>
-      <c r="Q45">
-        <v>1.02</v>
-      </c>
-      <c r="R45">
-        <v>0</v>
-      </c>
-      <c r="S45">
-        <v>0</v>
-      </c>
-      <c r="T45">
-        <v>0</v>
-      </c>
-      <c r="U45">
-        <v>0</v>
-      </c>
-      <c r="V45">
-        <v>0</v>
-      </c>
-      <c r="W45">
-        <v>0</v>
-      </c>
-      <c r="X45">
-        <v>0</v>
-      </c>
-      <c r="Y45">
-        <v>0</v>
-      </c>
-      <c r="Z45">
-        <v>0</v>
-      </c>
-      <c r="AA45">
-        <v>0</v>
-      </c>
-      <c r="AB45">
-        <v>0</v>
-      </c>
-      <c r="AC45">
-        <v>0</v>
-      </c>
-      <c r="AD45">
-        <v>0</v>
-      </c>
-      <c r="AE45">
-        <v>0</v>
-      </c>
-      <c r="AF45">
-        <v>0</v>
-      </c>
-      <c r="AG45">
-        <v>0</v>
-      </c>
-      <c r="AH45">
-        <v>0</v>
-      </c>
-      <c r="AI45">
-        <v>0</v>
-      </c>
-      <c r="AJ45">
-        <v>0</v>
-      </c>
-      <c r="AK45">
-        <v>0</v>
-      </c>
-      <c r="AL45">
-        <v>0</v>
-      </c>
-      <c r="AM45">
-        <v>0</v>
-      </c>
       <c r="AN45">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AO45">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AP45">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AQ45">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AR45">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AS45">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT45">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AU45">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV45">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AW45">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AX45">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AY45">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ45">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BA45">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BB45">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BC45">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BD45">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BE45">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BF45">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BG45">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BH45">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BI45">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="BJ45">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BK45">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BL45">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM45">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN45">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BO45">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BP45">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BQ45">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BR45">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BS45">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BT45">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BU45">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BV45">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BW45">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BX45">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BY45">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BZ45">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="CA45">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="CB45" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="46" spans="1:80">
@@ -11915,483 +11924,725 @@
         <v>109</v>
       </c>
       <c r="B46" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C46" t="s">
         <v>129</v>
       </c>
       <c r="D46" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E46" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F46">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="G46">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="H46">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="I46">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="J46">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="K46">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="L46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P46">
-        <v>1.96</v>
+        <v>1.24</v>
       </c>
       <c r="Q46">
-        <v>1.75</v>
+        <v>1.27</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH46">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI46">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL46">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM46">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN46">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO46">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH46">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ46">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL46">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN46">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP46">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR46">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT46">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV46">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX46">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ46">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB46" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="47" spans="1:80">
       <c r="A47" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="B47" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C47" t="s">
         <v>130</v>
       </c>
       <c r="D47" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E47" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F47">
+        <v>2.36</v>
+      </c>
+      <c r="G47">
+        <v>2.64</v>
+      </c>
+      <c r="H47">
         <v>3.1</v>
       </c>
-      <c r="G47">
-        <v>3.15</v>
-      </c>
-      <c r="H47">
-        <v>2.46</v>
-      </c>
       <c r="I47">
-        <v>2.48</v>
+        <v>3.5</v>
       </c>
       <c r="J47">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="K47">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L47">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="M47">
         <v>1.06</v>
       </c>
       <c r="N47">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="O47">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P47">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="Q47">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="R47">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="S47">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="T47">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="U47">
-        <v>2.38</v>
+        <v>1.99</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X47">
+        <v>18</v>
+      </c>
+      <c r="Y47">
+        <v>14</v>
+      </c>
+      <c r="Z47">
+        <v>24</v>
+      </c>
+      <c r="AA47">
+        <v>70</v>
+      </c>
+      <c r="AB47">
+        <v>11.5</v>
+      </c>
+      <c r="AC47">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD47">
+        <v>15</v>
+      </c>
+      <c r="AE47">
+        <v>46</v>
+      </c>
+      <c r="AF47">
+        <v>17.5</v>
+      </c>
+      <c r="AG47">
+        <v>12.5</v>
+      </c>
+      <c r="AH47">
         <v>17</v>
       </c>
-      <c r="Y47">
+      <c r="AI47">
+        <v>55</v>
+      </c>
+      <c r="AJ47">
+        <v>42</v>
+      </c>
+      <c r="AK47">
+        <v>28</v>
+      </c>
+      <c r="AL47">
+        <v>46</v>
+      </c>
+      <c r="AM47">
+        <v>100</v>
+      </c>
+      <c r="AN47">
+        <v>21</v>
+      </c>
+      <c r="AO47">
+        <v>46</v>
+      </c>
+      <c r="AP47">
         <v>12.5</v>
-      </c>
-      <c r="Z47">
-        <v>17.5</v>
-      </c>
-      <c r="AA47">
-        <v>34</v>
-      </c>
-      <c r="AB47">
-        <v>14.5</v>
-      </c>
-      <c r="AC47">
-        <v>8.4</v>
-      </c>
-      <c r="AD47">
-        <v>11.5</v>
-      </c>
-      <c r="AE47">
-        <v>25</v>
-      </c>
-      <c r="AF47">
-        <v>23</v>
-      </c>
-      <c r="AG47">
-        <v>13.5</v>
-      </c>
-      <c r="AH47">
-        <v>15.5</v>
-      </c>
-      <c r="AI47">
-        <v>36</v>
-      </c>
-      <c r="AJ47">
-        <v>50</v>
-      </c>
-      <c r="AK47">
-        <v>34</v>
-      </c>
-      <c r="AL47">
-        <v>40</v>
-      </c>
-      <c r="AM47">
-        <v>1000</v>
-      </c>
-      <c r="AN47">
-        <v>26</v>
-      </c>
-      <c r="AO47">
-        <v>17.5</v>
-      </c>
-      <c r="AP47">
-        <v>15</v>
       </c>
       <c r="AQ47">
         <v>11</v>
       </c>
       <c r="AR47">
+        <v>19</v>
+      </c>
+      <c r="AS47">
+        <v>6.4</v>
+      </c>
+      <c r="AT47">
+        <v>9.6</v>
+      </c>
+      <c r="AU47">
+        <v>6.8</v>
+      </c>
+      <c r="AV47">
+        <v>12</v>
+      </c>
+      <c r="AW47">
+        <v>6.2</v>
+      </c>
+      <c r="AX47">
+        <v>14</v>
+      </c>
+      <c r="AY47">
+        <v>10</v>
+      </c>
+      <c r="AZ47">
+        <v>14</v>
+      </c>
+      <c r="BA47">
+        <v>6.4</v>
+      </c>
+      <c r="BB47">
+        <v>6.2</v>
+      </c>
+      <c r="BC47">
+        <v>18.5</v>
+      </c>
+      <c r="BD47">
+        <v>6.2</v>
+      </c>
+      <c r="BE47">
+        <v>6.6</v>
+      </c>
+      <c r="BF47">
+        <v>17</v>
+      </c>
+      <c r="BG47">
+        <v>5.9</v>
+      </c>
+      <c r="BH47">
+        <v>1000</v>
+      </c>
+      <c r="BI47">
+        <v>2.84</v>
+      </c>
+      <c r="BJ47">
+        <v>1000</v>
+      </c>
+      <c r="BK47">
+        <v>1.01</v>
+      </c>
+      <c r="BL47">
+        <v>1000</v>
+      </c>
+      <c r="BM47">
+        <v>1.01</v>
+      </c>
+      <c r="BN47">
+        <v>1000</v>
+      </c>
+      <c r="BO47">
+        <v>1.01</v>
+      </c>
+      <c r="BP47">
+        <v>1000</v>
+      </c>
+      <c r="BQ47">
+        <v>1.01</v>
+      </c>
+      <c r="BR47">
+        <v>1000</v>
+      </c>
+      <c r="BS47">
+        <v>1.01</v>
+      </c>
+      <c r="BT47">
+        <v>1000</v>
+      </c>
+      <c r="BU47">
+        <v>1.01</v>
+      </c>
+      <c r="BV47">
+        <v>1000</v>
+      </c>
+      <c r="BW47">
+        <v>1.01</v>
+      </c>
+      <c r="BX47">
+        <v>1000</v>
+      </c>
+      <c r="BY47">
+        <v>1.01</v>
+      </c>
+      <c r="BZ47">
+        <v>1000</v>
+      </c>
+      <c r="CA47">
+        <v>1.01</v>
+      </c>
+      <c r="CB47" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="48" spans="1:80">
+      <c r="A48" t="s">
+        <v>94</v>
+      </c>
+      <c r="B48" t="s">
+        <v>111</v>
+      </c>
+      <c r="C48" t="s">
+        <v>131</v>
+      </c>
+      <c r="D48" t="s">
+        <v>178</v>
+      </c>
+      <c r="E48" t="s">
+        <v>225</v>
+      </c>
+      <c r="F48">
+        <v>3.1</v>
+      </c>
+      <c r="G48">
+        <v>3.2</v>
+      </c>
+      <c r="H48">
+        <v>2.44</v>
+      </c>
+      <c r="I48">
+        <v>2.48</v>
+      </c>
+      <c r="J48">
+        <v>3.65</v>
+      </c>
+      <c r="K48">
+        <v>3.7</v>
+      </c>
+      <c r="L48">
+        <v>1.39</v>
+      </c>
+      <c r="M48">
+        <v>1.06</v>
+      </c>
+      <c r="N48">
+        <v>4.4</v>
+      </c>
+      <c r="O48">
+        <v>1.28</v>
+      </c>
+      <c r="P48">
+        <v>2.18</v>
+      </c>
+      <c r="Q48">
+        <v>1.82</v>
+      </c>
+      <c r="R48">
+        <v>1.45</v>
+      </c>
+      <c r="S48">
+        <v>3.05</v>
+      </c>
+      <c r="T48">
+        <v>1.68</v>
+      </c>
+      <c r="U48">
+        <v>2.38</v>
+      </c>
+      <c r="V48">
+        <v>1.67</v>
+      </c>
+      <c r="W48">
+        <v>1.46</v>
+      </c>
+      <c r="X48">
+        <v>16.5</v>
+      </c>
+      <c r="Y48">
+        <v>12.5</v>
+      </c>
+      <c r="Z48">
+        <v>17</v>
+      </c>
+      <c r="AA48">
+        <v>34</v>
+      </c>
+      <c r="AB48">
+        <v>14.5</v>
+      </c>
+      <c r="AC48">
+        <v>8.4</v>
+      </c>
+      <c r="AD48">
+        <v>11.5</v>
+      </c>
+      <c r="AE48">
+        <v>25</v>
+      </c>
+      <c r="AF48">
+        <v>23</v>
+      </c>
+      <c r="AG48">
+        <v>13.5</v>
+      </c>
+      <c r="AH48">
         <v>15.5</v>
       </c>
-      <c r="AS47">
+      <c r="AI48">
+        <v>34</v>
+      </c>
+      <c r="AJ48">
+        <v>50</v>
+      </c>
+      <c r="AK48">
+        <v>32</v>
+      </c>
+      <c r="AL48">
+        <v>40</v>
+      </c>
+      <c r="AM48">
+        <v>85</v>
+      </c>
+      <c r="AN48">
+        <v>26</v>
+      </c>
+      <c r="AO48">
+        <v>17.5</v>
+      </c>
+      <c r="AP48">
+        <v>15</v>
+      </c>
+      <c r="AQ48">
+        <v>11.5</v>
+      </c>
+      <c r="AR48">
+        <v>15.5</v>
+      </c>
+      <c r="AS48">
+        <v>30</v>
+      </c>
+      <c r="AT48">
+        <v>13.5</v>
+      </c>
+      <c r="AU48">
+        <v>7.6</v>
+      </c>
+      <c r="AV48">
+        <v>10.5</v>
+      </c>
+      <c r="AW48">
+        <v>22</v>
+      </c>
+      <c r="AX48">
+        <v>20</v>
+      </c>
+      <c r="AY48">
+        <v>12</v>
+      </c>
+      <c r="AZ48">
+        <v>14</v>
+      </c>
+      <c r="BA48">
+        <v>30</v>
+      </c>
+      <c r="BB48">
+        <v>42</v>
+      </c>
+      <c r="BC48">
+        <v>29</v>
+      </c>
+      <c r="BD48">
+        <v>36</v>
+      </c>
+      <c r="BE48">
+        <v>60</v>
+      </c>
+      <c r="BF48">
+        <v>22</v>
+      </c>
+      <c r="BG48">
+        <v>15.5</v>
+      </c>
+      <c r="BH48">
+        <v>3.6</v>
+      </c>
+      <c r="BI48">
+        <v>3.3</v>
+      </c>
+      <c r="BJ48">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BK48">
+        <v>7.2</v>
+      </c>
+      <c r="BL48">
+        <v>100</v>
+      </c>
+      <c r="BM48">
         <v>21</v>
       </c>
-      <c r="AT47">
-        <v>12.5</v>
-      </c>
-      <c r="AU47">
-        <v>7.6</v>
-      </c>
-      <c r="AV47">
-        <v>10.5</v>
-      </c>
-      <c r="AW47">
+      <c r="BN48">
+        <v>6.4</v>
+      </c>
+      <c r="BO48">
+        <v>5.7</v>
+      </c>
+      <c r="BP48">
+        <v>23</v>
+      </c>
+      <c r="BQ48">
+        <v>17.5</v>
+      </c>
+      <c r="BR48">
+        <v>32</v>
+      </c>
+      <c r="BS48">
+        <v>24</v>
+      </c>
+      <c r="BT48">
+        <v>5.6</v>
+      </c>
+      <c r="BU48">
+        <v>5</v>
+      </c>
+      <c r="BV48">
+        <v>18</v>
+      </c>
+      <c r="BW48">
+        <v>14</v>
+      </c>
+      <c r="BX48">
+        <v>29</v>
+      </c>
+      <c r="BY48">
         <v>21</v>
       </c>
-      <c r="AX47">
-        <v>19.5</v>
-      </c>
-      <c r="AY47">
-        <v>12</v>
-      </c>
-      <c r="AZ47">
-        <v>13.5</v>
-      </c>
-      <c r="BA47">
-        <v>22</v>
-      </c>
-      <c r="BB47">
-        <v>26</v>
-      </c>
-      <c r="BC47">
-        <v>21</v>
-      </c>
-      <c r="BD47">
-        <v>24</v>
-      </c>
-      <c r="BE47">
-        <v>48</v>
-      </c>
-      <c r="BF47">
+      <c r="BZ48">
+        <v>23</v>
+      </c>
+      <c r="CA48">
         <v>17.5</v>
       </c>
-      <c r="BG47">
-        <v>15</v>
-      </c>
-      <c r="BH47">
-        <v>3.65</v>
-      </c>
-      <c r="BI47">
-        <v>3</v>
-      </c>
-      <c r="BJ47">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BK47">
-        <v>7</v>
-      </c>
-      <c r="BL47">
-        <v>100</v>
-      </c>
-      <c r="BM47">
-        <v>1.01</v>
-      </c>
-      <c r="BN47">
-        <v>6.4</v>
-      </c>
-      <c r="BO47">
-        <v>5</v>
-      </c>
-      <c r="BP47">
-        <v>23</v>
-      </c>
-      <c r="BQ47">
-        <v>17</v>
-      </c>
-      <c r="BR47">
-        <v>32</v>
-      </c>
-      <c r="BS47">
-        <v>24</v>
-      </c>
-      <c r="BT47">
-        <v>5.6</v>
-      </c>
-      <c r="BU47">
-        <v>4.4</v>
-      </c>
-      <c r="BV47">
-        <v>18</v>
-      </c>
-      <c r="BW47">
-        <v>13.5</v>
-      </c>
-      <c r="BX47">
-        <v>29</v>
-      </c>
-      <c r="BY47">
-        <v>21</v>
-      </c>
-      <c r="BZ47">
-        <v>23</v>
-      </c>
-      <c r="CA47">
-        <v>17</v>
-      </c>
-      <c r="CB47" t="s">
-        <v>223</v>
+      <c r="CB48" t="s">
+        <v>226</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-07.xlsx
@@ -694,7 +694,7 @@
     <t>Real Sociedad</t>
   </si>
   <si>
-    <t>2026-09-05 18:05:27</t>
+    <t>2026-09-05 20:27:18</t>
   </si>
 </sst>
 </file>
@@ -1294,7 +1294,7 @@
         <v>1.65</v>
       </c>
       <c r="H2">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="I2">
         <v>8.199999999999999</v>
@@ -1312,13 +1312,13 @@
         <v>1.01</v>
       </c>
       <c r="N2">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="O2">
         <v>1.19</v>
       </c>
       <c r="P2">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q2">
         <v>1.19</v>
@@ -1327,7 +1327,7 @@
         <v>1.08</v>
       </c>
       <c r="S2">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="T2">
         <v>1.01</v>
@@ -1336,7 +1336,7 @@
         <v>1.01</v>
       </c>
       <c r="V2">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W2">
         <v>2.52</v>
@@ -1530,58 +1530,58 @@
         <v>180</v>
       </c>
       <c r="F3">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="G3">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H3">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="I3">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="J3">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="K3">
-        <v>3.55</v>
+        <v>5.7</v>
       </c>
       <c r="L3">
+        <v>1.42</v>
+      </c>
+      <c r="M3">
+        <v>1.06</v>
+      </c>
+      <c r="N3">
+        <v>2.52</v>
+      </c>
+      <c r="O3">
         <v>1.41</v>
       </c>
-      <c r="M3">
-        <v>1.09</v>
-      </c>
-      <c r="N3">
-        <v>2.98</v>
-      </c>
-      <c r="O3">
-        <v>1.42</v>
-      </c>
       <c r="P3">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="Q3">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="R3">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="S3">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="T3">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="U3">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="V3">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W3">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="X3">
         <v>13</v>
@@ -1593,7 +1593,7 @@
         <v>36</v>
       </c>
       <c r="AA3">
-        <v>940</v>
+        <v>900</v>
       </c>
       <c r="AB3">
         <v>9.4</v>
@@ -1605,10 +1605,10 @@
         <v>21</v>
       </c>
       <c r="AE3">
-        <v>940</v>
+        <v>900</v>
       </c>
       <c r="AF3">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG3">
         <v>13.5</v>
@@ -1617,139 +1617,139 @@
         <v>26</v>
       </c>
       <c r="AI3">
-        <v>940</v>
+        <v>900</v>
       </c>
       <c r="AJ3">
         <v>34</v>
       </c>
       <c r="AK3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL3">
         <v>60</v>
       </c>
       <c r="AM3">
-        <v>940</v>
+        <v>900</v>
       </c>
       <c r="AN3">
         <v>28</v>
       </c>
       <c r="AO3">
-        <v>940</v>
+        <v>900</v>
       </c>
       <c r="AP3">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AR3">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AS3">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="AT3">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AU3">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AV3">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW3">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="AX3">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AY3">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BA3">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BB3">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BC3">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BD3">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BE3">
-        <v>100</v>
+        <v>1.01</v>
       </c>
       <c r="BF3">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG3">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BH3">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BJ3">
         <v>1000</v>
       </c>
       <c r="BK3">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="BN3">
         <v>1000</v>
       </c>
       <c r="BO3">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="BT3">
         <v>1000</v>
       </c>
       <c r="BU3">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="CB3" t="s">
         <v>226</v>
@@ -1781,7 +1781,7 @@
         <v>4.6</v>
       </c>
       <c r="I4">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="J4">
         <v>3.5</v>
@@ -1793,7 +1793,7 @@
         <v>1.35</v>
       </c>
       <c r="M4">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N4">
         <v>3</v>
@@ -1805,13 +1805,13 @@
         <v>1.72</v>
       </c>
       <c r="Q4">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R4">
         <v>1.25</v>
       </c>
       <c r="S4">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="T4">
         <v>1.01</v>
@@ -2014,73 +2014,73 @@
         <v>182</v>
       </c>
       <c r="F5">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="G5">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="H5">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="I5">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J5">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="K5">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L5">
         <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N5">
         <v>2.74</v>
       </c>
       <c r="O5">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P5">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q5">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="R5">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="S5">
-        <v>4.2</v>
+        <v>2.42</v>
       </c>
       <c r="T5">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="U5">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="V5">
         <v>1.21</v>
       </c>
       <c r="W5">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="X5">
         <v>10.5</v>
       </c>
       <c r="Y5">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z5">
         <v>50</v>
       </c>
       <c r="AA5">
-        <v>960</v>
+        <v>910</v>
       </c>
       <c r="AB5">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AC5">
         <v>9.6</v>
@@ -2089,7 +2089,7 @@
         <v>27</v>
       </c>
       <c r="AE5">
-        <v>960</v>
+        <v>910</v>
       </c>
       <c r="AF5">
         <v>12</v>
@@ -2101,7 +2101,7 @@
         <v>32</v>
       </c>
       <c r="AI5">
-        <v>960</v>
+        <v>910</v>
       </c>
       <c r="AJ5">
         <v>26</v>
@@ -2113,67 +2113,67 @@
         <v>70</v>
       </c>
       <c r="AM5">
-        <v>960</v>
+        <v>910</v>
       </c>
       <c r="AN5">
         <v>24</v>
       </c>
       <c r="AO5">
-        <v>960</v>
+        <v>910</v>
       </c>
       <c r="AP5">
-        <v>8.6</v>
+        <v>1.28</v>
       </c>
       <c r="AQ5">
-        <v>11.5</v>
+        <v>1.28</v>
       </c>
       <c r="AR5">
-        <v>4.6</v>
+        <v>1.25</v>
       </c>
       <c r="AS5">
-        <v>5</v>
+        <v>1.28</v>
       </c>
       <c r="AT5">
-        <v>5.7</v>
+        <v>1.28</v>
       </c>
       <c r="AU5">
-        <v>6.8</v>
+        <v>1.28</v>
       </c>
       <c r="AV5">
-        <v>18.5</v>
+        <v>1.22</v>
       </c>
       <c r="AW5">
-        <v>5</v>
+        <v>1.28</v>
       </c>
       <c r="AX5">
-        <v>8.6</v>
+        <v>1.28</v>
       </c>
       <c r="AY5">
-        <v>9.4</v>
+        <v>1.28</v>
       </c>
       <c r="AZ5">
-        <v>21</v>
+        <v>1.23</v>
       </c>
       <c r="BA5">
-        <v>5</v>
+        <v>1.28</v>
       </c>
       <c r="BB5">
-        <v>18.5</v>
+        <v>1.22</v>
       </c>
       <c r="BC5">
-        <v>21</v>
+        <v>1.23</v>
       </c>
       <c r="BD5">
-        <v>4.8</v>
+        <v>1.26</v>
       </c>
       <c r="BE5">
-        <v>5.1</v>
+        <v>1.28</v>
       </c>
       <c r="BF5">
-        <v>14.5</v>
+        <v>1.21</v>
       </c>
       <c r="BG5">
-        <v>5</v>
+        <v>1.28</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -2259,19 +2259,19 @@
         <v>3.05</v>
       </c>
       <c r="G6">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="I6">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="J6">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K6">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -2280,22 +2280,22 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="O6">
         <v>1.26</v>
       </c>
       <c r="P6">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="Q6">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="R6">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S6">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="T6">
         <v>1.01</v>
@@ -2304,10 +2304,10 @@
         <v>1.01</v>
       </c>
       <c r="V6">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W6">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2421,7 +2421,7 @@
         <v>4.6</v>
       </c>
       <c r="BI6">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="BJ6">
         <v>1000</v>
@@ -2504,7 +2504,7 @@
         <v>3.7</v>
       </c>
       <c r="H7">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="I7">
         <v>2.7</v>
@@ -2531,13 +2531,13 @@
         <v>1.54</v>
       </c>
       <c r="Q7">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R7">
         <v>1.18</v>
       </c>
       <c r="S7">
-        <v>4.6</v>
+        <v>2.42</v>
       </c>
       <c r="T7">
         <v>1.01</v>
@@ -2546,7 +2546,7 @@
         <v>1.01</v>
       </c>
       <c r="V7">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W7">
         <v>1.4</v>
@@ -2740,40 +2740,40 @@
         <v>185</v>
       </c>
       <c r="F8">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="G8">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="H8">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="I8">
-        <v>6</v>
+        <v>110</v>
       </c>
       <c r="J8">
-        <v>3.25</v>
+        <v>1.95</v>
       </c>
       <c r="K8">
-        <v>3.65</v>
+        <v>320</v>
       </c>
       <c r="L8">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M8">
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="O8">
         <v>1.4</v>
       </c>
       <c r="P8">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="Q8">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R8">
         <v>1.22</v>
@@ -2791,7 +2791,7 @@
         <v>1.22</v>
       </c>
       <c r="W8">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2982,166 +2982,166 @@
         <v>186</v>
       </c>
       <c r="F9">
-        <v>2.26</v>
+        <v>2.06</v>
       </c>
       <c r="G9">
-        <v>2.46</v>
+        <v>2.86</v>
       </c>
       <c r="H9">
-        <v>3.05</v>
+        <v>2.54</v>
       </c>
       <c r="I9">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="J9">
-        <v>3.5</v>
+        <v>2.52</v>
       </c>
       <c r="K9">
-        <v>3.95</v>
+        <v>110</v>
       </c>
       <c r="L9">
         <v>1.01</v>
       </c>
       <c r="M9">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N9">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="O9">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="P9">
-        <v>2.06</v>
+        <v>1.86</v>
       </c>
       <c r="Q9">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="R9">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="S9">
-        <v>3</v>
+        <v>2.64</v>
       </c>
       <c r="T9">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="U9">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="W9">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="X9">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Y9">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Z9">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AA9">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB9">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AC9">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD9">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AE9">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AF9">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AG9">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH9">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AI9">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AJ9">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK9">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL9">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM9">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN9">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AO9">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AP9">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AR9">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AS9">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AT9">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AU9">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV9">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AW9">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX9">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY9">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA9">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB9">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC9">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BD9">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE9">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF9">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG9">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH9">
         <v>1000</v>
@@ -3224,145 +3224,145 @@
         <v>187</v>
       </c>
       <c r="F10">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="G10">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="H10">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="I10">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="J10">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K10">
-        <v>3.8</v>
+        <v>5.4</v>
       </c>
       <c r="L10">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="M10">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N10">
-        <v>3.55</v>
+        <v>1.92</v>
       </c>
       <c r="O10">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="P10">
-        <v>1.78</v>
+        <v>1.92</v>
       </c>
       <c r="Q10">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="R10">
         <v>1.15</v>
       </c>
       <c r="S10">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="T10">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="U10">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="V10">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="W10">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="X10">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Y10">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z10">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AA10">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AB10">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AC10">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AD10">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE10">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AF10">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AG10">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH10">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI10">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AJ10">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK10">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL10">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM10">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN10">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AO10">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AP10">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR10">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AS10">
         <v>1.01</v>
       </c>
       <c r="AT10">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU10">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV10">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW10">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AX10">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY10">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BA10">
         <v>1.01</v>
@@ -3371,7 +3371,7 @@
         <v>1.01</v>
       </c>
       <c r="BC10">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BD10">
         <v>1.01</v>
@@ -3380,22 +3380,22 @@
         <v>1.01</v>
       </c>
       <c r="BF10">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BG10">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BH10">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="BI10">
-        <v>2.78</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL10">
         <v>1000</v>
@@ -3404,46 +3404,46 @@
         <v>1.01</v>
       </c>
       <c r="BN10">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BO10">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BP10">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR10">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BT10">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU10">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV10">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BX10">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="s">
         <v>226</v>
@@ -3469,13 +3469,13 @@
         <v>1.08</v>
       </c>
       <c r="G11">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H11">
         <v>1.08</v>
       </c>
       <c r="I11">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J11">
         <v>1.08</v>
@@ -3502,7 +3502,7 @@
         <v>1.11</v>
       </c>
       <c r="R11">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="S11">
         <v>1.12</v>
@@ -3514,7 +3514,7 @@
         <v>1.01</v>
       </c>
       <c r="V11">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W11">
         <v>1.02</v>
@@ -3708,22 +3708,22 @@
         <v>189</v>
       </c>
       <c r="F12">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="G12">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="H12">
         <v>6.6</v>
       </c>
       <c r="I12">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J12">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="K12">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3741,13 +3741,13 @@
         <v>2.12</v>
       </c>
       <c r="Q12">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="R12">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S12">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="T12">
         <v>1.01</v>
@@ -3759,7 +3759,7 @@
         <v>1.05</v>
       </c>
       <c r="W12">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3962,7 +3962,7 @@
         <v>1000</v>
       </c>
       <c r="J13">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="K13">
         <v>320</v>
@@ -4001,7 +4001,7 @@
         <v>1.01</v>
       </c>
       <c r="W13">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -4198,10 +4198,10 @@
         <v>2.12</v>
       </c>
       <c r="H14">
+        <v>4.4</v>
+      </c>
+      <c r="I14">
         <v>4.5</v>
-      </c>
-      <c r="I14">
-        <v>4.6</v>
       </c>
       <c r="J14">
         <v>3.3</v>
@@ -4237,13 +4237,13 @@
         <v>2.12</v>
       </c>
       <c r="U14">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="V14">
         <v>1.28</v>
       </c>
       <c r="W14">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="X14">
         <v>9.4</v>
@@ -4252,7 +4252,7 @@
         <v>12.5</v>
       </c>
       <c r="Z14">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA14">
         <v>110</v>
@@ -4297,7 +4297,7 @@
         <v>23</v>
       </c>
       <c r="AO14">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP14">
         <v>8.800000000000001</v>
@@ -4321,7 +4321,7 @@
         <v>17</v>
       </c>
       <c r="AW14">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AX14">
         <v>10.5</v>
@@ -4336,7 +4336,7 @@
         <v>36</v>
       </c>
       <c r="BB14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC14">
         <v>24</v>
@@ -4351,7 +4351,7 @@
         <v>21</v>
       </c>
       <c r="BG14">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4369,7 +4369,7 @@
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="BN14">
         <v>1000</v>
@@ -4387,7 +4387,7 @@
         <v>1000</v>
       </c>
       <c r="BS14">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="BT14">
         <v>1000</v>
@@ -4399,13 +4399,13 @@
         <v>1000</v>
       </c>
       <c r="BW14">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="BZ14">
         <v>0</v>
@@ -4434,22 +4434,22 @@
         <v>192</v>
       </c>
       <c r="F15">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="G15">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H15">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I15">
         <v>4.3</v>
       </c>
       <c r="J15">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K15">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L15">
         <v>1.01</v>
@@ -4458,22 +4458,22 @@
         <v>1.01</v>
       </c>
       <c r="N15">
-        <v>2.6</v>
+        <v>4.6</v>
       </c>
       <c r="O15">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="P15">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="Q15">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="R15">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="S15">
-        <v>2.66</v>
+        <v>2.42</v>
       </c>
       <c r="T15">
         <v>1.01</v>
@@ -4485,7 +4485,7 @@
         <v>1.3</v>
       </c>
       <c r="W15">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4700,7 +4700,7 @@
         <v>1.04</v>
       </c>
       <c r="N16">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="O16">
         <v>1.21</v>
@@ -4712,16 +4712,16 @@
         <v>1.66</v>
       </c>
       <c r="R16">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S16">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T16">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="U16">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="V16">
         <v>1.48</v>
@@ -4730,112 +4730,112 @@
         <v>1.65</v>
       </c>
       <c r="X16">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y16">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Z16">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AA16">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB16">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AC16">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD16">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE16">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AF16">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AG16">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH16">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AI16">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ16">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AK16">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AL16">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM16">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN16">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AO16">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AP16">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR16">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AS16">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="AT16">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU16">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV16">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW16">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AX16">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AY16">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA16">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BB16">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BC16">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BD16">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BE16">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BF16">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BG16">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -4918,7 +4918,7 @@
         <v>194</v>
       </c>
       <c r="F17">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="G17">
         <v>1.99</v>
@@ -4927,10 +4927,10 @@
         <v>4.5</v>
       </c>
       <c r="I17">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="J17">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="K17">
         <v>3.95</v>
@@ -4939,22 +4939,22 @@
         <v>1.01</v>
       </c>
       <c r="M17">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N17">
-        <v>4.1</v>
+        <v>2.34</v>
       </c>
       <c r="O17">
         <v>1.27</v>
       </c>
       <c r="P17">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q17">
-        <v>1.67</v>
+        <v>1.27</v>
       </c>
       <c r="R17">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S17">
         <v>2.96</v>
@@ -4966,7 +4966,7 @@
         <v>1.01</v>
       </c>
       <c r="V17">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W17">
         <v>2</v>
@@ -5083,7 +5083,7 @@
         <v>1000</v>
       </c>
       <c r="BI17">
-        <v>2.88</v>
+        <v>1.01</v>
       </c>
       <c r="BJ17">
         <v>1000</v>
@@ -5160,22 +5160,22 @@
         <v>195</v>
       </c>
       <c r="F18">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="G18">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="H18">
         <v>4.7</v>
       </c>
       <c r="I18">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J18">
         <v>3.55</v>
       </c>
       <c r="K18">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L18">
         <v>1.01</v>
@@ -5199,19 +5199,19 @@
         <v>1.33</v>
       </c>
       <c r="S18">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="T18">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="U18">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V18">
         <v>1.25</v>
       </c>
       <c r="W18">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="X18">
         <v>16.5</v>
@@ -5223,7 +5223,7 @@
         <v>44</v>
       </c>
       <c r="AA18">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB18">
         <v>10.5</v>
@@ -5259,7 +5259,7 @@
         <v>48</v>
       </c>
       <c r="AM18">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN18">
         <v>18</v>
@@ -5268,70 +5268,70 @@
         <v>95</v>
       </c>
       <c r="AP18">
-        <v>12</v>
+        <v>1.44</v>
       </c>
       <c r="AQ18">
-        <v>11.5</v>
+        <v>1.34</v>
       </c>
       <c r="AR18">
-        <v>3.95</v>
+        <v>1.3</v>
       </c>
       <c r="AS18">
-        <v>4.2</v>
+        <v>1.32</v>
       </c>
       <c r="AT18">
-        <v>3.05</v>
+        <v>1.44</v>
       </c>
       <c r="AU18">
-        <v>7.4</v>
+        <v>1.44</v>
       </c>
       <c r="AV18">
-        <v>13.5</v>
+        <v>1.35</v>
       </c>
       <c r="AW18">
-        <v>4.1</v>
+        <v>1.32</v>
       </c>
       <c r="AX18">
-        <v>10</v>
+        <v>1.44</v>
       </c>
       <c r="AY18">
-        <v>9.199999999999999</v>
+        <v>1.44</v>
       </c>
       <c r="AZ18">
-        <v>17</v>
+        <v>1.27</v>
       </c>
       <c r="BA18">
-        <v>4.1</v>
+        <v>1.32</v>
       </c>
       <c r="BB18">
-        <v>3.75</v>
+        <v>1.27</v>
       </c>
       <c r="BC18">
-        <v>3.7</v>
+        <v>1.27</v>
       </c>
       <c r="BD18">
-        <v>4</v>
+        <v>1.3</v>
       </c>
       <c r="BE18">
-        <v>4.2</v>
+        <v>1.55</v>
       </c>
       <c r="BF18">
-        <v>10.5</v>
+        <v>1.34</v>
       </c>
       <c r="BG18">
-        <v>4.1</v>
+        <v>1.32</v>
       </c>
       <c r="BH18">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="BI18">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="BJ18">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK18">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL18">
         <v>1000</v>
@@ -5340,46 +5340,46 @@
         <v>1.01</v>
       </c>
       <c r="BN18">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BO18">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BP18">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BR18">
         <v>1000</v>
       </c>
       <c r="BS18">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BT18">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU18">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BV18">
         <v>1000</v>
       </c>
       <c r="BW18">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BZ18">
         <v>1000</v>
       </c>
       <c r="CA18">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="CB18" t="s">
         <v>226</v>
@@ -5402,22 +5402,22 @@
         <v>196</v>
       </c>
       <c r="F19">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="G19">
         <v>6.2</v>
       </c>
       <c r="H19">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="I19">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="J19">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="K19">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="L19">
         <v>1.01</v>
@@ -5435,13 +5435,13 @@
         <v>2.06</v>
       </c>
       <c r="Q19">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="R19">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S19">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="T19">
         <v>1.01</v>
@@ -5644,10 +5644,10 @@
         <v>197</v>
       </c>
       <c r="F20">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="G20">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="H20">
         <v>4.4</v>
@@ -5671,7 +5671,7 @@
         <v>5.8</v>
       </c>
       <c r="O20">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P20">
         <v>2.62</v>
@@ -5686,7 +5686,7 @@
         <v>2.36</v>
       </c>
       <c r="T20">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U20">
         <v>2.54</v>
@@ -5695,7 +5695,7 @@
         <v>1.28</v>
       </c>
       <c r="W20">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X20">
         <v>32</v>
@@ -5704,7 +5704,7 @@
         <v>29</v>
       </c>
       <c r="Z20">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AA20">
         <v>110</v>
@@ -5713,13 +5713,13 @@
         <v>17</v>
       </c>
       <c r="AC20">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD20">
         <v>23</v>
       </c>
       <c r="AE20">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF20">
         <v>17.5</v>
@@ -5728,7 +5728,7 @@
         <v>13.5</v>
       </c>
       <c r="AH20">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AI20">
         <v>55</v>
@@ -5746,64 +5746,64 @@
         <v>70</v>
       </c>
       <c r="AN20">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AO20">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP20">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="AQ20">
         <v>20</v>
       </c>
       <c r="AR20">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="AS20">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="AT20">
         <v>12</v>
       </c>
       <c r="AU20">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV20">
         <v>16</v>
       </c>
       <c r="AW20">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="AX20">
         <v>12.5</v>
       </c>
       <c r="AY20">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ20">
         <v>13.5</v>
       </c>
       <c r="BA20">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="BB20">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BC20">
         <v>15</v>
       </c>
       <c r="BD20">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="BE20">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="BF20">
         <v>6.8</v>
       </c>
       <c r="BG20">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5812,58 +5812,58 @@
         <v>1.01</v>
       </c>
       <c r="BJ20">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK20">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN20">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BO20">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="BP20">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BR20">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BS20">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BT20">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BU20">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV20">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BW20">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX20">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BY20">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BZ20">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="CA20">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="CB20" t="s">
         <v>226</v>
@@ -5886,7 +5886,7 @@
         <v>198</v>
       </c>
       <c r="F21">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G21">
         <v>2.56</v>
@@ -5901,10 +5901,10 @@
         <v>2.98</v>
       </c>
       <c r="K21">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="L21">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="M21">
         <v>1.16</v>
@@ -5913,13 +5913,13 @@
         <v>2.38</v>
       </c>
       <c r="O21">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="P21">
         <v>1.44</v>
       </c>
       <c r="Q21">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="R21">
         <v>1.15</v>
@@ -6030,7 +6030,7 @@
         <v>40</v>
       </c>
       <c r="BB21">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="BC21">
         <v>24</v>
@@ -6048,64 +6048,64 @@
         <v>38</v>
       </c>
       <c r="BH21">
-        <v>2.44</v>
+        <v>1000</v>
       </c>
       <c r="BI21">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="BJ21">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK21">
-        <v>7.2</v>
+        <v>2.94</v>
       </c>
       <c r="BL21">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="BM21">
-        <v>15.5</v>
+        <v>1.38</v>
       </c>
       <c r="BN21">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BO21">
-        <v>4.7</v>
+        <v>2</v>
       </c>
       <c r="BP21">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BQ21">
-        <v>10</v>
+        <v>1.38</v>
       </c>
       <c r="BR21">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS21">
-        <v>13</v>
+        <v>1.38</v>
       </c>
       <c r="BT21">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU21">
-        <v>6</v>
+        <v>2.18</v>
       </c>
       <c r="BV21">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BW21">
-        <v>12</v>
+        <v>1.38</v>
       </c>
       <c r="BX21">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BY21">
-        <v>13.5</v>
+        <v>1.38</v>
       </c>
       <c r="BZ21">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="CA21">
-        <v>13.5</v>
+        <v>1.38</v>
       </c>
       <c r="CB21" t="s">
         <v>226</v>
@@ -6158,16 +6158,16 @@
         <v>1.23</v>
       </c>
       <c r="P22">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="Q22">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R22">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S22">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="T22">
         <v>1.6</v>
@@ -6197,10 +6197,10 @@
         <v>22</v>
       </c>
       <c r="AC22">
+        <v>10</v>
+      </c>
+      <c r="AD22">
         <v>11</v>
-      </c>
-      <c r="AD22">
-        <v>12</v>
       </c>
       <c r="AE22">
         <v>21</v>
@@ -6209,13 +6209,13 @@
         <v>42</v>
       </c>
       <c r="AG22">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AH22">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AI22">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AJ22">
         <v>110</v>
@@ -6227,7 +6227,7 @@
         <v>60</v>
       </c>
       <c r="AM22">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN22">
         <v>55</v>
@@ -6242,13 +6242,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR22">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AS22">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AT22">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AU22">
         <v>8</v>
@@ -6257,37 +6257,37 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW22">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AX22">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="AY22">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AZ22">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BA22">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BB22">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BC22">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BD22">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BE22">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BF22">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BG22">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -6370,13 +6370,13 @@
         <v>200</v>
       </c>
       <c r="F23">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="G23">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="H23">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="I23">
         <v>19</v>
@@ -6385,7 +6385,7 @@
         <v>4.4</v>
       </c>
       <c r="K23">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="L23">
         <v>1.27</v>
@@ -6400,16 +6400,16 @@
         <v>1.24</v>
       </c>
       <c r="P23">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="Q23">
         <v>1.64</v>
       </c>
       <c r="R23">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S23">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="T23">
         <v>1.01</v>
@@ -6418,10 +6418,10 @@
         <v>1.01</v>
       </c>
       <c r="V23">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="W23">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="X23">
         <v>1000</v>
@@ -6612,22 +6612,22 @@
         <v>201</v>
       </c>
       <c r="F24">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="G24">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="H24">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="I24">
-        <v>2.36</v>
+        <v>2.74</v>
       </c>
       <c r="J24">
-        <v>3</v>
+        <v>2.46</v>
       </c>
       <c r="K24">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="L24">
         <v>1.01</v>
@@ -6636,22 +6636,22 @@
         <v>1.01</v>
       </c>
       <c r="N24">
-        <v>2.72</v>
+        <v>2.96</v>
       </c>
       <c r="O24">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="P24">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q24">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="R24">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S24">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="T24">
         <v>1.01</v>
@@ -6660,10 +6660,10 @@
         <v>1.01</v>
       </c>
       <c r="V24">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="W24">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="X24">
         <v>1000</v>
@@ -6774,10 +6774,10 @@
         <v>1.01</v>
       </c>
       <c r="BH24">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="BI24">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BJ24">
         <v>1000</v>
@@ -6863,13 +6863,13 @@
         <v>5.6</v>
       </c>
       <c r="I25">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="J25">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="K25">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L25">
         <v>1.01</v>
@@ -6884,7 +6884,7 @@
         <v>1.01</v>
       </c>
       <c r="P25">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Q25">
         <v>2.6</v>
@@ -7016,10 +7016,10 @@
         <v>1.01</v>
       </c>
       <c r="BH25">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="BI25">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="BJ25">
         <v>1000</v>
@@ -7120,28 +7120,28 @@
         <v>1.04</v>
       </c>
       <c r="N26">
-        <v>5.1</v>
+        <v>2.34</v>
       </c>
       <c r="O26">
         <v>1.21</v>
       </c>
       <c r="P26">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="Q26">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R26">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="S26">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="T26">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="U26">
-        <v>2.46</v>
+        <v>1.01</v>
       </c>
       <c r="V26">
         <v>1.37</v>
@@ -7150,112 +7150,112 @@
         <v>1.92</v>
       </c>
       <c r="X26">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="Y26">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z26">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA26">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB26">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AC26">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD26">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AE26">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AF26">
+        <v>1000</v>
+      </c>
+      <c r="AG26">
+        <v>1000</v>
+      </c>
+      <c r="AH26">
+        <v>1000</v>
+      </c>
+      <c r="AI26">
+        <v>1000</v>
+      </c>
+      <c r="AJ26">
+        <v>1000</v>
+      </c>
+      <c r="AK26">
+        <v>1000</v>
+      </c>
+      <c r="AL26">
+        <v>1000</v>
+      </c>
+      <c r="AM26">
+        <v>1000</v>
+      </c>
+      <c r="AN26">
+        <v>1000</v>
+      </c>
+      <c r="AO26">
+        <v>1000</v>
+      </c>
+      <c r="AP26">
         <v>18</v>
       </c>
-      <c r="AG26">
-        <v>13.5</v>
-      </c>
-      <c r="AH26">
+      <c r="AQ26">
+        <v>14.5</v>
+      </c>
+      <c r="AR26">
         <v>19.5</v>
       </c>
-      <c r="AI26">
-        <v>48</v>
-      </c>
-      <c r="AJ26">
-        <v>32</v>
-      </c>
-      <c r="AK26">
-        <v>24</v>
-      </c>
-      <c r="AL26">
-        <v>36</v>
-      </c>
-      <c r="AM26">
-        <v>75</v>
-      </c>
-      <c r="AN26">
-        <v>13</v>
-      </c>
-      <c r="AO26">
-        <v>32</v>
-      </c>
-      <c r="AP26">
-        <v>3.8</v>
-      </c>
-      <c r="AQ26">
-        <v>3.7</v>
-      </c>
-      <c r="AR26">
-        <v>3.95</v>
-      </c>
       <c r="AS26">
-        <v>4.2</v>
+        <v>40</v>
       </c>
       <c r="AT26">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="AU26">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV26">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AW26">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="AX26">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="AY26">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ26">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA26">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="BB26">
-        <v>3.9</v>
+        <v>18.5</v>
       </c>
       <c r="BC26">
-        <v>3.75</v>
+        <v>14.5</v>
       </c>
       <c r="BD26">
-        <v>3.95</v>
+        <v>20</v>
       </c>
       <c r="BE26">
-        <v>4.2</v>
+        <v>40</v>
       </c>
       <c r="BF26">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG26">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BH26">
         <v>1000</v>
@@ -7338,22 +7338,22 @@
         <v>204</v>
       </c>
       <c r="F27">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="G27">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="H27">
         <v>2</v>
       </c>
       <c r="I27">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="J27">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="K27">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="L27">
         <v>1.01</v>
@@ -7371,7 +7371,7 @@
         <v>2.2</v>
       </c>
       <c r="Q27">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R27">
         <v>1.46</v>
@@ -7580,22 +7580,22 @@
         <v>205</v>
       </c>
       <c r="F28">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="G28">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H28">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="I28">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="J28">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="K28">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="L28">
         <v>1.01</v>
@@ -7604,22 +7604,22 @@
         <v>1.01</v>
       </c>
       <c r="N28">
-        <v>2.68</v>
+        <v>4</v>
       </c>
       <c r="O28">
         <v>1.24</v>
       </c>
       <c r="P28">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q28">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="R28">
         <v>1.41</v>
       </c>
       <c r="S28">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="T28">
         <v>1.01</v>
@@ -7631,7 +7631,7 @@
         <v>1.22</v>
       </c>
       <c r="W28">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X28">
         <v>1000</v>
@@ -7822,43 +7822,43 @@
         <v>206</v>
       </c>
       <c r="F29">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="G29">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="H29">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="I29">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="J29">
-        <v>2.66</v>
+        <v>3.5</v>
       </c>
       <c r="K29">
         <v>6</v>
       </c>
       <c r="L29">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M29">
         <v>1.01</v>
       </c>
       <c r="N29">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="O29">
         <v>1.27</v>
       </c>
       <c r="P29">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q29">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R29">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="S29">
         <v>2.68</v>
@@ -7870,10 +7870,10 @@
         <v>1.01</v>
       </c>
       <c r="V29">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="W29">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="X29">
         <v>1000</v>
@@ -7984,10 +7984,10 @@
         <v>1.01</v>
       </c>
       <c r="BH29">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BI29">
-        <v>2.8</v>
+        <v>1.01</v>
       </c>
       <c r="BJ29">
         <v>1000</v>
@@ -8064,22 +8064,22 @@
         <v>207</v>
       </c>
       <c r="F30">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="G30">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="H30">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="I30">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="J30">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="K30">
-        <v>6.8</v>
+        <v>4.8</v>
       </c>
       <c r="L30">
         <v>1.01</v>
@@ -8088,22 +8088,22 @@
         <v>1.01</v>
       </c>
       <c r="N30">
-        <v>4.2</v>
+        <v>2.42</v>
       </c>
       <c r="O30">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P30">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="Q30">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="R30">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="S30">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="T30">
         <v>1.01</v>
@@ -8112,10 +8112,10 @@
         <v>1.01</v>
       </c>
       <c r="V30">
-        <v>2.58</v>
+        <v>2.4</v>
       </c>
       <c r="W30">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X30">
         <v>1000</v>
@@ -8306,22 +8306,22 @@
         <v>208</v>
       </c>
       <c r="F31">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="G31">
         <v>2.88</v>
       </c>
       <c r="H31">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="I31">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J31">
         <v>3.1</v>
       </c>
       <c r="K31">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="L31">
         <v>1.01</v>
@@ -8330,13 +8330,13 @@
         <v>1.01</v>
       </c>
       <c r="N31">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="O31">
         <v>1.45</v>
       </c>
       <c r="P31">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="Q31">
         <v>2.42</v>
@@ -8345,7 +8345,7 @@
         <v>1.08</v>
       </c>
       <c r="S31">
-        <v>4.5</v>
+        <v>2.42</v>
       </c>
       <c r="T31">
         <v>1.01</v>
@@ -8354,7 +8354,7 @@
         <v>1.01</v>
       </c>
       <c r="V31">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="W31">
         <v>1.53</v>
@@ -8551,19 +8551,19 @@
         <v>2.48</v>
       </c>
       <c r="G32">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="H32">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="I32">
         <v>2.92</v>
       </c>
       <c r="J32">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K32">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L32">
         <v>1.01</v>
@@ -8572,7 +8572,7 @@
         <v>1.01</v>
       </c>
       <c r="N32">
-        <v>4.7</v>
+        <v>2.36</v>
       </c>
       <c r="O32">
         <v>1.19</v>
@@ -8581,13 +8581,13 @@
         <v>2.36</v>
       </c>
       <c r="Q32">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="R32">
         <v>1.53</v>
       </c>
       <c r="S32">
-        <v>2.42</v>
+        <v>2.22</v>
       </c>
       <c r="T32">
         <v>1.01</v>
@@ -8599,7 +8599,7 @@
         <v>1.52</v>
       </c>
       <c r="W32">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="X32">
         <v>1000</v>
@@ -8799,43 +8799,43 @@
         <v>5.6</v>
       </c>
       <c r="I33">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="J33">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K33">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="L33">
         <v>1.01</v>
       </c>
       <c r="M33">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N33">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="O33">
         <v>1.23</v>
       </c>
       <c r="P33">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q33">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="R33">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="S33">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="T33">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="U33">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="V33">
         <v>1.17</v>
@@ -8844,112 +8844,112 @@
         <v>2.42</v>
       </c>
       <c r="X33">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y33">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Z33">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA33">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AB33">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC33">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AD33">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AE33">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AF33">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AG33">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH33">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI33">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ33">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AK33">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AL33">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM33">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN33">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AO33">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AP33">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AQ33">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR33">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AS33">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT33">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AU33">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV33">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW33">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AX33">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AY33">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ33">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BA33">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BB33">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC33">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BD33">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BE33">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF33">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BG33">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH33">
         <v>1000</v>
@@ -9032,16 +9032,16 @@
         <v>211</v>
       </c>
       <c r="F34">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="G34">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="H34">
         <v>3.6</v>
       </c>
       <c r="I34">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="J34">
         <v>3.15</v>
@@ -9056,22 +9056,22 @@
         <v>1.01</v>
       </c>
       <c r="N34">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O34">
         <v>1.39</v>
       </c>
       <c r="P34">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q34">
         <v>2.02</v>
       </c>
       <c r="R34">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S34">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T34">
         <v>1.01</v>
@@ -9080,10 +9080,10 @@
         <v>1.01</v>
       </c>
       <c r="V34">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="W34">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="X34">
         <v>1000</v>
@@ -9197,7 +9197,7 @@
         <v>1000</v>
       </c>
       <c r="BI34">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="BJ34">
         <v>1000</v>
@@ -9274,25 +9274,25 @@
         <v>212</v>
       </c>
       <c r="F35">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="G35">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="H35">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="I35">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="J35">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="K35">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="L35">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M35">
         <v>1.01</v>
@@ -9322,10 +9322,10 @@
         <v>1.01</v>
       </c>
       <c r="V35">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W35">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="X35">
         <v>1000</v>
@@ -9516,7 +9516,7 @@
         <v>213</v>
       </c>
       <c r="F36">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="G36">
         <v>2.68</v>
@@ -9531,7 +9531,7 @@
         <v>3.8</v>
       </c>
       <c r="K36">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L36">
         <v>1.01</v>
@@ -9555,7 +9555,7 @@
         <v>1.6</v>
       </c>
       <c r="S36">
-        <v>2.28</v>
+        <v>1.8</v>
       </c>
       <c r="T36">
         <v>1.01</v>
@@ -9758,58 +9758,58 @@
         <v>214</v>
       </c>
       <c r="F37">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="G37">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="H37">
+        <v>3.15</v>
+      </c>
+      <c r="I37">
+        <v>4.5</v>
+      </c>
+      <c r="J37">
+        <v>3.9</v>
+      </c>
+      <c r="K37">
+        <v>7.4</v>
+      </c>
+      <c r="L37">
+        <v>1.01</v>
+      </c>
+      <c r="M37">
+        <v>1.01</v>
+      </c>
+      <c r="N37">
         <v>3.1</v>
       </c>
-      <c r="I37">
-        <v>3.7</v>
-      </c>
-      <c r="J37">
-        <v>3.8</v>
-      </c>
-      <c r="K37">
-        <v>5.1</v>
-      </c>
-      <c r="L37">
-        <v>1.01</v>
-      </c>
-      <c r="M37">
-        <v>1.01</v>
-      </c>
-      <c r="N37">
-        <v>8.800000000000001</v>
-      </c>
       <c r="O37">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="P37">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="Q37">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="R37">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="S37">
-        <v>1.79</v>
+        <v>1.48</v>
       </c>
       <c r="T37">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="U37">
         <v>1.01</v>
       </c>
       <c r="V37">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="W37">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="X37">
         <v>1000</v>
@@ -10000,7 +10000,7 @@
         <v>215</v>
       </c>
       <c r="F38">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="G38">
         <v>1.39</v>
@@ -10012,7 +10012,7 @@
         <v>110</v>
       </c>
       <c r="J38">
-        <v>4.8</v>
+        <v>2.78</v>
       </c>
       <c r="K38">
         <v>110</v>
@@ -10024,22 +10024,22 @@
         <v>1.01</v>
       </c>
       <c r="N38">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="O38">
         <v>1.12</v>
       </c>
       <c r="P38">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="Q38">
         <v>1.35</v>
       </c>
       <c r="R38">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="S38">
-        <v>2.08</v>
+        <v>1.74</v>
       </c>
       <c r="T38">
         <v>1.01</v>
@@ -10048,10 +10048,10 @@
         <v>1.01</v>
       </c>
       <c r="V38">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="W38">
-        <v>2.92</v>
+        <v>1.01</v>
       </c>
       <c r="X38">
         <v>1000</v>
@@ -10108,52 +10108,52 @@
         <v>1000</v>
       </c>
       <c r="AP38">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AQ38">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="AR38">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AS38">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AT38">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU38">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AV38">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="AW38">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AX38">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY38">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ38">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BA38">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BB38">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BC38">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BD38">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BE38">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF38">
         <v>1.01</v>
@@ -10245,13 +10245,13 @@
         <v>1.82</v>
       </c>
       <c r="G39">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="H39">
         <v>4.8</v>
       </c>
       <c r="I39">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J39">
         <v>3.5</v>
@@ -10272,7 +10272,7 @@
         <v>1.35</v>
       </c>
       <c r="P39">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="Q39">
         <v>2.02</v>
@@ -10305,13 +10305,13 @@
         <v>48</v>
       </c>
       <c r="AA39">
-        <v>970</v>
+        <v>870</v>
       </c>
       <c r="AB39">
         <v>10</v>
       </c>
       <c r="AC39">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="AD39">
         <v>24</v>
@@ -10320,31 +10320,31 @@
         <v>90</v>
       </c>
       <c r="AF39">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AG39">
         <v>12.5</v>
       </c>
       <c r="AH39">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI39">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ39">
         <v>25</v>
       </c>
       <c r="AK39">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL39">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM39">
-        <v>970</v>
+        <v>870</v>
       </c>
       <c r="AN39">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO39">
         <v>110</v>
@@ -10356,10 +10356,10 @@
         <v>13.5</v>
       </c>
       <c r="AR39">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="AS39">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="AT39">
         <v>7.2</v>
@@ -10371,7 +10371,7 @@
         <v>17</v>
       </c>
       <c r="AW39">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AX39">
         <v>9.6</v>
@@ -10383,7 +10383,7 @@
         <v>17.5</v>
       </c>
       <c r="BA39">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BB39">
         <v>18</v>
@@ -10392,16 +10392,16 @@
         <v>18</v>
       </c>
       <c r="BD39">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BE39">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BF39">
         <v>10</v>
       </c>
       <c r="BG39">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BH39">
         <v>1000</v>
@@ -10487,7 +10487,7 @@
         <v>1.9</v>
       </c>
       <c r="G40">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H40">
         <v>3.85</v>
@@ -10496,7 +10496,7 @@
         <v>4.6</v>
       </c>
       <c r="J40">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K40">
         <v>4.3</v>
@@ -10508,22 +10508,22 @@
         <v>1.01</v>
       </c>
       <c r="N40">
-        <v>2.18</v>
+        <v>4</v>
       </c>
       <c r="O40">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P40">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="Q40">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="R40">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="S40">
-        <v>2.4</v>
+        <v>2.92</v>
       </c>
       <c r="T40">
         <v>1.01</v>
@@ -10535,115 +10535,115 @@
         <v>1.27</v>
       </c>
       <c r="W40">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="X40">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y40">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Z40">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA40">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB40">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC40">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD40">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE40">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF40">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG40">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH40">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI40">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ40">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK40">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL40">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM40">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN40">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AO40">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AP40">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AQ40">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AR40">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="AS40">
-        <v>1.01</v>
+        <v>60</v>
       </c>
       <c r="AT40">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AU40">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV40">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AW40">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="AX40">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AY40">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ40">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA40">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BB40">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BC40">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BD40">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BE40">
-        <v>1.01</v>
+        <v>60</v>
       </c>
       <c r="BF40">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BG40">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BH40">
         <v>4.6</v>
@@ -10655,55 +10655,55 @@
         <v>1000</v>
       </c>
       <c r="BK40">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BL40">
         <v>1000</v>
       </c>
       <c r="BM40">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BN40">
         <v>1000</v>
       </c>
       <c r="BO40">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BP40">
         <v>1000</v>
       </c>
       <c r="BQ40">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BR40">
         <v>1000</v>
       </c>
       <c r="BS40">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BT40">
         <v>1000</v>
       </c>
       <c r="BU40">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BV40">
         <v>1000</v>
       </c>
       <c r="BW40">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BX40">
         <v>1000</v>
       </c>
       <c r="BY40">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BZ40">
         <v>1000</v>
       </c>
       <c r="CA40">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="CB40" t="s">
         <v>226</v>
@@ -10726,23 +10726,23 @@
         <v>218</v>
       </c>
       <c r="F41">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="G41">
         <v>2.46</v>
       </c>
       <c r="H41">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="I41">
+        <v>4.6</v>
+      </c>
+      <c r="J41">
+        <v>2.66</v>
+      </c>
+      <c r="K41">
         <v>4.4</v>
       </c>
-      <c r="J41">
-        <v>2.86</v>
-      </c>
-      <c r="K41">
-        <v>3.55</v>
-      </c>
       <c r="L41">
         <v>1.01</v>
       </c>
@@ -10750,7 +10750,7 @@
         <v>1.01</v>
       </c>
       <c r="N41">
-        <v>2.88</v>
+        <v>1.01</v>
       </c>
       <c r="O41">
         <v>1.37</v>
@@ -10759,10 +10759,10 @@
         <v>1.61</v>
       </c>
       <c r="Q41">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="R41">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S41">
         <v>3.6</v>
@@ -10774,7 +10774,7 @@
         <v>1.01</v>
       </c>
       <c r="V41">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W41">
         <v>1.68</v>
@@ -10834,52 +10834,52 @@
         <v>1000</v>
       </c>
       <c r="AP41">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ41">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AR41">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS41">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AT41">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU41">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV41">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW41">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="AX41">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AY41">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ41">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BA41">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BB41">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BC41">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BD41">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BE41">
-        <v>80</v>
+        <v>1.01</v>
       </c>
       <c r="BF41">
         <v>1.01</v>
@@ -10968,43 +10968,43 @@
         <v>219</v>
       </c>
       <c r="F42">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="G42">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="H42">
         <v>3.65</v>
       </c>
       <c r="I42">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="J42">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K42">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="L42">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M42">
         <v>1.01</v>
       </c>
       <c r="N42">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="O42">
         <v>1.3</v>
       </c>
       <c r="P42">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q42">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="R42">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S42">
         <v>2.88</v>
@@ -11016,10 +11016,10 @@
         <v>1.01</v>
       </c>
       <c r="V42">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W42">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="X42">
         <v>1000</v>
@@ -11130,10 +11130,10 @@
         <v>1.01</v>
       </c>
       <c r="BH42">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI42">
-        <v>2.72</v>
+        <v>1.01</v>
       </c>
       <c r="BJ42">
         <v>1000</v>
@@ -11216,7 +11216,7 @@
         <v>3.1</v>
       </c>
       <c r="H43">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="I43">
         <v>2.78</v>
@@ -11228,13 +11228,13 @@
         <v>3.25</v>
       </c>
       <c r="L43">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="M43">
         <v>1.11</v>
       </c>
       <c r="N43">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="O43">
         <v>1.47</v>
@@ -11243,7 +11243,7 @@
         <v>1.66</v>
       </c>
       <c r="Q43">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="R43">
         <v>1.24</v>
@@ -11252,10 +11252,10 @@
         <v>4.8</v>
       </c>
       <c r="T43">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="U43">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V43">
         <v>1.56</v>
@@ -11273,10 +11273,10 @@
         <v>16.5</v>
       </c>
       <c r="AA43">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB43">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC43">
         <v>7.2</v>
@@ -11285,16 +11285,16 @@
         <v>13</v>
       </c>
       <c r="AE43">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF43">
         <v>18.5</v>
       </c>
       <c r="AG43">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH43">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI43">
         <v>60</v>
@@ -11306,19 +11306,19 @@
         <v>42</v>
       </c>
       <c r="AL43">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM43">
         <v>140</v>
       </c>
       <c r="AN43">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AO43">
         <v>38</v>
       </c>
       <c r="AP43">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ43">
         <v>8.4</v>
@@ -11342,7 +11342,7 @@
         <v>32</v>
       </c>
       <c r="AX43">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AY43">
         <v>12.5</v>
@@ -11351,7 +11351,7 @@
         <v>18.5</v>
       </c>
       <c r="BA43">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BB43">
         <v>46</v>
@@ -11369,61 +11369,61 @@
         <v>38</v>
       </c>
       <c r="BG43">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="BH43">
         <v>1000</v>
       </c>
       <c r="BI43">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="BJ43">
         <v>1000</v>
       </c>
       <c r="BK43">
-        <v>1.31</v>
+        <v>2.56</v>
       </c>
       <c r="BL43">
         <v>1000</v>
       </c>
       <c r="BM43">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="BN43">
         <v>1000</v>
       </c>
       <c r="BO43">
-        <v>1.14</v>
+        <v>1.91</v>
       </c>
       <c r="BP43">
         <v>1000</v>
       </c>
       <c r="BQ43">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="BR43">
         <v>1000</v>
       </c>
       <c r="BS43">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="BT43">
         <v>1000</v>
       </c>
       <c r="BU43">
-        <v>1.13</v>
+        <v>1.86</v>
       </c>
       <c r="BV43">
         <v>1000</v>
       </c>
       <c r="BW43">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="BX43">
         <v>1000</v>
       </c>
       <c r="BY43">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="BZ43">
         <v>0</v>
@@ -11455,19 +11455,19 @@
         <v>3.75</v>
       </c>
       <c r="G44">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="H44">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="I44">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="J44">
         <v>1.1</v>
       </c>
       <c r="K44">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="L44">
         <v>1.3</v>
@@ -11482,16 +11482,16 @@
         <v>1.24</v>
       </c>
       <c r="P44">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="Q44">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R44">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S44">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="T44">
         <v>1.01</v>
@@ -11500,7 +11500,7 @@
         <v>1.01</v>
       </c>
       <c r="V44">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="W44">
         <v>1.2</v>
@@ -11614,7 +11614,7 @@
         <v>1.01</v>
       </c>
       <c r="BH44">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BI44">
         <v>1.01</v>
@@ -11700,22 +11700,22 @@
         <v>2.72</v>
       </c>
       <c r="H45">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="I45">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J45">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K45">
         <v>3.45</v>
       </c>
       <c r="L45">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M45">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N45">
         <v>3.4</v>
@@ -11724,7 +11724,7 @@
         <v>1.34</v>
       </c>
       <c r="P45">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="Q45">
         <v>2.1</v>
@@ -11733,16 +11733,16 @@
         <v>1.32</v>
       </c>
       <c r="S45">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="T45">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="U45">
         <v>2.08</v>
       </c>
       <c r="V45">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W45">
         <v>1.58</v>
@@ -11751,25 +11751,25 @@
         <v>13</v>
       </c>
       <c r="Y45">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Z45">
         <v>20</v>
       </c>
       <c r="AA45">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AB45">
         <v>12.5</v>
       </c>
       <c r="AC45">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD45">
         <v>13.5</v>
       </c>
       <c r="AE45">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AF45">
         <v>17.5</v>
@@ -11781,7 +11781,7 @@
         <v>18.5</v>
       </c>
       <c r="AI45">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ45">
         <v>40</v>
@@ -11808,7 +11808,7 @@
         <v>10</v>
       </c>
       <c r="AR45">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AS45">
         <v>42</v>
@@ -11847,7 +11847,7 @@
         <v>40</v>
       </c>
       <c r="BE45">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BF45">
         <v>23</v>
@@ -11856,16 +11856,16 @@
         <v>29</v>
       </c>
       <c r="BH45">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="BI45">
-        <v>2.94</v>
+        <v>1.01</v>
       </c>
       <c r="BJ45">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK45">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BL45">
         <v>1000</v>
@@ -11874,46 +11874,46 @@
         <v>1.01</v>
       </c>
       <c r="BN45">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BO45">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP45">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BQ45">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR45">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BS45">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BT45">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BU45">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV45">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BW45">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BX45">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BY45">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BZ45">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA45">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="CB45" t="s">
         <v>226</v>
@@ -11960,7 +11960,7 @@
         <v>1.01</v>
       </c>
       <c r="N46">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="O46">
         <v>1.28</v>
@@ -11975,7 +11975,7 @@
         <v>1.08</v>
       </c>
       <c r="S46">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="T46">
         <v>1.01</v>
@@ -12187,82 +12187,82 @@
         <v>3.1</v>
       </c>
       <c r="I47">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J47">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K47">
         <v>3.75</v>
       </c>
       <c r="L47">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="M47">
         <v>1.06</v>
       </c>
       <c r="N47">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="O47">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P47">
         <v>1.96</v>
       </c>
       <c r="Q47">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="R47">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S47">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="T47">
         <v>1.59</v>
       </c>
       <c r="U47">
-        <v>1.99</v>
+        <v>2.16</v>
       </c>
       <c r="V47">
         <v>1.4</v>
       </c>
       <c r="W47">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X47">
         <v>18</v>
       </c>
       <c r="Y47">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Z47">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AA47">
         <v>70</v>
       </c>
       <c r="AB47">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC47">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD47">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AE47">
         <v>46</v>
       </c>
       <c r="AF47">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AG47">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH47">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AI47">
         <v>55</v>
@@ -12271,7 +12271,7 @@
         <v>42</v>
       </c>
       <c r="AK47">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AL47">
         <v>46</v>
@@ -12280,22 +12280,22 @@
         <v>100</v>
       </c>
       <c r="AN47">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AO47">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AP47">
         <v>12.5</v>
       </c>
       <c r="AQ47">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR47">
         <v>19</v>
       </c>
       <c r="AS47">
-        <v>6.4</v>
+        <v>4</v>
       </c>
       <c r="AT47">
         <v>9.6</v>
@@ -12307,7 +12307,7 @@
         <v>12</v>
       </c>
       <c r="AW47">
-        <v>6.2</v>
+        <v>3.9</v>
       </c>
       <c r="AX47">
         <v>14</v>
@@ -12319,31 +12319,31 @@
         <v>14</v>
       </c>
       <c r="BA47">
-        <v>6.4</v>
+        <v>3.95</v>
       </c>
       <c r="BB47">
-        <v>6.2</v>
+        <v>24</v>
       </c>
       <c r="BC47">
         <v>18.5</v>
       </c>
       <c r="BD47">
-        <v>6.2</v>
+        <v>3.9</v>
       </c>
       <c r="BE47">
-        <v>6.6</v>
+        <v>4.1</v>
       </c>
       <c r="BF47">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="BG47">
-        <v>5.9</v>
+        <v>3.85</v>
       </c>
       <c r="BH47">
         <v>1000</v>
       </c>
       <c r="BI47">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="BJ47">
         <v>1000</v>
@@ -12429,7 +12429,7 @@
         <v>2.44</v>
       </c>
       <c r="I48">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="J48">
         <v>3.65</v>
@@ -12444,7 +12444,7 @@
         <v>1.06</v>
       </c>
       <c r="N48">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O48">
         <v>1.28</v>
@@ -12453,7 +12453,7 @@
         <v>2.18</v>
       </c>
       <c r="Q48">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="R48">
         <v>1.45</v>
@@ -12462,13 +12462,13 @@
         <v>3.05</v>
       </c>
       <c r="T48">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U48">
         <v>2.38</v>
       </c>
       <c r="V48">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W48">
         <v>1.46</v>
@@ -12504,7 +12504,7 @@
         <v>13.5</v>
       </c>
       <c r="AH48">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AI48">
         <v>34</v>
@@ -12519,7 +12519,7 @@
         <v>40</v>
       </c>
       <c r="AM48">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AN48">
         <v>26</v>
@@ -12582,64 +12582,64 @@
         <v>15.5</v>
       </c>
       <c r="BH48">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="BI48">
-        <v>3.3</v>
+        <v>1.49</v>
       </c>
       <c r="BJ48">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BK48">
-        <v>7.2</v>
+        <v>2.12</v>
       </c>
       <c r="BL48">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BM48">
-        <v>21</v>
+        <v>1.48</v>
       </c>
       <c r="BN48">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BO48">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="BP48">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="BQ48">
-        <v>17.5</v>
+        <v>1.48</v>
       </c>
       <c r="BR48">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BS48">
-        <v>24</v>
+        <v>1.48</v>
       </c>
       <c r="BT48">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BU48">
-        <v>5</v>
+        <v>1.81</v>
       </c>
       <c r="BV48">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BW48">
-        <v>14</v>
+        <v>1.81</v>
       </c>
       <c r="BX48">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BY48">
-        <v>21</v>
+        <v>1.48</v>
       </c>
       <c r="BZ48">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="CA48">
-        <v>17.5</v>
+        <v>1.48</v>
       </c>
       <c r="CB48" t="s">
         <v>226</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-07.xlsx
@@ -694,7 +694,7 @@
     <t>Real Sociedad</t>
   </si>
   <si>
-    <t>2026-09-05 20:27:18</t>
+    <t>2026-09-05 23:34:48</t>
   </si>
 </sst>
 </file>
@@ -1288,22 +1288,22 @@
         <v>179</v>
       </c>
       <c r="F2">
-        <v>1.49</v>
+        <v>1.59</v>
       </c>
       <c r="G2">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="H2">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="I2">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="J2">
         <v>4.1</v>
       </c>
       <c r="K2">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="L2">
         <v>1.01</v>
@@ -1312,142 +1312,142 @@
         <v>1.01</v>
       </c>
       <c r="N2">
-        <v>1.26</v>
+        <v>4.7</v>
       </c>
       <c r="O2">
         <v>1.19</v>
       </c>
       <c r="P2">
-        <v>1.25</v>
+        <v>2.18</v>
       </c>
       <c r="Q2">
+        <v>1.54</v>
+      </c>
+      <c r="R2">
+        <v>1.47</v>
+      </c>
+      <c r="S2">
+        <v>2.52</v>
+      </c>
+      <c r="T2">
+        <v>1.01</v>
+      </c>
+      <c r="U2">
+        <v>1.01</v>
+      </c>
+      <c r="V2">
         <v>1.19</v>
       </c>
-      <c r="R2">
-        <v>1.08</v>
-      </c>
-      <c r="S2">
-        <v>1.01</v>
-      </c>
-      <c r="T2">
-        <v>1.01</v>
-      </c>
-      <c r="U2">
-        <v>1.01</v>
-      </c>
-      <c r="V2">
-        <v>1.14</v>
-      </c>
       <c r="W2">
-        <v>2.52</v>
+        <v>2.32</v>
       </c>
       <c r="X2">
         <v>1000</v>
       </c>
       <c r="Y2">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA2">
         <v>1000</v>
       </c>
       <c r="AB2">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC2">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AD2">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AF2">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG2">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH2">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK2">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM2">
         <v>1000</v>
       </c>
       <c r="AN2">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP2">
         <v>1.01</v>
       </c>
       <c r="AQ2">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AR2">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS2">
-        <v>1.01</v>
+        <v>75</v>
       </c>
       <c r="AT2">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AU2">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV2">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AW2">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="AX2">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AY2">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AZ2">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BA2">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BB2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BC2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BD2">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BE2">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="BF2">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BG2">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1572,10 +1572,10 @@
         <v>3.65</v>
       </c>
       <c r="T3">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="U3">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="V3">
         <v>1.25</v>
@@ -1638,52 +1638,52 @@
         <v>900</v>
       </c>
       <c r="AP3">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AQ3">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AR3">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AS3">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AT3">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AU3">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AV3">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AW3">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AX3">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AY3">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AZ3">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BA3">
         <v>1.01</v>
       </c>
       <c r="BB3">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BC3">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BD3">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BE3">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BF3">
         <v>1.01</v>
@@ -1695,61 +1695,61 @@
         <v>1000</v>
       </c>
       <c r="BI3">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="BJ3">
         <v>1000</v>
       </c>
       <c r="BK3">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BN3">
         <v>1000</v>
       </c>
       <c r="BO3">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BP3">
         <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BT3">
         <v>1000</v>
       </c>
       <c r="BU3">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="s">
         <v>226</v>
@@ -1775,7 +1775,7 @@
         <v>1.76</v>
       </c>
       <c r="G4">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="H4">
         <v>4.6</v>
@@ -1793,13 +1793,13 @@
         <v>1.35</v>
       </c>
       <c r="M4">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N4">
         <v>3</v>
       </c>
       <c r="O4">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P4">
         <v>1.72</v>
@@ -1808,19 +1808,19 @@
         <v>2.08</v>
       </c>
       <c r="R4">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S4">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="T4">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="U4">
         <v>1.01</v>
       </c>
       <c r="V4">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W4">
         <v>2.04</v>
@@ -1829,7 +1829,7 @@
         <v>1000</v>
       </c>
       <c r="Y4">
-        <v>1000</v>
+        <v>940</v>
       </c>
       <c r="Z4">
         <v>1000</v>
@@ -1838,10 +1838,10 @@
         <v>1000</v>
       </c>
       <c r="AB4">
-        <v>1000</v>
+        <v>960</v>
       </c>
       <c r="AC4">
-        <v>1000</v>
+        <v>920</v>
       </c>
       <c r="AD4">
         <v>1000</v>
@@ -1862,7 +1862,7 @@
         <v>1000</v>
       </c>
       <c r="AJ4">
-        <v>1000</v>
+        <v>930</v>
       </c>
       <c r="AK4">
         <v>1000</v>
@@ -1904,7 +1904,7 @@
         <v>1.01</v>
       </c>
       <c r="AX4">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AY4">
         <v>1.01</v>
@@ -1916,7 +1916,7 @@
         <v>1.01</v>
       </c>
       <c r="BB4">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BC4">
         <v>1.01</v>
@@ -2014,22 +2014,22 @@
         <v>182</v>
       </c>
       <c r="F5">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="G5">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="H5">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="I5">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J5">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="K5">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -2038,10 +2038,10 @@
         <v>1.09</v>
       </c>
       <c r="N5">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="O5">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="P5">
         <v>1.63</v>
@@ -2050,13 +2050,13 @@
         <v>2.42</v>
       </c>
       <c r="R5">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="S5">
-        <v>2.42</v>
+        <v>4.3</v>
       </c>
       <c r="T5">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="U5">
         <v>1.01</v>
@@ -2065,7 +2065,7 @@
         <v>1.21</v>
       </c>
       <c r="W5">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="X5">
         <v>10.5</v>
@@ -2092,7 +2092,7 @@
         <v>910</v>
       </c>
       <c r="AF5">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG5">
         <v>13</v>
@@ -2122,58 +2122,58 @@
         <v>910</v>
       </c>
       <c r="AP5">
-        <v>1.28</v>
+        <v>2.4</v>
       </c>
       <c r="AQ5">
-        <v>1.28</v>
+        <v>2.68</v>
       </c>
       <c r="AR5">
-        <v>1.25</v>
+        <v>2.54</v>
       </c>
       <c r="AS5">
-        <v>1.28</v>
+        <v>2.4</v>
       </c>
       <c r="AT5">
-        <v>1.28</v>
+        <v>5.7</v>
       </c>
       <c r="AU5">
-        <v>1.28</v>
+        <v>6.4</v>
       </c>
       <c r="AV5">
-        <v>1.22</v>
+        <v>2.44</v>
       </c>
       <c r="AW5">
-        <v>1.28</v>
+        <v>2.4</v>
       </c>
       <c r="AX5">
-        <v>1.28</v>
+        <v>2.16</v>
       </c>
       <c r="AY5">
-        <v>1.28</v>
+        <v>2.22</v>
       </c>
       <c r="AZ5">
-        <v>1.23</v>
+        <v>20</v>
       </c>
       <c r="BA5">
-        <v>1.28</v>
+        <v>2.4</v>
       </c>
       <c r="BB5">
-        <v>1.22</v>
+        <v>2.42</v>
       </c>
       <c r="BC5">
-        <v>1.23</v>
+        <v>2.22</v>
       </c>
       <c r="BD5">
-        <v>1.26</v>
+        <v>2.32</v>
       </c>
       <c r="BE5">
-        <v>1.28</v>
+        <v>2.4</v>
       </c>
       <c r="BF5">
-        <v>1.21</v>
+        <v>2.4</v>
       </c>
       <c r="BG5">
-        <v>1.28</v>
+        <v>2.22</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -2268,7 +2268,7 @@
         <v>2.64</v>
       </c>
       <c r="J6">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="K6">
         <v>4.6</v>
@@ -2280,7 +2280,7 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="O6">
         <v>1.26</v>
@@ -2427,55 +2427,55 @@
         <v>1000</v>
       </c>
       <c r="BK6">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BN6">
         <v>1000</v>
       </c>
       <c r="BO6">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BT6">
         <v>1000</v>
       </c>
       <c r="BU6">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BZ6">
         <v>1000</v>
       </c>
       <c r="CA6">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="CB6" t="s">
         <v>226</v>
@@ -2740,19 +2740,19 @@
         <v>185</v>
       </c>
       <c r="F8">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="G8">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="H8">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I8">
         <v>110</v>
       </c>
       <c r="J8">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="K8">
         <v>320</v>
@@ -2764,7 +2764,7 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="O8">
         <v>1.4</v>
@@ -2773,13 +2773,13 @@
         <v>1.6</v>
       </c>
       <c r="Q8">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R8">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="S8">
-        <v>4.1</v>
+        <v>2.62</v>
       </c>
       <c r="T8">
         <v>1.01</v>
@@ -2788,10 +2788,10 @@
         <v>1.01</v>
       </c>
       <c r="V8">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="W8">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -2982,22 +2982,22 @@
         <v>186</v>
       </c>
       <c r="F9">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="G9">
-        <v>2.86</v>
+        <v>110</v>
       </c>
       <c r="H9">
-        <v>2.54</v>
+        <v>1.1</v>
       </c>
       <c r="I9">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="J9">
-        <v>2.52</v>
+        <v>3.5</v>
       </c>
       <c r="K9">
-        <v>110</v>
+        <v>7.4</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -3006,7 +3006,7 @@
         <v>1.04</v>
       </c>
       <c r="N9">
-        <v>3.4</v>
+        <v>2.86</v>
       </c>
       <c r="O9">
         <v>1.24</v>
@@ -3030,10 +3030,10 @@
         <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W9">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -3490,7 +3490,7 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="O11">
         <v>1.11</v>
@@ -3514,10 +3514,10 @@
         <v>1.01</v>
       </c>
       <c r="V11">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W11">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3708,22 +3708,22 @@
         <v>189</v>
       </c>
       <c r="F12">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="G12">
         <v>1.5</v>
       </c>
       <c r="H12">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="I12">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="J12">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="K12">
-        <v>9</v>
+        <v>5.6</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3756,7 +3756,7 @@
         <v>1.01</v>
       </c>
       <c r="V12">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="W12">
         <v>3</v>
@@ -4192,7 +4192,7 @@
         <v>191</v>
       </c>
       <c r="F14">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G14">
         <v>2.12</v>
@@ -4201,7 +4201,7 @@
         <v>4.4</v>
       </c>
       <c r="I14">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J14">
         <v>3.3</v>
@@ -4243,7 +4243,7 @@
         <v>1.28</v>
       </c>
       <c r="W14">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="X14">
         <v>9.4</v>
@@ -4258,16 +4258,16 @@
         <v>110</v>
       </c>
       <c r="AB14">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AC14">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD14">
         <v>18.5</v>
       </c>
       <c r="AE14">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF14">
         <v>11.5</v>
@@ -4297,7 +4297,7 @@
         <v>23</v>
       </c>
       <c r="AO14">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AP14">
         <v>8.800000000000001</v>
@@ -4312,7 +4312,7 @@
         <v>38</v>
       </c>
       <c r="AT14">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU14">
         <v>7</v>
@@ -4458,10 +4458,10 @@
         <v>1.01</v>
       </c>
       <c r="N15">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="O15">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="P15">
         <v>2.16</v>
@@ -4470,7 +4470,7 @@
         <v>1.64</v>
       </c>
       <c r="R15">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S15">
         <v>2.42</v>
@@ -4706,22 +4706,22 @@
         <v>1.21</v>
       </c>
       <c r="P16">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="Q16">
         <v>1.66</v>
       </c>
       <c r="R16">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S16">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T16">
         <v>1.01</v>
       </c>
       <c r="U16">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="V16">
         <v>1.48</v>
@@ -4832,10 +4832,10 @@
         <v>1.01</v>
       </c>
       <c r="BF16">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BG16">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -5184,7 +5184,7 @@
         <v>1.08</v>
       </c>
       <c r="N18">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O18">
         <v>1.35</v>
@@ -5199,7 +5199,7 @@
         <v>1.33</v>
       </c>
       <c r="S18">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T18">
         <v>1.87</v>
@@ -5220,22 +5220,22 @@
         <v>19</v>
       </c>
       <c r="Z18">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA18">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AB18">
         <v>10.5</v>
       </c>
       <c r="AC18">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD18">
         <v>23</v>
       </c>
       <c r="AE18">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF18">
         <v>14</v>
@@ -5256,10 +5256,10 @@
         <v>26</v>
       </c>
       <c r="AL18">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM18">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN18">
         <v>18</v>
@@ -5268,58 +5268,58 @@
         <v>95</v>
       </c>
       <c r="AP18">
-        <v>1.44</v>
+        <v>12</v>
       </c>
       <c r="AQ18">
-        <v>1.34</v>
+        <v>13.5</v>
       </c>
       <c r="AR18">
-        <v>1.3</v>
+        <v>4.6</v>
       </c>
       <c r="AS18">
-        <v>1.32</v>
+        <v>4.8</v>
       </c>
       <c r="AT18">
-        <v>1.44</v>
+        <v>7.6</v>
       </c>
       <c r="AU18">
-        <v>1.44</v>
+        <v>7.4</v>
       </c>
       <c r="AV18">
-        <v>1.35</v>
+        <v>4.1</v>
       </c>
       <c r="AW18">
-        <v>1.32</v>
+        <v>4.7</v>
       </c>
       <c r="AX18">
-        <v>1.44</v>
+        <v>10</v>
       </c>
       <c r="AY18">
-        <v>1.44</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ18">
-        <v>1.27</v>
+        <v>17</v>
       </c>
       <c r="BA18">
-        <v>1.32</v>
+        <v>4.7</v>
       </c>
       <c r="BB18">
-        <v>1.27</v>
+        <v>4.3</v>
       </c>
       <c r="BC18">
-        <v>1.27</v>
+        <v>4.3</v>
       </c>
       <c r="BD18">
-        <v>1.3</v>
+        <v>4.7</v>
       </c>
       <c r="BE18">
-        <v>1.55</v>
+        <v>4.8</v>
       </c>
       <c r="BF18">
-        <v>1.34</v>
+        <v>10.5</v>
       </c>
       <c r="BG18">
-        <v>1.32</v>
+        <v>4.8</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5644,10 +5644,10 @@
         <v>197</v>
       </c>
       <c r="F20">
+        <v>1.8</v>
+      </c>
+      <c r="G20">
         <v>1.83</v>
-      </c>
-      <c r="G20">
-        <v>1.84</v>
       </c>
       <c r="H20">
         <v>4.4</v>
@@ -5671,7 +5671,7 @@
         <v>5.8</v>
       </c>
       <c r="O20">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P20">
         <v>2.62</v>
@@ -5683,7 +5683,7 @@
         <v>1.66</v>
       </c>
       <c r="S20">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="T20">
         <v>1.59</v>
@@ -5692,88 +5692,88 @@
         <v>2.54</v>
       </c>
       <c r="V20">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W20">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="X20">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="Y20">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Z20">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AA20">
         <v>110</v>
       </c>
       <c r="AB20">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AC20">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD20">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AE20">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF20">
-        <v>17.5</v>
+        <v>14</v>
       </c>
       <c r="AG20">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH20">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AI20">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AJ20">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AK20">
+        <v>18.5</v>
+      </c>
+      <c r="AL20">
+        <v>26</v>
+      </c>
+      <c r="AM20">
+        <v>65</v>
+      </c>
+      <c r="AN20">
+        <v>7.6</v>
+      </c>
+      <c r="AO20">
+        <v>34</v>
+      </c>
+      <c r="AP20">
+        <v>7.4</v>
+      </c>
+      <c r="AQ20">
         <v>21</v>
       </c>
-      <c r="AL20">
-        <v>32</v>
-      </c>
-      <c r="AM20">
-        <v>70</v>
-      </c>
-      <c r="AN20">
-        <v>9</v>
-      </c>
-      <c r="AO20">
-        <v>40</v>
-      </c>
-      <c r="AP20">
-        <v>3.8</v>
-      </c>
-      <c r="AQ20">
-        <v>20</v>
-      </c>
       <c r="AR20">
-        <v>3.95</v>
+        <v>34</v>
       </c>
       <c r="AS20">
-        <v>4.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT20">
         <v>12</v>
       </c>
       <c r="AU20">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV20">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW20">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="AX20">
         <v>12.5</v>
@@ -5782,28 +5782,28 @@
         <v>9.6</v>
       </c>
       <c r="AZ20">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA20">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="BB20">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BC20">
         <v>15</v>
       </c>
       <c r="BD20">
-        <v>3.8</v>
+        <v>22</v>
       </c>
       <c r="BE20">
-        <v>4.1</v>
+        <v>50</v>
       </c>
       <c r="BF20">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG20">
-        <v>3.9</v>
+        <v>28</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5913,7 +5913,7 @@
         <v>2.38</v>
       </c>
       <c r="O21">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="P21">
         <v>1.44</v>
@@ -6140,7 +6140,7 @@
         <v>1.87</v>
       </c>
       <c r="J22">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K22">
         <v>4.2</v>
@@ -6155,25 +6155,25 @@
         <v>4.6</v>
       </c>
       <c r="O22">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P22">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q22">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="R22">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="S22">
-        <v>2.58</v>
+        <v>2.72</v>
       </c>
       <c r="T22">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U22">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="V22">
         <v>2.14</v>
@@ -6370,7 +6370,7 @@
         <v>200</v>
       </c>
       <c r="F23">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="G23">
         <v>1.59</v>
@@ -6418,7 +6418,7 @@
         <v>1.01</v>
       </c>
       <c r="V23">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W23">
         <v>2.68</v>
@@ -6612,25 +6612,25 @@
         <v>201</v>
       </c>
       <c r="F24">
+        <v>3.85</v>
+      </c>
+      <c r="G24">
+        <v>4.6</v>
+      </c>
+      <c r="H24">
+        <v>2.12</v>
+      </c>
+      <c r="I24">
+        <v>2.36</v>
+      </c>
+      <c r="J24">
+        <v>3</v>
+      </c>
+      <c r="K24">
         <v>3.75</v>
       </c>
-      <c r="G24">
-        <v>6.2</v>
-      </c>
-      <c r="H24">
-        <v>2.08</v>
-      </c>
-      <c r="I24">
-        <v>2.74</v>
-      </c>
-      <c r="J24">
-        <v>2.46</v>
-      </c>
-      <c r="K24">
-        <v>3.95</v>
-      </c>
       <c r="L24">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M24">
         <v>1.01</v>
@@ -6639,7 +6639,7 @@
         <v>2.96</v>
       </c>
       <c r="O24">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P24">
         <v>1.58</v>
@@ -6660,10 +6660,10 @@
         <v>1.01</v>
       </c>
       <c r="V24">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="W24">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="X24">
         <v>1000</v>
@@ -6872,7 +6872,7 @@
         <v>3.5</v>
       </c>
       <c r="L25">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M25">
         <v>1.01</v>
@@ -7129,13 +7129,13 @@
         <v>2.34</v>
       </c>
       <c r="Q26">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="R26">
         <v>1.54</v>
       </c>
       <c r="S26">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="T26">
         <v>1.01</v>
@@ -7150,112 +7150,112 @@
         <v>1.92</v>
       </c>
       <c r="X26">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Y26">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z26">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA26">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB26">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC26">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD26">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE26">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF26">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG26">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH26">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI26">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ26">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AK26">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL26">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AM26">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN26">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AO26">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP26">
-        <v>18</v>
+        <v>4.4</v>
       </c>
       <c r="AQ26">
-        <v>14.5</v>
+        <v>4.2</v>
       </c>
       <c r="AR26">
-        <v>19.5</v>
+        <v>4.4</v>
       </c>
       <c r="AS26">
-        <v>40</v>
+        <v>4.9</v>
       </c>
       <c r="AT26">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AU26">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AV26">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AW26">
-        <v>25</v>
+        <v>4.7</v>
       </c>
       <c r="AX26">
-        <v>10.5</v>
+        <v>3.95</v>
       </c>
       <c r="AY26">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ26">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA26">
-        <v>26</v>
+        <v>4.7</v>
       </c>
       <c r="BB26">
-        <v>18.5</v>
+        <v>4.4</v>
       </c>
       <c r="BC26">
-        <v>14.5</v>
+        <v>4.3</v>
       </c>
       <c r="BD26">
-        <v>20</v>
+        <v>4.4</v>
       </c>
       <c r="BE26">
-        <v>40</v>
+        <v>4.9</v>
       </c>
       <c r="BF26">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BG26">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH26">
         <v>1000</v>
@@ -7362,7 +7362,7 @@
         <v>1.01</v>
       </c>
       <c r="N27">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="O27">
         <v>1.21</v>
@@ -7580,52 +7580,52 @@
         <v>205</v>
       </c>
       <c r="F28">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="G28">
         <v>1.86</v>
       </c>
       <c r="H28">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I28">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="J28">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="K28">
-        <v>6.6</v>
+        <v>5.1</v>
       </c>
       <c r="L28">
         <v>1.01</v>
       </c>
       <c r="M28">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N28">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O28">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P28">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q28">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="R28">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S28">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="T28">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="U28">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="V28">
         <v>1.22</v>
@@ -7634,112 +7634,112 @@
         <v>2.16</v>
       </c>
       <c r="X28">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y28">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z28">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA28">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB28">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC28">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD28">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE28">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF28">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG28">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH28">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI28">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ28">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK28">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL28">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM28">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN28">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AO28">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP28">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AQ28">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AR28">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="AS28">
-        <v>1.01</v>
+        <v>75</v>
       </c>
       <c r="AT28">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AU28">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV28">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AW28">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="AX28">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AY28">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ28">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA28">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BB28">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BC28">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BD28">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BE28">
-        <v>1.01</v>
+        <v>60</v>
       </c>
       <c r="BF28">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BG28">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BH28">
         <v>1000</v>
@@ -7846,7 +7846,7 @@
         <v>1.01</v>
       </c>
       <c r="N29">
-        <v>2.88</v>
+        <v>3.85</v>
       </c>
       <c r="O29">
         <v>1.27</v>
@@ -8064,19 +8064,19 @@
         <v>207</v>
       </c>
       <c r="F30">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="G30">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="H30">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="I30">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="J30">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K30">
         <v>4.8</v>
@@ -8088,22 +8088,22 @@
         <v>1.01</v>
       </c>
       <c r="N30">
-        <v>2.42</v>
+        <v>4.1</v>
       </c>
       <c r="O30">
         <v>1.24</v>
       </c>
       <c r="P30">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q30">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="R30">
         <v>1.41</v>
       </c>
       <c r="S30">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="T30">
         <v>1.01</v>
@@ -8112,10 +8112,10 @@
         <v>1.01</v>
       </c>
       <c r="V30">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="W30">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X30">
         <v>1000</v>
@@ -8324,7 +8324,7 @@
         <v>4.1</v>
       </c>
       <c r="L31">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M31">
         <v>1.01</v>
@@ -8342,7 +8342,7 @@
         <v>2.42</v>
       </c>
       <c r="R31">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="S31">
         <v>2.42</v>
@@ -8814,7 +8814,7 @@
         <v>1.03</v>
       </c>
       <c r="N33">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="O33">
         <v>1.23</v>
@@ -9032,25 +9032,25 @@
         <v>211</v>
       </c>
       <c r="F34">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="G34">
-        <v>2.48</v>
+        <v>2.22</v>
       </c>
       <c r="H34">
         <v>3.6</v>
       </c>
       <c r="I34">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="J34">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K34">
         <v>3.7</v>
       </c>
       <c r="L34">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M34">
         <v>1.01</v>
@@ -9080,10 +9080,10 @@
         <v>1.01</v>
       </c>
       <c r="V34">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W34">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="X34">
         <v>1000</v>
@@ -9555,7 +9555,7 @@
         <v>1.6</v>
       </c>
       <c r="S36">
-        <v>1.8</v>
+        <v>2.12</v>
       </c>
       <c r="T36">
         <v>1.01</v>
@@ -10000,19 +10000,19 @@
         <v>215</v>
       </c>
       <c r="F38">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="G38">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="H38">
-        <v>1.1</v>
+        <v>2.72</v>
       </c>
       <c r="I38">
-        <v>110</v>
+        <v>26</v>
       </c>
       <c r="J38">
-        <v>2.78</v>
+        <v>5.5</v>
       </c>
       <c r="K38">
         <v>110</v>
@@ -10021,10 +10021,10 @@
         <v>1.01</v>
       </c>
       <c r="M38">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N38">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O38">
         <v>1.12</v>
@@ -10048,10 +10048,10 @@
         <v>1.01</v>
       </c>
       <c r="V38">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="W38">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="X38">
         <v>1000</v>
@@ -10242,58 +10242,58 @@
         <v>216</v>
       </c>
       <c r="F39">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="G39">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="H39">
         <v>4.8</v>
       </c>
       <c r="I39">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J39">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="K39">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="L39">
         <v>1.37</v>
       </c>
       <c r="M39">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N39">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="O39">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="P39">
+        <v>1.93</v>
+      </c>
+      <c r="Q39">
+        <v>1.95</v>
+      </c>
+      <c r="R39">
+        <v>1.34</v>
+      </c>
+      <c r="S39">
+        <v>3.5</v>
+      </c>
+      <c r="T39">
         <v>1.86</v>
       </c>
-      <c r="Q39">
-        <v>2.02</v>
-      </c>
-      <c r="R39">
-        <v>1.31</v>
-      </c>
-      <c r="S39">
-        <v>3.65</v>
-      </c>
-      <c r="T39">
-        <v>1.74</v>
-      </c>
       <c r="U39">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="V39">
         <v>1.22</v>
       </c>
       <c r="W39">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="X39">
         <v>16</v>
@@ -10305,13 +10305,13 @@
         <v>48</v>
       </c>
       <c r="AA39">
-        <v>870</v>
+        <v>750</v>
       </c>
       <c r="AB39">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC39">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="AD39">
         <v>24</v>
@@ -10323,7 +10323,7 @@
         <v>13.5</v>
       </c>
       <c r="AG39">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH39">
         <v>24</v>
@@ -10332,19 +10332,19 @@
         <v>90</v>
       </c>
       <c r="AJ39">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AK39">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL39">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM39">
-        <v>870</v>
+        <v>750</v>
       </c>
       <c r="AN39">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO39">
         <v>110</v>
@@ -10356,13 +10356,13 @@
         <v>13.5</v>
       </c>
       <c r="AR39">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AS39">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AT39">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU39">
         <v>7.2</v>
@@ -10371,37 +10371,37 @@
         <v>17</v>
       </c>
       <c r="AW39">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AX39">
         <v>9.6</v>
       </c>
       <c r="AY39">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AZ39">
         <v>17.5</v>
       </c>
       <c r="BA39">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BB39">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BC39">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BD39">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BE39">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BF39">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BG39">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BH39">
         <v>1000</v>
@@ -10496,16 +10496,16 @@
         <v>4.6</v>
       </c>
       <c r="J40">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K40">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L40">
         <v>1.01</v>
       </c>
       <c r="M40">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N40">
         <v>4</v>
@@ -10520,10 +10520,10 @@
         <v>1.78</v>
       </c>
       <c r="R40">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="S40">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="T40">
         <v>1.01</v>
@@ -10532,7 +10532,7 @@
         <v>1.01</v>
       </c>
       <c r="V40">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W40">
         <v>1.92</v>
@@ -10750,13 +10750,13 @@
         <v>1.01</v>
       </c>
       <c r="N41">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="O41">
         <v>1.37</v>
       </c>
       <c r="P41">
-        <v>1.61</v>
+        <v>1.84</v>
       </c>
       <c r="Q41">
         <v>1.78</v>
@@ -10992,7 +10992,7 @@
         <v>1.01</v>
       </c>
       <c r="N42">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="O42">
         <v>1.3</v>
@@ -11001,10 +11001,10 @@
         <v>1.81</v>
       </c>
       <c r="Q42">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R42">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S42">
         <v>2.88</v>
@@ -11240,13 +11240,13 @@
         <v>1.47</v>
       </c>
       <c r="P43">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q43">
         <v>2.44</v>
       </c>
       <c r="R43">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S43">
         <v>4.8</v>
@@ -11261,7 +11261,7 @@
         <v>1.56</v>
       </c>
       <c r="W43">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X43">
         <v>9.800000000000001</v>
@@ -11452,22 +11452,22 @@
         <v>221</v>
       </c>
       <c r="F44">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="G44">
         <v>6.8</v>
       </c>
       <c r="H44">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="I44">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="J44">
         <v>1.1</v>
       </c>
       <c r="K44">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="L44">
         <v>1.3</v>
@@ -11482,7 +11482,7 @@
         <v>1.24</v>
       </c>
       <c r="P44">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="Q44">
         <v>1.64</v>
@@ -11694,22 +11694,22 @@
         <v>222</v>
       </c>
       <c r="F45">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="G45">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H45">
         <v>2.98</v>
       </c>
       <c r="I45">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J45">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K45">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L45">
         <v>1.01</v>
@@ -11721,7 +11721,7 @@
         <v>3.4</v>
       </c>
       <c r="O45">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P45">
         <v>1.82</v>
@@ -11742,7 +11742,7 @@
         <v>2.08</v>
       </c>
       <c r="V45">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W45">
         <v>1.58</v>
@@ -11760,7 +11760,7 @@
         <v>55</v>
       </c>
       <c r="AB45">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC45">
         <v>7.8</v>
@@ -11808,13 +11808,13 @@
         <v>10</v>
       </c>
       <c r="AR45">
-        <v>7.6</v>
+        <v>18</v>
       </c>
       <c r="AS45">
         <v>42</v>
       </c>
       <c r="AT45">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU45">
         <v>6.8</v>
@@ -11960,13 +11960,13 @@
         <v>1.01</v>
       </c>
       <c r="N46">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O46">
         <v>1.28</v>
       </c>
       <c r="P46">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q46">
         <v>1.27</v>
@@ -11975,7 +11975,7 @@
         <v>1.08</v>
       </c>
       <c r="S46">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T46">
         <v>1.01</v>
@@ -12202,7 +12202,7 @@
         <v>1.06</v>
       </c>
       <c r="N47">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="O47">
         <v>1.28</v>
@@ -12211,28 +12211,28 @@
         <v>1.96</v>
       </c>
       <c r="Q47">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="R47">
         <v>1.37</v>
       </c>
       <c r="S47">
-        <v>3.05</v>
+        <v>2.28</v>
       </c>
       <c r="T47">
         <v>1.59</v>
       </c>
       <c r="U47">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V47">
         <v>1.4</v>
       </c>
       <c r="W47">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="X47">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y47">
         <v>16</v>
@@ -12244,10 +12244,10 @@
         <v>70</v>
       </c>
       <c r="AB47">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC47">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD47">
         <v>17</v>
@@ -12256,7 +12256,7 @@
         <v>46</v>
       </c>
       <c r="AF47">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG47">
         <v>14.5</v>
@@ -12289,13 +12289,13 @@
         <v>12.5</v>
       </c>
       <c r="AQ47">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AR47">
         <v>19</v>
       </c>
       <c r="AS47">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AT47">
         <v>9.6</v>
@@ -12307,7 +12307,7 @@
         <v>12</v>
       </c>
       <c r="AW47">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AX47">
         <v>14</v>
@@ -12319,25 +12319,25 @@
         <v>14</v>
       </c>
       <c r="BA47">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BB47">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BC47">
         <v>18.5</v>
       </c>
       <c r="BD47">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BE47">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF47">
         <v>14.5</v>
       </c>
       <c r="BG47">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BH47">
         <v>1000</v>
@@ -12426,7 +12426,7 @@
         <v>3.2</v>
       </c>
       <c r="H48">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="I48">
         <v>2.46</v>
@@ -12450,10 +12450,10 @@
         <v>1.28</v>
       </c>
       <c r="P48">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q48">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R48">
         <v>1.45</v>
@@ -12462,7 +12462,7 @@
         <v>3.05</v>
       </c>
       <c r="T48">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U48">
         <v>2.38</v>
@@ -12489,13 +12489,13 @@
         <v>14.5</v>
       </c>
       <c r="AC48">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD48">
         <v>11.5</v>
       </c>
       <c r="AE48">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF48">
         <v>23</v>
@@ -12504,7 +12504,7 @@
         <v>13.5</v>
       </c>
       <c r="AH48">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI48">
         <v>34</v>
@@ -12531,7 +12531,7 @@
         <v>15</v>
       </c>
       <c r="AQ48">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR48">
         <v>15.5</v>
@@ -12558,7 +12558,7 @@
         <v>12</v>
       </c>
       <c r="AZ48">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA48">
         <v>30</v>
@@ -12582,64 +12582,64 @@
         <v>15.5</v>
       </c>
       <c r="BH48">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="BI48">
-        <v>1.49</v>
+        <v>3.35</v>
       </c>
       <c r="BJ48">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK48">
-        <v>2.12</v>
+        <v>8</v>
       </c>
       <c r="BL48">
         <v>1000</v>
       </c>
       <c r="BM48">
-        <v>1.48</v>
+        <v>14.5</v>
       </c>
       <c r="BN48">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO48">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BP48">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ48">
-        <v>1.48</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR48">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS48">
-        <v>1.48</v>
+        <v>11</v>
       </c>
       <c r="BT48">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BU48">
-        <v>1.81</v>
+        <v>5</v>
       </c>
       <c r="BV48">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BW48">
-        <v>1.81</v>
+        <v>8.6</v>
       </c>
       <c r="BX48">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BY48">
-        <v>1.48</v>
+        <v>10.5</v>
       </c>
       <c r="BZ48">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="CA48">
-        <v>1.48</v>
+        <v>9.6</v>
       </c>
       <c r="CB48" t="s">
         <v>226</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-07.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="252">
   <si>
     <t>League</t>
   </si>
@@ -280,51 +280,51 @@
     <t>Lithuanian A Lyga</t>
   </si>
   <si>
+    <t>Cypriot 1st Division</t>
+  </si>
+  <si>
     <t>Latvian Virsliga</t>
   </si>
   <si>
-    <t>Cypriot 1st Division</t>
-  </si>
-  <si>
     <t>Italian Serie A</t>
   </si>
   <si>
     <t>Israeli Premier League</t>
   </si>
   <si>
+    <t>Danish Superliga</t>
+  </si>
+  <si>
+    <t>Egyptian Premier</t>
+  </si>
+  <si>
+    <t>Polish I Liga</t>
+  </si>
+  <si>
+    <t>Spanish La Liga</t>
+  </si>
+  <si>
     <t>Swedish Allsvenskan</t>
   </si>
   <si>
     <t>Turkish Super League</t>
   </si>
   <si>
-    <t>Spanish La Liga</t>
-  </si>
-  <si>
-    <t>Egyptian Premier</t>
-  </si>
-  <si>
-    <t>Danish Superliga</t>
-  </si>
-  <si>
-    <t>Polish I Liga</t>
-  </si>
-  <si>
     <t>Swedish Superettan</t>
   </si>
   <si>
     <t>Bulgarian A League</t>
   </si>
   <si>
+    <t>Dutch Eerste Divisie</t>
+  </si>
+  <si>
+    <t>Serbian Super League</t>
+  </si>
+  <si>
     <t>Uruguayan Primera Division</t>
   </si>
   <si>
-    <t>Serbian Super League</t>
-  </si>
-  <si>
-    <t>Dutch Eerste Divisie</t>
-  </si>
-  <si>
     <t>Italian Serie B</t>
   </si>
   <si>
@@ -349,6 +349,21 @@
     <t>Portuguese Primeira Liga</t>
   </si>
   <si>
+    <t>Brazilian Serie C</t>
+  </si>
+  <si>
+    <t>Uruguayan Segunda Division</t>
+  </si>
+  <si>
+    <t>Venezuelan Primera Division</t>
+  </si>
+  <si>
+    <t>Chilean Primera Division</t>
+  </si>
+  <si>
+    <t>Brazilian Serie A</t>
+  </si>
+  <si>
     <t>2026-09-07</t>
   </si>
   <si>
@@ -412,6 +427,18 @@
     <t>19:30:00</t>
   </si>
   <si>
+    <t>21:00:00</t>
+  </si>
+  <si>
+    <t>21:30:00</t>
+  </si>
+  <si>
+    <t>22:00:00</t>
+  </si>
+  <si>
+    <t>23:00:00</t>
+  </si>
+  <si>
     <t>Nacional Potosi</t>
   </si>
   <si>
@@ -439,60 +466,60 @@
     <t>Hegelmann Litauen</t>
   </si>
   <si>
+    <t>Pafos FC</t>
+  </si>
+  <si>
+    <t>FK Riga</t>
+  </si>
+  <si>
     <t>Rigas Futbola Skola</t>
   </si>
   <si>
-    <t>Pafos FC</t>
-  </si>
-  <si>
-    <t>FK Riga</t>
-  </si>
-  <si>
     <t>Cagliari</t>
   </si>
   <si>
     <t>Maccabi Netanya</t>
   </si>
   <si>
+    <t>Aris FC Limassol</t>
+  </si>
+  <si>
+    <t>Midtjylland</t>
+  </si>
+  <si>
+    <t>National Bank</t>
+  </si>
+  <si>
+    <t>Petrojet</t>
+  </si>
+  <si>
+    <t>Hapoel Tel Aviv</t>
+  </si>
+  <si>
+    <t>Ruch Chorzow</t>
+  </si>
+  <si>
+    <t>Getafe</t>
+  </si>
+  <si>
     <t>Mjallby</t>
   </si>
   <si>
+    <t>Malmo FF</t>
+  </si>
+  <si>
+    <t>Kalmar FF</t>
+  </si>
+  <si>
+    <t>Manisa FK</t>
+  </si>
+  <si>
+    <t>Rizespor</t>
+  </si>
+  <si>
     <t>Goztepe</t>
   </si>
   <si>
-    <t>Rizespor</t>
-  </si>
-  <si>
-    <t>Manisa FK</t>
-  </si>
-  <si>
-    <t>Malmo FF</t>
-  </si>
-  <si>
-    <t>Getafe</t>
-  </si>
-  <si>
-    <t>Kalmar FF</t>
-  </si>
-  <si>
-    <t>Hapoel Tel Aviv</t>
-  </si>
-  <si>
-    <t>Petrojet</t>
-  </si>
-  <si>
-    <t>National Bank</t>
-  </si>
-  <si>
-    <t>Midtjylland</t>
-  </si>
-  <si>
-    <t>Aris FC Limassol</t>
-  </si>
-  <si>
-    <t>Ruch Chorzow</t>
-  </si>
-  <si>
     <t>Orebro</t>
   </si>
   <si>
@@ -508,21 +535,21 @@
     <t>Universitatea Craiova</t>
   </si>
   <si>
+    <t>Jong PSV Eindhoven</t>
+  </si>
+  <si>
+    <t>Jong FC Utrecht</t>
+  </si>
+  <si>
+    <t>Al-Hilal</t>
+  </si>
+  <si>
+    <t>OFK Beograd</t>
+  </si>
+  <si>
     <t>Albion FC</t>
   </si>
   <si>
-    <t>OFK Beograd</t>
-  </si>
-  <si>
-    <t>Jong FC Utrecht</t>
-  </si>
-  <si>
-    <t>Jong PSV Eindhoven</t>
-  </si>
-  <si>
-    <t>Al-Hilal</t>
-  </si>
-  <si>
     <t>Palermo</t>
   </si>
   <si>
@@ -532,12 +559,12 @@
     <t>Sabadell</t>
   </si>
   <si>
+    <t>Udinese</t>
+  </si>
+  <si>
     <t>Nantes</t>
   </si>
   <si>
-    <t>Udinese</t>
-  </si>
-  <si>
     <t>HFX Wanderers</t>
   </si>
   <si>
@@ -553,6 +580,30 @@
     <t>Elche</t>
   </si>
   <si>
+    <t>Paysandu</t>
+  </si>
+  <si>
+    <t>Cerro Porteno</t>
+  </si>
+  <si>
+    <t>Barracas Central</t>
+  </si>
+  <si>
+    <t>Plaza Colonia</t>
+  </si>
+  <si>
+    <t>Carabobo FC</t>
+  </si>
+  <si>
+    <t>Deportes Limache</t>
+  </si>
+  <si>
+    <t>EC Vitoria Salvador</t>
+  </si>
+  <si>
+    <t>Universidad de Venezuela</t>
+  </si>
+  <si>
     <t>Blooming Santa Cruz</t>
   </si>
   <si>
@@ -580,60 +631,60 @@
     <t>Panevezys</t>
   </si>
   <si>
+    <t>Olympiakos Nicosia FC</t>
+  </si>
+  <si>
+    <t>BFC Daugavpils</t>
+  </si>
+  <si>
     <t>Liepajas Metalurgs</t>
   </si>
   <si>
-    <t>Olympiakos Nicosia FC</t>
-  </si>
-  <si>
-    <t>BFC Daugavpils</t>
-  </si>
-  <si>
     <t>Lecce</t>
   </si>
   <si>
     <t>Hapoel Haifa</t>
   </si>
   <si>
+    <t>Omonia</t>
+  </si>
+  <si>
+    <t>FC Nordsjaelland</t>
+  </si>
+  <si>
+    <t>Ghazl El Mahallah</t>
+  </si>
+  <si>
+    <t>Al-Masry</t>
+  </si>
+  <si>
+    <t>Hapoel Ramat Gan</t>
+  </si>
+  <si>
+    <t>Unia Skierniewice</t>
+  </si>
+  <si>
+    <t>Celta Vigo</t>
+  </si>
+  <si>
     <t>IFK Goteborg</t>
   </si>
   <si>
+    <t>AIK</t>
+  </si>
+  <si>
+    <t>Djurgardens</t>
+  </si>
+  <si>
+    <t>Bursaspor</t>
+  </si>
+  <si>
+    <t>Alanyaspor</t>
+  </si>
+  <si>
     <t>Gaziantep FK</t>
   </si>
   <si>
-    <t>Alanyaspor</t>
-  </si>
-  <si>
-    <t>Bursaspor</t>
-  </si>
-  <si>
-    <t>AIK</t>
-  </si>
-  <si>
-    <t>Celta Vigo</t>
-  </si>
-  <si>
-    <t>Djurgardens</t>
-  </si>
-  <si>
-    <t>Hapoel Ramat Gan</t>
-  </si>
-  <si>
-    <t>Al-Masry</t>
-  </si>
-  <si>
-    <t>Ghazl El Mahallah</t>
-  </si>
-  <si>
-    <t>FC Nordsjaelland</t>
-  </si>
-  <si>
-    <t>Omonia</t>
-  </si>
-  <si>
-    <t>Unia Skierniewice</t>
-  </si>
-  <si>
     <t>Ostersunds FK</t>
   </si>
   <si>
@@ -649,21 +700,21 @@
     <t>Universitatea Cluj</t>
   </si>
   <si>
+    <t>Den Bosch</t>
+  </si>
+  <si>
+    <t>FC Eindhoven</t>
+  </si>
+  <si>
+    <t>NEOM Sports Club</t>
+  </si>
+  <si>
+    <t>FK IMT Novi Beograd</t>
+  </si>
+  <si>
     <t>Progreso</t>
   </si>
   <si>
-    <t>FK IMT Novi Beograd</t>
-  </si>
-  <si>
-    <t>FC Eindhoven</t>
-  </si>
-  <si>
-    <t>Den Bosch</t>
-  </si>
-  <si>
-    <t>NEOM Sports Club</t>
-  </si>
-  <si>
     <t>Sampdoria</t>
   </si>
   <si>
@@ -673,12 +724,12 @@
     <t>Cordoba</t>
   </si>
   <si>
+    <t>Lazio</t>
+  </si>
+  <si>
     <t>Nancy</t>
   </si>
   <si>
-    <t>Lazio</t>
-  </si>
-  <si>
     <t>Cavalry</t>
   </si>
   <si>
@@ -694,7 +745,31 @@
     <t>Real Sociedad</t>
   </si>
   <si>
-    <t>2026-09-05 23:34:48</t>
+    <t>Brusque FC</t>
+  </si>
+  <si>
+    <t>Nacional (Par)</t>
+  </si>
+  <si>
+    <t>Argentinos Juniors</t>
+  </si>
+  <si>
+    <t>Uruguay Montevideo FC</t>
+  </si>
+  <si>
+    <t>Estudiantes de Merida</t>
+  </si>
+  <si>
+    <t>Cobresal</t>
+  </si>
+  <si>
+    <t>Gremio</t>
+  </si>
+  <si>
+    <t>Puerto Cabello</t>
+  </si>
+  <si>
+    <t>2026-09-06 01:56:42</t>
   </si>
 </sst>
 </file>
@@ -1026,7 +1101,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB48"/>
+  <dimension ref="A1:CB56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1276,178 +1351,178 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C2" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D2" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="E2" t="s">
-        <v>179</v>
+        <v>196</v>
       </c>
       <c r="F2">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="G2">
         <v>1.75</v>
       </c>
       <c r="H2">
+        <v>4.8</v>
+      </c>
+      <c r="I2">
+        <v>6.4</v>
+      </c>
+      <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2">
         <v>5</v>
       </c>
-      <c r="I2">
-        <v>6.2</v>
-      </c>
-      <c r="J2">
-        <v>4.1</v>
-      </c>
-      <c r="K2">
-        <v>4.7</v>
-      </c>
       <c r="L2">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M2">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N2">
         <v>4.7</v>
       </c>
       <c r="O2">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="P2">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="Q2">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="R2">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="S2">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="T2">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="U2">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="V2">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W2">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="X2">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y2">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="Z2">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB2">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="AC2">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD2">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AE2">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AF2">
-        <v>17</v>
+        <v>12.5</v>
       </c>
       <c r="AG2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AH2">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="AI2">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AJ2">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AK2">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="AL2">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN2">
         <v>10.5</v>
       </c>
       <c r="AO2">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AP2">
         <v>1.01</v>
       </c>
       <c r="AQ2">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AR2">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS2">
-        <v>75</v>
+        <v>1.01</v>
       </c>
       <c r="AT2">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AU2">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV2">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AW2">
-        <v>38</v>
+        <v>1.72</v>
       </c>
       <c r="AX2">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AY2">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA2">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BB2">
         <v>1.04</v>
       </c>
       <c r="BC2">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BD2">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE2">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BF2">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG2">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1510,7 +1585,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1518,58 +1593,58 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C3" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D3" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="E3" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="F3">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="G3">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="H3">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="J3">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="K3">
-        <v>5.7</v>
+        <v>3.6</v>
       </c>
       <c r="L3">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="M3">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="N3">
-        <v>2.52</v>
+        <v>3.1</v>
       </c>
       <c r="O3">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="P3">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="Q3">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="R3">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="S3">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="T3">
         <v>1.92</v>
@@ -1578,16 +1653,16 @@
         <v>1.76</v>
       </c>
       <c r="V3">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W3">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="X3">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="Y3">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="Z3">
         <v>36</v>
@@ -1596,10 +1671,10 @@
         <v>900</v>
       </c>
       <c r="AB3">
-        <v>9.4</v>
+        <v>970</v>
       </c>
       <c r="AC3">
-        <v>9.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AD3">
         <v>21</v>
@@ -1608,10 +1683,10 @@
         <v>900</v>
       </c>
       <c r="AF3">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AG3">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AH3">
         <v>26</v>
@@ -1638,58 +1713,58 @@
         <v>900</v>
       </c>
       <c r="AP3">
-        <v>7.2</v>
+        <v>1.31</v>
       </c>
       <c r="AQ3">
-        <v>7.2</v>
+        <v>1.82</v>
       </c>
       <c r="AR3">
-        <v>12.5</v>
+        <v>1.85</v>
       </c>
       <c r="AS3">
-        <v>14</v>
+        <v>1.31</v>
       </c>
       <c r="AT3">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="AU3">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AV3">
         <v>9.4</v>
       </c>
       <c r="AW3">
-        <v>11</v>
+        <v>1.31</v>
       </c>
       <c r="AX3">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AY3">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AZ3">
         <v>12.5</v>
       </c>
       <c r="BA3">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BB3">
-        <v>14</v>
+        <v>1.26</v>
       </c>
       <c r="BC3">
-        <v>14</v>
+        <v>1.85</v>
       </c>
       <c r="BD3">
-        <v>21</v>
+        <v>1.28</v>
       </c>
       <c r="BE3">
-        <v>17</v>
+        <v>1.31</v>
       </c>
       <c r="BF3">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="BG3">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1752,7 +1827,7 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1760,58 +1835,58 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C4" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D4" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="E4" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="F4">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="G4">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="H4">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="I4">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="J4">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K4">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L4">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="M4">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="N4">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="O4">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="P4">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="Q4">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="R4">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="S4">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="T4">
         <v>1.92</v>
@@ -1820,16 +1895,16 @@
         <v>1.01</v>
       </c>
       <c r="V4">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W4">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="X4">
         <v>1000</v>
       </c>
       <c r="Y4">
-        <v>940</v>
+        <v>850</v>
       </c>
       <c r="Z4">
         <v>1000</v>
@@ -1838,10 +1913,10 @@
         <v>1000</v>
       </c>
       <c r="AB4">
-        <v>960</v>
+        <v>970</v>
       </c>
       <c r="AC4">
-        <v>920</v>
+        <v>970</v>
       </c>
       <c r="AD4">
         <v>1000</v>
@@ -1862,7 +1937,7 @@
         <v>1000</v>
       </c>
       <c r="AJ4">
-        <v>930</v>
+        <v>860</v>
       </c>
       <c r="AK4">
         <v>1000</v>
@@ -1904,7 +1979,7 @@
         <v>1.01</v>
       </c>
       <c r="AX4">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY4">
         <v>1.01</v>
@@ -1916,7 +1991,7 @@
         <v>1.01</v>
       </c>
       <c r="BB4">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC4">
         <v>1.01</v>
@@ -1994,7 +2069,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -2002,178 +2077,178 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C5" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D5" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="E5" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="F5">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="G5">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="H5">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="I5">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="J5">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K5">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="L5">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="M5">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N5">
         <v>2.84</v>
       </c>
       <c r="O5">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="P5">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="Q5">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="R5">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="S5">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="T5">
+        <v>2.16</v>
+      </c>
+      <c r="U5">
+        <v>1.6</v>
+      </c>
+      <c r="V5">
+        <v>1.23</v>
+      </c>
+      <c r="W5">
         <v>2.06</v>
       </c>
-      <c r="U5">
-        <v>1.01</v>
-      </c>
-      <c r="V5">
-        <v>1.21</v>
-      </c>
-      <c r="W5">
-        <v>2.04</v>
-      </c>
       <c r="X5">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="Y5">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="Z5">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AA5">
-        <v>910</v>
+        <v>880</v>
       </c>
       <c r="AB5">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AC5">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD5">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AE5">
-        <v>910</v>
+        <v>880</v>
       </c>
       <c r="AF5">
+        <v>11</v>
+      </c>
+      <c r="AG5">
         <v>11.5</v>
       </c>
-      <c r="AG5">
-        <v>13</v>
-      </c>
       <c r="AH5">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AI5">
-        <v>910</v>
+        <v>880</v>
       </c>
       <c r="AJ5">
         <v>26</v>
       </c>
       <c r="AK5">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AL5">
         <v>70</v>
       </c>
       <c r="AM5">
-        <v>910</v>
+        <v>880</v>
       </c>
       <c r="AN5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO5">
-        <v>910</v>
+        <v>880</v>
       </c>
       <c r="AP5">
-        <v>2.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ5">
-        <v>2.68</v>
+        <v>5.4</v>
       </c>
       <c r="AR5">
-        <v>2.54</v>
+        <v>32</v>
       </c>
       <c r="AS5">
-        <v>2.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT5">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU5">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV5">
-        <v>2.44</v>
+        <v>18</v>
       </c>
       <c r="AW5">
-        <v>2.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX5">
-        <v>2.16</v>
+        <v>8.6</v>
       </c>
       <c r="AY5">
-        <v>2.22</v>
+        <v>9.4</v>
       </c>
       <c r="AZ5">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BA5">
-        <v>2.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB5">
-        <v>2.42</v>
+        <v>18.5</v>
       </c>
       <c r="BC5">
-        <v>2.22</v>
+        <v>21</v>
       </c>
       <c r="BD5">
-        <v>2.32</v>
+        <v>7.8</v>
       </c>
       <c r="BE5">
-        <v>2.4</v>
+        <v>8</v>
       </c>
       <c r="BF5">
-        <v>2.4</v>
+        <v>15</v>
       </c>
       <c r="BG5">
-        <v>2.22</v>
+        <v>7.8</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -2236,7 +2311,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2244,16 +2319,16 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C6" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D6" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="E6" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="F6">
         <v>3.05</v>
@@ -2478,7 +2553,7 @@
         <v>1.29</v>
       </c>
       <c r="CB6" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2486,16 +2561,16 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C7" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D7" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="E7" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="F7">
         <v>3.1</v>
@@ -2537,7 +2612,7 @@
         <v>1.18</v>
       </c>
       <c r="S7">
-        <v>2.42</v>
+        <v>4.6</v>
       </c>
       <c r="T7">
         <v>1.01</v>
@@ -2552,7 +2627,7 @@
         <v>1.4</v>
       </c>
       <c r="X7">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y7">
         <v>1000</v>
@@ -2609,55 +2684,55 @@
         <v>1.01</v>
       </c>
       <c r="AQ7">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AR7">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AS7">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AT7">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AU7">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AV7">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AW7">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AX7">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AY7">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AZ7">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BA7">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BB7">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BC7">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BD7">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BE7">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BF7">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BG7">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2720,7 +2795,7 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2728,31 +2803,31 @@
         <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C8" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D8" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="E8" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="F8">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="G8">
         <v>1.98</v>
       </c>
       <c r="H8">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="I8">
-        <v>110</v>
+        <v>5.6</v>
       </c>
       <c r="J8">
-        <v>2.06</v>
+        <v>3.15</v>
       </c>
       <c r="K8">
         <v>320</v>
@@ -2764,13 +2839,13 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="O8">
         <v>1.4</v>
       </c>
       <c r="P8">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="Q8">
         <v>2.22</v>
@@ -2848,52 +2923,52 @@
         <v>1000</v>
       </c>
       <c r="AP8">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AR8">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AS8">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AT8">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU8">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV8">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW8">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AX8">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AY8">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BA8">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BB8">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC8">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD8">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BE8">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF8">
         <v>1.01</v>
@@ -2962,7 +3037,7 @@
         <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2970,31 +3045,31 @@
         <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C9" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="D9" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="E9" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="F9">
-        <v>2.24</v>
+        <v>2.02</v>
       </c>
       <c r="G9">
-        <v>110</v>
+        <v>2.8</v>
       </c>
       <c r="H9">
-        <v>1.1</v>
+        <v>2.68</v>
       </c>
       <c r="I9">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="J9">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K9">
         <v>7.4</v>
@@ -3018,7 +3093,7 @@
         <v>1.68</v>
       </c>
       <c r="R9">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="S9">
         <v>2.64</v>
@@ -3030,10 +3105,10 @@
         <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W9">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -3204,7 +3279,7 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3212,16 +3287,16 @@
         <v>87</v>
       </c>
       <c r="B10" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C10" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D10" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="E10" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="F10">
         <v>2.5</v>
@@ -3446,7 +3521,7 @@
         <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3454,34 +3529,34 @@
         <v>88</v>
       </c>
       <c r="B11" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C11" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D11" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="E11" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="F11">
-        <v>1.08</v>
+        <v>1.31</v>
       </c>
       <c r="G11">
-        <v>110</v>
+        <v>1.49</v>
       </c>
       <c r="H11">
-        <v>1.08</v>
+        <v>6.6</v>
       </c>
       <c r="I11">
-        <v>110</v>
+        <v>250</v>
       </c>
       <c r="J11">
-        <v>1.08</v>
+        <v>4.3</v>
       </c>
       <c r="K11">
-        <v>270</v>
+        <v>12</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3490,22 +3565,22 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="O11">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="P11">
-        <v>1.09</v>
+        <v>2.12</v>
       </c>
       <c r="Q11">
-        <v>1.11</v>
+        <v>1.52</v>
       </c>
       <c r="R11">
-        <v>1.09</v>
+        <v>1.42</v>
       </c>
       <c r="S11">
-        <v>1.12</v>
+        <v>2.4</v>
       </c>
       <c r="T11">
         <v>1.01</v>
@@ -3514,10 +3589,10 @@
         <v>1.01</v>
       </c>
       <c r="V11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W11">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3688,7 +3763,7 @@
         <v>1.01</v>
       </c>
       <c r="CB11" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3696,34 +3771,34 @@
         <v>89</v>
       </c>
       <c r="B12" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C12" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D12" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="E12" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="F12">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="G12">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="H12">
-        <v>7.6</v>
+        <v>4.1</v>
       </c>
       <c r="I12">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="J12">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="K12">
-        <v>5.6</v>
+        <v>320</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3732,22 +3807,22 @@
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>2.44</v>
+        <v>1.26</v>
       </c>
       <c r="O12">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="P12">
-        <v>2.12</v>
+        <v>1.25</v>
       </c>
       <c r="Q12">
-        <v>1.52</v>
+        <v>1.09</v>
       </c>
       <c r="R12">
-        <v>1.42</v>
+        <v>1.07</v>
       </c>
       <c r="S12">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="T12">
         <v>1.01</v>
@@ -3756,10 +3831,10 @@
         <v>1.01</v>
       </c>
       <c r="V12">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="W12">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3930,42 +4005,42 @@
         <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B13" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C13" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D13" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="E13" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="F13">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="G13">
-        <v>1.34</v>
+        <v>110</v>
       </c>
       <c r="H13">
-        <v>4</v>
+        <v>1.08</v>
       </c>
       <c r="I13">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J13">
-        <v>5.5</v>
+        <v>1.1</v>
       </c>
       <c r="K13">
-        <v>320</v>
+        <v>270</v>
       </c>
       <c r="L13">
         <v>1.01</v>
@@ -3974,22 +4049,22 @@
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="O13">
+        <v>1.11</v>
+      </c>
+      <c r="P13">
         <v>1.09</v>
       </c>
-      <c r="P13">
-        <v>1.25</v>
-      </c>
       <c r="Q13">
+        <v>1.11</v>
+      </c>
+      <c r="R13">
         <v>1.09</v>
       </c>
-      <c r="R13">
-        <v>1.07</v>
-      </c>
       <c r="S13">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="T13">
         <v>1.01</v>
@@ -3998,10 +4073,10 @@
         <v>1.01</v>
       </c>
       <c r="V13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W13">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -4172,7 +4247,7 @@
         <v>1.01</v>
       </c>
       <c r="CB13" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4180,28 +4255,28 @@
         <v>90</v>
       </c>
       <c r="B14" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C14" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D14" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="E14" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
       <c r="F14">
         <v>2.1</v>
       </c>
       <c r="G14">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H14">
         <v>4.4</v>
       </c>
       <c r="I14">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J14">
         <v>3.3</v>
@@ -4210,7 +4285,7 @@
         <v>3.35</v>
       </c>
       <c r="L14">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="M14">
         <v>1.11</v>
@@ -4225,7 +4300,7 @@
         <v>1.64</v>
       </c>
       <c r="Q14">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="R14">
         <v>1.23</v>
@@ -4297,7 +4372,7 @@
         <v>23</v>
       </c>
       <c r="AO14">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP14">
         <v>8.800000000000001</v>
@@ -4369,7 +4444,7 @@
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BN14">
         <v>1000</v>
@@ -4387,7 +4462,7 @@
         <v>1000</v>
       </c>
       <c r="BS14">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="BT14">
         <v>1000</v>
@@ -4399,13 +4474,13 @@
         <v>1000</v>
       </c>
       <c r="BW14">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="BZ14">
         <v>0</v>
@@ -4414,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4422,16 +4497,16 @@
         <v>91</v>
       </c>
       <c r="B15" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C15" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D15" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="E15" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="F15">
         <v>1.94</v>
@@ -4458,10 +4533,10 @@
         <v>1.01</v>
       </c>
       <c r="N15">
-        <v>2.7</v>
+        <v>4.6</v>
       </c>
       <c r="O15">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="P15">
         <v>2.16</v>
@@ -4656,78 +4731,78 @@
         <v>1.01</v>
       </c>
       <c r="CB15" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B16" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C16" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D16" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="E16" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="F16">
-        <v>2.42</v>
+        <v>3</v>
       </c>
       <c r="G16">
-        <v>2.54</v>
+        <v>3.9</v>
       </c>
       <c r="H16">
-        <v>2.94</v>
+        <v>2</v>
       </c>
       <c r="I16">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="J16">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="K16">
-        <v>3.9</v>
+        <v>5.9</v>
       </c>
       <c r="L16">
         <v>1.01</v>
       </c>
       <c r="M16">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N16">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="O16">
         <v>1.21</v>
       </c>
       <c r="P16">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="Q16">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="R16">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="S16">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="T16">
         <v>1.01</v>
       </c>
       <c r="U16">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="V16">
-        <v>1.48</v>
+        <v>1.78</v>
       </c>
       <c r="W16">
-        <v>1.65</v>
+        <v>1.36</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -4832,10 +4907,10 @@
         <v>1.01</v>
       </c>
       <c r="BF16">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="BG16">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -4898,186 +4973,186 @@
         <v>1.01</v>
       </c>
       <c r="CB16" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B17" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C17" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D17" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="E17" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="F17">
+        <v>2.06</v>
+      </c>
+      <c r="G17">
+        <v>2.08</v>
+      </c>
+      <c r="H17">
+        <v>3.6</v>
+      </c>
+      <c r="I17">
+        <v>3.65</v>
+      </c>
+      <c r="J17">
+        <v>4</v>
+      </c>
+      <c r="K17">
+        <v>4.2</v>
+      </c>
+      <c r="L17">
+        <v>1.01</v>
+      </c>
+      <c r="M17">
+        <v>1.03</v>
+      </c>
+      <c r="N17">
+        <v>4.9</v>
+      </c>
+      <c r="O17">
+        <v>1.22</v>
+      </c>
+      <c r="P17">
+        <v>2.36</v>
+      </c>
+      <c r="Q17">
+        <v>1.65</v>
+      </c>
+      <c r="R17">
+        <v>1.55</v>
+      </c>
+      <c r="S17">
+        <v>2.62</v>
+      </c>
+      <c r="T17">
+        <v>1.51</v>
+      </c>
+      <c r="U17">
+        <v>2.42</v>
+      </c>
+      <c r="V17">
+        <v>1.37</v>
+      </c>
+      <c r="W17">
         <v>1.92</v>
       </c>
-      <c r="G17">
-        <v>1.99</v>
-      </c>
-      <c r="H17">
+      <c r="X17">
+        <v>26</v>
+      </c>
+      <c r="Y17">
+        <v>22</v>
+      </c>
+      <c r="Z17">
+        <v>36</v>
+      </c>
+      <c r="AA17">
+        <v>75</v>
+      </c>
+      <c r="AB17">
+        <v>15.5</v>
+      </c>
+      <c r="AC17">
+        <v>11.5</v>
+      </c>
+      <c r="AD17">
+        <v>16</v>
+      </c>
+      <c r="AE17">
+        <v>46</v>
+      </c>
+      <c r="AF17">
+        <v>15.5</v>
+      </c>
+      <c r="AG17">
+        <v>13.5</v>
+      </c>
+      <c r="AH17">
+        <v>19.5</v>
+      </c>
+      <c r="AI17">
+        <v>48</v>
+      </c>
+      <c r="AJ17">
+        <v>26</v>
+      </c>
+      <c r="AK17">
+        <v>24</v>
+      </c>
+      <c r="AL17">
+        <v>29</v>
+      </c>
+      <c r="AM17">
+        <v>80</v>
+      </c>
+      <c r="AN17">
+        <v>12.5</v>
+      </c>
+      <c r="AO17">
+        <v>34</v>
+      </c>
+      <c r="AP17">
+        <v>4.3</v>
+      </c>
+      <c r="AQ17">
+        <v>4.2</v>
+      </c>
+      <c r="AR17">
         <v>4.5</v>
       </c>
-      <c r="I17">
+      <c r="AS17">
         <v>4.9</v>
       </c>
-      <c r="J17">
-        <v>3.4</v>
-      </c>
-      <c r="K17">
-        <v>3.95</v>
-      </c>
-      <c r="L17">
-        <v>1.01</v>
-      </c>
-      <c r="M17">
-        <v>1.05</v>
-      </c>
-      <c r="N17">
-        <v>2.34</v>
-      </c>
-      <c r="O17">
-        <v>1.27</v>
-      </c>
-      <c r="P17">
-        <v>2</v>
-      </c>
-      <c r="Q17">
-        <v>1.27</v>
-      </c>
-      <c r="R17">
-        <v>1.38</v>
-      </c>
-      <c r="S17">
-        <v>2.96</v>
-      </c>
-      <c r="T17">
-        <v>1.01</v>
-      </c>
-      <c r="U17">
-        <v>1.01</v>
-      </c>
-      <c r="V17">
-        <v>1.25</v>
-      </c>
-      <c r="W17">
-        <v>2</v>
-      </c>
-      <c r="X17">
-        <v>1000</v>
-      </c>
-      <c r="Y17">
-        <v>1000</v>
-      </c>
-      <c r="Z17">
-        <v>1000</v>
-      </c>
-      <c r="AA17">
-        <v>1000</v>
-      </c>
-      <c r="AB17">
-        <v>1000</v>
-      </c>
-      <c r="AC17">
-        <v>1000</v>
-      </c>
-      <c r="AD17">
-        <v>1000</v>
-      </c>
-      <c r="AE17">
-        <v>1000</v>
-      </c>
-      <c r="AF17">
-        <v>1000</v>
-      </c>
-      <c r="AG17">
-        <v>1000</v>
-      </c>
-      <c r="AH17">
-        <v>1000</v>
-      </c>
-      <c r="AI17">
-        <v>1000</v>
-      </c>
-      <c r="AJ17">
-        <v>1000</v>
-      </c>
-      <c r="AK17">
-        <v>1000</v>
-      </c>
-      <c r="AL17">
-        <v>1000</v>
-      </c>
-      <c r="AM17">
-        <v>1000</v>
-      </c>
-      <c r="AN17">
-        <v>1000</v>
-      </c>
-      <c r="AO17">
-        <v>1000</v>
-      </c>
-      <c r="AP17">
-        <v>1.01</v>
-      </c>
-      <c r="AQ17">
-        <v>1.01</v>
-      </c>
-      <c r="AR17">
-        <v>1.01</v>
-      </c>
-      <c r="AS17">
-        <v>1.01</v>
-      </c>
       <c r="AT17">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AU17">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AV17">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AW17">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AX17">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AY17">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ17">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA17">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB17">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BC17">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD17">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BE17">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF17">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BG17">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -5140,7 +5215,7 @@
         <v>1.01</v>
       </c>
       <c r="CB17" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -5148,178 +5223,178 @@
         <v>93</v>
       </c>
       <c r="B18" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C18" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D18" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="E18" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="F18">
-        <v>1.93</v>
+        <v>1.72</v>
       </c>
       <c r="G18">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="H18">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="I18">
-        <v>4.9</v>
+        <v>8.6</v>
       </c>
       <c r="J18">
-        <v>3.55</v>
+        <v>2.78</v>
       </c>
       <c r="K18">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="L18">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M18">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N18">
-        <v>3.55</v>
+        <v>2.36</v>
       </c>
       <c r="O18">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="P18">
-        <v>1.86</v>
+        <v>1.45</v>
       </c>
       <c r="Q18">
-        <v>2.02</v>
+        <v>2.6</v>
       </c>
       <c r="R18">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="S18">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="T18">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="U18">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="V18">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="W18">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="X18">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Y18">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Z18">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AA18">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB18">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC18">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD18">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AE18">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF18">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AG18">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH18">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI18">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AJ18">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AK18">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL18">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM18">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN18">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AO18">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AP18">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR18">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS18">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT18">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU18">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV18">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AW18">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AX18">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AY18">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BA18">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BB18">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BC18">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BD18">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BE18">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF18">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG18">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH18">
         <v>1000</v>
@@ -5382,66 +5457,66 @@
         <v>1.01</v>
       </c>
       <c r="CB18" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="B19" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C19" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D19" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="E19" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="F19">
         <v>3.85</v>
       </c>
       <c r="G19">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="H19">
-        <v>1.67</v>
+        <v>2.12</v>
       </c>
       <c r="I19">
-        <v>1.96</v>
+        <v>2.34</v>
       </c>
       <c r="J19">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="K19">
-        <v>7.2</v>
+        <v>3.75</v>
       </c>
       <c r="L19">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M19">
         <v>1.01</v>
       </c>
       <c r="N19">
-        <v>2.42</v>
+        <v>2.96</v>
       </c>
       <c r="O19">
-        <v>1.21</v>
+        <v>1.02</v>
       </c>
       <c r="P19">
-        <v>2.06</v>
+        <v>1.58</v>
       </c>
       <c r="Q19">
-        <v>1.57</v>
+        <v>2.12</v>
       </c>
       <c r="R19">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="S19">
-        <v>2.36</v>
+        <v>3.45</v>
       </c>
       <c r="T19">
         <v>1.01</v>
@@ -5450,10 +5525,10 @@
         <v>1.01</v>
       </c>
       <c r="V19">
-        <v>2.04</v>
+        <v>1.74</v>
       </c>
       <c r="W19">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="X19">
         <v>1000</v>
@@ -5624,186 +5699,186 @@
         <v>1.01</v>
       </c>
       <c r="CB19" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B20" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C20" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D20" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="E20" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="F20">
-        <v>1.8</v>
+        <v>1.42</v>
       </c>
       <c r="G20">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="H20">
+        <v>7.8</v>
+      </c>
+      <c r="I20">
+        <v>11.5</v>
+      </c>
+      <c r="J20">
         <v>4.4</v>
       </c>
-      <c r="I20">
-        <v>4.6</v>
-      </c>
-      <c r="J20">
-        <v>4.3</v>
-      </c>
       <c r="K20">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="L20">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M20">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N20">
-        <v>5.8</v>
+        <v>4</v>
       </c>
       <c r="O20">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="P20">
-        <v>2.62</v>
+        <v>2.04</v>
       </c>
       <c r="Q20">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="R20">
-        <v>1.66</v>
+        <v>1.41</v>
       </c>
       <c r="S20">
-        <v>2.38</v>
+        <v>2.92</v>
       </c>
       <c r="T20">
-        <v>1.59</v>
+        <v>1.96</v>
       </c>
       <c r="U20">
-        <v>2.54</v>
+        <v>1.84</v>
       </c>
       <c r="V20">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="W20">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="X20">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="Y20">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="Z20">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="AA20">
-        <v>110</v>
+        <v>350</v>
       </c>
       <c r="AB20">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AC20">
+        <v>13.5</v>
+      </c>
+      <c r="AD20">
+        <v>38</v>
+      </c>
+      <c r="AE20">
+        <v>170</v>
+      </c>
+      <c r="AF20">
         <v>10.5</v>
       </c>
-      <c r="AD20">
-        <v>20</v>
-      </c>
-      <c r="AE20">
+      <c r="AG20">
+        <v>12.5</v>
+      </c>
+      <c r="AH20">
+        <v>32</v>
+      </c>
+      <c r="AI20">
+        <v>140</v>
+      </c>
+      <c r="AJ20">
+        <v>15.5</v>
+      </c>
+      <c r="AK20">
+        <v>19.5</v>
+      </c>
+      <c r="AL20">
+        <v>46</v>
+      </c>
+      <c r="AM20">
+        <v>180</v>
+      </c>
+      <c r="AN20">
+        <v>8.6</v>
+      </c>
+      <c r="AO20">
+        <v>220</v>
+      </c>
+      <c r="AP20">
+        <v>13</v>
+      </c>
+      <c r="AQ20">
+        <v>19.5</v>
+      </c>
+      <c r="AR20">
         <v>50</v>
       </c>
-      <c r="AF20">
-        <v>14</v>
-      </c>
-      <c r="AG20">
+      <c r="AS20">
+        <v>200</v>
+      </c>
+      <c r="AT20">
+        <v>6.2</v>
+      </c>
+      <c r="AU20">
+        <v>8</v>
+      </c>
+      <c r="AV20">
+        <v>22</v>
+      </c>
+      <c r="AW20">
+        <v>95</v>
+      </c>
+      <c r="AX20">
+        <v>6.4</v>
+      </c>
+      <c r="AY20">
+        <v>7.4</v>
+      </c>
+      <c r="AZ20">
+        <v>18</v>
+      </c>
+      <c r="BA20">
+        <v>80</v>
+      </c>
+      <c r="BB20">
+        <v>9.4</v>
+      </c>
+      <c r="BC20">
         <v>11.5</v>
       </c>
-      <c r="AH20">
-        <v>16</v>
-      </c>
-      <c r="AI20">
-        <v>46</v>
-      </c>
-      <c r="AJ20">
-        <v>20</v>
-      </c>
-      <c r="AK20">
-        <v>18.5</v>
-      </c>
-      <c r="AL20">
-        <v>26</v>
-      </c>
-      <c r="AM20">
-        <v>65</v>
-      </c>
-      <c r="AN20">
-        <v>7.6</v>
-      </c>
-      <c r="AO20">
-        <v>34</v>
-      </c>
-      <c r="AP20">
-        <v>7.4</v>
-      </c>
-      <c r="AQ20">
-        <v>21</v>
-      </c>
-      <c r="AR20">
-        <v>34</v>
-      </c>
-      <c r="AS20">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT20">
-        <v>12</v>
-      </c>
-      <c r="AU20">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV20">
-        <v>16.5</v>
-      </c>
-      <c r="AW20">
-        <v>40</v>
-      </c>
-      <c r="AX20">
-        <v>12.5</v>
-      </c>
-      <c r="AY20">
-        <v>9.6</v>
-      </c>
-      <c r="AZ20">
-        <v>14</v>
-      </c>
-      <c r="BA20">
-        <v>38</v>
-      </c>
-      <c r="BB20">
-        <v>18.5</v>
-      </c>
-      <c r="BC20">
-        <v>15</v>
-      </c>
       <c r="BD20">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="BE20">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="BF20">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="BG20">
-        <v>28</v>
+        <v>120</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5866,7 +5941,7 @@
         <v>1.01</v>
       </c>
       <c r="CB20" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5874,662 +5949,662 @@
         <v>94</v>
       </c>
       <c r="B21" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C21" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D21" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="E21" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="F21">
-        <v>2.54</v>
+        <v>1.72</v>
       </c>
       <c r="G21">
-        <v>2.56</v>
+        <v>1.83</v>
       </c>
       <c r="H21">
-        <v>3.65</v>
+        <v>4.7</v>
       </c>
       <c r="I21">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="J21">
-        <v>2.98</v>
+        <v>3.9</v>
       </c>
       <c r="K21">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="L21">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="M21">
-        <v>1.16</v>
+        <v>1.05</v>
       </c>
       <c r="N21">
-        <v>2.38</v>
+        <v>4.2</v>
       </c>
       <c r="O21">
-        <v>1.69</v>
+        <v>1.25</v>
       </c>
       <c r="P21">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="Q21">
-        <v>3.15</v>
+        <v>1.74</v>
       </c>
       <c r="R21">
-        <v>1.15</v>
+        <v>1.43</v>
       </c>
       <c r="S21">
-        <v>7.2</v>
+        <v>2.88</v>
       </c>
       <c r="T21">
-        <v>2.4</v>
+        <v>1.74</v>
       </c>
       <c r="U21">
-        <v>1.68</v>
+        <v>2.14</v>
       </c>
       <c r="V21">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="W21">
-        <v>1.64</v>
+        <v>2.2</v>
       </c>
       <c r="X21">
+        <v>22</v>
+      </c>
+      <c r="Y21">
+        <v>24</v>
+      </c>
+      <c r="Z21">
+        <v>48</v>
+      </c>
+      <c r="AA21">
+        <v>140</v>
+      </c>
+      <c r="AB21">
+        <v>12</v>
+      </c>
+      <c r="AC21">
+        <v>11.5</v>
+      </c>
+      <c r="AD21">
+        <v>24</v>
+      </c>
+      <c r="AE21">
+        <v>65</v>
+      </c>
+      <c r="AF21">
+        <v>14</v>
+      </c>
+      <c r="AG21">
+        <v>12.5</v>
+      </c>
+      <c r="AH21">
+        <v>23</v>
+      </c>
+      <c r="AI21">
+        <v>65</v>
+      </c>
+      <c r="AJ21">
+        <v>22</v>
+      </c>
+      <c r="AK21">
+        <v>22</v>
+      </c>
+      <c r="AL21">
+        <v>40</v>
+      </c>
+      <c r="AM21">
+        <v>110</v>
+      </c>
+      <c r="AN21">
+        <v>11.5</v>
+      </c>
+      <c r="AO21">
+        <v>65</v>
+      </c>
+      <c r="AP21">
+        <v>13</v>
+      </c>
+      <c r="AQ21">
+        <v>14</v>
+      </c>
+      <c r="AR21">
+        <v>28</v>
+      </c>
+      <c r="AS21">
+        <v>75</v>
+      </c>
+      <c r="AT21">
+        <v>7.4</v>
+      </c>
+      <c r="AU21">
         <v>7</v>
       </c>
-      <c r="Y21">
-        <v>9</v>
-      </c>
-      <c r="Z21">
+      <c r="AV21">
+        <v>14</v>
+      </c>
+      <c r="AW21">
+        <v>42</v>
+      </c>
+      <c r="AX21">
+        <v>8.6</v>
+      </c>
+      <c r="AY21">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ21">
+        <v>13.5</v>
+      </c>
+      <c r="BA21">
+        <v>42</v>
+      </c>
+      <c r="BB21">
+        <v>14</v>
+      </c>
+      <c r="BC21">
+        <v>13</v>
+      </c>
+      <c r="BD21">
         <v>23</v>
       </c>
-      <c r="AA21">
-        <v>85</v>
-      </c>
-      <c r="AB21">
-        <v>6.8</v>
-      </c>
-      <c r="AC21">
-        <v>7</v>
-      </c>
-      <c r="AD21">
-        <v>17.5</v>
-      </c>
-      <c r="AE21">
-        <v>70</v>
-      </c>
-      <c r="AF21">
-        <v>13.5</v>
-      </c>
-      <c r="AG21">
-        <v>13.5</v>
-      </c>
-      <c r="AH21">
-        <v>28</v>
-      </c>
-      <c r="AI21">
-        <v>110</v>
-      </c>
-      <c r="AJ21">
-        <v>42</v>
-      </c>
-      <c r="AK21">
-        <v>42</v>
-      </c>
-      <c r="AL21">
-        <v>80</v>
-      </c>
-      <c r="AM21">
-        <v>260</v>
-      </c>
-      <c r="AN21">
-        <v>50</v>
-      </c>
-      <c r="AO21">
-        <v>110</v>
-      </c>
-      <c r="AP21">
-        <v>6.6</v>
-      </c>
-      <c r="AQ21">
-        <v>8.4</v>
-      </c>
-      <c r="AR21">
-        <v>21</v>
-      </c>
-      <c r="AS21">
-        <v>34</v>
-      </c>
-      <c r="AT21">
-        <v>6.4</v>
-      </c>
-      <c r="AU21">
-        <v>6.6</v>
-      </c>
-      <c r="AV21">
-        <v>16</v>
-      </c>
-      <c r="AW21">
+      <c r="BE21">
         <v>60</v>
       </c>
-      <c r="AX21">
-        <v>12.5</v>
-      </c>
-      <c r="AY21">
-        <v>12.5</v>
-      </c>
-      <c r="AZ21">
-        <v>26</v>
-      </c>
-      <c r="BA21">
-        <v>40</v>
-      </c>
-      <c r="BB21">
-        <v>34</v>
-      </c>
-      <c r="BC21">
-        <v>24</v>
-      </c>
-      <c r="BD21">
-        <v>36</v>
-      </c>
-      <c r="BE21">
-        <v>50</v>
-      </c>
       <c r="BF21">
+        <v>7.4</v>
+      </c>
+      <c r="BG21">
         <v>44</v>
       </c>
-      <c r="BG21">
-        <v>38</v>
-      </c>
       <c r="BH21">
         <v>1000</v>
       </c>
       <c r="BI21">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="BJ21">
         <v>1000</v>
       </c>
       <c r="BK21">
-        <v>2.94</v>
+        <v>1.01</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="BN21">
         <v>1000</v>
       </c>
       <c r="BO21">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="BP21">
         <v>1000</v>
       </c>
       <c r="BQ21">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="BR21">
         <v>1000</v>
       </c>
       <c r="BS21">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="BT21">
         <v>1000</v>
       </c>
       <c r="BU21">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="BV21">
         <v>1000</v>
       </c>
       <c r="BW21">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="BX21">
         <v>1000</v>
       </c>
       <c r="BY21">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="BZ21">
         <v>1000</v>
       </c>
       <c r="CA21">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="CB21" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
     </row>
     <row r="22" spans="1:80">
       <c r="A22" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B22" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C22" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D22" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="E22" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="F22">
-        <v>4.5</v>
+        <v>2.54</v>
       </c>
       <c r="G22">
-        <v>4.7</v>
+        <v>2.56</v>
       </c>
       <c r="H22">
-        <v>1.84</v>
+        <v>3.7</v>
       </c>
       <c r="I22">
-        <v>1.87</v>
+        <v>3.75</v>
       </c>
       <c r="J22">
-        <v>4.1</v>
+        <v>2.94</v>
       </c>
       <c r="K22">
-        <v>4.2</v>
+        <v>2.96</v>
       </c>
       <c r="L22">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="M22">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="N22">
-        <v>4.6</v>
+        <v>2.4</v>
       </c>
       <c r="O22">
-        <v>1.24</v>
+        <v>1.69</v>
       </c>
       <c r="P22">
-        <v>2.2</v>
+        <v>1.44</v>
       </c>
       <c r="Q22">
-        <v>1.7</v>
+        <v>3.15</v>
       </c>
       <c r="R22">
-        <v>1.48</v>
+        <v>1.15</v>
       </c>
       <c r="S22">
-        <v>2.72</v>
+        <v>7.2</v>
       </c>
       <c r="T22">
-        <v>1.61</v>
+        <v>2.4</v>
       </c>
       <c r="U22">
-        <v>2.28</v>
+        <v>1.68</v>
       </c>
       <c r="V22">
-        <v>2.14</v>
+        <v>1.36</v>
       </c>
       <c r="W22">
-        <v>1.27</v>
+        <v>1.64</v>
       </c>
       <c r="X22">
+        <v>7</v>
+      </c>
+      <c r="Y22">
+        <v>9</v>
+      </c>
+      <c r="Z22">
         <v>23</v>
       </c>
-      <c r="Y22">
+      <c r="AA22">
+        <v>85</v>
+      </c>
+      <c r="AB22">
+        <v>6.8</v>
+      </c>
+      <c r="AC22">
+        <v>7</v>
+      </c>
+      <c r="AD22">
+        <v>17.5</v>
+      </c>
+      <c r="AE22">
+        <v>70</v>
+      </c>
+      <c r="AF22">
+        <v>14</v>
+      </c>
+      <c r="AG22">
+        <v>13.5</v>
+      </c>
+      <c r="AH22">
+        <v>28</v>
+      </c>
+      <c r="AI22">
+        <v>110</v>
+      </c>
+      <c r="AJ22">
+        <v>42</v>
+      </c>
+      <c r="AK22">
+        <v>42</v>
+      </c>
+      <c r="AL22">
+        <v>80</v>
+      </c>
+      <c r="AM22">
+        <v>260</v>
+      </c>
+      <c r="AN22">
+        <v>50</v>
+      </c>
+      <c r="AO22">
+        <v>110</v>
+      </c>
+      <c r="AP22">
+        <v>6.6</v>
+      </c>
+      <c r="AQ22">
+        <v>8.4</v>
+      </c>
+      <c r="AR22">
+        <v>21</v>
+      </c>
+      <c r="AS22">
+        <v>34</v>
+      </c>
+      <c r="AT22">
+        <v>6.4</v>
+      </c>
+      <c r="AU22">
+        <v>6.4</v>
+      </c>
+      <c r="AV22">
+        <v>16</v>
+      </c>
+      <c r="AW22">
+        <v>60</v>
+      </c>
+      <c r="AX22">
         <v>12.5</v>
       </c>
-      <c r="Z22">
-        <v>15</v>
-      </c>
-      <c r="AA22">
+      <c r="AY22">
+        <v>12.5</v>
+      </c>
+      <c r="AZ22">
+        <v>26</v>
+      </c>
+      <c r="BA22">
+        <v>40</v>
+      </c>
+      <c r="BB22">
+        <v>34</v>
+      </c>
+      <c r="BC22">
         <v>24</v>
       </c>
-      <c r="AB22">
-        <v>22</v>
-      </c>
-      <c r="AC22">
-        <v>10</v>
-      </c>
-      <c r="AD22">
-        <v>11</v>
-      </c>
-      <c r="AE22">
-        <v>21</v>
-      </c>
-      <c r="AF22">
-        <v>42</v>
-      </c>
-      <c r="AG22">
-        <v>19</v>
-      </c>
-      <c r="AH22">
-        <v>18.5</v>
-      </c>
-      <c r="AI22">
-        <v>32</v>
-      </c>
-      <c r="AJ22">
-        <v>110</v>
-      </c>
-      <c r="AK22">
-        <v>60</v>
-      </c>
-      <c r="AL22">
-        <v>60</v>
-      </c>
-      <c r="AM22">
-        <v>90</v>
-      </c>
-      <c r="AN22">
-        <v>55</v>
-      </c>
-      <c r="AO22">
-        <v>11.5</v>
-      </c>
-      <c r="AP22">
-        <v>17</v>
-      </c>
-      <c r="AQ22">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR22">
-        <v>10.5</v>
-      </c>
-      <c r="AS22">
-        <v>17</v>
-      </c>
-      <c r="AT22">
-        <v>16</v>
-      </c>
-      <c r="AU22">
-        <v>8</v>
-      </c>
-      <c r="AV22">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW22">
-        <v>15.5</v>
-      </c>
-      <c r="AX22">
-        <v>5.3</v>
-      </c>
-      <c r="AY22">
-        <v>15</v>
-      </c>
-      <c r="AZ22">
-        <v>14.5</v>
-      </c>
-      <c r="BA22">
-        <v>5.1</v>
-      </c>
-      <c r="BB22">
-        <v>5.7</v>
-      </c>
-      <c r="BC22">
-        <v>5.5</v>
-      </c>
       <c r="BD22">
-        <v>5.5</v>
+        <v>36</v>
       </c>
       <c r="BE22">
-        <v>5.7</v>
+        <v>50</v>
       </c>
       <c r="BF22">
-        <v>5.4</v>
+        <v>44</v>
       </c>
       <c r="BG22">
-        <v>8.6</v>
+        <v>38</v>
       </c>
       <c r="BH22">
         <v>1000</v>
       </c>
       <c r="BI22">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="BJ22">
         <v>1000</v>
       </c>
       <c r="BK22">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="BN22">
         <v>1000</v>
       </c>
       <c r="BO22">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BP22">
         <v>1000</v>
       </c>
       <c r="BQ22">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="BR22">
         <v>1000</v>
       </c>
       <c r="BS22">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="BT22">
         <v>1000</v>
       </c>
       <c r="BU22">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BV22">
         <v>1000</v>
       </c>
       <c r="BW22">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="BX22">
         <v>1000</v>
       </c>
       <c r="BY22">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="BZ22">
         <v>1000</v>
       </c>
       <c r="CA22">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="CB22" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B23" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C23" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D23" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="E23" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="F23">
-        <v>1.38</v>
+        <v>2.42</v>
       </c>
       <c r="G23">
+        <v>2.54</v>
+      </c>
+      <c r="H23">
+        <v>2.94</v>
+      </c>
+      <c r="I23">
+        <v>3.05</v>
+      </c>
+      <c r="J23">
+        <v>3.75</v>
+      </c>
+      <c r="K23">
+        <v>3.9</v>
+      </c>
+      <c r="L23">
+        <v>1.01</v>
+      </c>
+      <c r="M23">
+        <v>1.05</v>
+      </c>
+      <c r="N23">
+        <v>4.5</v>
+      </c>
+      <c r="O23">
+        <v>1.23</v>
+      </c>
+      <c r="P23">
+        <v>2.2</v>
+      </c>
+      <c r="Q23">
         <v>1.59</v>
       </c>
-      <c r="H23">
-        <v>6</v>
-      </c>
-      <c r="I23">
+      <c r="R23">
+        <v>1.48</v>
+      </c>
+      <c r="S23">
+        <v>2.68</v>
+      </c>
+      <c r="T23">
+        <v>1.5</v>
+      </c>
+      <c r="U23">
+        <v>2.38</v>
+      </c>
+      <c r="V23">
+        <v>1.48</v>
+      </c>
+      <c r="W23">
+        <v>1.65</v>
+      </c>
+      <c r="X23">
+        <v>24</v>
+      </c>
+      <c r="Y23">
+        <v>18.5</v>
+      </c>
+      <c r="Z23">
+        <v>28</v>
+      </c>
+      <c r="AA23">
+        <v>60</v>
+      </c>
+      <c r="AB23">
+        <v>16</v>
+      </c>
+      <c r="AC23">
+        <v>11</v>
+      </c>
+      <c r="AD23">
+        <v>16.5</v>
+      </c>
+      <c r="AE23">
+        <v>38</v>
+      </c>
+      <c r="AF23">
+        <v>22</v>
+      </c>
+      <c r="AG23">
+        <v>14.5</v>
+      </c>
+      <c r="AH23">
         <v>19</v>
       </c>
-      <c r="J23">
-        <v>4.4</v>
-      </c>
-      <c r="K23">
-        <v>10.5</v>
-      </c>
-      <c r="L23">
-        <v>1.27</v>
-      </c>
-      <c r="M23">
-        <v>1.01</v>
-      </c>
-      <c r="N23">
-        <v>2.2</v>
-      </c>
-      <c r="O23">
-        <v>1.24</v>
-      </c>
-      <c r="P23">
-        <v>1.96</v>
-      </c>
-      <c r="Q23">
-        <v>1.64</v>
-      </c>
-      <c r="R23">
-        <v>1.38</v>
-      </c>
-      <c r="S23">
-        <v>2.64</v>
-      </c>
-      <c r="T23">
-        <v>1.01</v>
-      </c>
-      <c r="U23">
-        <v>1.01</v>
-      </c>
-      <c r="V23">
-        <v>1.11</v>
-      </c>
-      <c r="W23">
-        <v>2.68</v>
-      </c>
-      <c r="X23">
-        <v>1000</v>
-      </c>
-      <c r="Y23">
-        <v>1000</v>
-      </c>
-      <c r="Z23">
-        <v>1000</v>
-      </c>
-      <c r="AA23">
-        <v>1000</v>
-      </c>
-      <c r="AB23">
-        <v>1000</v>
-      </c>
-      <c r="AC23">
-        <v>1000</v>
-      </c>
-      <c r="AD23">
-        <v>1000</v>
-      </c>
-      <c r="AE23">
-        <v>1000</v>
-      </c>
-      <c r="AF23">
-        <v>1000</v>
-      </c>
-      <c r="AG23">
-        <v>1000</v>
-      </c>
-      <c r="AH23">
-        <v>1000</v>
-      </c>
       <c r="AI23">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ23">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK23">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL23">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM23">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN23">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AO23">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AP23">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AQ23">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AR23">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AS23">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AT23">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU23">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AV23">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW23">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AX23">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AY23">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ23">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA23">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BB23">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BC23">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BD23">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BE23">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BF23">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG23">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BH23">
         <v>1000</v>
@@ -6592,429 +6667,429 @@
         <v>1.01</v>
       </c>
       <c r="CB23" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
     </row>
     <row r="24" spans="1:80">
       <c r="A24" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B24" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C24" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D24" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="E24" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="F24">
-        <v>3.85</v>
+        <v>1.8</v>
       </c>
       <c r="G24">
+        <v>1.83</v>
+      </c>
+      <c r="H24">
+        <v>4.4</v>
+      </c>
+      <c r="I24">
         <v>4.6</v>
       </c>
-      <c r="H24">
-        <v>2.12</v>
-      </c>
-      <c r="I24">
+      <c r="J24">
+        <v>4.3</v>
+      </c>
+      <c r="K24">
+        <v>4.4</v>
+      </c>
+      <c r="L24">
+        <v>1.01</v>
+      </c>
+      <c r="M24">
+        <v>1.04</v>
+      </c>
+      <c r="N24">
+        <v>5.8</v>
+      </c>
+      <c r="O24">
+        <v>1.19</v>
+      </c>
+      <c r="P24">
+        <v>2.6</v>
+      </c>
+      <c r="Q24">
+        <v>1.56</v>
+      </c>
+      <c r="R24">
+        <v>1.66</v>
+      </c>
+      <c r="S24">
         <v>2.36</v>
       </c>
-      <c r="J24">
-        <v>3</v>
-      </c>
-      <c r="K24">
-        <v>3.75</v>
-      </c>
-      <c r="L24">
-        <v>1.41</v>
-      </c>
-      <c r="M24">
-        <v>1.01</v>
-      </c>
-      <c r="N24">
-        <v>2.96</v>
-      </c>
-      <c r="O24">
-        <v>1.02</v>
-      </c>
-      <c r="P24">
+      <c r="T24">
         <v>1.58</v>
       </c>
-      <c r="Q24">
-        <v>2.12</v>
-      </c>
-      <c r="R24">
-        <v>1.22</v>
-      </c>
-      <c r="S24">
-        <v>3.45</v>
-      </c>
-      <c r="T24">
-        <v>1.01</v>
-      </c>
       <c r="U24">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="V24">
-        <v>1.73</v>
+        <v>1.27</v>
       </c>
       <c r="W24">
-        <v>1.27</v>
+        <v>2.2</v>
       </c>
       <c r="X24">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Y24">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Z24">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA24">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB24">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC24">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD24">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE24">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF24">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG24">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH24">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AI24">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ24">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AK24">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AL24">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AM24">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN24">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AO24">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AP24">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="AQ24">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AR24">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="AS24">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="AT24">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AU24">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV24">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AW24">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="AX24">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AY24">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ24">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BA24">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BB24">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BC24">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BD24">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BE24">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BF24">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BG24">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BH24">
         <v>1000</v>
       </c>
       <c r="BI24">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="BJ24">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK24">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="BN24">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO24">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BP24">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BQ24">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="BR24">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS24">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="BT24">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BU24">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BV24">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW24">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="BX24">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY24">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="BZ24">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="CA24">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="CB24" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B25" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C25" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D25" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="E25" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="F25">
-        <v>1.72</v>
+        <v>4.5</v>
       </c>
       <c r="G25">
-        <v>1.91</v>
+        <v>4.7</v>
       </c>
       <c r="H25">
-        <v>5.6</v>
+        <v>1.84</v>
       </c>
       <c r="I25">
+        <v>1.87</v>
+      </c>
+      <c r="J25">
+        <v>4.1</v>
+      </c>
+      <c r="K25">
+        <v>4.2</v>
+      </c>
+      <c r="L25">
+        <v>1.01</v>
+      </c>
+      <c r="M25">
+        <v>1.05</v>
+      </c>
+      <c r="N25">
+        <v>4.6</v>
+      </c>
+      <c r="O25">
+        <v>1.24</v>
+      </c>
+      <c r="P25">
+        <v>2.2</v>
+      </c>
+      <c r="Q25">
+        <v>1.7</v>
+      </c>
+      <c r="R25">
+        <v>1.47</v>
+      </c>
+      <c r="S25">
+        <v>2.72</v>
+      </c>
+      <c r="T25">
+        <v>1.66</v>
+      </c>
+      <c r="U25">
+        <v>2.26</v>
+      </c>
+      <c r="V25">
+        <v>2.14</v>
+      </c>
+      <c r="W25">
+        <v>1.27</v>
+      </c>
+      <c r="X25">
+        <v>23</v>
+      </c>
+      <c r="Y25">
+        <v>12.5</v>
+      </c>
+      <c r="Z25">
+        <v>15</v>
+      </c>
+      <c r="AA25">
+        <v>24</v>
+      </c>
+      <c r="AB25">
+        <v>22</v>
+      </c>
+      <c r="AC25">
+        <v>10</v>
+      </c>
+      <c r="AD25">
+        <v>11</v>
+      </c>
+      <c r="AE25">
+        <v>21</v>
+      </c>
+      <c r="AF25">
+        <v>42</v>
+      </c>
+      <c r="AG25">
+        <v>19</v>
+      </c>
+      <c r="AH25">
+        <v>18.5</v>
+      </c>
+      <c r="AI25">
+        <v>32</v>
+      </c>
+      <c r="AJ25">
+        <v>110</v>
+      </c>
+      <c r="AK25">
+        <v>60</v>
+      </c>
+      <c r="AL25">
+        <v>60</v>
+      </c>
+      <c r="AM25">
+        <v>90</v>
+      </c>
+      <c r="AN25">
+        <v>55</v>
+      </c>
+      <c r="AO25">
+        <v>11.5</v>
+      </c>
+      <c r="AP25">
+        <v>17</v>
+      </c>
+      <c r="AQ25">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR25">
+        <v>10.5</v>
+      </c>
+      <c r="AS25">
+        <v>17</v>
+      </c>
+      <c r="AT25">
+        <v>16</v>
+      </c>
+      <c r="AU25">
+        <v>8</v>
+      </c>
+      <c r="AV25">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW25">
+        <v>15.5</v>
+      </c>
+      <c r="AX25">
+        <v>5.3</v>
+      </c>
+      <c r="AY25">
+        <v>15</v>
+      </c>
+      <c r="AZ25">
+        <v>14.5</v>
+      </c>
+      <c r="BA25">
+        <v>5.1</v>
+      </c>
+      <c r="BB25">
+        <v>5.7</v>
+      </c>
+      <c r="BC25">
+        <v>5.5</v>
+      </c>
+      <c r="BD25">
+        <v>5.5</v>
+      </c>
+      <c r="BE25">
+        <v>5.7</v>
+      </c>
+      <c r="BF25">
+        <v>5.4</v>
+      </c>
+      <c r="BG25">
         <v>8.6</v>
       </c>
-      <c r="J25">
-        <v>2.78</v>
-      </c>
-      <c r="K25">
-        <v>3.5</v>
-      </c>
-      <c r="L25">
-        <v>1.47</v>
-      </c>
-      <c r="M25">
-        <v>1.01</v>
-      </c>
-      <c r="N25">
-        <v>2.36</v>
-      </c>
-      <c r="O25">
-        <v>1.01</v>
-      </c>
-      <c r="P25">
-        <v>1.45</v>
-      </c>
-      <c r="Q25">
-        <v>2.6</v>
-      </c>
-      <c r="R25">
-        <v>1.15</v>
-      </c>
-      <c r="S25">
-        <v>5.1</v>
-      </c>
-      <c r="T25">
-        <v>1.01</v>
-      </c>
-      <c r="U25">
-        <v>1.01</v>
-      </c>
-      <c r="V25">
-        <v>1.14</v>
-      </c>
-      <c r="W25">
-        <v>2.08</v>
-      </c>
-      <c r="X25">
-        <v>1000</v>
-      </c>
-      <c r="Y25">
-        <v>1000</v>
-      </c>
-      <c r="Z25">
-        <v>1000</v>
-      </c>
-      <c r="AA25">
-        <v>1000</v>
-      </c>
-      <c r="AB25">
-        <v>1000</v>
-      </c>
-      <c r="AC25">
-        <v>1000</v>
-      </c>
-      <c r="AD25">
-        <v>1000</v>
-      </c>
-      <c r="AE25">
-        <v>1000</v>
-      </c>
-      <c r="AF25">
-        <v>1000</v>
-      </c>
-      <c r="AG25">
-        <v>1000</v>
-      </c>
-      <c r="AH25">
-        <v>1000</v>
-      </c>
-      <c r="AI25">
-        <v>1000</v>
-      </c>
-      <c r="AJ25">
-        <v>1000</v>
-      </c>
-      <c r="AK25">
-        <v>1000</v>
-      </c>
-      <c r="AL25">
-        <v>1000</v>
-      </c>
-      <c r="AM25">
-        <v>1000</v>
-      </c>
-      <c r="AN25">
-        <v>1000</v>
-      </c>
-      <c r="AO25">
-        <v>1000</v>
-      </c>
-      <c r="AP25">
-        <v>1.01</v>
-      </c>
-      <c r="AQ25">
-        <v>1.01</v>
-      </c>
-      <c r="AR25">
-        <v>1.01</v>
-      </c>
-      <c r="AS25">
-        <v>1.01</v>
-      </c>
-      <c r="AT25">
-        <v>1.01</v>
-      </c>
-      <c r="AU25">
-        <v>1.01</v>
-      </c>
-      <c r="AV25">
-        <v>1.01</v>
-      </c>
-      <c r="AW25">
-        <v>1.01</v>
-      </c>
-      <c r="AX25">
-        <v>1.01</v>
-      </c>
-      <c r="AY25">
-        <v>1.01</v>
-      </c>
-      <c r="AZ25">
-        <v>1.01</v>
-      </c>
-      <c r="BA25">
-        <v>1.01</v>
-      </c>
-      <c r="BB25">
-        <v>1.01</v>
-      </c>
-      <c r="BC25">
-        <v>1.01</v>
-      </c>
-      <c r="BD25">
-        <v>1.01</v>
-      </c>
-      <c r="BE25">
-        <v>1.01</v>
-      </c>
-      <c r="BF25">
-        <v>1.01</v>
-      </c>
-      <c r="BG25">
-        <v>1.01</v>
-      </c>
       <c r="BH25">
         <v>1000</v>
       </c>
@@ -7076,66 +7151,66 @@
         <v>1.01</v>
       </c>
       <c r="CB25" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
     </row>
     <row r="26" spans="1:80">
       <c r="A26" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="B26" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C26" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D26" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="E26" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="F26">
-        <v>2.06</v>
+        <v>3.85</v>
       </c>
       <c r="G26">
-        <v>2.08</v>
+        <v>6.2</v>
       </c>
       <c r="H26">
-        <v>3.6</v>
+        <v>1.67</v>
       </c>
       <c r="I26">
-        <v>3.65</v>
+        <v>1.96</v>
       </c>
       <c r="J26">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="K26">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="L26">
         <v>1.01</v>
       </c>
       <c r="M26">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N26">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="O26">
         <v>1.21</v>
       </c>
       <c r="P26">
-        <v>2.34</v>
+        <v>2.06</v>
       </c>
       <c r="Q26">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="R26">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="S26">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="T26">
         <v>1.01</v>
@@ -7144,118 +7219,118 @@
         <v>1.01</v>
       </c>
       <c r="V26">
-        <v>1.37</v>
+        <v>2.04</v>
       </c>
       <c r="W26">
-        <v>1.92</v>
+        <v>1.2</v>
       </c>
       <c r="X26">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="Y26">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z26">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AA26">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB26">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AC26">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD26">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE26">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AF26">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AG26">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH26">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI26">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AJ26">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AK26">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL26">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AM26">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN26">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AO26">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AP26">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ26">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AR26">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS26">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AT26">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AU26">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV26">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW26">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AX26">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="AY26">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ26">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BA26">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BB26">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC26">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BD26">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE26">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BF26">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG26">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH26">
         <v>1000</v>
@@ -7318,186 +7393,186 @@
         <v>1.01</v>
       </c>
       <c r="CB26" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
     </row>
     <row r="27" spans="1:80">
       <c r="A27" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="B27" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C27" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D27" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="E27" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="F27">
-        <v>3</v>
+        <v>1.93</v>
       </c>
       <c r="G27">
-        <v>3.9</v>
+        <v>1.95</v>
       </c>
       <c r="H27">
+        <v>4.7</v>
+      </c>
+      <c r="I27">
+        <v>4.9</v>
+      </c>
+      <c r="J27">
+        <v>3.55</v>
+      </c>
+      <c r="K27">
+        <v>3.75</v>
+      </c>
+      <c r="L27">
+        <v>1.01</v>
+      </c>
+      <c r="M27">
+        <v>1.07</v>
+      </c>
+      <c r="N27">
+        <v>3.55</v>
+      </c>
+      <c r="O27">
+        <v>1.35</v>
+      </c>
+      <c r="P27">
+        <v>1.87</v>
+      </c>
+      <c r="Q27">
         <v>2</v>
       </c>
-      <c r="I27">
-        <v>2.3</v>
-      </c>
-      <c r="J27">
-        <v>3.25</v>
-      </c>
-      <c r="K27">
-        <v>5.9</v>
-      </c>
-      <c r="L27">
-        <v>1.01</v>
-      </c>
-      <c r="M27">
-        <v>1.01</v>
-      </c>
-      <c r="N27">
+      <c r="R27">
+        <v>1.33</v>
+      </c>
+      <c r="S27">
+        <v>3.6</v>
+      </c>
+      <c r="T27">
+        <v>1.87</v>
+      </c>
+      <c r="U27">
+        <v>2.02</v>
+      </c>
+      <c r="V27">
+        <v>1.25</v>
+      </c>
+      <c r="W27">
+        <v>2.04</v>
+      </c>
+      <c r="X27">
+        <v>16.5</v>
+      </c>
+      <c r="Y27">
+        <v>19</v>
+      </c>
+      <c r="Z27">
+        <v>42</v>
+      </c>
+      <c r="AA27">
+        <v>130</v>
+      </c>
+      <c r="AB27">
+        <v>10.5</v>
+      </c>
+      <c r="AC27">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD27">
+        <v>23</v>
+      </c>
+      <c r="AE27">
+        <v>75</v>
+      </c>
+      <c r="AF27">
+        <v>14</v>
+      </c>
+      <c r="AG27">
+        <v>12.5</v>
+      </c>
+      <c r="AH27">
+        <v>24</v>
+      </c>
+      <c r="AI27">
+        <v>85</v>
+      </c>
+      <c r="AJ27">
+        <v>27</v>
+      </c>
+      <c r="AK27">
+        <v>26</v>
+      </c>
+      <c r="AL27">
+        <v>46</v>
+      </c>
+      <c r="AM27">
+        <v>140</v>
+      </c>
+      <c r="AN27">
+        <v>18</v>
+      </c>
+      <c r="AO27">
+        <v>95</v>
+      </c>
+      <c r="AP27">
+        <v>12</v>
+      </c>
+      <c r="AQ27">
+        <v>13.5</v>
+      </c>
+      <c r="AR27">
+        <v>4.6</v>
+      </c>
+      <c r="AS27">
+        <v>4.8</v>
+      </c>
+      <c r="AT27">
+        <v>7.6</v>
+      </c>
+      <c r="AU27">
+        <v>7.4</v>
+      </c>
+      <c r="AV27">
+        <v>4.1</v>
+      </c>
+      <c r="AW27">
+        <v>4.7</v>
+      </c>
+      <c r="AX27">
+        <v>10</v>
+      </c>
+      <c r="AY27">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ27">
+        <v>17</v>
+      </c>
+      <c r="BA27">
+        <v>4.7</v>
+      </c>
+      <c r="BB27">
         <v>4.3</v>
       </c>
-      <c r="O27">
-        <v>1.21</v>
-      </c>
-      <c r="P27">
-        <v>2.2</v>
-      </c>
-      <c r="Q27">
-        <v>1.63</v>
-      </c>
-      <c r="R27">
-        <v>1.46</v>
-      </c>
-      <c r="S27">
-        <v>2.56</v>
-      </c>
-      <c r="T27">
-        <v>1.01</v>
-      </c>
-      <c r="U27">
-        <v>1.01</v>
-      </c>
-      <c r="V27">
-        <v>1.78</v>
-      </c>
-      <c r="W27">
-        <v>1.36</v>
-      </c>
-      <c r="X27">
-        <v>1000</v>
-      </c>
-      <c r="Y27">
-        <v>1000</v>
-      </c>
-      <c r="Z27">
-        <v>1000</v>
-      </c>
-      <c r="AA27">
-        <v>1000</v>
-      </c>
-      <c r="AB27">
-        <v>1000</v>
-      </c>
-      <c r="AC27">
-        <v>1000</v>
-      </c>
-      <c r="AD27">
-        <v>1000</v>
-      </c>
-      <c r="AE27">
-        <v>1000</v>
-      </c>
-      <c r="AF27">
-        <v>1000</v>
-      </c>
-      <c r="AG27">
-        <v>1000</v>
-      </c>
-      <c r="AH27">
-        <v>1000</v>
-      </c>
-      <c r="AI27">
-        <v>1000</v>
-      </c>
-      <c r="AJ27">
-        <v>1000</v>
-      </c>
-      <c r="AK27">
-        <v>1000</v>
-      </c>
-      <c r="AL27">
-        <v>1000</v>
-      </c>
-      <c r="AM27">
-        <v>1000</v>
-      </c>
-      <c r="AN27">
-        <v>1000</v>
-      </c>
-      <c r="AO27">
-        <v>1000</v>
-      </c>
-      <c r="AP27">
-        <v>1.01</v>
-      </c>
-      <c r="AQ27">
-        <v>1.01</v>
-      </c>
-      <c r="AR27">
-        <v>1.01</v>
-      </c>
-      <c r="AS27">
-        <v>1.01</v>
-      </c>
-      <c r="AT27">
-        <v>1.01</v>
-      </c>
-      <c r="AU27">
-        <v>1.01</v>
-      </c>
-      <c r="AV27">
-        <v>1.01</v>
-      </c>
-      <c r="AW27">
-        <v>1.01</v>
-      </c>
-      <c r="AX27">
-        <v>1.01</v>
-      </c>
-      <c r="AY27">
-        <v>1.01</v>
-      </c>
-      <c r="AZ27">
-        <v>1.01</v>
-      </c>
-      <c r="BA27">
-        <v>1.01</v>
-      </c>
-      <c r="BB27">
-        <v>1.01</v>
-      </c>
       <c r="BC27">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD27">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE27">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF27">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BG27">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH27">
         <v>1000</v>
@@ -7560,7 +7635,7 @@
         <v>1.01</v>
       </c>
       <c r="CB27" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
     </row>
     <row r="28" spans="1:80">
@@ -7568,178 +7643,178 @@
         <v>97</v>
       </c>
       <c r="B28" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C28" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D28" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="E28" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="F28">
-        <v>1.72</v>
+        <v>1.92</v>
       </c>
       <c r="G28">
-        <v>1.86</v>
+        <v>1.99</v>
       </c>
       <c r="H28">
         <v>4.5</v>
       </c>
       <c r="I28">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="J28">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="K28">
-        <v>5.1</v>
+        <v>3.95</v>
       </c>
       <c r="L28">
         <v>1.01</v>
       </c>
       <c r="M28">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N28">
-        <v>4.2</v>
+        <v>2.34</v>
       </c>
       <c r="O28">
+        <v>1.27</v>
+      </c>
+      <c r="P28">
+        <v>2</v>
+      </c>
+      <c r="Q28">
+        <v>1.58</v>
+      </c>
+      <c r="R28">
+        <v>1.38</v>
+      </c>
+      <c r="S28">
+        <v>2.96</v>
+      </c>
+      <c r="T28">
+        <v>1.01</v>
+      </c>
+      <c r="U28">
+        <v>1.01</v>
+      </c>
+      <c r="V28">
         <v>1.25</v>
       </c>
-      <c r="P28">
-        <v>2.1</v>
-      </c>
-      <c r="Q28">
-        <v>1.74</v>
-      </c>
-      <c r="R28">
-        <v>1.43</v>
-      </c>
-      <c r="S28">
-        <v>2.88</v>
-      </c>
-      <c r="T28">
-        <v>1.62</v>
-      </c>
-      <c r="U28">
-        <v>2.1</v>
-      </c>
-      <c r="V28">
-        <v>1.22</v>
-      </c>
       <c r="W28">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="X28">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y28">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Z28">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AA28">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB28">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC28">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD28">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE28">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF28">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AG28">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH28">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI28">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ28">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AK28">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL28">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM28">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN28">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AO28">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP28">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AQ28">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AR28">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="AS28">
-        <v>75</v>
+        <v>1.01</v>
       </c>
       <c r="AT28">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU28">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV28">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AW28">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="AX28">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY28">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ28">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA28">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BB28">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BC28">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BD28">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BE28">
-        <v>60</v>
+        <v>1.01</v>
       </c>
       <c r="BF28">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG28">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BH28">
         <v>1000</v>
@@ -7802,7 +7877,7 @@
         <v>1.01</v>
       </c>
       <c r="CB28" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
     </row>
     <row r="29" spans="1:80">
@@ -7810,16 +7885,16 @@
         <v>98</v>
       </c>
       <c r="B29" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C29" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="D29" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="E29" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="F29">
         <v>2.6</v>
@@ -7846,7 +7921,7 @@
         <v>1.01</v>
       </c>
       <c r="N29">
-        <v>3.85</v>
+        <v>2.9</v>
       </c>
       <c r="O29">
         <v>1.27</v>
@@ -8044,7 +8119,7 @@
         <v>1.01</v>
       </c>
       <c r="CB29" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
     </row>
     <row r="30" spans="1:80">
@@ -8052,16 +8127,16 @@
         <v>91</v>
       </c>
       <c r="B30" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C30" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="D30" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="E30" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="F30">
         <v>5.7</v>
@@ -8088,7 +8163,7 @@
         <v>1.01</v>
       </c>
       <c r="N30">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O30">
         <v>1.24</v>
@@ -8109,7 +8184,7 @@
         <v>1.01</v>
       </c>
       <c r="U30">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="V30">
         <v>2.44</v>
@@ -8118,112 +8193,112 @@
         <v>1.17</v>
       </c>
       <c r="X30">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y30">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Z30">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AA30">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AB30">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AC30">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD30">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE30">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AF30">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AG30">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AH30">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI30">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ30">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AK30">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AL30">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AM30">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN30">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AO30">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AP30">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AQ30">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AR30">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AS30">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AT30">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AU30">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AV30">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AW30">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AX30">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="AY30">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AZ30">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BA30">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BB30">
-        <v>1.01</v>
+        <v>120</v>
       </c>
       <c r="BC30">
-        <v>1.01</v>
+        <v>60</v>
       </c>
       <c r="BD30">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BE30">
-        <v>1.01</v>
+        <v>75</v>
       </c>
       <c r="BF30">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="BG30">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BH30">
         <v>1000</v>
@@ -8286,7 +8361,7 @@
         <v>1.01</v>
       </c>
       <c r="CB30" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
     </row>
     <row r="31" spans="1:80">
@@ -8294,16 +8369,16 @@
         <v>99</v>
       </c>
       <c r="B31" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C31" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D31" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="E31" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="F31">
         <v>2.64</v>
@@ -8342,7 +8417,7 @@
         <v>2.42</v>
       </c>
       <c r="R31">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="S31">
         <v>2.42</v>
@@ -8528,7 +8603,7 @@
         <v>0</v>
       </c>
       <c r="CB31" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
     </row>
     <row r="32" spans="1:80">
@@ -8536,16 +8611,16 @@
         <v>91</v>
       </c>
       <c r="B32" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C32" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D32" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="E32" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="F32">
         <v>2.48</v>
@@ -8770,7 +8845,7 @@
         <v>1.01</v>
       </c>
       <c r="CB32" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
     </row>
     <row r="33" spans="1:80">
@@ -8778,16 +8853,16 @@
         <v>84</v>
       </c>
       <c r="B33" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C33" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D33" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="E33" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="F33">
         <v>1.58</v>
@@ -9012,7 +9087,7 @@
         <v>1.01</v>
       </c>
       <c r="CB33" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
     </row>
     <row r="34" spans="1:80">
@@ -9020,37 +9095,37 @@
         <v>100</v>
       </c>
       <c r="B34" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C34" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D34" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="E34" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="F34">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="G34">
-        <v>2.22</v>
+        <v>2.36</v>
       </c>
       <c r="H34">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="I34">
         <v>4.5</v>
       </c>
       <c r="J34">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="K34">
-        <v>3.7</v>
+        <v>7.4</v>
       </c>
       <c r="L34">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="M34">
         <v>1.01</v>
@@ -9059,19 +9134,19 @@
         <v>3.1</v>
       </c>
       <c r="O34">
-        <v>1.39</v>
+        <v>1.07</v>
       </c>
       <c r="P34">
-        <v>1.77</v>
+        <v>3.1</v>
       </c>
       <c r="Q34">
-        <v>2.02</v>
+        <v>1.25</v>
       </c>
       <c r="R34">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="S34">
-        <v>3.55</v>
+        <v>1.48</v>
       </c>
       <c r="T34">
         <v>1.01</v>
@@ -9080,10 +9155,10 @@
         <v>1.01</v>
       </c>
       <c r="V34">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W34">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="X34">
         <v>1000</v>
@@ -9254,67 +9329,67 @@
         <v>1.01</v>
       </c>
       <c r="CB34" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
     </row>
     <row r="35" spans="1:80">
       <c r="A35" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B35" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C35" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D35" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="E35" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="F35">
+        <v>2.26</v>
+      </c>
+      <c r="G35">
+        <v>2.68</v>
+      </c>
+      <c r="H35">
+        <v>2.66</v>
+      </c>
+      <c r="I35">
+        <v>3.15</v>
+      </c>
+      <c r="J35">
+        <v>3.8</v>
+      </c>
+      <c r="K35">
+        <v>5.8</v>
+      </c>
+      <c r="L35">
+        <v>1.01</v>
+      </c>
+      <c r="M35">
+        <v>1.01</v>
+      </c>
+      <c r="N35">
+        <v>2.48</v>
+      </c>
+      <c r="O35">
+        <v>1.15</v>
+      </c>
+      <c r="P35">
+        <v>2.48</v>
+      </c>
+      <c r="Q35">
+        <v>1.5</v>
+      </c>
+      <c r="R35">
+        <v>1.6</v>
+      </c>
+      <c r="S35">
         <v>2.16</v>
       </c>
-      <c r="G35">
-        <v>2.74</v>
-      </c>
-      <c r="H35">
-        <v>2.88</v>
-      </c>
-      <c r="I35">
-        <v>4.4</v>
-      </c>
-      <c r="J35">
-        <v>2.76</v>
-      </c>
-      <c r="K35">
-        <v>5.2</v>
-      </c>
-      <c r="L35">
-        <v>1.38</v>
-      </c>
-      <c r="M35">
-        <v>1.01</v>
-      </c>
-      <c r="N35">
-        <v>2.5</v>
-      </c>
-      <c r="O35">
-        <v>1.37</v>
-      </c>
-      <c r="P35">
-        <v>1.54</v>
-      </c>
-      <c r="Q35">
-        <v>2.02</v>
-      </c>
-      <c r="R35">
-        <v>1.15</v>
-      </c>
-      <c r="S35">
-        <v>2.86</v>
-      </c>
       <c r="T35">
         <v>1.01</v>
       </c>
@@ -9322,10 +9397,10 @@
         <v>1.01</v>
       </c>
       <c r="V35">
-        <v>1.29</v>
+        <v>1.47</v>
       </c>
       <c r="W35">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="X35">
         <v>1000</v>
@@ -9496,66 +9571,66 @@
         <v>1.01</v>
       </c>
       <c r="CB35" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
     </row>
     <row r="36" spans="1:80">
       <c r="A36" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="B36" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C36" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D36" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="E36" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="F36">
-        <v>2.3</v>
+        <v>1.25</v>
       </c>
       <c r="G36">
-        <v>2.68</v>
+        <v>1.38</v>
       </c>
       <c r="H36">
-        <v>2.66</v>
+        <v>1.1</v>
       </c>
       <c r="I36">
-        <v>3.15</v>
+        <v>15.5</v>
       </c>
       <c r="J36">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="K36">
-        <v>5.3</v>
+        <v>110</v>
       </c>
       <c r="L36">
         <v>1.01</v>
       </c>
       <c r="M36">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N36">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="O36">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P36">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="Q36">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="R36">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="S36">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="T36">
         <v>1.01</v>
@@ -9564,10 +9639,10 @@
         <v>1.01</v>
       </c>
       <c r="V36">
-        <v>1.47</v>
+        <v>1.07</v>
       </c>
       <c r="W36">
-        <v>1.6</v>
+        <v>3.55</v>
       </c>
       <c r="X36">
         <v>1000</v>
@@ -9738,66 +9813,66 @@
         <v>1.01</v>
       </c>
       <c r="CB36" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
     </row>
     <row r="37" spans="1:80">
       <c r="A37" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B37" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C37" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D37" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="E37" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="F37">
-        <v>1.83</v>
+        <v>2.16</v>
       </c>
       <c r="G37">
-        <v>2.36</v>
+        <v>2.74</v>
       </c>
       <c r="H37">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="I37">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J37">
-        <v>3.9</v>
+        <v>2.76</v>
       </c>
       <c r="K37">
-        <v>7.4</v>
+        <v>5.2</v>
       </c>
       <c r="L37">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M37">
         <v>1.01</v>
       </c>
       <c r="N37">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="O37">
-        <v>1.07</v>
+        <v>1.37</v>
       </c>
       <c r="P37">
-        <v>3.1</v>
+        <v>1.54</v>
       </c>
       <c r="Q37">
-        <v>1.25</v>
+        <v>2.02</v>
       </c>
       <c r="R37">
-        <v>2</v>
+        <v>1.15</v>
       </c>
       <c r="S37">
-        <v>1.48</v>
+        <v>2.86</v>
       </c>
       <c r="T37">
         <v>1.01</v>
@@ -9809,7 +9884,7 @@
         <v>1.29</v>
       </c>
       <c r="W37">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="X37">
         <v>1000</v>
@@ -9980,66 +10055,66 @@
         <v>1.01</v>
       </c>
       <c r="CB37" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
     </row>
     <row r="38" spans="1:80">
       <c r="A38" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="B38" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C38" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D38" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="E38" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="F38">
-        <v>1.28</v>
+        <v>1.97</v>
       </c>
       <c r="G38">
-        <v>1.43</v>
+        <v>2.48</v>
       </c>
       <c r="H38">
-        <v>2.72</v>
+        <v>3.6</v>
       </c>
       <c r="I38">
-        <v>26</v>
+        <v>4.8</v>
       </c>
       <c r="J38">
-        <v>5.5</v>
+        <v>3.15</v>
       </c>
       <c r="K38">
-        <v>110</v>
+        <v>3.7</v>
       </c>
       <c r="L38">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M38">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N38">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="O38">
-        <v>1.12</v>
+        <v>1.39</v>
       </c>
       <c r="P38">
-        <v>2.6</v>
+        <v>1.77</v>
       </c>
       <c r="Q38">
-        <v>1.35</v>
+        <v>2.02</v>
       </c>
       <c r="R38">
-        <v>1.71</v>
+        <v>1.3</v>
       </c>
       <c r="S38">
-        <v>1.74</v>
+        <v>3.55</v>
       </c>
       <c r="T38">
         <v>1.01</v>
@@ -10048,10 +10123,10 @@
         <v>1.01</v>
       </c>
       <c r="V38">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="W38">
-        <v>3.05</v>
+        <v>1.68</v>
       </c>
       <c r="X38">
         <v>1000</v>
@@ -10222,7 +10297,7 @@
         <v>1.01</v>
       </c>
       <c r="CB38" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
     </row>
     <row r="39" spans="1:80">
@@ -10230,16 +10305,16 @@
         <v>103</v>
       </c>
       <c r="B39" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C39" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D39" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="E39" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="F39">
         <v>1.78</v>
@@ -10266,7 +10341,7 @@
         <v>1.07</v>
       </c>
       <c r="N39">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="O39">
         <v>1.32</v>
@@ -10275,13 +10350,13 @@
         <v>1.93</v>
       </c>
       <c r="Q39">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="R39">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S39">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T39">
         <v>1.86</v>
@@ -10293,7 +10368,7 @@
         <v>1.22</v>
       </c>
       <c r="W39">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="X39">
         <v>16</v>
@@ -10305,7 +10380,7 @@
         <v>48</v>
       </c>
       <c r="AA39">
-        <v>750</v>
+        <v>660</v>
       </c>
       <c r="AB39">
         <v>9.800000000000001</v>
@@ -10317,7 +10392,7 @@
         <v>24</v>
       </c>
       <c r="AE39">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF39">
         <v>13.5</v>
@@ -10341,7 +10416,7 @@
         <v>46</v>
       </c>
       <c r="AM39">
-        <v>750</v>
+        <v>660</v>
       </c>
       <c r="AN39">
         <v>15</v>
@@ -10398,7 +10473,7 @@
         <v>4.9</v>
       </c>
       <c r="BF39">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG39">
         <v>4.9</v>
@@ -10464,7 +10539,7 @@
         <v>1.01</v>
       </c>
       <c r="CB39" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
     </row>
     <row r="40" spans="1:80">
@@ -10472,16 +10547,16 @@
         <v>104</v>
       </c>
       <c r="B40" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C40" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D40" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="E40" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="F40">
         <v>1.9</v>
@@ -10526,10 +10601,10 @@
         <v>3</v>
       </c>
       <c r="T40">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="U40">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="V40">
         <v>1.28</v>
@@ -10706,7 +10781,7 @@
         <v>1.29</v>
       </c>
       <c r="CB40" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
     </row>
     <row r="41" spans="1:80">
@@ -10714,16 +10789,16 @@
         <v>105</v>
       </c>
       <c r="B41" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C41" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D41" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="E41" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="F41">
         <v>2.22</v>
@@ -10948,491 +11023,491 @@
         <v>1.01</v>
       </c>
       <c r="CB41" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
     </row>
     <row r="42" spans="1:80">
       <c r="A42" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="B42" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C42" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D42" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="E42" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="F42">
-        <v>1.89</v>
+        <v>3</v>
       </c>
       <c r="G42">
-        <v>2.08</v>
+        <v>3.1</v>
       </c>
       <c r="H42">
-        <v>3.65</v>
+        <v>2.74</v>
       </c>
       <c r="I42">
-        <v>5.3</v>
+        <v>2.78</v>
       </c>
       <c r="J42">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="K42">
-        <v>5</v>
+        <v>3.25</v>
       </c>
       <c r="L42">
-        <v>1.31</v>
+        <v>1.54</v>
       </c>
       <c r="M42">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N42">
-        <v>2.86</v>
+        <v>3.05</v>
       </c>
       <c r="O42">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="P42">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="Q42">
-        <v>1.89</v>
+        <v>2.44</v>
       </c>
       <c r="R42">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="S42">
-        <v>2.88</v>
+        <v>4.8</v>
       </c>
       <c r="T42">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="U42">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="V42">
-        <v>1.23</v>
+        <v>1.56</v>
       </c>
       <c r="W42">
-        <v>1.93</v>
+        <v>1.47</v>
       </c>
       <c r="X42">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y42">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z42">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AA42">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AB42">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC42">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AD42">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE42">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF42">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG42">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH42">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI42">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ42">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK42">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL42">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM42">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN42">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AO42">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP42">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ42">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AR42">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AS42">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="AT42">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU42">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV42">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AW42">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="AX42">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AY42">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AZ42">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BA42">
-        <v>1.01</v>
+        <v>48</v>
       </c>
       <c r="BB42">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="BC42">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BD42">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BE42">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BF42">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BG42">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BH42">
         <v>1000</v>
       </c>
       <c r="BI42">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BJ42">
         <v>1000</v>
       </c>
       <c r="BK42">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="BL42">
         <v>1000</v>
       </c>
       <c r="BM42">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="BN42">
         <v>1000</v>
       </c>
       <c r="BO42">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="BP42">
         <v>1000</v>
       </c>
       <c r="BQ42">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BR42">
         <v>1000</v>
       </c>
       <c r="BS42">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BT42">
         <v>1000</v>
       </c>
       <c r="BU42">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="BV42">
         <v>1000</v>
       </c>
       <c r="BW42">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BX42">
         <v>1000</v>
       </c>
       <c r="BY42">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BZ42">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA42">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB42" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
     </row>
     <row r="43" spans="1:80">
       <c r="A43" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="B43" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C43" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D43" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="E43" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="F43">
-        <v>3</v>
+        <v>1.89</v>
       </c>
       <c r="G43">
-        <v>3.1</v>
+        <v>2.08</v>
       </c>
       <c r="H43">
-        <v>2.74</v>
+        <v>3.65</v>
       </c>
       <c r="I43">
-        <v>2.78</v>
+        <v>5.4</v>
       </c>
       <c r="J43">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="K43">
-        <v>3.25</v>
+        <v>5</v>
       </c>
       <c r="L43">
-        <v>1.54</v>
+        <v>1.31</v>
       </c>
       <c r="M43">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N43">
-        <v>3.05</v>
+        <v>2.86</v>
       </c>
       <c r="O43">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="P43">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="Q43">
-        <v>2.44</v>
+        <v>1.89</v>
       </c>
       <c r="R43">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="S43">
-        <v>4.8</v>
+        <v>2.88</v>
       </c>
       <c r="T43">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="U43">
+        <v>1.01</v>
+      </c>
+      <c r="V43">
+        <v>1.22</v>
+      </c>
+      <c r="W43">
         <v>1.93</v>
       </c>
-      <c r="V43">
-        <v>1.56</v>
-      </c>
-      <c r="W43">
-        <v>1.47</v>
-      </c>
       <c r="X43">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Y43">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Z43">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AA43">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AB43">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AC43">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AD43">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE43">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AF43">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AG43">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH43">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI43">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ43">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK43">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AL43">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM43">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN43">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AO43">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AP43">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AQ43">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR43">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AS43">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="AT43">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU43">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV43">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW43">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="AX43">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY43">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ43">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA43">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="BB43">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BC43">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BD43">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BE43">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BF43">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BG43">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BH43">
         <v>1000</v>
       </c>
       <c r="BI43">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="BJ43">
         <v>1000</v>
       </c>
       <c r="BK43">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="BL43">
         <v>1000</v>
       </c>
       <c r="BM43">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="BN43">
         <v>1000</v>
       </c>
       <c r="BO43">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="BP43">
         <v>1000</v>
       </c>
       <c r="BQ43">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="BR43">
         <v>1000</v>
       </c>
       <c r="BS43">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="BT43">
         <v>1000</v>
       </c>
       <c r="BU43">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="BV43">
         <v>1000</v>
       </c>
       <c r="BW43">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="BX43">
         <v>1000</v>
       </c>
       <c r="BY43">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="BZ43">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA43">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB43" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
     </row>
     <row r="44" spans="1:80">
@@ -11440,16 +11515,16 @@
         <v>107</v>
       </c>
       <c r="B44" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C44" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D44" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="E44" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="F44">
         <v>4</v>
@@ -11674,7 +11749,7 @@
         <v>1.01</v>
       </c>
       <c r="CB44" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
     </row>
     <row r="45" spans="1:80">
@@ -11682,16 +11757,16 @@
         <v>108</v>
       </c>
       <c r="B45" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C45" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D45" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="E45" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="F45">
         <v>2.56</v>
@@ -11733,7 +11808,7 @@
         <v>1.32</v>
       </c>
       <c r="S45">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="T45">
         <v>1.79</v>
@@ -11916,7 +11991,7 @@
         <v>1.01</v>
       </c>
       <c r="CB45" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
     </row>
     <row r="46" spans="1:80">
@@ -11924,16 +11999,16 @@
         <v>109</v>
       </c>
       <c r="B46" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C46" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D46" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="E46" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="F46">
         <v>0</v>
@@ -12158,7 +12233,7 @@
         <v>1.01</v>
       </c>
       <c r="CB46" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
     </row>
     <row r="47" spans="1:80">
@@ -12166,22 +12241,22 @@
         <v>110</v>
       </c>
       <c r="B47" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C47" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D47" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="E47" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="F47">
         <v>2.36</v>
       </c>
       <c r="G47">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="H47">
         <v>3.1</v>
@@ -12190,7 +12265,7 @@
         <v>3.45</v>
       </c>
       <c r="J47">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K47">
         <v>3.75</v>
@@ -12199,49 +12274,49 @@
         <v>1.01</v>
       </c>
       <c r="M47">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N47">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="O47">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P47">
         <v>1.96</v>
       </c>
       <c r="Q47">
-        <v>1.88</v>
+        <v>1.74</v>
       </c>
       <c r="R47">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S47">
-        <v>2.28</v>
+        <v>3.1</v>
       </c>
       <c r="T47">
         <v>1.59</v>
       </c>
       <c r="U47">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V47">
         <v>1.4</v>
       </c>
       <c r="W47">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="X47">
         <v>17.5</v>
       </c>
       <c r="Y47">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Z47">
         <v>28</v>
       </c>
       <c r="AA47">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB47">
         <v>13</v>
@@ -12250,22 +12325,22 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD47">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AE47">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AF47">
         <v>21</v>
       </c>
       <c r="AG47">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH47">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AI47">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ47">
         <v>42</v>
@@ -12277,13 +12352,13 @@
         <v>46</v>
       </c>
       <c r="AM47">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN47">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AO47">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AP47">
         <v>12.5</v>
@@ -12295,10 +12370,10 @@
         <v>19</v>
       </c>
       <c r="AS47">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="AT47">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AU47">
         <v>6.8</v>
@@ -12307,7 +12382,7 @@
         <v>12</v>
       </c>
       <c r="AW47">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="AX47">
         <v>14</v>
@@ -12319,7 +12394,7 @@
         <v>14</v>
       </c>
       <c r="BA47">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="BB47">
         <v>26</v>
@@ -12328,16 +12403,16 @@
         <v>18.5</v>
       </c>
       <c r="BD47">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="BE47">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="BF47">
         <v>14.5</v>
       </c>
       <c r="BG47">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="BH47">
         <v>1000</v>
@@ -12400,30 +12475,30 @@
         <v>1.01</v>
       </c>
       <c r="CB47" t="s">
-        <v>226</v>
+        <v>251</v>
       </c>
     </row>
     <row r="48" spans="1:80">
       <c r="A48" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B48" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C48" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D48" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="E48" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="F48">
         <v>3.1</v>
       </c>
       <c r="G48">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H48">
         <v>2.42</v>
@@ -12459,10 +12534,10 @@
         <v>1.45</v>
       </c>
       <c r="S48">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T48">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U48">
         <v>2.38</v>
@@ -12525,13 +12600,13 @@
         <v>26</v>
       </c>
       <c r="AO48">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AP48">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ48">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR48">
         <v>15.5</v>
@@ -12585,7 +12660,7 @@
         <v>3.7</v>
       </c>
       <c r="BI48">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BJ48">
         <v>9</v>
@@ -12642,7 +12717,1943 @@
         <v>9.6</v>
       </c>
       <c r="CB48" t="s">
-        <v>226</v>
+        <v>251</v>
+      </c>
+    </row>
+    <row r="49" spans="1:80">
+      <c r="A49" t="s">
+        <v>111</v>
+      </c>
+      <c r="B49" t="s">
+        <v>116</v>
+      </c>
+      <c r="C49" t="s">
+        <v>137</v>
+      </c>
+      <c r="D49" t="s">
+        <v>188</v>
+      </c>
+      <c r="E49" t="s">
+        <v>243</v>
+      </c>
+      <c r="F49">
+        <v>1.7</v>
+      </c>
+      <c r="G49">
+        <v>2</v>
+      </c>
+      <c r="H49">
+        <v>4.1</v>
+      </c>
+      <c r="I49">
+        <v>6.4</v>
+      </c>
+      <c r="J49">
+        <v>3.6</v>
+      </c>
+      <c r="K49">
+        <v>6</v>
+      </c>
+      <c r="L49">
+        <v>1.31</v>
+      </c>
+      <c r="M49">
+        <v>1.01</v>
+      </c>
+      <c r="N49">
+        <v>3.4</v>
+      </c>
+      <c r="O49">
+        <v>1.3</v>
+      </c>
+      <c r="P49">
+        <v>1.89</v>
+      </c>
+      <c r="Q49">
+        <v>1.87</v>
+      </c>
+      <c r="R49">
+        <v>1.17</v>
+      </c>
+      <c r="S49">
+        <v>2.98</v>
+      </c>
+      <c r="T49">
+        <v>1.01</v>
+      </c>
+      <c r="U49">
+        <v>1.01</v>
+      </c>
+      <c r="V49">
+        <v>1.23</v>
+      </c>
+      <c r="W49">
+        <v>2</v>
+      </c>
+      <c r="X49">
+        <v>1000</v>
+      </c>
+      <c r="Y49">
+        <v>1000</v>
+      </c>
+      <c r="Z49">
+        <v>1000</v>
+      </c>
+      <c r="AA49">
+        <v>1000</v>
+      </c>
+      <c r="AB49">
+        <v>1000</v>
+      </c>
+      <c r="AC49">
+        <v>1000</v>
+      </c>
+      <c r="AD49">
+        <v>1000</v>
+      </c>
+      <c r="AE49">
+        <v>1000</v>
+      </c>
+      <c r="AF49">
+        <v>1000</v>
+      </c>
+      <c r="AG49">
+        <v>1000</v>
+      </c>
+      <c r="AH49">
+        <v>1000</v>
+      </c>
+      <c r="AI49">
+        <v>1000</v>
+      </c>
+      <c r="AJ49">
+        <v>1000</v>
+      </c>
+      <c r="AK49">
+        <v>1000</v>
+      </c>
+      <c r="AL49">
+        <v>1000</v>
+      </c>
+      <c r="AM49">
+        <v>1000</v>
+      </c>
+      <c r="AN49">
+        <v>1000</v>
+      </c>
+      <c r="AO49">
+        <v>1000</v>
+      </c>
+      <c r="AP49">
+        <v>1.01</v>
+      </c>
+      <c r="AQ49">
+        <v>1.01</v>
+      </c>
+      <c r="AR49">
+        <v>1.01</v>
+      </c>
+      <c r="AS49">
+        <v>1.01</v>
+      </c>
+      <c r="AT49">
+        <v>1.01</v>
+      </c>
+      <c r="AU49">
+        <v>1.01</v>
+      </c>
+      <c r="AV49">
+        <v>1.01</v>
+      </c>
+      <c r="AW49">
+        <v>1.01</v>
+      </c>
+      <c r="AX49">
+        <v>1.01</v>
+      </c>
+      <c r="AY49">
+        <v>1.01</v>
+      </c>
+      <c r="AZ49">
+        <v>1.01</v>
+      </c>
+      <c r="BA49">
+        <v>1.01</v>
+      </c>
+      <c r="BB49">
+        <v>1.01</v>
+      </c>
+      <c r="BC49">
+        <v>1.01</v>
+      </c>
+      <c r="BD49">
+        <v>1.01</v>
+      </c>
+      <c r="BE49">
+        <v>1.01</v>
+      </c>
+      <c r="BF49">
+        <v>1.01</v>
+      </c>
+      <c r="BG49">
+        <v>1.01</v>
+      </c>
+      <c r="BH49">
+        <v>1000</v>
+      </c>
+      <c r="BI49">
+        <v>1.01</v>
+      </c>
+      <c r="BJ49">
+        <v>1000</v>
+      </c>
+      <c r="BK49">
+        <v>1.01</v>
+      </c>
+      <c r="BL49">
+        <v>1000</v>
+      </c>
+      <c r="BM49">
+        <v>1.01</v>
+      </c>
+      <c r="BN49">
+        <v>1000</v>
+      </c>
+      <c r="BO49">
+        <v>1.01</v>
+      </c>
+      <c r="BP49">
+        <v>1000</v>
+      </c>
+      <c r="BQ49">
+        <v>1.01</v>
+      </c>
+      <c r="BR49">
+        <v>1000</v>
+      </c>
+      <c r="BS49">
+        <v>1.01</v>
+      </c>
+      <c r="BT49">
+        <v>1000</v>
+      </c>
+      <c r="BU49">
+        <v>1.01</v>
+      </c>
+      <c r="BV49">
+        <v>1000</v>
+      </c>
+      <c r="BW49">
+        <v>1.01</v>
+      </c>
+      <c r="BX49">
+        <v>1000</v>
+      </c>
+      <c r="BY49">
+        <v>1.01</v>
+      </c>
+      <c r="BZ49">
+        <v>0</v>
+      </c>
+      <c r="CA49">
+        <v>0</v>
+      </c>
+      <c r="CB49" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="50" spans="1:80">
+      <c r="A50" t="s">
+        <v>109</v>
+      </c>
+      <c r="B50" t="s">
+        <v>116</v>
+      </c>
+      <c r="C50" t="s">
+        <v>138</v>
+      </c>
+      <c r="D50" t="s">
+        <v>189</v>
+      </c>
+      <c r="E50" t="s">
+        <v>244</v>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="L50">
+        <v>1.01</v>
+      </c>
+      <c r="M50">
+        <v>1.01</v>
+      </c>
+      <c r="N50">
+        <v>1.26</v>
+      </c>
+      <c r="O50">
+        <v>1.01</v>
+      </c>
+      <c r="P50">
+        <v>1.25</v>
+      </c>
+      <c r="Q50">
+        <v>1.5</v>
+      </c>
+      <c r="R50">
+        <v>1.08</v>
+      </c>
+      <c r="S50">
+        <v>1.51</v>
+      </c>
+      <c r="T50">
+        <v>1.01</v>
+      </c>
+      <c r="U50">
+        <v>1.01</v>
+      </c>
+      <c r="V50">
+        <v>1.01</v>
+      </c>
+      <c r="W50">
+        <v>1.01</v>
+      </c>
+      <c r="X50">
+        <v>1000</v>
+      </c>
+      <c r="Y50">
+        <v>1000</v>
+      </c>
+      <c r="Z50">
+        <v>1000</v>
+      </c>
+      <c r="AA50">
+        <v>1000</v>
+      </c>
+      <c r="AB50">
+        <v>1000</v>
+      </c>
+      <c r="AC50">
+        <v>1000</v>
+      </c>
+      <c r="AD50">
+        <v>1000</v>
+      </c>
+      <c r="AE50">
+        <v>1000</v>
+      </c>
+      <c r="AF50">
+        <v>1000</v>
+      </c>
+      <c r="AG50">
+        <v>1000</v>
+      </c>
+      <c r="AH50">
+        <v>1000</v>
+      </c>
+      <c r="AI50">
+        <v>1000</v>
+      </c>
+      <c r="AJ50">
+        <v>1000</v>
+      </c>
+      <c r="AK50">
+        <v>1000</v>
+      </c>
+      <c r="AL50">
+        <v>1000</v>
+      </c>
+      <c r="AM50">
+        <v>1000</v>
+      </c>
+      <c r="AN50">
+        <v>1000</v>
+      </c>
+      <c r="AO50">
+        <v>1000</v>
+      </c>
+      <c r="AP50">
+        <v>1.01</v>
+      </c>
+      <c r="AQ50">
+        <v>1.01</v>
+      </c>
+      <c r="AR50">
+        <v>1.01</v>
+      </c>
+      <c r="AS50">
+        <v>1.01</v>
+      </c>
+      <c r="AT50">
+        <v>1.01</v>
+      </c>
+      <c r="AU50">
+        <v>1.01</v>
+      </c>
+      <c r="AV50">
+        <v>1.01</v>
+      </c>
+      <c r="AW50">
+        <v>1.01</v>
+      </c>
+      <c r="AX50">
+        <v>1.01</v>
+      </c>
+      <c r="AY50">
+        <v>1.01</v>
+      </c>
+      <c r="AZ50">
+        <v>1.01</v>
+      </c>
+      <c r="BA50">
+        <v>1.01</v>
+      </c>
+      <c r="BB50">
+        <v>1.01</v>
+      </c>
+      <c r="BC50">
+        <v>1.01</v>
+      </c>
+      <c r="BD50">
+        <v>1.01</v>
+      </c>
+      <c r="BE50">
+        <v>1.01</v>
+      </c>
+      <c r="BF50">
+        <v>1.01</v>
+      </c>
+      <c r="BG50">
+        <v>1.01</v>
+      </c>
+      <c r="BH50">
+        <v>1000</v>
+      </c>
+      <c r="BI50">
+        <v>1.01</v>
+      </c>
+      <c r="BJ50">
+        <v>1000</v>
+      </c>
+      <c r="BK50">
+        <v>1.01</v>
+      </c>
+      <c r="BL50">
+        <v>1000</v>
+      </c>
+      <c r="BM50">
+        <v>1.01</v>
+      </c>
+      <c r="BN50">
+        <v>1000</v>
+      </c>
+      <c r="BO50">
+        <v>1.01</v>
+      </c>
+      <c r="BP50">
+        <v>1000</v>
+      </c>
+      <c r="BQ50">
+        <v>1.01</v>
+      </c>
+      <c r="BR50">
+        <v>1000</v>
+      </c>
+      <c r="BS50">
+        <v>1.01</v>
+      </c>
+      <c r="BT50">
+        <v>1000</v>
+      </c>
+      <c r="BU50">
+        <v>1.01</v>
+      </c>
+      <c r="BV50">
+        <v>1000</v>
+      </c>
+      <c r="BW50">
+        <v>1.01</v>
+      </c>
+      <c r="BX50">
+        <v>1000</v>
+      </c>
+      <c r="BY50">
+        <v>1.01</v>
+      </c>
+      <c r="BZ50">
+        <v>1000</v>
+      </c>
+      <c r="CA50">
+        <v>1.01</v>
+      </c>
+      <c r="CB50" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="51" spans="1:80">
+      <c r="A51" t="s">
+        <v>82</v>
+      </c>
+      <c r="B51" t="s">
+        <v>116</v>
+      </c>
+      <c r="C51" t="s">
+        <v>139</v>
+      </c>
+      <c r="D51" t="s">
+        <v>190</v>
+      </c>
+      <c r="E51" t="s">
+        <v>245</v>
+      </c>
+      <c r="F51">
+        <v>4.4</v>
+      </c>
+      <c r="G51">
+        <v>5.2</v>
+      </c>
+      <c r="H51">
+        <v>2.08</v>
+      </c>
+      <c r="I51">
+        <v>2.28</v>
+      </c>
+      <c r="J51">
+        <v>2.86</v>
+      </c>
+      <c r="K51">
+        <v>3.2</v>
+      </c>
+      <c r="L51">
+        <v>1.01</v>
+      </c>
+      <c r="M51">
+        <v>1.15</v>
+      </c>
+      <c r="N51">
+        <v>1.01</v>
+      </c>
+      <c r="O51">
+        <v>1.61</v>
+      </c>
+      <c r="P51">
+        <v>1.4</v>
+      </c>
+      <c r="Q51">
+        <v>2.98</v>
+      </c>
+      <c r="R51">
+        <v>1.13</v>
+      </c>
+      <c r="S51">
+        <v>2.98</v>
+      </c>
+      <c r="T51">
+        <v>1.01</v>
+      </c>
+      <c r="U51">
+        <v>1.01</v>
+      </c>
+      <c r="V51">
+        <v>1.78</v>
+      </c>
+      <c r="W51">
+        <v>1.23</v>
+      </c>
+      <c r="X51">
+        <v>8.4</v>
+      </c>
+      <c r="Y51">
+        <v>6.8</v>
+      </c>
+      <c r="Z51">
+        <v>12</v>
+      </c>
+      <c r="AA51">
+        <v>32</v>
+      </c>
+      <c r="AB51">
+        <v>12</v>
+      </c>
+      <c r="AC51">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD51">
+        <v>13</v>
+      </c>
+      <c r="AE51">
+        <v>48</v>
+      </c>
+      <c r="AF51">
+        <v>48</v>
+      </c>
+      <c r="AG51">
+        <v>23</v>
+      </c>
+      <c r="AH51">
+        <v>32</v>
+      </c>
+      <c r="AI51">
+        <v>90</v>
+      </c>
+      <c r="AJ51">
+        <v>900</v>
+      </c>
+      <c r="AK51">
+        <v>900</v>
+      </c>
+      <c r="AL51">
+        <v>900</v>
+      </c>
+      <c r="AM51">
+        <v>910</v>
+      </c>
+      <c r="AN51">
+        <v>900</v>
+      </c>
+      <c r="AO51">
+        <v>50</v>
+      </c>
+      <c r="AP51">
+        <v>1.22</v>
+      </c>
+      <c r="AQ51">
+        <v>1.22</v>
+      </c>
+      <c r="AR51">
+        <v>1.22</v>
+      </c>
+      <c r="AS51">
+        <v>1.18</v>
+      </c>
+      <c r="AT51">
+        <v>1.22</v>
+      </c>
+      <c r="AU51">
+        <v>1.22</v>
+      </c>
+      <c r="AV51">
+        <v>1.22</v>
+      </c>
+      <c r="AW51">
+        <v>1.19</v>
+      </c>
+      <c r="AX51">
+        <v>1.19</v>
+      </c>
+      <c r="AY51">
+        <v>1.62</v>
+      </c>
+      <c r="AZ51">
+        <v>1.18</v>
+      </c>
+      <c r="BA51">
+        <v>1.2</v>
+      </c>
+      <c r="BB51">
+        <v>1.22</v>
+      </c>
+      <c r="BC51">
+        <v>1.22</v>
+      </c>
+      <c r="BD51">
+        <v>1.22</v>
+      </c>
+      <c r="BE51">
+        <v>1.22</v>
+      </c>
+      <c r="BF51">
+        <v>1.22</v>
+      </c>
+      <c r="BG51">
+        <v>1.19</v>
+      </c>
+      <c r="BH51">
+        <v>1000</v>
+      </c>
+      <c r="BI51">
+        <v>1.01</v>
+      </c>
+      <c r="BJ51">
+        <v>1000</v>
+      </c>
+      <c r="BK51">
+        <v>1.01</v>
+      </c>
+      <c r="BL51">
+        <v>1000</v>
+      </c>
+      <c r="BM51">
+        <v>1.01</v>
+      </c>
+      <c r="BN51">
+        <v>1000</v>
+      </c>
+      <c r="BO51">
+        <v>1.01</v>
+      </c>
+      <c r="BP51">
+        <v>1000</v>
+      </c>
+      <c r="BQ51">
+        <v>1.01</v>
+      </c>
+      <c r="BR51">
+        <v>1000</v>
+      </c>
+      <c r="BS51">
+        <v>1.01</v>
+      </c>
+      <c r="BT51">
+        <v>1000</v>
+      </c>
+      <c r="BU51">
+        <v>1.01</v>
+      </c>
+      <c r="BV51">
+        <v>1000</v>
+      </c>
+      <c r="BW51">
+        <v>1.01</v>
+      </c>
+      <c r="BX51">
+        <v>1000</v>
+      </c>
+      <c r="BY51">
+        <v>1.01</v>
+      </c>
+      <c r="BZ51">
+        <v>1000</v>
+      </c>
+      <c r="CA51">
+        <v>1.01</v>
+      </c>
+      <c r="CB51" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="52" spans="1:80">
+      <c r="A52" t="s">
+        <v>112</v>
+      </c>
+      <c r="B52" t="s">
+        <v>116</v>
+      </c>
+      <c r="C52" t="s">
+        <v>139</v>
+      </c>
+      <c r="D52" t="s">
+        <v>191</v>
+      </c>
+      <c r="E52" t="s">
+        <v>246</v>
+      </c>
+      <c r="F52">
+        <v>1.79</v>
+      </c>
+      <c r="G52">
+        <v>2.02</v>
+      </c>
+      <c r="H52">
+        <v>4.6</v>
+      </c>
+      <c r="I52">
+        <v>6.6</v>
+      </c>
+      <c r="J52">
+        <v>3.15</v>
+      </c>
+      <c r="K52">
+        <v>3.6</v>
+      </c>
+      <c r="L52">
+        <v>1.44</v>
+      </c>
+      <c r="M52">
+        <v>1.01</v>
+      </c>
+      <c r="N52">
+        <v>2.48</v>
+      </c>
+      <c r="O52">
+        <v>1.28</v>
+      </c>
+      <c r="P52">
+        <v>1.51</v>
+      </c>
+      <c r="Q52">
+        <v>2.3</v>
+      </c>
+      <c r="R52">
+        <v>1.09</v>
+      </c>
+      <c r="S52">
+        <v>2.86</v>
+      </c>
+      <c r="T52">
+        <v>1.01</v>
+      </c>
+      <c r="U52">
+        <v>1.01</v>
+      </c>
+      <c r="V52">
+        <v>1.18</v>
+      </c>
+      <c r="W52">
+        <v>1.98</v>
+      </c>
+      <c r="X52">
+        <v>1000</v>
+      </c>
+      <c r="Y52">
+        <v>1000</v>
+      </c>
+      <c r="Z52">
+        <v>1000</v>
+      </c>
+      <c r="AA52">
+        <v>1000</v>
+      </c>
+      <c r="AB52">
+        <v>1000</v>
+      </c>
+      <c r="AC52">
+        <v>1000</v>
+      </c>
+      <c r="AD52">
+        <v>1000</v>
+      </c>
+      <c r="AE52">
+        <v>1000</v>
+      </c>
+      <c r="AF52">
+        <v>1000</v>
+      </c>
+      <c r="AG52">
+        <v>1000</v>
+      </c>
+      <c r="AH52">
+        <v>1000</v>
+      </c>
+      <c r="AI52">
+        <v>1000</v>
+      </c>
+      <c r="AJ52">
+        <v>1000</v>
+      </c>
+      <c r="AK52">
+        <v>1000</v>
+      </c>
+      <c r="AL52">
+        <v>1000</v>
+      </c>
+      <c r="AM52">
+        <v>1000</v>
+      </c>
+      <c r="AN52">
+        <v>1000</v>
+      </c>
+      <c r="AO52">
+        <v>1000</v>
+      </c>
+      <c r="AP52">
+        <v>1.01</v>
+      </c>
+      <c r="AQ52">
+        <v>1.01</v>
+      </c>
+      <c r="AR52">
+        <v>1.01</v>
+      </c>
+      <c r="AS52">
+        <v>1.01</v>
+      </c>
+      <c r="AT52">
+        <v>1.01</v>
+      </c>
+      <c r="AU52">
+        <v>1.01</v>
+      </c>
+      <c r="AV52">
+        <v>1.01</v>
+      </c>
+      <c r="AW52">
+        <v>1.01</v>
+      </c>
+      <c r="AX52">
+        <v>1.01</v>
+      </c>
+      <c r="AY52">
+        <v>1.01</v>
+      </c>
+      <c r="AZ52">
+        <v>1.01</v>
+      </c>
+      <c r="BA52">
+        <v>1.01</v>
+      </c>
+      <c r="BB52">
+        <v>1.01</v>
+      </c>
+      <c r="BC52">
+        <v>1.01</v>
+      </c>
+      <c r="BD52">
+        <v>1.01</v>
+      </c>
+      <c r="BE52">
+        <v>1.01</v>
+      </c>
+      <c r="BF52">
+        <v>1.01</v>
+      </c>
+      <c r="BG52">
+        <v>1.01</v>
+      </c>
+      <c r="BH52">
+        <v>1000</v>
+      </c>
+      <c r="BI52">
+        <v>1.01</v>
+      </c>
+      <c r="BJ52">
+        <v>1000</v>
+      </c>
+      <c r="BK52">
+        <v>1.01</v>
+      </c>
+      <c r="BL52">
+        <v>1000</v>
+      </c>
+      <c r="BM52">
+        <v>1.01</v>
+      </c>
+      <c r="BN52">
+        <v>1000</v>
+      </c>
+      <c r="BO52">
+        <v>1.01</v>
+      </c>
+      <c r="BP52">
+        <v>1000</v>
+      </c>
+      <c r="BQ52">
+        <v>1.01</v>
+      </c>
+      <c r="BR52">
+        <v>1000</v>
+      </c>
+      <c r="BS52">
+        <v>1.01</v>
+      </c>
+      <c r="BT52">
+        <v>1000</v>
+      </c>
+      <c r="BU52">
+        <v>1.01</v>
+      </c>
+      <c r="BV52">
+        <v>1000</v>
+      </c>
+      <c r="BW52">
+        <v>1.01</v>
+      </c>
+      <c r="BX52">
+        <v>1000</v>
+      </c>
+      <c r="BY52">
+        <v>1.01</v>
+      </c>
+      <c r="BZ52">
+        <v>0</v>
+      </c>
+      <c r="CA52">
+        <v>0</v>
+      </c>
+      <c r="CB52" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="53" spans="1:80">
+      <c r="A53" t="s">
+        <v>113</v>
+      </c>
+      <c r="B53" t="s">
+        <v>116</v>
+      </c>
+      <c r="C53" t="s">
+        <v>139</v>
+      </c>
+      <c r="D53" t="s">
+        <v>192</v>
+      </c>
+      <c r="E53" t="s">
+        <v>247</v>
+      </c>
+      <c r="F53">
+        <v>1.54</v>
+      </c>
+      <c r="G53">
+        <v>1.77</v>
+      </c>
+      <c r="H53">
+        <v>5.4</v>
+      </c>
+      <c r="I53">
+        <v>10.5</v>
+      </c>
+      <c r="J53">
+        <v>3.75</v>
+      </c>
+      <c r="K53">
+        <v>6.2</v>
+      </c>
+      <c r="L53">
+        <v>1.31</v>
+      </c>
+      <c r="M53">
+        <v>1.01</v>
+      </c>
+      <c r="N53">
+        <v>3.25</v>
+      </c>
+      <c r="O53">
+        <v>1.29</v>
+      </c>
+      <c r="P53">
+        <v>1.89</v>
+      </c>
+      <c r="Q53">
+        <v>1.87</v>
+      </c>
+      <c r="R53">
+        <v>1.3</v>
+      </c>
+      <c r="S53">
+        <v>2.92</v>
+      </c>
+      <c r="T53">
+        <v>1.01</v>
+      </c>
+      <c r="U53">
+        <v>1.01</v>
+      </c>
+      <c r="V53">
+        <v>1.13</v>
+      </c>
+      <c r="W53">
+        <v>2.28</v>
+      </c>
+      <c r="X53">
+        <v>1000</v>
+      </c>
+      <c r="Y53">
+        <v>1000</v>
+      </c>
+      <c r="Z53">
+        <v>1000</v>
+      </c>
+      <c r="AA53">
+        <v>1000</v>
+      </c>
+      <c r="AB53">
+        <v>1000</v>
+      </c>
+      <c r="AC53">
+        <v>1000</v>
+      </c>
+      <c r="AD53">
+        <v>1000</v>
+      </c>
+      <c r="AE53">
+        <v>1000</v>
+      </c>
+      <c r="AF53">
+        <v>1000</v>
+      </c>
+      <c r="AG53">
+        <v>1000</v>
+      </c>
+      <c r="AH53">
+        <v>1000</v>
+      </c>
+      <c r="AI53">
+        <v>1000</v>
+      </c>
+      <c r="AJ53">
+        <v>1000</v>
+      </c>
+      <c r="AK53">
+        <v>1000</v>
+      </c>
+      <c r="AL53">
+        <v>1000</v>
+      </c>
+      <c r="AM53">
+        <v>1000</v>
+      </c>
+      <c r="AN53">
+        <v>1000</v>
+      </c>
+      <c r="AO53">
+        <v>1000</v>
+      </c>
+      <c r="AP53">
+        <v>1.01</v>
+      </c>
+      <c r="AQ53">
+        <v>1.01</v>
+      </c>
+      <c r="AR53">
+        <v>1.01</v>
+      </c>
+      <c r="AS53">
+        <v>1.01</v>
+      </c>
+      <c r="AT53">
+        <v>1.01</v>
+      </c>
+      <c r="AU53">
+        <v>1.01</v>
+      </c>
+      <c r="AV53">
+        <v>1.01</v>
+      </c>
+      <c r="AW53">
+        <v>1.01</v>
+      </c>
+      <c r="AX53">
+        <v>1.01</v>
+      </c>
+      <c r="AY53">
+        <v>1.01</v>
+      </c>
+      <c r="AZ53">
+        <v>1.01</v>
+      </c>
+      <c r="BA53">
+        <v>1.01</v>
+      </c>
+      <c r="BB53">
+        <v>1.01</v>
+      </c>
+      <c r="BC53">
+        <v>1.01</v>
+      </c>
+      <c r="BD53">
+        <v>1.01</v>
+      </c>
+      <c r="BE53">
+        <v>1.01</v>
+      </c>
+      <c r="BF53">
+        <v>1.01</v>
+      </c>
+      <c r="BG53">
+        <v>1.01</v>
+      </c>
+      <c r="BH53">
+        <v>1000</v>
+      </c>
+      <c r="BI53">
+        <v>2.64</v>
+      </c>
+      <c r="BJ53">
+        <v>1000</v>
+      </c>
+      <c r="BK53">
+        <v>1.01</v>
+      </c>
+      <c r="BL53">
+        <v>1000</v>
+      </c>
+      <c r="BM53">
+        <v>1.01</v>
+      </c>
+      <c r="BN53">
+        <v>1000</v>
+      </c>
+      <c r="BO53">
+        <v>1.01</v>
+      </c>
+      <c r="BP53">
+        <v>1000</v>
+      </c>
+      <c r="BQ53">
+        <v>1.01</v>
+      </c>
+      <c r="BR53">
+        <v>1000</v>
+      </c>
+      <c r="BS53">
+        <v>1.01</v>
+      </c>
+      <c r="BT53">
+        <v>1000</v>
+      </c>
+      <c r="BU53">
+        <v>1.01</v>
+      </c>
+      <c r="BV53">
+        <v>1000</v>
+      </c>
+      <c r="BW53">
+        <v>1.01</v>
+      </c>
+      <c r="BX53">
+        <v>1000</v>
+      </c>
+      <c r="BY53">
+        <v>1.01</v>
+      </c>
+      <c r="BZ53">
+        <v>1000</v>
+      </c>
+      <c r="CA53">
+        <v>1.01</v>
+      </c>
+      <c r="CB53" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="54" spans="1:80">
+      <c r="A54" t="s">
+        <v>114</v>
+      </c>
+      <c r="B54" t="s">
+        <v>116</v>
+      </c>
+      <c r="C54" t="s">
+        <v>140</v>
+      </c>
+      <c r="D54" t="s">
+        <v>193</v>
+      </c>
+      <c r="E54" t="s">
+        <v>248</v>
+      </c>
+      <c r="F54">
+        <v>1.68</v>
+      </c>
+      <c r="G54">
+        <v>1.83</v>
+      </c>
+      <c r="H54">
+        <v>4.3</v>
+      </c>
+      <c r="I54">
+        <v>5.2</v>
+      </c>
+      <c r="J54">
+        <v>3.8</v>
+      </c>
+      <c r="K54">
+        <v>5.6</v>
+      </c>
+      <c r="L54">
+        <v>1.01</v>
+      </c>
+      <c r="M54">
+        <v>1.01</v>
+      </c>
+      <c r="N54">
+        <v>5.3</v>
+      </c>
+      <c r="O54">
+        <v>1.17</v>
+      </c>
+      <c r="P54">
+        <v>2.54</v>
+      </c>
+      <c r="Q54">
+        <v>1.52</v>
+      </c>
+      <c r="R54">
+        <v>1.61</v>
+      </c>
+      <c r="S54">
+        <v>2.34</v>
+      </c>
+      <c r="T54">
+        <v>1.49</v>
+      </c>
+      <c r="U54">
+        <v>2.38</v>
+      </c>
+      <c r="V54">
+        <v>1.23</v>
+      </c>
+      <c r="W54">
+        <v>2.2</v>
+      </c>
+      <c r="X54">
+        <v>32</v>
+      </c>
+      <c r="Y54">
+        <v>29</v>
+      </c>
+      <c r="Z54">
+        <v>50</v>
+      </c>
+      <c r="AA54">
+        <v>120</v>
+      </c>
+      <c r="AB54">
+        <v>16</v>
+      </c>
+      <c r="AC54">
+        <v>13</v>
+      </c>
+      <c r="AD54">
+        <v>24</v>
+      </c>
+      <c r="AE54">
+        <v>60</v>
+      </c>
+      <c r="AF54">
+        <v>16.5</v>
+      </c>
+      <c r="AG54">
+        <v>13</v>
+      </c>
+      <c r="AH54">
+        <v>21</v>
+      </c>
+      <c r="AI54">
+        <v>60</v>
+      </c>
+      <c r="AJ54">
+        <v>23</v>
+      </c>
+      <c r="AK54">
+        <v>20</v>
+      </c>
+      <c r="AL54">
+        <v>32</v>
+      </c>
+      <c r="AM54">
+        <v>80</v>
+      </c>
+      <c r="AN54">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AO54">
+        <v>46</v>
+      </c>
+      <c r="AP54">
+        <v>19</v>
+      </c>
+      <c r="AQ54">
+        <v>17</v>
+      </c>
+      <c r="AR54">
+        <v>1.01</v>
+      </c>
+      <c r="AS54">
+        <v>1.01</v>
+      </c>
+      <c r="AT54">
+        <v>9.6</v>
+      </c>
+      <c r="AU54">
+        <v>8</v>
+      </c>
+      <c r="AV54">
+        <v>14</v>
+      </c>
+      <c r="AW54">
+        <v>1.01</v>
+      </c>
+      <c r="AX54">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY54">
+        <v>7.8</v>
+      </c>
+      <c r="AZ54">
+        <v>12</v>
+      </c>
+      <c r="BA54">
+        <v>1.01</v>
+      </c>
+      <c r="BB54">
+        <v>13.5</v>
+      </c>
+      <c r="BC54">
+        <v>12</v>
+      </c>
+      <c r="BD54">
+        <v>19</v>
+      </c>
+      <c r="BE54">
+        <v>1.01</v>
+      </c>
+      <c r="BF54">
+        <v>5.5</v>
+      </c>
+      <c r="BG54">
+        <v>1.01</v>
+      </c>
+      <c r="BH54">
+        <v>1000</v>
+      </c>
+      <c r="BI54">
+        <v>1.01</v>
+      </c>
+      <c r="BJ54">
+        <v>1000</v>
+      </c>
+      <c r="BK54">
+        <v>1.01</v>
+      </c>
+      <c r="BL54">
+        <v>1000</v>
+      </c>
+      <c r="BM54">
+        <v>1.01</v>
+      </c>
+      <c r="BN54">
+        <v>1000</v>
+      </c>
+      <c r="BO54">
+        <v>1.01</v>
+      </c>
+      <c r="BP54">
+        <v>1000</v>
+      </c>
+      <c r="BQ54">
+        <v>1.01</v>
+      </c>
+      <c r="BR54">
+        <v>1000</v>
+      </c>
+      <c r="BS54">
+        <v>1.01</v>
+      </c>
+      <c r="BT54">
+        <v>1000</v>
+      </c>
+      <c r="BU54">
+        <v>1.01</v>
+      </c>
+      <c r="BV54">
+        <v>1000</v>
+      </c>
+      <c r="BW54">
+        <v>1.01</v>
+      </c>
+      <c r="BX54">
+        <v>1000</v>
+      </c>
+      <c r="BY54">
+        <v>1.01</v>
+      </c>
+      <c r="BZ54">
+        <v>1000</v>
+      </c>
+      <c r="CA54">
+        <v>1.01</v>
+      </c>
+      <c r="CB54" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="55" spans="1:80">
+      <c r="A55" t="s">
+        <v>115</v>
+      </c>
+      <c r="B55" t="s">
+        <v>116</v>
+      </c>
+      <c r="C55" t="s">
+        <v>140</v>
+      </c>
+      <c r="D55" t="s">
+        <v>194</v>
+      </c>
+      <c r="E55" t="s">
+        <v>249</v>
+      </c>
+      <c r="F55">
+        <v>2.2</v>
+      </c>
+      <c r="G55">
+        <v>2.3</v>
+      </c>
+      <c r="H55">
+        <v>3.7</v>
+      </c>
+      <c r="I55">
+        <v>4</v>
+      </c>
+      <c r="J55">
+        <v>3.4</v>
+      </c>
+      <c r="K55">
+        <v>3.55</v>
+      </c>
+      <c r="L55">
+        <v>1.01</v>
+      </c>
+      <c r="M55">
+        <v>1.09</v>
+      </c>
+      <c r="N55">
+        <v>3.15</v>
+      </c>
+      <c r="O55">
+        <v>1.4</v>
+      </c>
+      <c r="P55">
+        <v>1.76</v>
+      </c>
+      <c r="Q55">
+        <v>2.14</v>
+      </c>
+      <c r="R55">
+        <v>1.29</v>
+      </c>
+      <c r="S55">
+        <v>4.1</v>
+      </c>
+      <c r="T55">
+        <v>1.77</v>
+      </c>
+      <c r="U55">
+        <v>2</v>
+      </c>
+      <c r="V55">
+        <v>1.34</v>
+      </c>
+      <c r="W55">
+        <v>1.77</v>
+      </c>
+      <c r="X55">
+        <v>13.5</v>
+      </c>
+      <c r="Y55">
+        <v>12.5</v>
+      </c>
+      <c r="Z55">
+        <v>32</v>
+      </c>
+      <c r="AA55">
+        <v>90</v>
+      </c>
+      <c r="AB55">
+        <v>8.6</v>
+      </c>
+      <c r="AC55">
+        <v>7.6</v>
+      </c>
+      <c r="AD55">
+        <v>970</v>
+      </c>
+      <c r="AE55">
+        <v>60</v>
+      </c>
+      <c r="AF55">
+        <v>970</v>
+      </c>
+      <c r="AG55">
+        <v>11.5</v>
+      </c>
+      <c r="AH55">
+        <v>970</v>
+      </c>
+      <c r="AI55">
+        <v>75</v>
+      </c>
+      <c r="AJ55">
+        <v>34</v>
+      </c>
+      <c r="AK55">
+        <v>26</v>
+      </c>
+      <c r="AL55">
+        <v>55</v>
+      </c>
+      <c r="AM55">
+        <v>140</v>
+      </c>
+      <c r="AN55">
+        <v>22</v>
+      </c>
+      <c r="AO55">
+        <v>70</v>
+      </c>
+      <c r="AP55">
+        <v>10.5</v>
+      </c>
+      <c r="AQ55">
+        <v>11</v>
+      </c>
+      <c r="AR55">
+        <v>18.5</v>
+      </c>
+      <c r="AS55">
+        <v>9</v>
+      </c>
+      <c r="AT55">
+        <v>7.6</v>
+      </c>
+      <c r="AU55">
+        <v>6.8</v>
+      </c>
+      <c r="AV55">
+        <v>14</v>
+      </c>
+      <c r="AW55">
+        <v>8.6</v>
+      </c>
+      <c r="AX55">
+        <v>12</v>
+      </c>
+      <c r="AY55">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ55">
+        <v>17</v>
+      </c>
+      <c r="BA55">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB55">
+        <v>22</v>
+      </c>
+      <c r="BC55">
+        <v>20</v>
+      </c>
+      <c r="BD55">
+        <v>8.6</v>
+      </c>
+      <c r="BE55">
+        <v>9.4</v>
+      </c>
+      <c r="BF55">
+        <v>16.5</v>
+      </c>
+      <c r="BG55">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BH55">
+        <v>1000</v>
+      </c>
+      <c r="BI55">
+        <v>1.01</v>
+      </c>
+      <c r="BJ55">
+        <v>1000</v>
+      </c>
+      <c r="BK55">
+        <v>1.01</v>
+      </c>
+      <c r="BL55">
+        <v>1000</v>
+      </c>
+      <c r="BM55">
+        <v>1.01</v>
+      </c>
+      <c r="BN55">
+        <v>1000</v>
+      </c>
+      <c r="BO55">
+        <v>1.01</v>
+      </c>
+      <c r="BP55">
+        <v>1000</v>
+      </c>
+      <c r="BQ55">
+        <v>1.01</v>
+      </c>
+      <c r="BR55">
+        <v>1000</v>
+      </c>
+      <c r="BS55">
+        <v>1.01</v>
+      </c>
+      <c r="BT55">
+        <v>1000</v>
+      </c>
+      <c r="BU55">
+        <v>1.01</v>
+      </c>
+      <c r="BV55">
+        <v>1000</v>
+      </c>
+      <c r="BW55">
+        <v>1.01</v>
+      </c>
+      <c r="BX55">
+        <v>1000</v>
+      </c>
+      <c r="BY55">
+        <v>1.01</v>
+      </c>
+      <c r="BZ55">
+        <v>1000</v>
+      </c>
+      <c r="CA55">
+        <v>1.01</v>
+      </c>
+      <c r="CB55" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="56" spans="1:80">
+      <c r="A56" t="s">
+        <v>113</v>
+      </c>
+      <c r="B56" t="s">
+        <v>116</v>
+      </c>
+      <c r="C56" t="s">
+        <v>140</v>
+      </c>
+      <c r="D56" t="s">
+        <v>195</v>
+      </c>
+      <c r="E56" t="s">
+        <v>250</v>
+      </c>
+      <c r="F56">
+        <v>2.94</v>
+      </c>
+      <c r="G56">
+        <v>3.95</v>
+      </c>
+      <c r="H56">
+        <v>2.3</v>
+      </c>
+      <c r="I56">
+        <v>2.72</v>
+      </c>
+      <c r="J56">
+        <v>2.96</v>
+      </c>
+      <c r="K56">
+        <v>4.5</v>
+      </c>
+      <c r="L56">
+        <v>1.01</v>
+      </c>
+      <c r="M56">
+        <v>1.01</v>
+      </c>
+      <c r="N56">
+        <v>1.01</v>
+      </c>
+      <c r="O56">
+        <v>1.38</v>
+      </c>
+      <c r="P56">
+        <v>1.66</v>
+      </c>
+      <c r="Q56">
+        <v>2.16</v>
+      </c>
+      <c r="R56">
+        <v>1.2</v>
+      </c>
+      <c r="S56">
+        <v>3.15</v>
+      </c>
+      <c r="T56">
+        <v>1.01</v>
+      </c>
+      <c r="U56">
+        <v>1.01</v>
+      </c>
+      <c r="V56">
+        <v>1.58</v>
+      </c>
+      <c r="W56">
+        <v>1.34</v>
+      </c>
+      <c r="X56">
+        <v>1000</v>
+      </c>
+      <c r="Y56">
+        <v>1000</v>
+      </c>
+      <c r="Z56">
+        <v>1000</v>
+      </c>
+      <c r="AA56">
+        <v>1000</v>
+      </c>
+      <c r="AB56">
+        <v>1000</v>
+      </c>
+      <c r="AC56">
+        <v>1000</v>
+      </c>
+      <c r="AD56">
+        <v>1000</v>
+      </c>
+      <c r="AE56">
+        <v>1000</v>
+      </c>
+      <c r="AF56">
+        <v>1000</v>
+      </c>
+      <c r="AG56">
+        <v>1000</v>
+      </c>
+      <c r="AH56">
+        <v>1000</v>
+      </c>
+      <c r="AI56">
+        <v>1000</v>
+      </c>
+      <c r="AJ56">
+        <v>1000</v>
+      </c>
+      <c r="AK56">
+        <v>1000</v>
+      </c>
+      <c r="AL56">
+        <v>1000</v>
+      </c>
+      <c r="AM56">
+        <v>1000</v>
+      </c>
+      <c r="AN56">
+        <v>1000</v>
+      </c>
+      <c r="AO56">
+        <v>1000</v>
+      </c>
+      <c r="AP56">
+        <v>1.01</v>
+      </c>
+      <c r="AQ56">
+        <v>1.01</v>
+      </c>
+      <c r="AR56">
+        <v>1.01</v>
+      </c>
+      <c r="AS56">
+        <v>1.01</v>
+      </c>
+      <c r="AT56">
+        <v>1.01</v>
+      </c>
+      <c r="AU56">
+        <v>1.01</v>
+      </c>
+      <c r="AV56">
+        <v>1.01</v>
+      </c>
+      <c r="AW56">
+        <v>1.01</v>
+      </c>
+      <c r="AX56">
+        <v>1.01</v>
+      </c>
+      <c r="AY56">
+        <v>1.01</v>
+      </c>
+      <c r="AZ56">
+        <v>1.01</v>
+      </c>
+      <c r="BA56">
+        <v>1.01</v>
+      </c>
+      <c r="BB56">
+        <v>1.01</v>
+      </c>
+      <c r="BC56">
+        <v>1.01</v>
+      </c>
+      <c r="BD56">
+        <v>1.01</v>
+      </c>
+      <c r="BE56">
+        <v>1.01</v>
+      </c>
+      <c r="BF56">
+        <v>1.01</v>
+      </c>
+      <c r="BG56">
+        <v>1.01</v>
+      </c>
+      <c r="BH56">
+        <v>3.65</v>
+      </c>
+      <c r="BI56">
+        <v>2.36</v>
+      </c>
+      <c r="BJ56">
+        <v>1000</v>
+      </c>
+      <c r="BK56">
+        <v>1.01</v>
+      </c>
+      <c r="BL56">
+        <v>1000</v>
+      </c>
+      <c r="BM56">
+        <v>1.01</v>
+      </c>
+      <c r="BN56">
+        <v>1000</v>
+      </c>
+      <c r="BO56">
+        <v>1.01</v>
+      </c>
+      <c r="BP56">
+        <v>1000</v>
+      </c>
+      <c r="BQ56">
+        <v>1.01</v>
+      </c>
+      <c r="BR56">
+        <v>1000</v>
+      </c>
+      <c r="BS56">
+        <v>1.01</v>
+      </c>
+      <c r="BT56">
+        <v>1000</v>
+      </c>
+      <c r="BU56">
+        <v>1.01</v>
+      </c>
+      <c r="BV56">
+        <v>1000</v>
+      </c>
+      <c r="BW56">
+        <v>1.01</v>
+      </c>
+      <c r="BX56">
+        <v>1000</v>
+      </c>
+      <c r="BY56">
+        <v>1.01</v>
+      </c>
+      <c r="BZ56">
+        <v>1000</v>
+      </c>
+      <c r="CA56">
+        <v>1.01</v>
+      </c>
+      <c r="CB56" t="s">
+        <v>251</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-07.xlsx
@@ -769,7 +769,7 @@
     <t>Puerto Cabello</t>
   </si>
   <si>
-    <t>2026-09-06 01:56:42</t>
+    <t>2026-09-06 04:17:41</t>
   </si>
 </sst>
 </file>
@@ -1363,70 +1363,70 @@
         <v>196</v>
       </c>
       <c r="F2">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="G2">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="H2">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="I2">
         <v>6.4</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="K2">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L2">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M2">
         <v>1.04</v>
       </c>
       <c r="N2">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="O2">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P2">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="Q2">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R2">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="S2">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="T2">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="U2">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="V2">
         <v>1.2</v>
       </c>
       <c r="W2">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="X2">
         <v>25</v>
       </c>
       <c r="Y2">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Z2">
         <v>55</v>
       </c>
       <c r="AA2">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="AB2">
         <v>11.5</v>
@@ -1435,28 +1435,28 @@
         <v>11.5</v>
       </c>
       <c r="AD2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AE2">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AF2">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG2">
         <v>11</v>
       </c>
       <c r="AH2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI2">
         <v>75</v>
       </c>
       <c r="AJ2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AK2">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL2">
         <v>32</v>
@@ -1465,16 +1465,16 @@
         <v>110</v>
       </c>
       <c r="AN2">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="AO2">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AP2">
         <v>1.01</v>
       </c>
       <c r="AQ2">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="AR2">
         <v>1.01</v>
@@ -1483,19 +1483,19 @@
         <v>1.01</v>
       </c>
       <c r="AT2">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU2">
         <v>1.01</v>
       </c>
       <c r="AV2">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AW2">
         <v>1.72</v>
       </c>
       <c r="AX2">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AY2">
         <v>1.01</v>
@@ -1504,22 +1504,22 @@
         <v>1.01</v>
       </c>
       <c r="BA2">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="BB2">
         <v>1.04</v>
       </c>
       <c r="BC2">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BD2">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BE2">
         <v>1.01</v>
       </c>
       <c r="BF2">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BG2">
         <v>1.01</v>
@@ -1605,166 +1605,166 @@
         <v>197</v>
       </c>
       <c r="F3">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="G3">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I3">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="J3">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K3">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L3">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="M3">
         <v>1.09</v>
       </c>
       <c r="N3">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O3">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P3">
         <v>1.7</v>
       </c>
       <c r="Q3">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="R3">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S3">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="T3">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="U3">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="V3">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="W3">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="X3">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="Y3">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="Z3">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AA3">
-        <v>900</v>
+        <v>840</v>
       </c>
       <c r="AB3">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="AC3">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="AD3">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AE3">
-        <v>900</v>
+        <v>840</v>
       </c>
       <c r="AF3">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AG3">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="AH3">
         <v>26</v>
       </c>
       <c r="AI3">
-        <v>900</v>
+        <v>840</v>
       </c>
       <c r="AJ3">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="AK3">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AL3">
         <v>60</v>
       </c>
       <c r="AM3">
-        <v>900</v>
+        <v>840</v>
       </c>
       <c r="AN3">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AO3">
-        <v>900</v>
+        <v>840</v>
       </c>
       <c r="AP3">
-        <v>1.31</v>
+        <v>8.4</v>
       </c>
       <c r="AQ3">
-        <v>1.82</v>
+        <v>11</v>
       </c>
       <c r="AR3">
-        <v>1.85</v>
+        <v>4.6</v>
       </c>
       <c r="AS3">
-        <v>1.31</v>
+        <v>4.7</v>
       </c>
       <c r="AT3">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="AU3">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="AV3">
-        <v>9.4</v>
+        <v>16.5</v>
       </c>
       <c r="AW3">
-        <v>1.31</v>
+        <v>4.6</v>
       </c>
       <c r="AX3">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY3">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AZ3">
-        <v>12.5</v>
+        <v>18</v>
       </c>
       <c r="BA3">
-        <v>1.31</v>
+        <v>4.6</v>
       </c>
       <c r="BB3">
-        <v>1.26</v>
+        <v>20</v>
       </c>
       <c r="BC3">
-        <v>1.85</v>
+        <v>20</v>
       </c>
       <c r="BD3">
-        <v>1.28</v>
+        <v>4.6</v>
       </c>
       <c r="BE3">
-        <v>1.31</v>
+        <v>4.7</v>
       </c>
       <c r="BF3">
-        <v>1.25</v>
+        <v>15.5</v>
       </c>
       <c r="BG3">
-        <v>1.31</v>
+        <v>4.7</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1847,22 +1847,22 @@
         <v>198</v>
       </c>
       <c r="F4">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="G4">
         <v>1.88</v>
       </c>
       <c r="H4">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="I4">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J4">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K4">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L4">
         <v>1.46</v>
@@ -1877,22 +1877,22 @@
         <v>1.39</v>
       </c>
       <c r="P4">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="Q4">
         <v>2.2</v>
       </c>
       <c r="R4">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S4">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T4">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="U4">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="V4">
         <v>1.22</v>
@@ -1901,112 +1901,112 @@
         <v>2.12</v>
       </c>
       <c r="X4">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y4">
-        <v>850</v>
+        <v>18.5</v>
       </c>
       <c r="Z4">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>930</v>
       </c>
       <c r="AB4">
-        <v>970</v>
+        <v>7.8</v>
       </c>
       <c r="AC4">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD4">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE4">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF4">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG4">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH4">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ4">
-        <v>860</v>
+        <v>21</v>
       </c>
       <c r="AK4">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL4">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM4">
-        <v>1000</v>
+        <v>920</v>
       </c>
       <c r="AN4">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>930</v>
       </c>
       <c r="AP4">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AQ4">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AR4">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AS4">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AT4">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AU4">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV4">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AW4">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AX4">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AY4">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ4">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BA4">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BB4">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BC4">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BD4">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BE4">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BF4">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BG4">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BH4">
         <v>1000</v>
@@ -2089,22 +2089,22 @@
         <v>199</v>
       </c>
       <c r="F5">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="G5">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="H5">
         <v>5</v>
       </c>
       <c r="I5">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J5">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K5">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L5">
         <v>1.55</v>
@@ -2119,7 +2119,7 @@
         <v>1.51</v>
       </c>
       <c r="P5">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q5">
         <v>2.58</v>
@@ -2131,10 +2131,10 @@
         <v>5.3</v>
       </c>
       <c r="T5">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="U5">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="V5">
         <v>1.23</v>
@@ -2143,40 +2143,40 @@
         <v>2.06</v>
       </c>
       <c r="X5">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Y5">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z5">
         <v>42</v>
       </c>
       <c r="AA5">
-        <v>880</v>
+        <v>780</v>
       </c>
       <c r="AB5">
         <v>6.8</v>
       </c>
       <c r="AC5">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD5">
         <v>23</v>
       </c>
       <c r="AE5">
-        <v>880</v>
+        <v>780</v>
       </c>
       <c r="AF5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG5">
         <v>11.5</v>
       </c>
       <c r="AH5">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI5">
-        <v>880</v>
+        <v>780</v>
       </c>
       <c r="AJ5">
         <v>26</v>
@@ -2188,25 +2188,25 @@
         <v>70</v>
       </c>
       <c r="AM5">
-        <v>880</v>
+        <v>780</v>
       </c>
       <c r="AN5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO5">
-        <v>880</v>
+        <v>790</v>
       </c>
       <c r="AP5">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AQ5">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AR5">
         <v>32</v>
       </c>
       <c r="AS5">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AT5">
         <v>5.8</v>
@@ -2218,10 +2218,10 @@
         <v>18</v>
       </c>
       <c r="AW5">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX5">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AY5">
         <v>9.4</v>
@@ -2230,25 +2230,25 @@
         <v>22</v>
       </c>
       <c r="BA5">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB5">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BC5">
         <v>21</v>
       </c>
       <c r="BD5">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE5">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BF5">
         <v>15</v>
       </c>
       <c r="BG5">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -2355,7 +2355,7 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="O6">
         <v>1.26</v>
@@ -2573,16 +2573,16 @@
         <v>201</v>
       </c>
       <c r="F7">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G7">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="H7">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="I7">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="J7">
         <v>3.15</v>
@@ -2621,10 +2621,10 @@
         <v>1.01</v>
       </c>
       <c r="V7">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W7">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="X7">
         <v>11</v>
@@ -2815,7 +2815,7 @@
         <v>202</v>
       </c>
       <c r="F8">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="G8">
         <v>1.98</v>
@@ -2827,10 +2827,10 @@
         <v>5.6</v>
       </c>
       <c r="J8">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K8">
-        <v>320</v>
+        <v>4.1</v>
       </c>
       <c r="L8">
         <v>1.43</v>
@@ -3057,22 +3057,22 @@
         <v>203</v>
       </c>
       <c r="F9">
-        <v>2.02</v>
+        <v>2.26</v>
       </c>
       <c r="G9">
-        <v>2.8</v>
+        <v>2.44</v>
       </c>
       <c r="H9">
-        <v>2.68</v>
+        <v>3.05</v>
       </c>
       <c r="I9">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="J9">
         <v>3.55</v>
       </c>
       <c r="K9">
-        <v>7.4</v>
+        <v>3.9</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -3081,7 +3081,7 @@
         <v>1.04</v>
       </c>
       <c r="N9">
-        <v>2.86</v>
+        <v>2.14</v>
       </c>
       <c r="O9">
         <v>1.24</v>
@@ -3090,10 +3090,10 @@
         <v>1.86</v>
       </c>
       <c r="Q9">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R9">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="S9">
         <v>2.64</v>
@@ -3102,13 +3102,13 @@
         <v>1.01</v>
       </c>
       <c r="U9">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V9">
         <v>1.4</v>
       </c>
       <c r="W9">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -3299,10 +3299,10 @@
         <v>204</v>
       </c>
       <c r="F10">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="G10">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="H10">
         <v>2.42</v>
@@ -3311,10 +3311,10 @@
         <v>3.4</v>
       </c>
       <c r="J10">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="K10">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="L10">
         <v>1.32</v>
@@ -3350,7 +3350,7 @@
         <v>1.42</v>
       </c>
       <c r="W10">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3541,22 +3541,22 @@
         <v>205</v>
       </c>
       <c r="F11">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="G11">
-        <v>1.49</v>
+        <v>1.58</v>
       </c>
       <c r="H11">
         <v>6.6</v>
       </c>
       <c r="I11">
-        <v>250</v>
+        <v>120</v>
       </c>
       <c r="J11">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="K11">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3589,10 +3589,10 @@
         <v>1.01</v>
       </c>
       <c r="V11">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W11">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3789,7 +3789,7 @@
         <v>1.34</v>
       </c>
       <c r="H12">
-        <v>4.1</v>
+        <v>1.1</v>
       </c>
       <c r="I12">
         <v>1000</v>
@@ -3810,13 +3810,13 @@
         <v>1.26</v>
       </c>
       <c r="O12">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="P12">
         <v>1.25</v>
       </c>
       <c r="Q12">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="R12">
         <v>1.07</v>
@@ -3834,7 +3834,7 @@
         <v>1.01</v>
       </c>
       <c r="W12">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -4025,13 +4025,13 @@
         <v>207</v>
       </c>
       <c r="F13">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="G13">
         <v>110</v>
       </c>
       <c r="H13">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="I13">
         <v>110</v>
@@ -4073,10 +4073,10 @@
         <v>1.01</v>
       </c>
       <c r="V13">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W13">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -4276,7 +4276,7 @@
         <v>4.4</v>
       </c>
       <c r="I14">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J14">
         <v>3.3</v>
@@ -4285,7 +4285,7 @@
         <v>3.35</v>
       </c>
       <c r="L14">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="M14">
         <v>1.11</v>
@@ -4294,7 +4294,7 @@
         <v>2.96</v>
       </c>
       <c r="O14">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="P14">
         <v>1.64</v>
@@ -4306,13 +4306,13 @@
         <v>1.23</v>
       </c>
       <c r="S14">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="T14">
         <v>2.12</v>
       </c>
       <c r="U14">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="V14">
         <v>1.28</v>
@@ -4375,13 +4375,13 @@
         <v>100</v>
       </c>
       <c r="AP14">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ14">
         <v>11.5</v>
       </c>
       <c r="AR14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS14">
         <v>38</v>
@@ -4390,7 +4390,7 @@
         <v>6.8</v>
       </c>
       <c r="AU14">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV14">
         <v>17</v>
@@ -4408,7 +4408,7 @@
         <v>21</v>
       </c>
       <c r="BA14">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="BB14">
         <v>24</v>
@@ -4444,7 +4444,7 @@
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>2.26</v>
+        <v>34</v>
       </c>
       <c r="BN14">
         <v>1000</v>
@@ -4462,7 +4462,7 @@
         <v>1000</v>
       </c>
       <c r="BS14">
-        <v>2.14</v>
+        <v>15</v>
       </c>
       <c r="BT14">
         <v>1000</v>
@@ -4474,13 +4474,13 @@
         <v>1000</v>
       </c>
       <c r="BW14">
-        <v>2.26</v>
+        <v>14</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>2.14</v>
+        <v>17</v>
       </c>
       <c r="BZ14">
         <v>0</v>
@@ -4509,7 +4509,7 @@
         <v>209</v>
       </c>
       <c r="F15">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="G15">
         <v>2.1</v>
@@ -4524,7 +4524,7 @@
         <v>3.4</v>
       </c>
       <c r="K15">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L15">
         <v>1.01</v>
@@ -4533,10 +4533,10 @@
         <v>1.01</v>
       </c>
       <c r="N15">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="O15">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="P15">
         <v>2.16</v>
@@ -4548,7 +4548,7 @@
         <v>1.48</v>
       </c>
       <c r="S15">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="T15">
         <v>1.01</v>
@@ -4569,16 +4569,16 @@
         <v>1000</v>
       </c>
       <c r="Z15">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA15">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB15">
         <v>1000</v>
       </c>
       <c r="AC15">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD15">
         <v>1000</v>
@@ -4587,13 +4587,13 @@
         <v>1000</v>
       </c>
       <c r="AF15">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG15">
         <v>1000</v>
       </c>
       <c r="AH15">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI15">
         <v>1000</v>
@@ -4605,10 +4605,10 @@
         <v>1000</v>
       </c>
       <c r="AL15">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM15">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN15">
         <v>1000</v>
@@ -4629,7 +4629,7 @@
         <v>1.01</v>
       </c>
       <c r="AT15">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AU15">
         <v>1.01</v>
@@ -4641,10 +4641,10 @@
         <v>1.01</v>
       </c>
       <c r="AX15">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AY15">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AZ15">
         <v>1.01</v>
@@ -4653,7 +4653,7 @@
         <v>1.01</v>
       </c>
       <c r="BB15">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BC15">
         <v>1.01</v>
@@ -4784,7 +4784,7 @@
         <v>2.2</v>
       </c>
       <c r="Q16">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R16">
         <v>1.46</v>
@@ -5008,37 +5008,37 @@
         <v>4</v>
       </c>
       <c r="K17">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L17">
         <v>1.01</v>
       </c>
       <c r="M17">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N17">
-        <v>4.9</v>
+        <v>2.36</v>
       </c>
       <c r="O17">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="P17">
         <v>2.36</v>
       </c>
       <c r="Q17">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="R17">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="S17">
-        <v>2.62</v>
+        <v>2.46</v>
       </c>
       <c r="T17">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="U17">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="V17">
         <v>1.37</v>
@@ -5047,7 +5047,7 @@
         <v>1.92</v>
       </c>
       <c r="X17">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y17">
         <v>22</v>
@@ -5059,7 +5059,7 @@
         <v>75</v>
       </c>
       <c r="AB17">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC17">
         <v>11.5</v>
@@ -5071,7 +5071,7 @@
         <v>46</v>
       </c>
       <c r="AF17">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG17">
         <v>13.5</v>
@@ -5083,13 +5083,13 @@
         <v>48</v>
       </c>
       <c r="AJ17">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="AK17">
         <v>24</v>
       </c>
       <c r="AL17">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="AM17">
         <v>80</v>
@@ -5101,16 +5101,16 @@
         <v>34</v>
       </c>
       <c r="AP17">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AQ17">
-        <v>4.2</v>
+        <v>16</v>
       </c>
       <c r="AR17">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AS17">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AT17">
         <v>11</v>
@@ -5122,7 +5122,7 @@
         <v>13.5</v>
       </c>
       <c r="AW17">
-        <v>4.7</v>
+        <v>14.5</v>
       </c>
       <c r="AX17">
         <v>12.5</v>
@@ -5134,25 +5134,25 @@
         <v>14</v>
       </c>
       <c r="BA17">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB17">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BC17">
         <v>4.3</v>
       </c>
       <c r="BD17">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BE17">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF17">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG17">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BH17">
         <v>1000</v>
@@ -5235,7 +5235,7 @@
         <v>212</v>
       </c>
       <c r="F18">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G18">
         <v>1.91</v>
@@ -5244,10 +5244,10 @@
         <v>5.6</v>
       </c>
       <c r="I18">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J18">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="K18">
         <v>3.5</v>
@@ -5256,22 +5256,22 @@
         <v>1.47</v>
       </c>
       <c r="M18">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N18">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="O18">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="P18">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="Q18">
         <v>2.6</v>
       </c>
       <c r="R18">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="S18">
         <v>5.1</v>
@@ -5477,22 +5477,22 @@
         <v>213</v>
       </c>
       <c r="F19">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="G19">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="H19">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="I19">
-        <v>2.34</v>
+        <v>2.7</v>
       </c>
       <c r="J19">
-        <v>3</v>
+        <v>2.46</v>
       </c>
       <c r="K19">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="L19">
         <v>1.41</v>
@@ -5501,7 +5501,7 @@
         <v>1.01</v>
       </c>
       <c r="N19">
-        <v>2.96</v>
+        <v>2.56</v>
       </c>
       <c r="O19">
         <v>1.02</v>
@@ -5510,13 +5510,13 @@
         <v>1.58</v>
       </c>
       <c r="Q19">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="R19">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S19">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="T19">
         <v>1.01</v>
@@ -5525,10 +5525,10 @@
         <v>1.01</v>
       </c>
       <c r="V19">
-        <v>1.74</v>
+        <v>1.58</v>
       </c>
       <c r="W19">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="X19">
         <v>1000</v>
@@ -5728,7 +5728,7 @@
         <v>7.8</v>
       </c>
       <c r="I20">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="J20">
         <v>4.4</v>
@@ -5740,31 +5740,31 @@
         <v>1.27</v>
       </c>
       <c r="M20">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N20">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O20">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P20">
         <v>2.04</v>
       </c>
       <c r="Q20">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="R20">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="S20">
-        <v>2.92</v>
+        <v>2.68</v>
       </c>
       <c r="T20">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="U20">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="V20">
         <v>1.11</v>
@@ -5773,112 +5773,112 @@
         <v>2.88</v>
       </c>
       <c r="X20">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y20">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Z20">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AA20">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AB20">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AC20">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AD20">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AE20">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AF20">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AG20">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH20">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI20">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ20">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AK20">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AL20">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM20">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AN20">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AO20">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AP20">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR20">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="AS20">
-        <v>200</v>
+        <v>1.01</v>
       </c>
       <c r="AT20">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU20">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AV20">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AW20">
-        <v>95</v>
+        <v>1.01</v>
       </c>
       <c r="AX20">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY20">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BA20">
-        <v>80</v>
+        <v>1.01</v>
       </c>
       <c r="BB20">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC20">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD20">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BE20">
-        <v>100</v>
+        <v>1.01</v>
       </c>
       <c r="BF20">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG20">
-        <v>120</v>
+        <v>1.01</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5961,25 +5961,25 @@
         <v>215</v>
       </c>
       <c r="F21">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G21">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="H21">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="I21">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="J21">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K21">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="L21">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M21">
         <v>1.05</v>
@@ -6009,22 +6009,22 @@
         <v>2.14</v>
       </c>
       <c r="V21">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W21">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="X21">
         <v>22</v>
       </c>
       <c r="Y21">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z21">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AA21">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB21">
         <v>12</v>
@@ -6033,10 +6033,10 @@
         <v>11.5</v>
       </c>
       <c r="AD21">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE21">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF21">
         <v>14</v>
@@ -6045,10 +6045,10 @@
         <v>12.5</v>
       </c>
       <c r="AH21">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI21">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ21">
         <v>22</v>
@@ -6066,7 +6066,7 @@
         <v>11.5</v>
       </c>
       <c r="AO21">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP21">
         <v>13</v>
@@ -6093,7 +6093,7 @@
         <v>42</v>
       </c>
       <c r="AX21">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY21">
         <v>8.800000000000001</v>
@@ -6123,16 +6123,16 @@
         <v>44</v>
       </c>
       <c r="BH21">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="BI21">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BJ21">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK21">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BL21">
         <v>1000</v>
@@ -6141,46 +6141,46 @@
         <v>1.01</v>
       </c>
       <c r="BN21">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO21">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BP21">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BQ21">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR21">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS21">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BT21">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU21">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BV21">
         <v>1000</v>
       </c>
       <c r="BW21">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BX21">
         <v>1000</v>
       </c>
       <c r="BY21">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BZ21">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="CA21">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="CB21" t="s">
         <v>251</v>
@@ -6221,34 +6221,34 @@
         <v>2.96</v>
       </c>
       <c r="L22">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="M22">
         <v>1.16</v>
       </c>
       <c r="N22">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="O22">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="P22">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Q22">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="R22">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="S22">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="T22">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="U22">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="V22">
         <v>1.36</v>
@@ -6260,13 +6260,13 @@
         <v>7</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="Z22">
         <v>23</v>
       </c>
       <c r="AA22">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AB22">
         <v>6.8</v>
@@ -6275,19 +6275,19 @@
         <v>7</v>
       </c>
       <c r="AD22">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE22">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AF22">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG22">
         <v>13.5</v>
       </c>
       <c r="AH22">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI22">
         <v>110</v>
@@ -6296,22 +6296,22 @@
         <v>42</v>
       </c>
       <c r="AK22">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AL22">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AM22">
-        <v>260</v>
+        <v>340</v>
       </c>
       <c r="AN22">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AO22">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AP22">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ22">
         <v>8.4</v>
@@ -6323,13 +6323,13 @@
         <v>34</v>
       </c>
       <c r="AT22">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU22">
         <v>6.4</v>
       </c>
       <c r="AV22">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW22">
         <v>60</v>
@@ -6344,85 +6344,85 @@
         <v>26</v>
       </c>
       <c r="BA22">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="BB22">
         <v>34</v>
       </c>
       <c r="BC22">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="BD22">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="BE22">
         <v>50</v>
       </c>
       <c r="BF22">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BG22">
         <v>38</v>
       </c>
       <c r="BH22">
-        <v>1000</v>
+        <v>2.44</v>
       </c>
       <c r="BI22">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="BJ22">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK22">
-        <v>2.94</v>
+        <v>7.2</v>
       </c>
       <c r="BL22">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="BM22">
-        <v>1.38</v>
+        <v>15.5</v>
       </c>
       <c r="BN22">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO22">
-        <v>2</v>
+        <v>4.7</v>
       </c>
       <c r="BP22">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BQ22">
-        <v>1.38</v>
+        <v>10</v>
       </c>
       <c r="BR22">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS22">
-        <v>1.38</v>
+        <v>13</v>
       </c>
       <c r="BT22">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BU22">
-        <v>2.18</v>
+        <v>6</v>
       </c>
       <c r="BV22">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BW22">
-        <v>1.38</v>
+        <v>12</v>
       </c>
       <c r="BX22">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BY22">
-        <v>1.38</v>
+        <v>13.5</v>
       </c>
       <c r="BZ22">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="CA22">
-        <v>1.38</v>
+        <v>13.5</v>
       </c>
       <c r="CB22" t="s">
         <v>251</v>
@@ -6466,31 +6466,31 @@
         <v>1.01</v>
       </c>
       <c r="M23">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N23">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O23">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="P23">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="Q23">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="R23">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S23">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="T23">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="U23">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V23">
         <v>1.48</v>
@@ -6502,31 +6502,31 @@
         <v>24</v>
       </c>
       <c r="Y23">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z23">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA23">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB23">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AC23">
         <v>11</v>
       </c>
       <c r="AD23">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE23">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF23">
         <v>22</v>
       </c>
       <c r="AG23">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH23">
         <v>19</v>
@@ -6535,10 +6535,10 @@
         <v>44</v>
       </c>
       <c r="AJ23">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AK23">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AL23">
         <v>40</v>
@@ -6547,7 +6547,7 @@
         <v>80</v>
       </c>
       <c r="AN23">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO23">
         <v>27</v>
@@ -6556,13 +6556,13 @@
         <v>17</v>
       </c>
       <c r="AQ23">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AR23">
         <v>19</v>
       </c>
       <c r="AS23">
-        <v>3.95</v>
+        <v>16.5</v>
       </c>
       <c r="AT23">
         <v>9.800000000000001</v>
@@ -6571,10 +6571,10 @@
         <v>7.8</v>
       </c>
       <c r="AV23">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AW23">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AX23">
         <v>13</v>
@@ -6583,25 +6583,25 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ23">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BA23">
+        <v>3.95</v>
+      </c>
+      <c r="BB23">
         <v>3.9</v>
       </c>
-      <c r="BB23">
-        <v>3.85</v>
-      </c>
       <c r="BC23">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BD23">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BE23">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="BF23">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BG23">
         <v>15.5</v>
@@ -6687,7 +6687,7 @@
         <v>218</v>
       </c>
       <c r="F24">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="G24">
         <v>1.83</v>
@@ -6705,34 +6705,34 @@
         <v>4.4</v>
       </c>
       <c r="L24">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M24">
         <v>1.04</v>
       </c>
       <c r="N24">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="O24">
         <v>1.19</v>
       </c>
       <c r="P24">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="Q24">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R24">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S24">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="T24">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U24">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="V24">
         <v>1.27</v>
@@ -6744,28 +6744,28 @@
         <v>28</v>
       </c>
       <c r="Y24">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Z24">
         <v>40</v>
       </c>
       <c r="AA24">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB24">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC24">
         <v>10.5</v>
       </c>
       <c r="AD24">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE24">
         <v>50</v>
       </c>
       <c r="AF24">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG24">
         <v>10.5</v>
@@ -6780,7 +6780,7 @@
         <v>20</v>
       </c>
       <c r="AK24">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL24">
         <v>26</v>
@@ -6792,10 +6792,10 @@
         <v>7.6</v>
       </c>
       <c r="AO24">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="AP24">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AQ24">
         <v>21</v>
@@ -6825,10 +6825,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ24">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA24">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB24">
         <v>18.5</v>
@@ -6837,7 +6837,7 @@
         <v>15</v>
       </c>
       <c r="BD24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BE24">
         <v>50</v>
@@ -6846,67 +6846,67 @@
         <v>7</v>
       </c>
       <c r="BG24">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="BH24">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BI24">
-        <v>1.98</v>
+        <v>3.55</v>
       </c>
       <c r="BJ24">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BK24">
-        <v>1.72</v>
+        <v>5.6</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>1.98</v>
+        <v>12</v>
       </c>
       <c r="BN24">
-        <v>6.8</v>
+        <v>5</v>
       </c>
       <c r="BO24">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="BP24">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="BQ24">
-        <v>1.76</v>
+        <v>6.4</v>
       </c>
       <c r="BR24">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="BS24">
-        <v>1.86</v>
+        <v>8.4</v>
       </c>
       <c r="BT24">
-        <v>12</v>
+        <v>8.4</v>
       </c>
       <c r="BU24">
         <v>5.3</v>
       </c>
       <c r="BV24">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="BW24">
-        <v>1.9</v>
+        <v>10</v>
       </c>
       <c r="BX24">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="BY24">
-        <v>1.91</v>
+        <v>10</v>
       </c>
       <c r="BZ24">
-        <v>20</v>
+        <v>13.5</v>
       </c>
       <c r="CA24">
-        <v>1.8</v>
+        <v>7</v>
       </c>
       <c r="CB24" t="s">
         <v>251</v>
@@ -6956,25 +6956,25 @@
         <v>4.6</v>
       </c>
       <c r="O25">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P25">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q25">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R25">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="S25">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="T25">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="U25">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="V25">
         <v>2.14</v>
@@ -6986,10 +6986,10 @@
         <v>23</v>
       </c>
       <c r="Y25">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z25">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AA25">
         <v>24</v>
@@ -6998,10 +6998,10 @@
         <v>22</v>
       </c>
       <c r="AC25">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AD25">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE25">
         <v>21</v>
@@ -7010,10 +7010,10 @@
         <v>42</v>
       </c>
       <c r="AG25">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AH25">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI25">
         <v>32</v>
@@ -7034,58 +7034,58 @@
         <v>55</v>
       </c>
       <c r="AO25">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AP25">
         <v>17</v>
       </c>
       <c r="AQ25">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AR25">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS25">
         <v>17</v>
       </c>
       <c r="AT25">
-        <v>16</v>
+        <v>5.8</v>
       </c>
       <c r="AU25">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AV25">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW25">
         <v>15.5</v>
       </c>
       <c r="AX25">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="AY25">
         <v>15</v>
       </c>
       <c r="AZ25">
-        <v>14.5</v>
+        <v>6.6</v>
       </c>
       <c r="BA25">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BB25">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BC25">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BD25">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BE25">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BF25">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BG25">
         <v>8.6</v>
@@ -7434,28 +7434,28 @@
         <v>1.01</v>
       </c>
       <c r="M27">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N27">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O27">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P27">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="Q27">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="R27">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S27">
         <v>3.6</v>
       </c>
       <c r="T27">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="U27">
         <v>2.02</v>
@@ -7467,22 +7467,22 @@
         <v>2.04</v>
       </c>
       <c r="X27">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y27">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z27">
         <v>42</v>
       </c>
       <c r="AA27">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AB27">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC27">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD27">
         <v>23</v>
@@ -7494,10 +7494,10 @@
         <v>14</v>
       </c>
       <c r="AG27">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH27">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI27">
         <v>85</v>
@@ -7518,7 +7518,7 @@
         <v>18</v>
       </c>
       <c r="AO27">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AP27">
         <v>12</v>
@@ -7527,22 +7527,22 @@
         <v>13.5</v>
       </c>
       <c r="AR27">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="AS27">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AT27">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU27">
-        <v>7.4</v>
+        <v>3.55</v>
       </c>
       <c r="AV27">
-        <v>4.1</v>
+        <v>15.5</v>
       </c>
       <c r="AW27">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AX27">
         <v>10</v>
@@ -7554,25 +7554,25 @@
         <v>17</v>
       </c>
       <c r="BA27">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BB27">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BC27">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BD27">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BE27">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BF27">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BG27">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BH27">
         <v>1000</v>
@@ -7655,103 +7655,103 @@
         <v>222</v>
       </c>
       <c r="F28">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="G28">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="H28">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="I28">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="J28">
         <v>3.6</v>
       </c>
       <c r="K28">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L28">
         <v>1.01</v>
       </c>
       <c r="M28">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="N28">
-        <v>2.34</v>
+        <v>3.75</v>
       </c>
       <c r="O28">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P28">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q28">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="R28">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S28">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="T28">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="U28">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="V28">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="W28">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="X28">
-        <v>1000</v>
+        <v>910</v>
       </c>
       <c r="Y28">
-        <v>1000</v>
+        <v>910</v>
       </c>
       <c r="Z28">
-        <v>1000</v>
+        <v>910</v>
       </c>
       <c r="AA28">
         <v>1000</v>
       </c>
       <c r="AB28">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AC28">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AD28">
-        <v>1000</v>
+        <v>910</v>
       </c>
       <c r="AE28">
         <v>1000</v>
       </c>
       <c r="AF28">
-        <v>1000</v>
+        <v>910</v>
       </c>
       <c r="AG28">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AH28">
-        <v>1000</v>
+        <v>910</v>
       </c>
       <c r="AI28">
         <v>1000</v>
       </c>
       <c r="AJ28">
-        <v>1000</v>
+        <v>910</v>
       </c>
       <c r="AK28">
-        <v>1000</v>
+        <v>910</v>
       </c>
       <c r="AL28">
-        <v>1000</v>
+        <v>920</v>
       </c>
       <c r="AM28">
         <v>1000</v>
@@ -7763,58 +7763,58 @@
         <v>1000</v>
       </c>
       <c r="AP28">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AQ28">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="AR28">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="AS28">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="AT28">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AU28">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="AV28">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="AW28">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="AX28">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="AY28">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AZ28">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BA28">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="BB28">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BC28">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="BD28">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="BE28">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="BF28">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BG28">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BH28">
         <v>1000</v>
@@ -7921,16 +7921,16 @@
         <v>1.01</v>
       </c>
       <c r="N29">
-        <v>2.9</v>
+        <v>1.01</v>
       </c>
       <c r="O29">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P29">
         <v>1.86</v>
       </c>
       <c r="Q29">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="R29">
         <v>1.34</v>
@@ -7945,10 +7945,10 @@
         <v>1.01</v>
       </c>
       <c r="V29">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W29">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X29">
         <v>1000</v>
@@ -8139,13 +8139,13 @@
         <v>224</v>
       </c>
       <c r="F30">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="G30">
         <v>6.8</v>
       </c>
       <c r="H30">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="I30">
         <v>1.69</v>
@@ -8154,7 +8154,7 @@
         <v>4.1</v>
       </c>
       <c r="K30">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="L30">
         <v>1.01</v>
@@ -8163,28 +8163,28 @@
         <v>1.01</v>
       </c>
       <c r="N30">
-        <v>4.2</v>
+        <v>2.46</v>
       </c>
       <c r="O30">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P30">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q30">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="R30">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S30">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="T30">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="U30">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="V30">
         <v>2.44</v>
@@ -8196,7 +8196,7 @@
         <v>22</v>
       </c>
       <c r="Y30">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z30">
         <v>12</v>
@@ -8214,7 +8214,7 @@
         <v>11.5</v>
       </c>
       <c r="AE30">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AF30">
         <v>60</v>
@@ -8244,7 +8244,7 @@
         <v>110</v>
       </c>
       <c r="AO30">
-        <v>9.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AP30">
         <v>14.5</v>
@@ -8271,7 +8271,7 @@
         <v>12.5</v>
       </c>
       <c r="AX30">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="AY30">
         <v>18</v>
@@ -8280,22 +8280,22 @@
         <v>15.5</v>
       </c>
       <c r="BA30">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BB30">
-        <v>120</v>
+        <v>1.01</v>
       </c>
       <c r="BC30">
-        <v>60</v>
+        <v>1.01</v>
       </c>
       <c r="BD30">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BE30">
-        <v>75</v>
+        <v>1.01</v>
       </c>
       <c r="BF30">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="BG30">
         <v>6.2</v>
@@ -8417,7 +8417,7 @@
         <v>2.42</v>
       </c>
       <c r="R31">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="S31">
         <v>2.42</v>
@@ -8429,7 +8429,7 @@
         <v>1.01</v>
       </c>
       <c r="V31">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W31">
         <v>1.53</v>
@@ -8635,7 +8635,7 @@
         <v>2.92</v>
       </c>
       <c r="J32">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="K32">
         <v>4.4</v>
@@ -8659,10 +8659,10 @@
         <v>1.54</v>
       </c>
       <c r="R32">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="S32">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="T32">
         <v>1.01</v>
@@ -8889,28 +8889,28 @@
         <v>1.03</v>
       </c>
       <c r="N33">
-        <v>2.78</v>
+        <v>4.4</v>
       </c>
       <c r="O33">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P33">
         <v>2.2</v>
       </c>
       <c r="Q33">
+        <v>1.69</v>
+      </c>
+      <c r="R33">
+        <v>1.44</v>
+      </c>
+      <c r="S33">
+        <v>2.74</v>
+      </c>
+      <c r="T33">
         <v>1.65</v>
       </c>
-      <c r="R33">
-        <v>1.43</v>
-      </c>
-      <c r="S33">
-        <v>2.6</v>
-      </c>
-      <c r="T33">
-        <v>1.01</v>
-      </c>
       <c r="U33">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="V33">
         <v>1.17</v>
@@ -9107,22 +9107,22 @@
         <v>228</v>
       </c>
       <c r="F34">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="G34">
-        <v>2.36</v>
+        <v>2.24</v>
       </c>
       <c r="H34">
         <v>3.15</v>
       </c>
       <c r="I34">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="J34">
         <v>3.9</v>
       </c>
       <c r="K34">
-        <v>7.4</v>
+        <v>5.9</v>
       </c>
       <c r="L34">
         <v>1.01</v>
@@ -9131,34 +9131,34 @@
         <v>1.01</v>
       </c>
       <c r="N34">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="O34">
         <v>1.07</v>
       </c>
       <c r="P34">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="Q34">
         <v>1.25</v>
       </c>
       <c r="R34">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S34">
-        <v>1.48</v>
+        <v>1.74</v>
       </c>
       <c r="T34">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="U34">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="V34">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="W34">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="X34">
         <v>1000</v>
@@ -9349,7 +9349,7 @@
         <v>229</v>
       </c>
       <c r="F35">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="G35">
         <v>2.68</v>
@@ -9364,7 +9364,7 @@
         <v>3.8</v>
       </c>
       <c r="K35">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="L35">
         <v>1.01</v>
@@ -9385,7 +9385,7 @@
         <v>1.5</v>
       </c>
       <c r="R35">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="S35">
         <v>2.16</v>
@@ -9591,16 +9591,16 @@
         <v>230</v>
       </c>
       <c r="F36">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="G36">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="H36">
-        <v>1.1</v>
+        <v>7</v>
       </c>
       <c r="I36">
-        <v>15.5</v>
+        <v>110</v>
       </c>
       <c r="J36">
         <v>5.5</v>
@@ -9615,22 +9615,22 @@
         <v>1.02</v>
       </c>
       <c r="N36">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="O36">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="P36">
         <v>2.6</v>
       </c>
       <c r="Q36">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="R36">
         <v>1.72</v>
       </c>
       <c r="S36">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="T36">
         <v>1.01</v>
@@ -9639,10 +9639,10 @@
         <v>1.01</v>
       </c>
       <c r="V36">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="W36">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="X36">
         <v>1000</v>
@@ -9836,10 +9836,10 @@
         <v>2.16</v>
       </c>
       <c r="G37">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="H37">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="I37">
         <v>4.4</v>
@@ -9848,7 +9848,7 @@
         <v>2.76</v>
       </c>
       <c r="K37">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="L37">
         <v>1.38</v>
@@ -9857,7 +9857,7 @@
         <v>1.01</v>
       </c>
       <c r="N37">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="O37">
         <v>1.37</v>
@@ -9881,10 +9881,10 @@
         <v>1.01</v>
       </c>
       <c r="V37">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W37">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="X37">
         <v>1000</v>
@@ -10075,22 +10075,22 @@
         <v>232</v>
       </c>
       <c r="F38">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="G38">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="H38">
         <v>3.6</v>
       </c>
       <c r="I38">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J38">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K38">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L38">
         <v>1.37</v>
@@ -10123,43 +10123,43 @@
         <v>1.01</v>
       </c>
       <c r="V38">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W38">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="X38">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="Y38">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="Z38">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AA38">
         <v>1000</v>
       </c>
       <c r="AB38">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AC38">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AD38">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AE38">
         <v>1000</v>
       </c>
       <c r="AF38">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AG38">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AH38">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AI38">
         <v>1000</v>
@@ -10183,52 +10183,52 @@
         <v>1000</v>
       </c>
       <c r="AP38">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AQ38">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AR38">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AS38">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AT38">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="AU38">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="AV38">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AW38">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AX38">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AY38">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AZ38">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BA38">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BB38">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BC38">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BD38">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BE38">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BF38">
         <v>1.01</v>
@@ -10317,7 +10317,7 @@
         <v>233</v>
       </c>
       <c r="F39">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G39">
         <v>1.85</v>
@@ -10341,7 +10341,7 @@
         <v>1.07</v>
       </c>
       <c r="N39">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O39">
         <v>1.32</v>
@@ -10350,25 +10350,25 @@
         <v>1.93</v>
       </c>
       <c r="Q39">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="R39">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S39">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="T39">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="U39">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="V39">
         <v>1.22</v>
       </c>
       <c r="W39">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X39">
         <v>16</v>
@@ -10380,7 +10380,7 @@
         <v>48</v>
       </c>
       <c r="AA39">
-        <v>660</v>
+        <v>560</v>
       </c>
       <c r="AB39">
         <v>9.800000000000001</v>
@@ -10392,10 +10392,10 @@
         <v>24</v>
       </c>
       <c r="AE39">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AF39">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AG39">
         <v>10.5</v>
@@ -10416,7 +10416,7 @@
         <v>46</v>
       </c>
       <c r="AM39">
-        <v>660</v>
+        <v>560</v>
       </c>
       <c r="AN39">
         <v>15</v>
@@ -10431,10 +10431,10 @@
         <v>13.5</v>
       </c>
       <c r="AR39">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AS39">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AT39">
         <v>7.4</v>
@@ -10446,7 +10446,7 @@
         <v>17</v>
       </c>
       <c r="AW39">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AX39">
         <v>9.6</v>
@@ -10458,7 +10458,7 @@
         <v>17.5</v>
       </c>
       <c r="BA39">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BB39">
         <v>16.5</v>
@@ -10467,16 +10467,16 @@
         <v>17</v>
       </c>
       <c r="BD39">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BE39">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BF39">
         <v>9.800000000000001</v>
       </c>
       <c r="BG39">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BH39">
         <v>1000</v>
@@ -10586,7 +10586,7 @@
         <v>4</v>
       </c>
       <c r="O40">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P40">
         <v>2.04</v>
@@ -10625,10 +10625,10 @@
         <v>100</v>
       </c>
       <c r="AB40">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC40">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD40">
         <v>18</v>
@@ -10640,7 +10640,7 @@
         <v>14</v>
       </c>
       <c r="AG40">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH40">
         <v>18.5</v>
@@ -10676,7 +10676,7 @@
         <v>24</v>
       </c>
       <c r="AS40">
-        <v>60</v>
+        <v>1.01</v>
       </c>
       <c r="AT40">
         <v>8</v>
@@ -10712,7 +10712,7 @@
         <v>25</v>
       </c>
       <c r="BE40">
-        <v>60</v>
+        <v>1.01</v>
       </c>
       <c r="BF40">
         <v>9.6</v>
@@ -10807,7 +10807,7 @@
         <v>2.46</v>
       </c>
       <c r="H41">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I41">
         <v>4.6</v>
@@ -10816,7 +10816,7 @@
         <v>2.66</v>
       </c>
       <c r="K41">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="L41">
         <v>1.01</v>
@@ -10843,7 +10843,7 @@
         <v>3.6</v>
       </c>
       <c r="T41">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="U41">
         <v>1.01</v>
@@ -11046,7 +11046,7 @@
         <v>3</v>
       </c>
       <c r="G42">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H42">
         <v>2.74</v>
@@ -11061,7 +11061,7 @@
         <v>3.25</v>
       </c>
       <c r="L42">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="M42">
         <v>1.11</v>
@@ -11070,7 +11070,7 @@
         <v>3.05</v>
       </c>
       <c r="O42">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P42">
         <v>1.67</v>
@@ -11079,7 +11079,7 @@
         <v>2.44</v>
       </c>
       <c r="R42">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S42">
         <v>4.8</v>
@@ -11094,7 +11094,7 @@
         <v>1.56</v>
       </c>
       <c r="W42">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X42">
         <v>9.800000000000001</v>
@@ -11154,7 +11154,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AQ42">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR42">
         <v>15</v>
@@ -11175,13 +11175,13 @@
         <v>32</v>
       </c>
       <c r="AX42">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AY42">
         <v>12.5</v>
       </c>
       <c r="AZ42">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BA42">
         <v>48</v>
@@ -11199,10 +11199,10 @@
         <v>44</v>
       </c>
       <c r="BF42">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BG42">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BH42">
         <v>1000</v>
@@ -11220,7 +11220,7 @@
         <v>1000</v>
       </c>
       <c r="BM42">
-        <v>2.22</v>
+        <v>34</v>
       </c>
       <c r="BN42">
         <v>1000</v>
@@ -11232,13 +11232,13 @@
         <v>1000</v>
       </c>
       <c r="BQ42">
-        <v>1.18</v>
+        <v>10</v>
       </c>
       <c r="BR42">
         <v>1000</v>
       </c>
       <c r="BS42">
-        <v>2.12</v>
+        <v>16.5</v>
       </c>
       <c r="BT42">
         <v>1000</v>
@@ -11250,13 +11250,13 @@
         <v>1000</v>
       </c>
       <c r="BW42">
-        <v>2.18</v>
+        <v>9.6</v>
       </c>
       <c r="BX42">
         <v>1000</v>
       </c>
       <c r="BY42">
-        <v>2.12</v>
+        <v>16</v>
       </c>
       <c r="BZ42">
         <v>0</v>
@@ -11309,7 +11309,7 @@
         <v>1.01</v>
       </c>
       <c r="N43">
-        <v>2.86</v>
+        <v>3.35</v>
       </c>
       <c r="O43">
         <v>1.3</v>
@@ -11318,7 +11318,7 @@
         <v>1.77</v>
       </c>
       <c r="Q43">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="R43">
         <v>1.31</v>
@@ -11530,13 +11530,13 @@
         <v>4</v>
       </c>
       <c r="G44">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="H44">
         <v>1.67</v>
       </c>
       <c r="I44">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="J44">
         <v>1.1</v>
@@ -11545,7 +11545,7 @@
         <v>6.8</v>
       </c>
       <c r="L44">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M44">
         <v>1.01</v>
@@ -11772,19 +11772,19 @@
         <v>2.56</v>
       </c>
       <c r="G45">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="H45">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="I45">
         <v>3.15</v>
       </c>
       <c r="J45">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K45">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L45">
         <v>1.01</v>
@@ -11799,7 +11799,7 @@
         <v>1.35</v>
       </c>
       <c r="P45">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q45">
         <v>2.1</v>
@@ -11808,10 +11808,10 @@
         <v>1.32</v>
       </c>
       <c r="S45">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T45">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="U45">
         <v>2.08</v>
@@ -11820,7 +11820,7 @@
         <v>1.47</v>
       </c>
       <c r="W45">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="X45">
         <v>13</v>
@@ -11835,10 +11835,10 @@
         <v>55</v>
       </c>
       <c r="AB45">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC45">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD45">
         <v>13.5</v>
@@ -11913,7 +11913,7 @@
         <v>40</v>
       </c>
       <c r="BB45">
-        <v>34</v>
+        <v>9.4</v>
       </c>
       <c r="BC45">
         <v>26</v>
@@ -11925,7 +11925,7 @@
         <v>11</v>
       </c>
       <c r="BF45">
-        <v>23</v>
+        <v>8.6</v>
       </c>
       <c r="BG45">
         <v>29</v>
@@ -12253,31 +12253,31 @@
         <v>241</v>
       </c>
       <c r="F47">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="G47">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H47">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I47">
         <v>3.45</v>
       </c>
       <c r="J47">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K47">
+        <v>3.65</v>
+      </c>
+      <c r="L47">
+        <v>1.01</v>
+      </c>
+      <c r="M47">
+        <v>1.06</v>
+      </c>
+      <c r="N47">
         <v>3.75</v>
-      </c>
-      <c r="L47">
-        <v>1.01</v>
-      </c>
-      <c r="M47">
-        <v>1.07</v>
-      </c>
-      <c r="N47">
-        <v>3.85</v>
       </c>
       <c r="O47">
         <v>1.29</v>
@@ -12286,25 +12286,25 @@
         <v>1.96</v>
       </c>
       <c r="Q47">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="R47">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S47">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T47">
         <v>1.59</v>
       </c>
       <c r="U47">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V47">
         <v>1.4</v>
       </c>
       <c r="W47">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X47">
         <v>17.5</v>
@@ -12319,10 +12319,10 @@
         <v>65</v>
       </c>
       <c r="AB47">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AC47">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD47">
         <v>14.5</v>
@@ -12331,10 +12331,10 @@
         <v>42</v>
       </c>
       <c r="AF47">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AG47">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH47">
         <v>17</v>
@@ -12370,10 +12370,10 @@
         <v>19</v>
       </c>
       <c r="AS47">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="AT47">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AU47">
         <v>6.8</v>
@@ -12382,7 +12382,7 @@
         <v>12</v>
       </c>
       <c r="AW47">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX47">
         <v>14</v>
@@ -12394,7 +12394,7 @@
         <v>14</v>
       </c>
       <c r="BA47">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BB47">
         <v>26</v>
@@ -12403,16 +12403,16 @@
         <v>18.5</v>
       </c>
       <c r="BD47">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BE47">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF47">
         <v>14.5</v>
       </c>
       <c r="BG47">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH47">
         <v>1000</v>
@@ -12507,7 +12507,7 @@
         <v>2.46</v>
       </c>
       <c r="J48">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K48">
         <v>3.7</v>
@@ -12519,7 +12519,7 @@
         <v>1.06</v>
       </c>
       <c r="N48">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O48">
         <v>1.28</v>
@@ -12537,7 +12537,7 @@
         <v>3.1</v>
       </c>
       <c r="T48">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U48">
         <v>2.38</v>
@@ -12570,7 +12570,7 @@
         <v>11.5</v>
       </c>
       <c r="AE48">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AF48">
         <v>23</v>
@@ -12600,13 +12600,13 @@
         <v>26</v>
       </c>
       <c r="AO48">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AP48">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AQ48">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AR48">
         <v>15.5</v>
@@ -12615,7 +12615,7 @@
         <v>30</v>
       </c>
       <c r="AT48">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AU48">
         <v>7.6</v>
@@ -12633,7 +12633,7 @@
         <v>12</v>
       </c>
       <c r="AZ48">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA48">
         <v>30</v>
@@ -12660,7 +12660,7 @@
         <v>3.7</v>
       </c>
       <c r="BI48">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BJ48">
         <v>9</v>
@@ -12672,7 +12672,7 @@
         <v>1000</v>
       </c>
       <c r="BM48">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BN48">
         <v>6.4</v>
@@ -12684,7 +12684,7 @@
         <v>23</v>
       </c>
       <c r="BQ48">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BR48">
         <v>32</v>
@@ -12702,7 +12702,7 @@
         <v>17.5</v>
       </c>
       <c r="BW48">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX48">
         <v>28</v>
@@ -12711,10 +12711,10 @@
         <v>10.5</v>
       </c>
       <c r="BZ48">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="CA48">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="CB48" t="s">
         <v>251</v>
@@ -12746,7 +12746,7 @@
         <v>4.1</v>
       </c>
       <c r="I49">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="J49">
         <v>3.6</v>
@@ -12773,7 +12773,7 @@
         <v>1.87</v>
       </c>
       <c r="R49">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="S49">
         <v>2.98</v>
@@ -13221,22 +13221,22 @@
         <v>245</v>
       </c>
       <c r="F51">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="G51">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="H51">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="I51">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="J51">
-        <v>2.86</v>
+        <v>1.1</v>
       </c>
       <c r="K51">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L51">
         <v>1.01</v>
@@ -13260,7 +13260,7 @@
         <v>1.13</v>
       </c>
       <c r="S51">
-        <v>2.98</v>
+        <v>5.5</v>
       </c>
       <c r="T51">
         <v>1.01</v>
@@ -13269,118 +13269,118 @@
         <v>1.01</v>
       </c>
       <c r="V51">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="W51">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X51">
         <v>8.4</v>
       </c>
       <c r="Y51">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="Z51">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA51">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AB51">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AC51">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD51">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AE51">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AF51">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AG51">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AH51">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AI51">
         <v>90</v>
       </c>
       <c r="AJ51">
-        <v>900</v>
+        <v>840</v>
       </c>
       <c r="AK51">
-        <v>900</v>
+        <v>840</v>
       </c>
       <c r="AL51">
-        <v>900</v>
+        <v>840</v>
       </c>
       <c r="AM51">
-        <v>910</v>
+        <v>850</v>
       </c>
       <c r="AN51">
-        <v>900</v>
+        <v>840</v>
       </c>
       <c r="AO51">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AP51">
-        <v>1.22</v>
+        <v>6.4</v>
       </c>
       <c r="AQ51">
-        <v>1.22</v>
+        <v>5.4</v>
       </c>
       <c r="AR51">
-        <v>1.22</v>
+        <v>9.6</v>
       </c>
       <c r="AS51">
-        <v>1.18</v>
+        <v>5.4</v>
       </c>
       <c r="AT51">
-        <v>1.22</v>
+        <v>9.4</v>
       </c>
       <c r="AU51">
-        <v>1.22</v>
+        <v>6.4</v>
       </c>
       <c r="AV51">
-        <v>1.22</v>
+        <v>10</v>
       </c>
       <c r="AW51">
-        <v>1.19</v>
+        <v>4.9</v>
       </c>
       <c r="AX51">
-        <v>1.19</v>
+        <v>4.9</v>
       </c>
       <c r="AY51">
-        <v>1.62</v>
+        <v>18.5</v>
       </c>
       <c r="AZ51">
-        <v>1.18</v>
+        <v>5.4</v>
       </c>
       <c r="BA51">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="BB51">
-        <v>1.22</v>
+        <v>5.2</v>
       </c>
       <c r="BC51">
-        <v>1.22</v>
+        <v>5.1</v>
       </c>
       <c r="BD51">
-        <v>1.22</v>
+        <v>5.1</v>
       </c>
       <c r="BE51">
-        <v>1.22</v>
+        <v>5.2</v>
       </c>
       <c r="BF51">
-        <v>1.22</v>
+        <v>5.2</v>
       </c>
       <c r="BG51">
-        <v>1.19</v>
+        <v>5.4</v>
       </c>
       <c r="BH51">
         <v>1000</v>
@@ -13753,7 +13753,7 @@
         <v>1.01</v>
       </c>
       <c r="V53">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W53">
         <v>2.28</v>
@@ -13947,7 +13947,7 @@
         <v>248</v>
       </c>
       <c r="F54">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="G54">
         <v>1.83</v>
@@ -13956,13 +13956,13 @@
         <v>4.3</v>
       </c>
       <c r="I54">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J54">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K54">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L54">
         <v>1.01</v>
@@ -13971,31 +13971,31 @@
         <v>1.01</v>
       </c>
       <c r="N54">
-        <v>5.3</v>
+        <v>2.5</v>
       </c>
       <c r="O54">
         <v>1.17</v>
       </c>
       <c r="P54">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="Q54">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="R54">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="S54">
+        <v>2.18</v>
+      </c>
+      <c r="T54">
+        <v>1.51</v>
+      </c>
+      <c r="U54">
         <v>2.34</v>
       </c>
-      <c r="T54">
-        <v>1.49</v>
-      </c>
-      <c r="U54">
-        <v>2.38</v>
-      </c>
       <c r="V54">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W54">
         <v>2.2</v>
@@ -14004,28 +14004,28 @@
         <v>32</v>
       </c>
       <c r="Y54">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Z54">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AA54">
         <v>120</v>
       </c>
       <c r="AB54">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC54">
         <v>13</v>
       </c>
       <c r="AD54">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE54">
         <v>60</v>
       </c>
       <c r="AF54">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG54">
         <v>13</v>
@@ -14037,28 +14037,28 @@
         <v>60</v>
       </c>
       <c r="AJ54">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK54">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL54">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM54">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AN54">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO54">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AP54">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AQ54">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AR54">
         <v>1.01</v>
@@ -14067,13 +14067,13 @@
         <v>1.01</v>
       </c>
       <c r="AT54">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU54">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV54">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AW54">
         <v>1.01</v>
@@ -14091,7 +14091,7 @@
         <v>1.01</v>
       </c>
       <c r="BB54">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BC54">
         <v>12</v>
@@ -14103,7 +14103,7 @@
         <v>1.01</v>
       </c>
       <c r="BF54">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BG54">
         <v>1.01</v>
@@ -14213,7 +14213,7 @@
         <v>1.09</v>
       </c>
       <c r="N55">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O55">
         <v>1.4</v>
@@ -14231,7 +14231,7 @@
         <v>4.1</v>
       </c>
       <c r="T55">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="U55">
         <v>2</v>
@@ -14440,7 +14440,7 @@
         <v>2.3</v>
       </c>
       <c r="I56">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="J56">
         <v>2.96</v>
